--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>212,227円</t>
+          <t>212,230円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2,937円</t>
+          <t>2,940円</t>
         </is>
       </c>
     </row>
@@ -1623,22 +1623,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>37.38</v>
+        <v>40.1</v>
       </c>
       <c r="F10" t="n">
-        <v>52.6</v>
+        <v>57.6</v>
       </c>
       <c r="G10" t="n">
-        <v>1.82</v>
+        <v>7.97</v>
       </c>
       <c r="H10" t="n">
-        <v>0.71</v>
+        <v>1.16</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="J10" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1647,14 +1647,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.67</v>
+        <v>33.71</v>
       </c>
       <c r="N10" t="n">
-        <v>31.45</v>
+        <v>31.49</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1685,37 +1685,41 @@
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>🚀 急騰</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+          <t>RSI適正、25日線上、+1σ、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>38.93</v>
+        <v>37.38</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.55</v>
+        <v>2.72</v>
       </c>
       <c r="Y10" t="n">
-        <v>-3.98</v>
+        <v>7.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6076</v>
+        <v>-6073</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.39</v>
+        <v>-99.34</v>
       </c>
     </row>
   </sheetData>
@@ -1729,7 +1733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1358"/>
+  <dimension ref="A1:C1367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22102,6 +22106,141 @@
       </c>
       <c r="C1358" t="n">
         <v>37.38</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1359" t="n">
+        <v>3265</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1360" t="n">
+        <v>175.7</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1361" t="n">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1362" t="n">
+        <v>3031</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1363" t="n">
+        <v>5005</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1364" t="n">
+        <v>8093</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1365" t="n">
+        <v>54030</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1366" t="n">
+        <v>9209</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1367" t="n">
+        <v>40.1</v>
       </c>
     </row>
   </sheetData>
@@ -22115,7 +22254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F237"/>
+  <dimension ref="A1:F238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26345,19 +26484,29 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
+      <c r="A235" t="inlineStr"/>
+      <c r="B235" s="1" t="n">
+        <v>46279.29166666666</v>
+      </c>
+      <c r="C235" t="n">
+        <v>212230</v>
+      </c>
+      <c r="D235" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E235" t="n">
+        <v>2940</v>
+      </c>
+      <c r="F235" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr"/>
-      <c r="C235" t="inlineStr"/>
-      <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr"/>
       <c r="B236" t="inlineStr"/>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr"/>
@@ -26365,16 +26514,24 @@
       <c r="F236" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A237" t="inlineStr"/>
       <c r="B237" t="inlineStr"/>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26539,31 +26696,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="F2" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.31</v>
+        <v>-2.4</v>
       </c>
       <c r="H2" t="n">
-        <v>442500</v>
+        <v>709600</v>
       </c>
       <c r="I2" t="n">
-        <v>53.4</v>
+        <v>53.3</v>
       </c>
       <c r="J2" t="n">
-        <v>4.77</v>
+        <v>4.67</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="L2" t="n">
-        <v>45.3</v>
+        <v>45.22</v>
       </c>
       <c r="M2" t="n">
-        <v>47.96</v>
+        <v>47.95</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -26576,10 +26733,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>832.03</v>
+        <v>832.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>1124.75</v>
+        <v>1124.74</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -26640,31 +26797,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3255</v>
+        <v>3265</v>
       </c>
       <c r="F3" t="n">
-        <v>-100</v>
+        <v>-90</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.98</v>
+        <v>-2.68</v>
       </c>
       <c r="H3" t="n">
-        <v>17800</v>
+        <v>66400</v>
       </c>
       <c r="I3" t="n">
-        <v>45.7</v>
+        <v>46.1</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.62</v>
+        <v>-4.34</v>
       </c>
       <c r="K3" t="n">
-        <v>0.34</v>
+        <v>1.07</v>
       </c>
       <c r="L3" t="n">
-        <v>46.99</v>
+        <v>47.79</v>
       </c>
       <c r="M3" t="n">
-        <v>96</v>
+        <v>96.16</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -26673,14 +26830,14 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2978.81</v>
+        <v>2978.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>2711.72</v>
+        <v>2711.77</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -26688,7 +26845,7 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -26707,7 +26864,7 @@
 ・MACDは売りシグナルです。
 ・デッドクロスが発生し、短期的な下落に注意が必要です。
 ・RSIは良好な水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -26742,31 +26899,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1338</v>
+        <v>1326</v>
       </c>
       <c r="F4" t="n">
-        <v>-13</v>
+        <v>-25</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.96</v>
+        <v>-1.85</v>
       </c>
       <c r="H4" t="n">
-        <v>3800</v>
+        <v>10200</v>
       </c>
       <c r="I4" t="n">
-        <v>60.6</v>
+        <v>58.8</v>
       </c>
       <c r="J4" t="n">
-        <v>5.36</v>
+        <v>4.45</v>
       </c>
       <c r="K4" t="n">
-        <v>0.35</v>
+        <v>0.84</v>
       </c>
       <c r="L4" t="n">
-        <v>44.45</v>
+        <v>43.49</v>
       </c>
       <c r="M4" t="n">
-        <v>42.66</v>
+        <v>42.47</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -26779,10 +26936,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1203.62</v>
+        <v>1203.46</v>
       </c>
       <c r="Q4" t="n">
-        <v>1643.2</v>
+        <v>1643.14</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -26807,6 +26964,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは買いシグナルです。
+・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -26842,31 +27000,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3410</v>
+        <v>3435</v>
       </c>
       <c r="F5" t="n">
-        <v>-35</v>
+        <v>-10</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.02</v>
+        <v>-0.29</v>
       </c>
       <c r="H5" t="n">
-        <v>4600</v>
+        <v>13000</v>
       </c>
       <c r="I5" t="n">
-        <v>49.3</v>
+        <v>50.5</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.93</v>
+        <v>-0.23</v>
       </c>
       <c r="K5" t="n">
-        <v>0.41</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>7.46</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>8.779999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -26879,10 +27037,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3443.13</v>
+        <v>3443.47</v>
       </c>
       <c r="Q5" t="n">
-        <v>3135.16</v>
+        <v>3135.29</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -26890,23 +27048,23 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
-・MACDは売りシグナルです。
+・MACDは買いシグナルです。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
@@ -26952,7 +27110,7 @@
         <v>-0.13</v>
       </c>
       <c r="H6" t="n">
-        <v>45000</v>
+        <v>111300</v>
       </c>
       <c r="I6" t="n">
         <v>43.7</v>
@@ -26961,7 +27119,7 @@
         <v>-0.96</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5</v>
+        <v>1.07</v>
       </c>
       <c r="L6" t="n">
         <v>-35.11</v>
@@ -27043,31 +27201,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3800</v>
+        <v>6400</v>
       </c>
       <c r="I7" t="n">
-        <v>36.8</v>
+        <v>33.3</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.76</v>
+        <v>-2.12</v>
       </c>
       <c r="K7" t="n">
-        <v>0.52</v>
+        <v>0.82</v>
       </c>
       <c r="L7" t="n">
-        <v>-7.5</v>
+        <v>-7.66</v>
       </c>
       <c r="M7" t="n">
-        <v>-8.17</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -27080,10 +27238,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>536.98</v>
+        <v>536.96</v>
       </c>
       <c r="Q7" t="n">
-        <v>585.74</v>
+        <v>585.73</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -27143,31 +27301,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1100</v>
+        <v>1079</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>-18</v>
       </c>
       <c r="G8" t="n">
-        <v>0.27</v>
+        <v>-1.64</v>
       </c>
       <c r="H8" t="n">
-        <v>1200</v>
+        <v>3500</v>
       </c>
       <c r="I8" t="n">
-        <v>33.3</v>
+        <v>30</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.28</v>
+        <v>-5.06</v>
       </c>
       <c r="K8" t="n">
-        <v>0.37</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>2.21</v>
+        <v>0.54</v>
       </c>
       <c r="M8" t="n">
-        <v>11.61</v>
+        <v>11.27</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -27180,10 +27338,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1052.85</v>
+        <v>1052.57</v>
       </c>
       <c r="Q8" t="n">
-        <v>1024.11</v>
+        <v>1024</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -27208,6 +27366,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
+・売られ過ぎ水準です。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -27243,31 +27402,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1542</v>
+        <v>1539</v>
       </c>
       <c r="F9" t="n">
-        <v>-16</v>
+        <v>-19</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.03</v>
+        <v>-1.22</v>
       </c>
       <c r="H9" t="n">
-        <v>34500</v>
+        <v>65600</v>
       </c>
       <c r="I9" t="n">
-        <v>28.5</v>
+        <v>28.2</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.72</v>
+        <v>-3.9</v>
       </c>
       <c r="K9" t="n">
-        <v>0.71</v>
+        <v>1.2</v>
       </c>
       <c r="L9" t="n">
-        <v>17.41</v>
+        <v>17.17</v>
       </c>
       <c r="M9" t="n">
-        <v>39.24</v>
+        <v>39.2</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -27280,10 +27439,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1444.03</v>
+        <v>1443.99</v>
       </c>
       <c r="Q9" t="n">
-        <v>1377.27</v>
+        <v>1377.25</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -27344,31 +27503,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="F10" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.71</v>
+        <v>-0.61</v>
       </c>
       <c r="H10" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I10" t="n">
-        <v>62.4</v>
+        <v>62.9</v>
       </c>
       <c r="J10" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="K10" t="n">
-        <v>1.21</v>
+        <v>1.49</v>
       </c>
       <c r="L10" t="n">
-        <v>22.16</v>
+        <v>22.24</v>
       </c>
       <c r="M10" t="n">
-        <v>25.5</v>
+        <v>25.51</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -27381,10 +27540,10 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>866.23</v>
+        <v>866.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>986.15</v>
+        <v>986.16</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -27444,31 +27603,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3480</v>
+        <v>3551</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>82</v>
       </c>
       <c r="G11" t="n">
-        <v>0.32</v>
+        <v>2.36</v>
       </c>
       <c r="H11" t="n">
-        <v>4476100</v>
+        <v>7812300</v>
       </c>
       <c r="I11" t="n">
-        <v>41.4</v>
+        <v>48.1</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.3</v>
+        <v>-2.43</v>
       </c>
       <c r="K11" t="n">
-        <v>0.99</v>
+        <v>1.51</v>
       </c>
       <c r="L11" t="n">
-        <v>-65.01000000000001</v>
+        <v>-59.35</v>
       </c>
       <c r="M11" t="n">
-        <v>-48.39</v>
+        <v>-47.26</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -27477,14 +27636,14 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3657.52</v>
+        <v>3658.47</v>
       </c>
       <c r="Q11" t="n">
-        <v>2910.81</v>
+        <v>2911.16</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -27509,7 +27668,9 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・RSIは良好な水準です。
+・出来高が増加しています。
+・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
@@ -27548,31 +27709,31 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>3730</v>
+        <v>3660</v>
       </c>
       <c r="F12" t="n">
-        <v>-155</v>
+        <v>-225</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.99</v>
+        <v>-5.79</v>
       </c>
       <c r="H12" t="n">
-        <v>480300</v>
+        <v>804000</v>
       </c>
       <c r="I12" t="n">
-        <v>59.3</v>
+        <v>56.5</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3</v>
+        <v>-0.53</v>
       </c>
       <c r="K12" t="n">
-        <v>0.65</v>
+        <v>1.01</v>
       </c>
       <c r="L12" t="n">
-        <v>101.87</v>
+        <v>96.28</v>
       </c>
       <c r="M12" t="n">
-        <v>116.28</v>
+        <v>115.16</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -27585,10 +27746,10 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3186.31</v>
+        <v>3185.37</v>
       </c>
       <c r="Q12" t="n">
-        <v>3048.38</v>
+        <v>3048.03</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -27596,16 +27757,16 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -27623,7 +27784,7 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>⚪ 様子見（押し目ではない）</t>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -27645,31 +27806,31 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>4999</v>
+        <v>4982</v>
       </c>
       <c r="F13" t="n">
-        <v>-210</v>
+        <v>-227</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.03</v>
+        <v>-4.36</v>
       </c>
       <c r="H13" t="n">
-        <v>23739500</v>
+        <v>38396400</v>
       </c>
       <c r="I13" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
       <c r="J13" t="n">
-        <v>-6.94</v>
+        <v>-7.24</v>
       </c>
       <c r="K13" t="n">
-        <v>0.68</v>
+        <v>1.02</v>
       </c>
       <c r="L13" t="n">
-        <v>9.1</v>
+        <v>7.75</v>
       </c>
       <c r="M13" t="n">
-        <v>44.77</v>
+        <v>44.5</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -27682,10 +27843,10 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5065.57</v>
+        <v>5065.35</v>
       </c>
       <c r="Q13" t="n">
-        <v>4457.33</v>
+        <v>4457.24</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -27763,7 +27924,7 @@
         <v>-1.48</v>
       </c>
       <c r="H14" t="n">
-        <v>148400</v>
+        <v>248100</v>
       </c>
       <c r="I14" t="n">
         <v>23.1</v>
@@ -27772,7 +27933,7 @@
         <v>-7.48</v>
       </c>
       <c r="K14" t="n">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="L14" t="n">
         <v>-12.84</v>
@@ -27855,31 +28016,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4020</v>
+        <v>3981</v>
       </c>
       <c r="F15" t="n">
-        <v>-4</v>
+        <v>-43</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1</v>
+        <v>-1.07</v>
       </c>
       <c r="H15" t="n">
-        <v>14716000</v>
+        <v>23237900</v>
       </c>
       <c r="I15" t="n">
-        <v>58.4</v>
+        <v>57.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1.92</v>
+        <v>0.97</v>
       </c>
       <c r="K15" t="n">
-        <v>0.67</v>
+        <v>0.99</v>
       </c>
       <c r="L15" t="n">
-        <v>32.87</v>
+        <v>29.76</v>
       </c>
       <c r="M15" t="n">
-        <v>19.43</v>
+        <v>18.8</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -27892,10 +28053,10 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>4077.76</v>
+        <v>4077.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>3124.94</v>
+        <v>3124.74</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -27960,31 +28121,31 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>3955</v>
+        <v>3900</v>
       </c>
       <c r="F16" t="n">
-        <v>-90</v>
+        <v>-145</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.22</v>
+        <v>-3.58</v>
       </c>
       <c r="H16" t="n">
-        <v>11000</v>
+        <v>18800</v>
       </c>
       <c r="I16" t="n">
-        <v>46.2</v>
+        <v>44.5</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.27</v>
+        <v>-5.55</v>
       </c>
       <c r="K16" t="n">
-        <v>0.46</v>
+        <v>0.74</v>
       </c>
       <c r="L16" t="n">
-        <v>73.38</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>126.02</v>
+        <v>125.14</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -27993,14 +28154,14 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3533.29</v>
+        <v>3532.56</v>
       </c>
       <c r="Q16" t="n">
-        <v>2810.38</v>
+        <v>2810.1</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -28008,7 +28169,7 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -28025,8 +28186,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -28057,31 +28217,31 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>2314</v>
+        <v>2319</v>
       </c>
       <c r="F17" t="n">
-        <v>-35.5</v>
+        <v>-30</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.51</v>
+        <v>-1.28</v>
       </c>
       <c r="H17" t="n">
-        <v>7505700</v>
+        <v>11489600</v>
       </c>
       <c r="I17" t="n">
-        <v>28.4</v>
+        <v>28.6</v>
       </c>
       <c r="J17" t="n">
-        <v>-10.99</v>
+        <v>-10.79</v>
       </c>
       <c r="K17" t="n">
-        <v>0.64</v>
+        <v>0.92</v>
       </c>
       <c r="L17" t="n">
-        <v>-104.37</v>
+        <v>-103.93</v>
       </c>
       <c r="M17" t="n">
-        <v>-85.13</v>
+        <v>-85.05</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -28094,10 +28254,10 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2773.18</v>
+        <v>2773.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>2822.71</v>
+        <v>2822.74</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -28167,31 +28327,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3016</v>
+        <v>3031</v>
       </c>
       <c r="F18" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="G18" t="n">
-        <v>0.73</v>
+        <v>1.24</v>
       </c>
       <c r="H18" t="n">
-        <v>16427400</v>
+        <v>27282400</v>
       </c>
       <c r="I18" t="n">
-        <v>40.6</v>
+        <v>42.1</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.29</v>
+        <v>-0.82</v>
       </c>
       <c r="K18" t="n">
-        <v>0.79</v>
+        <v>1.19</v>
       </c>
       <c r="L18" t="n">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="M18" t="n">
-        <v>26.89</v>
+        <v>27.13</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -28204,10 +28364,10 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2933</v>
+        <v>2933.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3164.46</v>
+        <v>3164.54</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -28271,31 +28431,31 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>1818</v>
+        <v>1822</v>
       </c>
       <c r="F19" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="H19" t="n">
-        <v>8396000</v>
+        <v>13120700</v>
       </c>
       <c r="I19" t="n">
-        <v>56.2</v>
+        <v>56.7</v>
       </c>
       <c r="J19" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="K19" t="n">
-        <v>0.86</v>
+        <v>1.23</v>
       </c>
       <c r="L19" t="n">
-        <v>37.5</v>
+        <v>37.86</v>
       </c>
       <c r="M19" t="n">
-        <v>39.62</v>
+        <v>39.69</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -28308,10 +28468,10 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1673.4</v>
+        <v>1673.46</v>
       </c>
       <c r="Q19" t="n">
-        <v>1554.72</v>
+        <v>1554.74</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -28380,31 +28540,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G20" t="n">
-        <v>2.93</v>
+        <v>3.15</v>
       </c>
       <c r="H20" t="n">
-        <v>505400</v>
+        <v>884800</v>
       </c>
       <c r="I20" t="n">
-        <v>48.4</v>
+        <v>48.8</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.63</v>
+        <v>-0.42</v>
       </c>
       <c r="K20" t="n">
-        <v>0.64</v>
+        <v>1.03</v>
       </c>
       <c r="L20" t="n">
-        <v>3.08</v>
+        <v>3.16</v>
       </c>
       <c r="M20" t="n">
-        <v>7.3</v>
+        <v>7.31</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -28417,10 +28577,10 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>432.36</v>
+        <v>432.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>410.8</v>
+        <v>410.81</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -28477,31 +28637,31 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>8956</v>
+        <v>9209</v>
       </c>
       <c r="F21" t="n">
-        <v>-447</v>
+        <v>-194</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.75</v>
+        <v>-2.06</v>
       </c>
       <c r="H21" t="n">
-        <v>16436300</v>
+        <v>31494700</v>
       </c>
       <c r="I21" t="n">
-        <v>47.7</v>
+        <v>50.8</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.24</v>
+        <v>-3.69</v>
       </c>
       <c r="K21" t="n">
-        <v>0.61</v>
+        <v>1.06</v>
       </c>
       <c r="L21" t="n">
-        <v>-522.52</v>
+        <v>-502.34</v>
       </c>
       <c r="M21" t="n">
-        <v>-651.13</v>
+        <v>-647.09</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -28514,10 +28674,10 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>13271.95</v>
+        <v>13275.32</v>
       </c>
       <c r="Q21" t="n">
-        <v>7834.53</v>
+        <v>7835.8</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -28525,16 +28685,16 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -28578,31 +28738,31 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>53420</v>
+        <v>54030</v>
       </c>
       <c r="F22" t="n">
-        <v>-4670</v>
+        <v>-4060</v>
       </c>
       <c r="G22" t="n">
-        <v>-8.039999999999999</v>
+        <v>-6.99</v>
       </c>
       <c r="H22" t="n">
-        <v>16224700</v>
+        <v>28051100</v>
       </c>
       <c r="I22" t="n">
-        <v>54.4</v>
+        <v>55.5</v>
       </c>
       <c r="J22" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="K22" t="n">
         <v>0.91</v>
       </c>
-      <c r="K22" t="n">
-        <v>0.57</v>
-      </c>
       <c r="L22" t="n">
-        <v>-32.03</v>
+        <v>16.63</v>
       </c>
       <c r="M22" t="n">
-        <v>-991.5</v>
+        <v>-981.77</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -28615,10 +28775,10 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>66493.33</v>
+        <v>66501.47</v>
       </c>
       <c r="Q22" t="n">
-        <v>39189.07</v>
+        <v>39192.11</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -28679,28 +28839,28 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>160.8</v>
+        <v>160.6</v>
       </c>
       <c r="F23" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="G23" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="H23" t="n">
-        <v>29386100</v>
+        <v>48335100</v>
       </c>
       <c r="I23" t="n">
-        <v>49.9</v>
+        <v>49.6</v>
       </c>
       <c r="J23" t="n">
-        <v>1.01</v>
+        <v>0.89</v>
       </c>
       <c r="K23" t="n">
-        <v>0.66</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M23" t="n">
         <v>1.93</v>
@@ -28780,31 +28940,31 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>3139</v>
+        <v>3192</v>
       </c>
       <c r="F24" t="n">
-        <v>-181</v>
+        <v>-128</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.45</v>
+        <v>-3.86</v>
       </c>
       <c r="H24" t="n">
-        <v>5463500</v>
+        <v>10122800</v>
       </c>
       <c r="I24" t="n">
-        <v>33.9</v>
+        <v>36.1</v>
       </c>
       <c r="J24" t="n">
-        <v>-9.66</v>
+        <v>-8.19</v>
       </c>
       <c r="K24" t="n">
-        <v>0.61</v>
+        <v>1.02</v>
       </c>
       <c r="L24" t="n">
-        <v>-150.42</v>
+        <v>-146.19</v>
       </c>
       <c r="M24" t="n">
-        <v>-158.95</v>
+        <v>-158.1</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -28817,130 +28977,30 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>4069.68</v>
+        <v>4070.39</v>
       </c>
       <c r="Q24" t="n">
-        <v>3165.8</v>
+        <v>3166.06</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>🔴 下降</t>
+          <t>🟡 反発中</t>
         </is>
       </c>
       <c r="S24" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは買いシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>2026/10/28</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>あと47日</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>PENG</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ペンギン・ソリューションズ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="n">
-        <v>48.62</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-2.44</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-4.78</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1041600</v>
-      </c>
-      <c r="I25" t="n">
-        <v>43</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-9.24</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="L25" t="n">
-        <v>-2.14</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>59.72</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S25" t="n">
-        <v>70</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -28950,6 +29010,106 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>2026/10/28</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>あと47日</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PENG</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ペンギン・ソリューションズ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>48.62</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-4.78</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1041600</v>
+      </c>
+      <c r="I25" t="n">
+        <v>43</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-9.24</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>59.72</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>70</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr">
         <is>
           <t>2026/10/13</t>
@@ -28980,31 +29140,31 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>8063</v>
+        <v>8093</v>
       </c>
       <c r="F26" t="n">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="G26" t="n">
-        <v>0.93</v>
+        <v>1.3</v>
       </c>
       <c r="H26" t="n">
-        <v>6286100</v>
+        <v>9954600</v>
       </c>
       <c r="I26" t="n">
-        <v>30.8</v>
+        <v>31.9</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.85</v>
+        <v>-6.51</v>
       </c>
       <c r="K26" t="n">
-        <v>0.71</v>
+        <v>1.04</v>
       </c>
       <c r="L26" t="n">
-        <v>81.22</v>
+        <v>83.61</v>
       </c>
       <c r="M26" t="n">
-        <v>229.98</v>
+        <v>230.46</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -29017,10 +29177,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7698.27</v>
+        <v>7698.67</v>
       </c>
       <c r="Q26" t="n">
-        <v>8794.540000000001</v>
+        <v>8794.690000000001</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>212,230円</t>
+          <t>209,595円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2,940円</t>
+          <t>305円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>0.15%</t>
         </is>
       </c>
     </row>
@@ -717,26 +717,26 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3265</v>
+        <v>3325</v>
       </c>
       <c r="F2" t="n">
-        <v>46.1</v>
+        <v>46.3</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.34</v>
+        <v>-2.73</v>
       </c>
       <c r="H2" t="n">
-        <v>1.07</v>
+        <v>0.95</v>
       </c>
       <c r="I2" t="n">
-        <v>47.79</v>
+        <v>36.78</v>
       </c>
       <c r="J2" t="n">
-        <v>96.16</v>
+        <v>84.28</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>2978.95</v>
+        <v>2993.61</v>
       </c>
       <c r="N2" t="n">
-        <v>2711.77</v>
+        <v>2714.49</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -757,249 +757,23 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟠 利益確定検討</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>押し目、デッドクロス、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W2" t="n">
-        <v>3355</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-90</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-2.68</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>13060</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>10800</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2260</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>20.93</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>9432.T</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NTT</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>100</v>
-      </c>
-      <c r="D3" t="n">
-        <v>158</v>
-      </c>
-      <c r="E3" t="n">
-        <v>175.7</v>
-      </c>
-      <c r="F3" t="n">
-        <v>68</v>
-      </c>
-      <c r="G3" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>155.05</v>
-      </c>
-      <c r="N3" t="n">
-        <v>153.66</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>85</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>RSIやや過熱、25日線上、+1σ、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>175.2</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>17570</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>15800</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1770</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>11.2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3673.T</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ブロードリーフ</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" t="n">
-        <v>420</v>
-      </c>
-      <c r="E4" t="n">
-        <v>458</v>
-      </c>
-      <c r="F4" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="J4" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>432.38</v>
-      </c>
-      <c r="N4" t="n">
-        <v>410.81</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>65</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -1010,32 +784,257 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>押し目、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>3265</v>
+      </c>
+      <c r="X2" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>13300</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>10800</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>23.15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NTT</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E3" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>155.4</v>
+      </c>
+      <c r="N3" t="n">
+        <v>153.79</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>85</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>RSIやや過熱、25日線上、+1σ、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>175.7</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>17650</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>15800</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1850</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>11.71</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ブロードリーフ</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>420</v>
+      </c>
+      <c r="E4" t="n">
+        <v>466</v>
+      </c>
+      <c r="F4" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>432.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>411.43</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>🟢 強い買い</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>95</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="X4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.15</v>
+        <v>1.75</v>
       </c>
       <c r="Z4" t="n">
-        <v>45800</v>
+        <v>46600</v>
       </c>
       <c r="AA4" t="n">
         <v>42000</v>
       </c>
       <c r="AB4" t="n">
-        <v>3800</v>
+        <v>4600</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.050000000000001</v>
+        <v>10.95</v>
       </c>
     </row>
     <row r="5">
@@ -1056,22 +1055,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3031</v>
+        <v>3021</v>
       </c>
       <c r="F5" t="n">
-        <v>42.1</v>
+        <v>44.6</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.82</v>
+        <v>-1.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.19</v>
+        <v>0.48</v>
       </c>
       <c r="I5" t="n">
-        <v>7.7</v>
+        <v>4.77</v>
       </c>
       <c r="J5" t="n">
-        <v>27.13</v>
+        <v>22.66</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1084,10 +1083,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2933.2</v>
+        <v>2933.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3164.54</v>
+        <v>3164.72</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1129,25 +1128,25 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>2994</v>
+        <v>3031</v>
       </c>
       <c r="X5" t="n">
-        <v>37</v>
+        <v>-10</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.24</v>
+        <v>-0.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>39403</v>
+        <v>39273</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>2304</v>
+        <v>2174</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.21</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="6">
@@ -1168,22 +1167,22 @@
         <v>4795</v>
       </c>
       <c r="E6" t="n">
-        <v>5005</v>
+        <v>5058</v>
       </c>
       <c r="F6" t="n">
-        <v>59.7</v>
+        <v>63.1</v>
       </c>
       <c r="G6" t="n">
-        <v>3.3</v>
+        <v>4.23</v>
       </c>
       <c r="H6" t="n">
-        <v>1.23</v>
+        <v>0.4</v>
       </c>
       <c r="I6" t="n">
-        <v>70.62</v>
+        <v>75.48</v>
       </c>
       <c r="J6" t="n">
-        <v>55.7</v>
+        <v>59.65</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1196,10 +1195,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4719.41</v>
+        <v>4719.68</v>
       </c>
       <c r="N6" t="n">
-        <v>4649.56</v>
+        <v>4657.04</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1229,7 +1228,6 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・RSIは良好な水準です。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -1242,25 +1240,25 @@
         </is>
       </c>
       <c r="W6" t="n">
-        <v>4987</v>
+        <v>5005</v>
       </c>
       <c r="X6" t="n">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.36</v>
+        <v>1.06</v>
       </c>
       <c r="Z6" t="n">
-        <v>25025</v>
+        <v>25290</v>
       </c>
       <c r="AA6" t="n">
         <v>23975</v>
       </c>
       <c r="AB6" t="n">
-        <v>1050</v>
+        <v>1315</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.38</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="7">
@@ -1281,22 +1279,22 @@
         <v>7993</v>
       </c>
       <c r="E7" t="n">
-        <v>8093</v>
+        <v>8224</v>
       </c>
       <c r="F7" t="n">
-        <v>31.9</v>
+        <v>33.9</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.51</v>
+        <v>-5.08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>0.65</v>
       </c>
       <c r="I7" t="n">
-        <v>83.61</v>
+        <v>52.57</v>
       </c>
       <c r="J7" t="n">
-        <v>230.46</v>
+        <v>194.88</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1309,10 +1307,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>7698.67</v>
+        <v>7715.36</v>
       </c>
       <c r="N7" t="n">
-        <v>8794.690000000001</v>
+        <v>8771.08</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1354,25 +1352,25 @@
         </is>
       </c>
       <c r="W7" t="n">
-        <v>7989</v>
+        <v>8093</v>
       </c>
       <c r="X7" t="n">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="Z7" t="n">
-        <v>8093</v>
+        <v>8224</v>
       </c>
       <c r="AA7" t="n">
         <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>100</v>
+        <v>231</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.25</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="8">
@@ -1393,22 +1391,22 @@
         <v>55510</v>
       </c>
       <c r="E8" t="n">
-        <v>54030</v>
+        <v>50510</v>
       </c>
       <c r="F8" t="n">
-        <v>55.5</v>
+        <v>48.8</v>
       </c>
       <c r="G8" t="n">
-        <v>2.01</v>
+        <v>-4.84</v>
       </c>
       <c r="H8" t="n">
-        <v>0.91</v>
+        <v>0.64</v>
       </c>
       <c r="I8" t="n">
-        <v>16.63</v>
+        <v>-316.42</v>
       </c>
       <c r="J8" t="n">
-        <v>-981.77</v>
+        <v>-848.7</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1421,10 +1419,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>66501.47</v>
+        <v>66357.87</v>
       </c>
       <c r="N8" t="n">
-        <v>39192.11</v>
+        <v>39393.36</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1433,20 +1431,20 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1467,29 +1465,29 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD買い、反発局面</t>
+          <t>押し目、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>58090</v>
+        <v>54030</v>
       </c>
       <c r="X8" t="n">
-        <v>-4060</v>
+        <v>-3520</v>
       </c>
       <c r="Y8" t="n">
-        <v>-6.99</v>
+        <v>-6.51</v>
       </c>
       <c r="Z8" t="n">
-        <v>54030</v>
+        <v>50510</v>
       </c>
       <c r="AA8" t="n">
         <v>55510</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1480</v>
+        <v>-5000</v>
       </c>
       <c r="AC8" t="n">
-        <v>-2.67</v>
+        <v>-9.01</v>
       </c>
     </row>
     <row r="9">
@@ -1510,22 +1508,22 @@
         <v>10000</v>
       </c>
       <c r="E9" t="n">
-        <v>9209</v>
+        <v>8708</v>
       </c>
       <c r="F9" t="n">
-        <v>50.8</v>
+        <v>43.4</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.69</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>1.06</v>
+        <v>0.58</v>
       </c>
       <c r="I9" t="n">
-        <v>-502.34</v>
+        <v>-511.56</v>
       </c>
       <c r="J9" t="n">
-        <v>-647.09</v>
+        <v>-619.99</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1534,14 +1532,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>13275.32</v>
+        <v>13217.96</v>
       </c>
       <c r="N9" t="n">
-        <v>7835.8</v>
+        <v>7863.87</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1550,20 +1548,20 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1571,38 +1569,41 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>⚠️ 急落</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD買い、反発局面</t>
+          <t>押し目、-1σ、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>9403</v>
+        <v>9209</v>
       </c>
       <c r="X9" t="n">
-        <v>-194</v>
+        <v>-501</v>
       </c>
       <c r="Y9" t="n">
-        <v>-2.06</v>
+        <v>-5.44</v>
       </c>
       <c r="Z9" t="n">
-        <v>9209</v>
+        <v>8708</v>
       </c>
       <c r="AA9" t="n">
         <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-791</v>
+        <v>-1292</v>
       </c>
       <c r="AC9" t="n">
-        <v>-7.91</v>
+        <v>-12.92</v>
       </c>
     </row>
     <row r="10">
@@ -1733,7 +1734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1367"/>
+  <dimension ref="A1:C1376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22240,6 +22241,141 @@
         </is>
       </c>
       <c r="C1367" t="n">
+        <v>40.1</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1368" t="n">
+        <v>3325</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1369" t="n">
+        <v>176.5</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1370" t="n">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1371" t="n">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1372" t="n">
+        <v>5058</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1373" t="n">
+        <v>8224</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1374" t="n">
+        <v>50510</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1375" t="n">
+        <v>8708</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1376" t="n">
         <v>40.1</v>
       </c>
     </row>
@@ -22254,7 +22390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F238"/>
+  <dimension ref="A1:F239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26502,19 +26638,29 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
+      <c r="A236" t="inlineStr"/>
+      <c r="B236" s="1" t="n">
+        <v>46279.5</v>
+      </c>
+      <c r="C236" t="n">
+        <v>209595</v>
+      </c>
+      <c r="D236" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E236" t="n">
+        <v>305</v>
+      </c>
+      <c r="F236" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr"/>
-      <c r="C236" t="inlineStr"/>
-      <c r="D236" t="inlineStr"/>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr"/>
       <c r="B237" t="inlineStr"/>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr"/>
@@ -26522,16 +26668,24 @@
       <c r="F237" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A238" t="inlineStr"/>
       <c r="B238" t="inlineStr"/>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr"/>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27682,7 +27836,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>あと48日</t>
+          <t>あと46日</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -27884,7 +28038,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>あと60日</t>
+          <t>あと58日</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -28094,7 +28248,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>あと59日</t>
+          <t>あと57日</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -28296,7 +28450,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>あと61日</t>
+          <t>あと59日</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -28404,7 +28558,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>あと55日</t>
+          <t>あと53日</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -28509,7 +28663,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>あと48日</t>
+          <t>あと46日</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -28715,7 +28869,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>あと55日</t>
+          <t>あと53日</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -28816,7 +28970,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>あと49日</t>
+          <t>あと47日</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -28917,7 +29071,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>あと62日</t>
+          <t>あと60日</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -29017,7 +29171,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>あと47日</t>
+          <t>あと45日</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -29040,31 +29194,31 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>48.62</v>
+        <v>51.16</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.44</v>
+        <v>2.54</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.78</v>
+        <v>5.22</v>
       </c>
       <c r="H25" t="n">
-        <v>1041600</v>
+        <v>1471000</v>
       </c>
       <c r="I25" t="n">
-        <v>43</v>
+        <v>46.2</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.24</v>
+        <v>-4.14</v>
       </c>
       <c r="K25" t="n">
-        <v>0.96</v>
+        <v>1.27</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.14</v>
+        <v>-1.94</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.25</v>
+        <v>-2.19</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -29073,14 +29227,14 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>59.72</v>
+        <v>59.67</v>
       </c>
       <c r="Q25" t="n">
-        <v>37.1</v>
+        <v>37.27</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -29088,7 +29242,7 @@
         </is>
       </c>
       <c r="S25" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -29105,7 +29259,8 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
@@ -29117,7 +29272,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>あと32日</t>
+          <t>あと30日</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -29217,7 +29372,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>あと53日</t>
+          <t>あと51日</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>209,595円</t>
+          <t>210,602円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>305円</t>
+          <t>1,312円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3325</v>
+        <v>3345</v>
       </c>
       <c r="F2" t="n">
-        <v>46.3</v>
+        <v>47.2</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.73</v>
+        <v>-2.16</v>
       </c>
       <c r="H2" t="n">
-        <v>0.95</v>
+        <v>1.68</v>
       </c>
       <c r="I2" t="n">
-        <v>36.78</v>
+        <v>38.37</v>
       </c>
       <c r="J2" t="n">
-        <v>84.28</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>2993.61</v>
+        <v>2993.88</v>
       </c>
       <c r="N2" t="n">
-        <v>2714.49</v>
+        <v>2714.59</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -774,6 +774,120 @@
         </is>
       </c>
       <c r="T2" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・出来高が増加しています。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>押し目、出来高微増、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>3265</v>
+      </c>
+      <c r="X2" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>13380</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>10800</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2580</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>23.89</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ブロードリーフ</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>420</v>
+      </c>
+      <c r="E3" t="n">
+        <v>475</v>
+      </c>
+      <c r="F3" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>432.62</v>
+      </c>
+      <c r="N3" t="n">
+        <v>411.47</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>🟢 強い買い</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>95</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -784,257 +898,144 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>押し目、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W2" t="n">
-        <v>3265</v>
-      </c>
-      <c r="X2" t="n">
-        <v>60</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>13300</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>10800</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2500</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>23.15</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>458</v>
+      </c>
+      <c r="X3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>47500</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>42000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>5500</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>9432.T</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>NTT</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C4" t="n">
         <v>100</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
         <v>158</v>
       </c>
-      <c r="E3" t="n">
-        <v>176.5</v>
-      </c>
-      <c r="F3" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="G3" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="E4" t="n">
+        <v>178.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>+1S</t>
         </is>
       </c>
-      <c r="M3" t="n">
-        <v>155.4</v>
-      </c>
-      <c r="N3" t="n">
-        <v>153.79</v>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="M4" t="n">
+        <v>155.43</v>
+      </c>
+      <c r="N4" t="n">
+        <v>153.8</v>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>85</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>🟢 強い買い</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>100</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
-・MACDは売りシグナルです。
+・MACDは買いシグナルです。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>RSIやや過熱、25日線上、+1σ、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>175.7</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>17650</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>15800</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1850</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>11.71</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3673.T</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ブロードリーフ</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" t="n">
-        <v>420</v>
-      </c>
-      <c r="E4" t="n">
-        <v>466</v>
-      </c>
-      <c r="F4" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>432.5</v>
-      </c>
-      <c r="N4" t="n">
-        <v>411.43</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>🟢 強い買い</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>95</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+          <t>RSIやや過熱、25日線上、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>458</v>
+        <v>175.7</v>
       </c>
       <c r="X4" t="n">
-        <v>8</v>
+        <v>2.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="Z4" t="n">
-        <v>46600</v>
+        <v>17830</v>
       </c>
       <c r="AA4" t="n">
-        <v>42000</v>
+        <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>4600</v>
+        <v>2030</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.95</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="5">
@@ -1055,22 +1056,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="F5" t="n">
-        <v>44.6</v>
+        <v>44.9</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2</v>
+        <v>-1.07</v>
       </c>
       <c r="H5" t="n">
-        <v>0.48</v>
+        <v>0.92</v>
       </c>
       <c r="I5" t="n">
-        <v>4.77</v>
+        <v>5.09</v>
       </c>
       <c r="J5" t="n">
-        <v>22.66</v>
+        <v>22.72</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1083,10 +1084,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2933.08</v>
+        <v>2933.13</v>
       </c>
       <c r="N5" t="n">
-        <v>3164.72</v>
+        <v>3164.74</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1131,22 +1132,22 @@
         <v>3031</v>
       </c>
       <c r="X5" t="n">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.33</v>
+        <v>-0.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>39273</v>
+        <v>39325</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>2174</v>
+        <v>2226</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.86</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -1167,22 +1168,22 @@
         <v>4795</v>
       </c>
       <c r="E6" t="n">
-        <v>5058</v>
+        <v>4991</v>
       </c>
       <c r="F6" t="n">
-        <v>63.1</v>
+        <v>60.4</v>
       </c>
       <c r="G6" t="n">
-        <v>4.23</v>
+        <v>2.91</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4</v>
+        <v>0.84</v>
       </c>
       <c r="I6" t="n">
-        <v>75.48</v>
+        <v>70.14</v>
       </c>
       <c r="J6" t="n">
-        <v>59.65</v>
+        <v>58.58</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1195,10 +1196,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4719.68</v>
+        <v>4718.79</v>
       </c>
       <c r="N6" t="n">
-        <v>4657.04</v>
+        <v>4656.71</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1243,22 +1244,22 @@
         <v>5005</v>
       </c>
       <c r="X6" t="n">
-        <v>53</v>
+        <v>-14</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.06</v>
+        <v>-0.28</v>
       </c>
       <c r="Z6" t="n">
-        <v>25290</v>
+        <v>24955</v>
       </c>
       <c r="AA6" t="n">
         <v>23975</v>
       </c>
       <c r="AB6" t="n">
-        <v>1315</v>
+        <v>980</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.48</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="7">
@@ -1279,22 +1280,22 @@
         <v>7993</v>
       </c>
       <c r="E7" t="n">
-        <v>8224</v>
+        <v>8268</v>
       </c>
       <c r="F7" t="n">
-        <v>33.9</v>
+        <v>35.4</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.08</v>
+        <v>-4.59</v>
       </c>
       <c r="H7" t="n">
-        <v>0.65</v>
+        <v>0.93</v>
       </c>
       <c r="I7" t="n">
-        <v>52.57</v>
+        <v>56.08</v>
       </c>
       <c r="J7" t="n">
-        <v>194.88</v>
+        <v>195.58</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1307,10 +1308,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>7715.36</v>
+        <v>7715.95</v>
       </c>
       <c r="N7" t="n">
-        <v>8771.08</v>
+        <v>8771.299999999999</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1355,22 +1356,22 @@
         <v>8093</v>
       </c>
       <c r="X7" t="n">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.62</v>
+        <v>2.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>8224</v>
+        <v>8268</v>
       </c>
       <c r="AA7" t="n">
         <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>231</v>
+        <v>275</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.89</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="8">
@@ -1391,22 +1392,22 @@
         <v>55510</v>
       </c>
       <c r="E8" t="n">
-        <v>50510</v>
+        <v>50590</v>
       </c>
       <c r="F8" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.84</v>
+        <v>-4.69</v>
       </c>
       <c r="H8" t="n">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="I8" t="n">
-        <v>-316.42</v>
+        <v>-310.04</v>
       </c>
       <c r="J8" t="n">
-        <v>-848.7</v>
+        <v>-847.4299999999999</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1419,10 +1420,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>66357.87</v>
+        <v>66358.92999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>39393.36</v>
+        <v>39393.76</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1472,22 +1473,22 @@
         <v>54030</v>
       </c>
       <c r="X8" t="n">
-        <v>-3520</v>
+        <v>-3440</v>
       </c>
       <c r="Y8" t="n">
-        <v>-6.51</v>
+        <v>-6.37</v>
       </c>
       <c r="Z8" t="n">
-        <v>50510</v>
+        <v>50590</v>
       </c>
       <c r="AA8" t="n">
         <v>55510</v>
       </c>
       <c r="AB8" t="n">
-        <v>-5000</v>
+        <v>-4920</v>
       </c>
       <c r="AC8" t="n">
-        <v>-9.01</v>
+        <v>-8.859999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1508,22 +1509,22 @@
         <v>10000</v>
       </c>
       <c r="E9" t="n">
-        <v>8708</v>
+        <v>8714</v>
       </c>
       <c r="F9" t="n">
         <v>43.4</v>
       </c>
       <c r="G9" t="n">
-        <v>-8.550000000000001</v>
+        <v>-8.49</v>
       </c>
       <c r="H9" t="n">
-        <v>0.58</v>
+        <v>0.87</v>
       </c>
       <c r="I9" t="n">
-        <v>-511.56</v>
+        <v>-511.08</v>
       </c>
       <c r="J9" t="n">
-        <v>-619.99</v>
+        <v>-619.89</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1536,10 +1537,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>13217.96</v>
+        <v>13218.04</v>
       </c>
       <c r="N9" t="n">
-        <v>7863.87</v>
+        <v>7863.9</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1588,22 +1589,22 @@
         <v>9209</v>
       </c>
       <c r="X9" t="n">
-        <v>-501</v>
+        <v>-495</v>
       </c>
       <c r="Y9" t="n">
-        <v>-5.44</v>
+        <v>-5.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>8708</v>
+        <v>8714</v>
       </c>
       <c r="AA9" t="n">
         <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1292</v>
+        <v>-1286</v>
       </c>
       <c r="AC9" t="n">
-        <v>-12.92</v>
+        <v>-12.86</v>
       </c>
     </row>
     <row r="10">
@@ -1734,7 +1735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1376"/>
+  <dimension ref="A1:C1385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22376,6 +22377,141 @@
         </is>
       </c>
       <c r="C1376" t="n">
+        <v>40.1</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1377" t="n">
+        <v>3345</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1378" t="n">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1379" t="n">
+        <v>178.3</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1380" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1381" t="n">
+        <v>4991</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1382" t="n">
+        <v>8268</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1383" t="n">
+        <v>50590</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1384" t="n">
+        <v>8714</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1385" t="n">
         <v>40.1</v>
       </c>
     </row>
@@ -22390,7 +22526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F239"/>
+  <dimension ref="A1:F240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26656,19 +26792,29 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr">
+      <c r="A237" t="inlineStr"/>
+      <c r="B237" s="1" t="n">
+        <v>46279.75</v>
+      </c>
+      <c r="C237" t="n">
+        <v>210602</v>
+      </c>
+      <c r="D237" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E237" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F237" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr"/>
-      <c r="C237" t="inlineStr"/>
-      <c r="D237" t="inlineStr"/>
-      <c r="E237" t="inlineStr"/>
-      <c r="F237" t="inlineStr"/>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr"/>
       <c r="B238" t="inlineStr"/>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr"/>
@@ -26676,16 +26822,24 @@
       <c r="F238" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A239" t="inlineStr"/>
       <c r="B239" t="inlineStr"/>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26850,31 +27004,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1015</v>
+        <v>995</v>
       </c>
       <c r="F2" t="n">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.4</v>
+        <v>-1.97</v>
       </c>
       <c r="H2" t="n">
-        <v>709600</v>
+        <v>662200</v>
       </c>
       <c r="I2" t="n">
-        <v>53.3</v>
+        <v>56.9</v>
       </c>
       <c r="J2" t="n">
-        <v>4.67</v>
+        <v>1.9</v>
       </c>
       <c r="K2" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="L2" t="n">
-        <v>45.22</v>
+        <v>39.98</v>
       </c>
       <c r="M2" t="n">
-        <v>47.95</v>
+        <v>46.35</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -26887,10 +27041,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>832.01</v>
+        <v>836.33</v>
       </c>
       <c r="Q2" t="n">
-        <v>1124.74</v>
+        <v>1122.86</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -26951,67 +27105,268 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3265</v>
+        <v>3325</v>
       </c>
       <c r="F3" t="n">
-        <v>-90</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.68</v>
+        <v>1.84</v>
       </c>
       <c r="H3" t="n">
-        <v>66400</v>
+        <v>56400</v>
       </c>
       <c r="I3" t="n">
-        <v>46.1</v>
+        <v>46.3</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.34</v>
+        <v>-2.73</v>
       </c>
       <c r="K3" t="n">
-        <v>1.07</v>
+        <v>0.95</v>
       </c>
       <c r="L3" t="n">
-        <v>47.79</v>
+        <v>36.78</v>
       </c>
       <c r="M3" t="n">
-        <v>96.16</v>
+        <v>84.28</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>2993.61</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2714.49</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>65</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>4412.T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>サイエンスアーツ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>現場向けコミュニケーション</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1344</v>
+      </c>
+      <c r="F4" t="n">
+        <v>18</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3800</v>
+      </c>
+      <c r="I4" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="L4" t="n">
+        <v>41.32</v>
+      </c>
+      <c r="M4" t="n">
+        <v>42.24</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1203.4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1642.2</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>85</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5532.T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>リアルゲイト</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>オフィス再生</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3455</v>
+      </c>
+      <c r="F5" t="n">
+        <v>20</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I5" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="M5" t="n">
+        <v>9</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>DC</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P3" t="n">
-        <v>2978.95</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2711.77</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P5" t="n">
+        <v>3435.67</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3139.53</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S3" t="n">
-        <v>50</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
+      <c r="S5" t="n">
+        <v>80</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -27023,198 +27378,1009 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>🟡 調整中押し目（段階的買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>4412.T</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>サイエンスアーツ</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3984.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ユーザーローカル</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>監視</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>現場向けコミュニケーション</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1326</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-25</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-1.85</v>
-      </c>
-      <c r="H4" t="n">
-        <v>10200</v>
-      </c>
-      <c r="I4" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="L4" t="n">
-        <v>43.49</v>
-      </c>
-      <c r="M4" t="n">
-        <v>42.47</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AI解析・データ分析</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1535</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H6" t="n">
+        <v>27700</v>
+      </c>
+      <c r="I6" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-32.98</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-39.99</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P4" t="n">
-        <v>1203.46</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1643.14</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>100</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
+      <c r="P6" t="n">
+        <v>1688.33</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1703</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>30</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟢 上昇
+・🔴 下降
 ・MACDは買いシグナルです。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4054.T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>日本情報クリエイト</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>不動産向けクラウド</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>520</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I7" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-7.26</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-8.01</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>537.11</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>584.87</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>30</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは買いシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7072.T</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>インティメート・マージャー</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>データマーケティング</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1066</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-13</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3400</v>
+      </c>
+      <c r="I8" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-6.08</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-3.44</v>
+      </c>
+      <c r="M8" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1053.01</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1022.86</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>85</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・売られ過ぎ水準です。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7033.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>マネジメントソリューションズ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PMO支援・DX案件増加</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1556</v>
+      </c>
+      <c r="F9" t="n">
+        <v>17</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20700</v>
+      </c>
+      <c r="I9" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L9" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="M9" t="n">
+        <v>34</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1446.59</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1378.32</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>65</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9342.T</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>スマサポ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>不動産DX</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>975</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I10" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="L10" t="n">
+        <v>22.24</v>
+      </c>
+      <c r="M10" t="n">
+        <v>25.51</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>866.24</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>986.16</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>85</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
         <is>
           <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>5532.T</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>リアルゲイト</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6971.T</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>京セラ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>自社株</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3526</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-25</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1784500</v>
+      </c>
+      <c r="I11" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-55.38</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-48.89</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>3661.87</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2918.85</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>45</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026/10/29</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>あと45日</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3778.T</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>さくらインターネット(株)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>監視</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>オフィス再生</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>3435</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-10</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="H5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="M5" t="n">
-        <v>9.18</v>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>3580</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-80</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="H12" t="n">
+        <v>385900</v>
+      </c>
+      <c r="I12" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L12" t="n">
+        <v>79.91</v>
+      </c>
+      <c r="M12" t="n">
+        <v>108.11</v>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P5" t="n">
-        <v>3443.47</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3135.29</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P12" t="n">
+        <v>3193.37</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3051.07</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>85</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5803.T</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>(株)フジクラ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>4864</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-118</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="H13" t="n">
+        <v>21964600</v>
+      </c>
+      <c r="I13" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-9.220000000000001</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-19.85</v>
+      </c>
+      <c r="M13" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>5063.31</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4466.74</v>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>🟡 反発中</t>
         </is>
       </c>
-      <c r="S5" t="n">
-        <v>85</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2026/11/10</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>あと57日</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>166A.T</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>タスキホールディングス</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>何度も高値更新中の強トレンド</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1060</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="H14" t="n">
+        <v>100500</v>
+      </c>
+      <c r="I14" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-7.45</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-16.48</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1106.17</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>924.13</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>65</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・売られ過ぎ水準です。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5801.T</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>古河電気工業</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>半導体設備関連</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-97</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="H15" t="n">
+        <v>13771900</v>
+      </c>
+      <c r="I15" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L15" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>4059.69</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3139.52</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>65</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -27225,499 +28391,305 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr">
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2026/11/09</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>あと56日</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
         <is>
           <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>3984.T</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ユーザーローカル</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3374.T</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>内外テック</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>監視</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>AI解析・データ分析</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1529</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="H6" t="n">
-        <v>111300</v>
-      </c>
-      <c r="I6" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-0.96</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-35.11</v>
-      </c>
-      <c r="M6" t="n">
-        <v>-41.74</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>3850</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-50</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="H16" t="n">
+        <v>13600</v>
+      </c>
+      <c r="I16" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-7.06</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L16" t="n">
+        <v>47.87</v>
+      </c>
+      <c r="M16" t="n">
+        <v>109.69</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>1689.93</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1704.91</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v>30</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは買いシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>4054.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>日本情報クリエイト</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>不動産向けクラウド</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>518</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>6400</v>
-      </c>
-      <c r="I7" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-2.12</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-7.66</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>536.96</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>585.73</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>30</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは買いシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7072.T</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>インティメート・マージャー</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>データマーケティング</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1079</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-18</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-1.64</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3500</v>
-      </c>
-      <c r="I8" t="n">
-        <v>30</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-5.06</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="M8" t="n">
-        <v>11.27</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>-1S</t>
         </is>
       </c>
-      <c r="P8" t="n">
-        <v>1052.57</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1024</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P16" t="n">
+        <v>3543.16</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2819.59</v>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S8" t="n">
+      <c r="S16" t="n">
         <v>70</v>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・売られ過ぎ水準です。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
         <is>
           <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>7033.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>マネジメントソリューションズ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>7012.T</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>川崎重工業(株)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>監視</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PMO支援・DX案件増加</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1539</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-19</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="H9" t="n">
-        <v>65600</v>
-      </c>
-      <c r="I9" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>17.17</v>
-      </c>
-      <c r="M9" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>2354</v>
+      </c>
+      <c r="F17" t="n">
+        <v>35</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4390200</v>
+      </c>
+      <c r="I17" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-8.84</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-104.4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-88.92</v>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>2763.45</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2824.42</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは売りシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>あと58日</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>トヨタ自動車(株)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4000円で売る予定</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3021</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="H18" t="n">
+        <v>10817600</v>
+      </c>
+      <c r="I18" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L18" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="M18" t="n">
+        <v>22.66</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P9" t="n">
-        <v>1443.99</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1377.25</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>80</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9342.T</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>スマサポ</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>不動産DX</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>975</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-6</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I10" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="L10" t="n">
-        <v>22.24</v>
-      </c>
-      <c r="M10" t="n">
-        <v>25.51</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>866.24</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>986.16</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P18" t="n">
+        <v>2933.08</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3164.72</v>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>🟢 上昇</t>
         </is>
       </c>
-      <c r="S10" t="n">
-        <v>85</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
+      <c r="S18" t="n">
+        <v>55</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 上昇
@@ -27727,203 +28699,101 @@
 順張りが有利な局面です。</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>6971.T</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>京セラ</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2026/11/05</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>あと52日</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>8053.T</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>住友商事</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>保有中</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>自社株</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>3551</v>
-      </c>
-      <c r="F11" t="n">
-        <v>82</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="H11" t="n">
-        <v>7812300</v>
-      </c>
-      <c r="I11" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>-2.43</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-59.35</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-47.26</v>
-      </c>
-      <c r="N11" t="inlineStr">
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>1825</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2487800</v>
+      </c>
+      <c r="I19" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="L19" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="M19" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P11" t="n">
-        <v>3658.47</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2911.16</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>50</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・出来高が増加しています。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2026/10/29</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>あと46日</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>3778.T</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>さくらインターネット(株)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="n">
-        <v>3660</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-225</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-5.79</v>
-      </c>
-      <c r="H12" t="n">
-        <v>804000</v>
-      </c>
-      <c r="I12" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="L12" t="n">
-        <v>96.28</v>
-      </c>
-      <c r="M12" t="n">
-        <v>115.16</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>3185.37</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3048.03</v>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="P19" t="n">
+        <v>1674.11</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1558.07</v>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S12" t="n">
-        <v>85</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
+      <c r="S19" t="n">
+        <v>95</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -27934,303 +28804,302 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>5803.T</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>(株)フジクラ</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2026/10/29</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>あと45日</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ブロードリーフ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>500円で売</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>466</v>
+      </c>
+      <c r="F20" t="n">
+        <v>8</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H20" t="n">
+        <v>152300</v>
+      </c>
+      <c r="I20" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M20" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>432.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>411.43</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>95</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>監視</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="n">
-        <v>4982</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-227</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-4.36</v>
-      </c>
-      <c r="H13" t="n">
-        <v>38396400</v>
-      </c>
-      <c r="I13" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-7.24</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="L13" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="M13" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>8708</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-501</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-5.44</v>
+      </c>
+      <c r="H21" t="n">
+        <v>15854400</v>
+      </c>
+      <c r="I21" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-8.550000000000001</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-511.56</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-619.99</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>-1S</t>
         </is>
       </c>
-      <c r="P13" t="n">
-        <v>5065.35</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4457.24</v>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="P21" t="n">
+        <v>13217.96</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>7863.87</v>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>🟡 反発中</t>
         </is>
       </c>
-      <c r="S13" t="n">
-        <v>50</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
+      <c r="S21" t="n">
+        <v>70</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
+・MACDは買いシグナルです。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>2026/11/10</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>あと58日</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2026/11/05</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>あと52日</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
         <is>
           <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>166A.T</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>タスキホールディングス</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>何度も高値更新中の強トレンド</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1063</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-16</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="H14" t="n">
-        <v>248100</v>
-      </c>
-      <c r="I14" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-7.48</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-12.84</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N14" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>キオクシアホールディングス</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>50510</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-3520</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-6.51</v>
+      </c>
+      <c r="H22" t="n">
+        <v>17850900</v>
+      </c>
+      <c r="I22" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-4.84</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-316.42</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-848.7</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1104.31</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>922.6</v>
-      </c>
-      <c r="R14" t="inlineStr">
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>66357.87</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>39393.36</v>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>🟡 反発中</t>
         </is>
       </c>
-      <c r="S14" t="n">
+      <c r="S22" t="n">
         <v>65</v>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>5801.T</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>古河電気工業</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>半導体設備関連</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>3981</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-43</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="H15" t="n">
-        <v>23237900</v>
-      </c>
-      <c r="I15" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="L15" t="n">
-        <v>29.76</v>
-      </c>
-      <c r="M15" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>4077.24</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3124.74</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S15" t="n">
-        <v>95</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -28241,411 +29110,97 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>2026/11/09</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>あと57日</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>3374.T</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>内外テック</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="n">
-        <v>3900</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-145</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-3.58</v>
-      </c>
-      <c r="H16" t="n">
-        <v>18800</v>
-      </c>
-      <c r="I16" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>-5.55</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="L16" t="n">
-        <v>68.98999999999999</v>
-      </c>
-      <c r="M16" t="n">
-        <v>125.14</v>
-      </c>
-      <c r="N16" t="inlineStr">
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2026/10/30</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>あと46日</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>8729.T</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ソニーファイナンシャル</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>161.2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H23" t="n">
+        <v>24161700</v>
+      </c>
+      <c r="I23" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>3532.56</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2810.1</v>
-      </c>
-      <c r="R16" t="inlineStr">
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>151.69</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>150.41</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S16" t="n">
-        <v>70</v>
-      </c>
-      <c r="T16" t="inlineStr">
+      <c r="S23" t="n">
+        <v>75</v>
+      </c>
+      <c r="T23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>7012.T</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>川崎重工業(株)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="n">
-        <v>2319</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-1.28</v>
-      </c>
-      <c r="H17" t="n">
-        <v>11489600</v>
-      </c>
-      <c r="I17" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-10.79</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-103.93</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-85.05</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>2773.25</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2822.74</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S17" t="n">
-        <v>15</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・25日線から大きく下に乖離しています。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>あと59日</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>7203.T</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>トヨタ自動車(株)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4000円で売る予定</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>3031</v>
-      </c>
-      <c r="F18" t="n">
-        <v>37</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="H18" t="n">
-        <v>27282400</v>
-      </c>
-      <c r="I18" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="L18" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="M18" t="n">
-        <v>27.13</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>2933.2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3164.54</v>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="S18" t="n">
-        <v>55</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>2026/11/05</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>あと53日</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>8053.T</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>住友商事</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="n">
-        <v>1822</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H19" t="n">
-        <v>13120700</v>
-      </c>
-      <c r="I19" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="L19" t="n">
-        <v>37.86</v>
-      </c>
-      <c r="M19" t="n">
-        <v>39.69</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1673.46</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1554.74</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S19" t="n">
-        <v>95</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -28656,202 +29211,197 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>2026/10/29</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>あと46日</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>2026/11/12</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>あと59日</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
         <is>
           <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>3673.T</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ブロードリーフ</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>500円で売</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>458</v>
-      </c>
-      <c r="F20" t="n">
-        <v>14</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="H20" t="n">
-        <v>884800</v>
-      </c>
-      <c r="I20" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="J20" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="L20" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="M20" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="N20" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6723.T</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ルネサスエレクトロニクス</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>3151</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-41</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5581700</v>
+      </c>
+      <c r="I24" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-8.74</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-149.67</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-156.41</v>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>4054.99</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3172.58</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>35</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは買いシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>2026/10/28</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>あと44日</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PENG</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ペンギン・ソリューションズ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>51.16</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1471000</v>
+      </c>
+      <c r="I25" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-4.14</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P20" t="n">
-        <v>432.38</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>410.81</v>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S20" t="n">
+      <c r="P25" t="n">
+        <v>59.67</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
         <v>65</v>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="n">
-        <v>9209</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-194</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-2.06</v>
-      </c>
-      <c r="H21" t="n">
-        <v>31494700</v>
-      </c>
-      <c r="I21" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-3.69</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-502.34</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-647.09</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>13275.32</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>7835.8</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S21" t="n">
-        <v>85</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -28862,409 +29412,6 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>2026/11/05</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>あと53日</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>285A.T</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>キオクシアホールディングス</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="n">
-        <v>54030</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-4060</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-6.99</v>
-      </c>
-      <c r="H22" t="n">
-        <v>28051100</v>
-      </c>
-      <c r="I22" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="L22" t="n">
-        <v>16.63</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-981.77</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>66501.47</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>39192.11</v>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S22" t="n">
-        <v>95</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>2026/10/30</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>あと47日</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>8729.T</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ソニーファイナンシャル</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>160.6</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="H23" t="n">
-        <v>48335100</v>
-      </c>
-      <c r="I23" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>151.43</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>150.34</v>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S23" t="n">
-        <v>75</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>2026/11/12</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>あと60日</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>6723.T</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>ルネサスエレクトロニクス</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="n">
-        <v>3192</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-128</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-3.86</v>
-      </c>
-      <c r="H24" t="n">
-        <v>10122800</v>
-      </c>
-      <c r="I24" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>-8.19</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="L24" t="n">
-        <v>-146.19</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-158.1</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>4070.39</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3166.06</v>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S24" t="n">
-        <v>70</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>2026/10/28</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>あと45日</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>PENG</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ペンギン・ソリューションズ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="n">
-        <v>51.16</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="G25" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1471000</v>
-      </c>
-      <c r="I25" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-4.14</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="L25" t="n">
-        <v>-1.94</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-2.19</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>59.67</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>37.27</v>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S25" t="n">
-        <v>65</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="W25" t="inlineStr">
         <is>
           <t>2026/10/13</t>
@@ -29272,7 +29419,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>あと30日</t>
+          <t>あと29日</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -29295,31 +29442,31 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>8093</v>
+        <v>8224</v>
       </c>
       <c r="F26" t="n">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="G26" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="H26" t="n">
-        <v>9954600</v>
+        <v>6219300</v>
       </c>
       <c r="I26" t="n">
-        <v>31.9</v>
+        <v>33.9</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.51</v>
+        <v>-5.08</v>
       </c>
       <c r="K26" t="n">
-        <v>1.04</v>
+        <v>0.65</v>
       </c>
       <c r="L26" t="n">
-        <v>83.61</v>
+        <v>52.57</v>
       </c>
       <c r="M26" t="n">
-        <v>230.46</v>
+        <v>194.88</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -29332,10 +29479,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7698.67</v>
+        <v>7715.36</v>
       </c>
       <c r="Q26" t="n">
-        <v>8794.690000000001</v>
+        <v>8771.08</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -29372,7 +29519,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>あと51日</t>
+          <t>あと50日</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>210,602円</t>
+          <t>210,599円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1,312円</t>
+          <t>1,309円</t>
         </is>
       </c>
     </row>
@@ -1625,22 +1625,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>40.1</v>
+        <v>36.74</v>
       </c>
       <c r="F10" t="n">
-        <v>57.6</v>
+        <v>53.9</v>
       </c>
       <c r="G10" t="n">
-        <v>7.97</v>
+        <v>-1.67</v>
       </c>
       <c r="H10" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="I10" t="n">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="J10" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.71</v>
+        <v>33.69</v>
       </c>
       <c r="N10" t="n">
-        <v>31.49</v>
+        <v>31.51</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1665,20 +1665,20 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1687,41 +1687,41 @@
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>🚀 急騰</t>
+          <t>⚠️ 急落</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+1σ、MACD売り、長期上昇</t>
+          <t>RSI適正、押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>37.38</v>
+        <v>40.1</v>
       </c>
       <c r="X10" t="n">
-        <v>2.72</v>
+        <v>-3.36</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.28</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6073</v>
+        <v>-6076</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.34</v>
+        <v>-99.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1735,7 +1735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1385"/>
+  <dimension ref="A1:C1394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22513,6 +22513,141 @@
       </c>
       <c r="C1385" t="n">
         <v>40.1</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1386" t="n">
+        <v>3345</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1387" t="n">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1388" t="n">
+        <v>178.3</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1389" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1390" t="n">
+        <v>4991</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1391" t="n">
+        <v>8268</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1392" t="n">
+        <v>50590</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1393" t="n">
+        <v>8714</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1394" t="n">
+        <v>36.74</v>
       </c>
     </row>
   </sheetData>
@@ -22526,7 +22661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F240"/>
+  <dimension ref="A1:F241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26810,19 +26945,29 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr">
+      <c r="A238" t="inlineStr"/>
+      <c r="B238" s="1" t="n">
+        <v>46280.29166666666</v>
+      </c>
+      <c r="C238" t="n">
+        <v>210599</v>
+      </c>
+      <c r="D238" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E238" t="n">
+        <v>1309</v>
+      </c>
+      <c r="F238" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr"/>
-      <c r="C238" t="inlineStr"/>
-      <c r="D238" t="inlineStr"/>
-      <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr"/>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr"/>
       <c r="B239" t="inlineStr"/>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr"/>
@@ -26830,16 +26975,24 @@
       <c r="F239" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr"/>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr"/>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27004,31 +27157,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>995</v>
+        <v>1019</v>
       </c>
       <c r="F2" t="n">
-        <v>-20</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.97</v>
+        <v>0.39</v>
       </c>
       <c r="H2" t="n">
-        <v>662200</v>
+        <v>902400</v>
       </c>
       <c r="I2" t="n">
-        <v>56.9</v>
+        <v>60</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9</v>
+        <v>4.26</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8</v>
+        <v>1.04</v>
       </c>
       <c r="L2" t="n">
-        <v>39.98</v>
+        <v>41.89</v>
       </c>
       <c r="M2" t="n">
-        <v>46.35</v>
+        <v>46.74</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -27041,10 +27194,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>836.33</v>
+        <v>836.65</v>
       </c>
       <c r="Q2" t="n">
-        <v>1122.86</v>
+        <v>1122.97</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -27105,31 +27258,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3325</v>
+        <v>3345</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G3" t="n">
-        <v>1.84</v>
+        <v>2.45</v>
       </c>
       <c r="H3" t="n">
-        <v>56400</v>
+        <v>122100</v>
       </c>
       <c r="I3" t="n">
-        <v>46.3</v>
+        <v>47.2</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.73</v>
+        <v>-2.16</v>
       </c>
       <c r="K3" t="n">
-        <v>0.95</v>
+        <v>1.68</v>
       </c>
       <c r="L3" t="n">
-        <v>36.78</v>
+        <v>38.37</v>
       </c>
       <c r="M3" t="n">
-        <v>84.28</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -27142,10 +27295,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2993.61</v>
+        <v>2993.88</v>
       </c>
       <c r="Q3" t="n">
-        <v>2714.49</v>
+        <v>2714.59</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -27153,7 +27306,7 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -27166,6 +27319,208 @@
         </is>
       </c>
       <c r="V3" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・出来高が増加しています。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>4412.T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>サイエンスアーツ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>現場向けコミュニケーション</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1355</v>
+      </c>
+      <c r="F4" t="n">
+        <v>29</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5400</v>
+      </c>
+      <c r="I4" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L4" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1203.54</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1642.25</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>85</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5532.T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>リアルゲイト</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>オフィス再生</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3465</v>
+      </c>
+      <c r="F5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H5" t="n">
+        <v>17300</v>
+      </c>
+      <c r="I5" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L5" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="M5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>3435.8</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3139.57</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>95</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -27176,208 +27531,6 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>4412.T</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>サイエンスアーツ</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>現場向けコミュニケーション</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1344</v>
-      </c>
-      <c r="F4" t="n">
-        <v>18</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3800</v>
-      </c>
-      <c r="I4" t="n">
-        <v>63.7</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5.19</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="L4" t="n">
-        <v>41.32</v>
-      </c>
-      <c r="M4" t="n">
-        <v>42.24</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>1203.4</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1642.2</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>85</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>5532.T</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>リアルゲイト</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>オフィス再生</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>3455</v>
-      </c>
-      <c r="F5" t="n">
-        <v>20</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2800</v>
-      </c>
-      <c r="I5" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L5" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="M5" t="n">
-        <v>9</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>DC</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>3435.67</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3139.53</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>80</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
@@ -27408,31 +27561,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1535</v>
+        <v>1548</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G6" t="n">
-        <v>0.39</v>
+        <v>1.24</v>
       </c>
       <c r="H6" t="n">
-        <v>27700</v>
+        <v>68000</v>
       </c>
       <c r="I6" t="n">
-        <v>49.1</v>
+        <v>51</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.59</v>
+        <v>0.21</v>
       </c>
       <c r="K6" t="n">
-        <v>0.34</v>
+        <v>0.76</v>
       </c>
       <c r="L6" t="n">
-        <v>-32.98</v>
+        <v>-31.94</v>
       </c>
       <c r="M6" t="n">
-        <v>-39.99</v>
+        <v>-39.78</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -27445,10 +27598,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1688.33</v>
+        <v>1688.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>1703</v>
+        <v>1703.06</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -27456,16 +27609,16 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -27509,31 +27662,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>0.39</v>
+        <v>0.77</v>
       </c>
       <c r="H7" t="n">
-        <v>3000</v>
+        <v>6200</v>
       </c>
       <c r="I7" t="n">
-        <v>42.4</v>
+        <v>45.7</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.52</v>
+        <v>-1.16</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4</v>
+        <v>0.76</v>
       </c>
       <c r="L7" t="n">
-        <v>-7.26</v>
+        <v>-7.1</v>
       </c>
       <c r="M7" t="n">
-        <v>-8.01</v>
+        <v>-7.98</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -27546,10 +27699,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>537.11</v>
+        <v>537.14</v>
       </c>
       <c r="Q7" t="n">
-        <v>584.87</v>
+        <v>584.88</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -27574,6 +27727,7 @@
           <t>【AI分析レポート】
 ・🔴 下降
 ・MACDは買いシグナルです。
+・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 ⚠️ 下落トレンドです。
 無理な買いは避け、反転サインを待ちましょう。</t>
@@ -27609,31 +27763,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1066</v>
+        <v>1076</v>
       </c>
       <c r="F8" t="n">
-        <v>-13</v>
+        <v>-3</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2</v>
+        <v>-0.28</v>
       </c>
       <c r="H8" t="n">
-        <v>3400</v>
+        <v>7200</v>
       </c>
       <c r="I8" t="n">
-        <v>29.8</v>
+        <v>31</v>
       </c>
       <c r="J8" t="n">
-        <v>-6.08</v>
+        <v>-5.23</v>
       </c>
       <c r="K8" t="n">
-        <v>0.86</v>
+        <v>1.53</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.44</v>
+        <v>-2.64</v>
       </c>
       <c r="M8" t="n">
-        <v>8.33</v>
+        <v>8.49</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -27646,10 +27800,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1053.01</v>
+        <v>1053.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>1022.86</v>
+        <v>1022.9</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -27657,16 +27811,16 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -27674,7 +27828,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・売られ過ぎ水準です。
+・出来高が増加しています。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -27710,31 +27864,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1556</v>
+        <v>1581</v>
       </c>
       <c r="F9" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1</v>
+        <v>2.73</v>
       </c>
       <c r="H9" t="n">
-        <v>20700</v>
+        <v>41700</v>
       </c>
       <c r="I9" t="n">
-        <v>34.1</v>
+        <v>38.2</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.12</v>
+        <v>-1.62</v>
       </c>
       <c r="K9" t="n">
-        <v>0.43</v>
+        <v>0.8</v>
       </c>
       <c r="L9" t="n">
-        <v>13.21</v>
+        <v>15.2</v>
       </c>
       <c r="M9" t="n">
-        <v>34</v>
+        <v>34.4</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -27747,10 +27901,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1446.59</v>
+        <v>1446.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>1378.32</v>
+        <v>1378.45</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -27910,31 +28064,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3526</v>
+        <v>3520</v>
       </c>
       <c r="F11" t="n">
-        <v>-25</v>
+        <v>-31</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7</v>
+        <v>-0.87</v>
       </c>
       <c r="H11" t="n">
-        <v>1784500</v>
+        <v>4002900</v>
       </c>
       <c r="I11" t="n">
-        <v>43.9</v>
+        <v>43.5</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.83</v>
+        <v>-2.99</v>
       </c>
       <c r="K11" t="n">
-        <v>0.36</v>
+        <v>0.74</v>
       </c>
       <c r="L11" t="n">
-        <v>-55.38</v>
+        <v>-55.86</v>
       </c>
       <c r="M11" t="n">
-        <v>-48.89</v>
+        <v>-48.98</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -27947,10 +28101,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3661.87</v>
+        <v>3661.79</v>
       </c>
       <c r="Q11" t="n">
-        <v>2918.85</v>
+        <v>2918.82</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -28014,31 +28168,31 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>3580</v>
+        <v>3605</v>
       </c>
       <c r="F12" t="n">
-        <v>-80</v>
+        <v>-55</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.19</v>
+        <v>-1.5</v>
       </c>
       <c r="H12" t="n">
-        <v>385900</v>
+        <v>612300</v>
       </c>
       <c r="I12" t="n">
-        <v>52.6</v>
+        <v>53.5</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.85</v>
+        <v>-2.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0.52</v>
+        <v>0.77</v>
       </c>
       <c r="L12" t="n">
-        <v>79.91</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>108.11</v>
+        <v>108.51</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -28051,10 +28205,10 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3193.37</v>
+        <v>3193.71</v>
       </c>
       <c r="Q12" t="n">
-        <v>3051.07</v>
+        <v>3051.2</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -28111,31 +28265,31 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>4864</v>
+        <v>4834</v>
       </c>
       <c r="F13" t="n">
-        <v>-118</v>
+        <v>-148</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.37</v>
+        <v>-2.97</v>
       </c>
       <c r="H13" t="n">
-        <v>21964600</v>
+        <v>35382300</v>
       </c>
       <c r="I13" t="n">
-        <v>41.7</v>
+        <v>41.2</v>
       </c>
       <c r="J13" t="n">
-        <v>-9.220000000000001</v>
+        <v>-9.76</v>
       </c>
       <c r="K13" t="n">
-        <v>0.61</v>
+        <v>0.91</v>
       </c>
       <c r="L13" t="n">
-        <v>-19.85</v>
+        <v>-22.24</v>
       </c>
       <c r="M13" t="n">
-        <v>31.63</v>
+        <v>31.15</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -28148,10 +28302,10 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5063.31</v>
+        <v>5062.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>4466.74</v>
+        <v>4466.59</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -28219,31 +28373,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1060</v>
+        <v>1073</v>
       </c>
       <c r="F14" t="n">
-        <v>-3</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.28</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>100500</v>
+        <v>262500</v>
       </c>
       <c r="I14" t="n">
-        <v>23.5</v>
+        <v>26.6</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.45</v>
+        <v>-6.36</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4</v>
+        <v>0.92</v>
       </c>
       <c r="L14" t="n">
-        <v>-16.48</v>
+        <v>-15.44</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.06</v>
+        <v>-0.85</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -28256,10 +28410,10 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1106.17</v>
+        <v>1106.35</v>
       </c>
       <c r="Q14" t="n">
-        <v>924.13</v>
+        <v>924.1900000000001</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -28320,31 +28474,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3884</v>
+        <v>3845</v>
       </c>
       <c r="F15" t="n">
-        <v>-97</v>
+        <v>-136</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.44</v>
+        <v>-3.42</v>
       </c>
       <c r="H15" t="n">
-        <v>13771900</v>
+        <v>22796400</v>
       </c>
       <c r="I15" t="n">
-        <v>47.2</v>
+        <v>46.4</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.51</v>
+        <v>-2.46</v>
       </c>
       <c r="K15" t="n">
-        <v>0.62</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>25.86</v>
+        <v>22.75</v>
       </c>
       <c r="M15" t="n">
-        <v>20.22</v>
+        <v>19.59</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -28357,10 +28511,10 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>4059.69</v>
+        <v>4059.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>3139.52</v>
+        <v>3139.33</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -28425,31 +28579,31 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>3850</v>
+        <v>3830</v>
       </c>
       <c r="F16" t="n">
-        <v>-50</v>
+        <v>-70</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.28</v>
+        <v>-1.79</v>
       </c>
       <c r="H16" t="n">
-        <v>13600</v>
+        <v>21900</v>
       </c>
       <c r="I16" t="n">
-        <v>36.3</v>
+        <v>35.8</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.06</v>
+        <v>-7.53</v>
       </c>
       <c r="K16" t="n">
-        <v>0.66</v>
+        <v>0.98</v>
       </c>
       <c r="L16" t="n">
-        <v>47.87</v>
+        <v>46.27</v>
       </c>
       <c r="M16" t="n">
-        <v>109.69</v>
+        <v>109.37</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -28462,10 +28616,10 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3543.16</v>
+        <v>3542.89</v>
       </c>
       <c r="Q16" t="n">
-        <v>2819.59</v>
+        <v>2819.49</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -28521,31 +28675,31 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>2354</v>
+        <v>2351</v>
       </c>
       <c r="F17" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G17" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="H17" t="n">
-        <v>4390200</v>
+        <v>9038600</v>
       </c>
       <c r="I17" t="n">
-        <v>30.2</v>
+        <v>29.8</v>
       </c>
       <c r="J17" t="n">
-        <v>-8.84</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.39</v>
+        <v>0.75</v>
       </c>
       <c r="L17" t="n">
-        <v>-104.4</v>
+        <v>-104.64</v>
       </c>
       <c r="M17" t="n">
-        <v>-88.92</v>
+        <v>-88.95999999999999</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -28558,10 +28712,10 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2763.45</v>
+        <v>2763.41</v>
       </c>
       <c r="Q17" t="n">
-        <v>2824.42</v>
+        <v>2824.41</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -28569,11 +28723,11 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -28586,6 +28740,7 @@
           <t>【AI分析レポート】
 ・🔴 下降
 ・MACDは売りシグナルです。
+・売られ過ぎ水準です。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 ⚠️ 下落トレンドです。
 無理な買いは避け、反転サインを待ちましょう。</t>
@@ -28629,31 +28784,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="F18" t="n">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.33</v>
+        <v>-0.2</v>
       </c>
       <c r="H18" t="n">
-        <v>10817600</v>
+        <v>22994300</v>
       </c>
       <c r="I18" t="n">
-        <v>44.6</v>
+        <v>44.9</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2</v>
+        <v>-1.07</v>
       </c>
       <c r="K18" t="n">
-        <v>0.48</v>
+        <v>0.92</v>
       </c>
       <c r="L18" t="n">
-        <v>4.77</v>
+        <v>5.09</v>
       </c>
       <c r="M18" t="n">
-        <v>22.66</v>
+        <v>22.72</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -28666,10 +28821,10 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2933.08</v>
+        <v>2933.13</v>
       </c>
       <c r="Q18" t="n">
-        <v>3164.72</v>
+        <v>3164.74</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -28733,31 +28888,31 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>1825</v>
+        <v>1811</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>-11.5</v>
       </c>
       <c r="G19" t="n">
-        <v>0.16</v>
+        <v>-0.63</v>
       </c>
       <c r="H19" t="n">
-        <v>2487800</v>
+        <v>6826000</v>
       </c>
       <c r="I19" t="n">
-        <v>57.3</v>
+        <v>55.3</v>
       </c>
       <c r="J19" t="n">
-        <v>2.16</v>
+        <v>1.38</v>
       </c>
       <c r="K19" t="n">
-        <v>0.27</v>
+        <v>0.68</v>
       </c>
       <c r="L19" t="n">
-        <v>35.99</v>
+        <v>34.84</v>
       </c>
       <c r="M19" t="n">
-        <v>38.95</v>
+        <v>38.72</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -28770,10 +28925,10 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1674.11</v>
+        <v>1673.91</v>
       </c>
       <c r="Q19" t="n">
-        <v>1558.07</v>
+        <v>1558</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -28842,31 +28997,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="F20" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G20" t="n">
-        <v>1.75</v>
+        <v>3.71</v>
       </c>
       <c r="H20" t="n">
-        <v>152300</v>
+        <v>510800</v>
       </c>
       <c r="I20" t="n">
-        <v>51.5</v>
+        <v>53.9</v>
       </c>
       <c r="J20" t="n">
-        <v>1.22</v>
+        <v>3.09</v>
       </c>
       <c r="K20" t="n">
-        <v>0.21</v>
+        <v>0.64</v>
       </c>
       <c r="L20" t="n">
-        <v>3.3</v>
+        <v>4.01</v>
       </c>
       <c r="M20" t="n">
-        <v>6.51</v>
+        <v>6.65</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -28879,10 +29034,10 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>432.5</v>
+        <v>432.62</v>
       </c>
       <c r="Q20" t="n">
-        <v>411.43</v>
+        <v>411.47</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -28939,31 +29094,31 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>8708</v>
+        <v>8714</v>
       </c>
       <c r="F21" t="n">
-        <v>-501</v>
+        <v>-495</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.44</v>
+        <v>-5.38</v>
       </c>
       <c r="H21" t="n">
-        <v>15854400</v>
+        <v>25803500</v>
       </c>
       <c r="I21" t="n">
         <v>43.4</v>
       </c>
       <c r="J21" t="n">
-        <v>-8.550000000000001</v>
+        <v>-8.49</v>
       </c>
       <c r="K21" t="n">
-        <v>0.58</v>
+        <v>0.87</v>
       </c>
       <c r="L21" t="n">
-        <v>-511.56</v>
+        <v>-511.08</v>
       </c>
       <c r="M21" t="n">
-        <v>-619.99</v>
+        <v>-619.89</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -28976,10 +29131,10 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>13217.96</v>
+        <v>13218.04</v>
       </c>
       <c r="Q21" t="n">
-        <v>7863.87</v>
+        <v>7863.9</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -29039,31 +29194,31 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>50510</v>
+        <v>50590</v>
       </c>
       <c r="F22" t="n">
-        <v>-3520</v>
+        <v>-3440</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.51</v>
+        <v>-6.37</v>
       </c>
       <c r="H22" t="n">
-        <v>17850900</v>
+        <v>28534900</v>
       </c>
       <c r="I22" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.84</v>
+        <v>-4.69</v>
       </c>
       <c r="K22" t="n">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="L22" t="n">
-        <v>-316.42</v>
+        <v>-310.04</v>
       </c>
       <c r="M22" t="n">
-        <v>-848.7</v>
+        <v>-847.4299999999999</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -29076,10 +29231,10 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>66357.87</v>
+        <v>66358.92999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>39393.36</v>
+        <v>39393.76</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -29140,31 +29295,31 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>161.2</v>
+        <v>163.8</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="G23" t="n">
-        <v>0.37</v>
+        <v>1.99</v>
       </c>
       <c r="H23" t="n">
-        <v>24161700</v>
+        <v>53785200</v>
       </c>
       <c r="I23" t="n">
-        <v>48.6</v>
+        <v>52.4</v>
       </c>
       <c r="J23" t="n">
-        <v>1.05</v>
+        <v>2.61</v>
       </c>
       <c r="K23" t="n">
-        <v>0.55</v>
+        <v>1.09</v>
       </c>
       <c r="L23" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="M23" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -29173,14 +29328,14 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>151.69</v>
+        <v>151.72</v>
       </c>
       <c r="Q23" t="n">
-        <v>150.41</v>
+        <v>150.43</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -29188,16 +29343,16 @@
         </is>
       </c>
       <c r="S23" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -29206,7 +29361,7 @@
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -29241,31 +29396,31 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>3151</v>
+        <v>3176</v>
       </c>
       <c r="F24" t="n">
-        <v>-41</v>
+        <v>-16</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.28</v>
+        <v>-0.5</v>
       </c>
       <c r="H24" t="n">
-        <v>5581700</v>
+        <v>9810200</v>
       </c>
       <c r="I24" t="n">
-        <v>35.4</v>
+        <v>36.5</v>
       </c>
       <c r="J24" t="n">
-        <v>-8.74</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.63</v>
+        <v>1.01</v>
       </c>
       <c r="L24" t="n">
-        <v>-149.67</v>
+        <v>-147.67</v>
       </c>
       <c r="M24" t="n">
-        <v>-156.41</v>
+        <v>-156.02</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -29278,37 +29433,37 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>4054.99</v>
+        <v>4055.32</v>
       </c>
       <c r="Q24" t="n">
-        <v>3172.58</v>
+        <v>3172.7</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>🔴 下降</t>
+          <t>🟡 反発中</t>
         </is>
       </c>
       <c r="S24" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🔴 下降
+・🟡 反発中
 ・MACDは買いシグナルです。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -29323,7 +29478,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -29442,31 +29597,31 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>8224</v>
+        <v>8268</v>
       </c>
       <c r="F26" t="n">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="G26" t="n">
-        <v>1.62</v>
+        <v>2.16</v>
       </c>
       <c r="H26" t="n">
-        <v>6219300</v>
+        <v>9454300</v>
       </c>
       <c r="I26" t="n">
-        <v>33.9</v>
+        <v>35.4</v>
       </c>
       <c r="J26" t="n">
-        <v>-5.08</v>
+        <v>-4.59</v>
       </c>
       <c r="K26" t="n">
-        <v>0.65</v>
+        <v>0.93</v>
       </c>
       <c r="L26" t="n">
-        <v>52.57</v>
+        <v>56.08</v>
       </c>
       <c r="M26" t="n">
-        <v>194.88</v>
+        <v>195.58</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -29479,10 +29634,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7715.36</v>
+        <v>7715.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>8771.08</v>
+        <v>8771.299999999999</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>210,599円</t>
+          <t>212,232円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1,309円</t>
+          <t>2,942円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3345</v>
+        <v>3375</v>
       </c>
       <c r="F2" t="n">
-        <v>47.2</v>
+        <v>47.8</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.16</v>
+        <v>-1.41</v>
       </c>
       <c r="H2" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>38.37</v>
+        <v>32.95</v>
       </c>
       <c r="J2" t="n">
-        <v>84.59999999999999</v>
+        <v>74.27</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>2993.88</v>
+        <v>3007.96</v>
       </c>
       <c r="N2" t="n">
-        <v>2714.59</v>
+        <v>2718.03</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -757,11 +757,11 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・出来高が増加しています。
+・出来高が急増しています。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -788,29 +788,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>押し目、出来高微増、MACD売り、長期上昇</t>
+          <t>押し目、出来高増加、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3265</v>
+        <v>3345</v>
       </c>
       <c r="X2" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.45</v>
+        <v>0.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>13380</v>
+        <v>13500</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2580</v>
+        <v>2700</v>
       </c>
       <c r="AC2" t="n">
-        <v>23.89</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -831,22 +831,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F3" t="n">
-        <v>53.9</v>
+        <v>54.4</v>
       </c>
       <c r="G3" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="H3" t="n">
-        <v>0.64</v>
+        <v>0.97</v>
       </c>
       <c r="I3" t="n">
-        <v>4.01</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>6.65</v>
+        <v>6.28</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>432.62</v>
+        <v>432.79</v>
       </c>
       <c r="N3" t="n">
-        <v>411.47</v>
+        <v>412.09</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -905,25 +905,25 @@
         </is>
       </c>
       <c r="W3" t="n">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="X3" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.71</v>
+        <v>0.42</v>
       </c>
       <c r="Z3" t="n">
-        <v>47500</v>
+        <v>47700</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>5500</v>
+        <v>5700</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.1</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="4">
@@ -944,22 +944,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>178.3</v>
+        <v>177.1</v>
       </c>
       <c r="F4" t="n">
-        <v>67.8</v>
+        <v>64.3</v>
       </c>
       <c r="G4" t="n">
-        <v>6.04</v>
+        <v>4.89</v>
       </c>
       <c r="H4" t="n">
-        <v>0.97</v>
+        <v>0.41</v>
       </c>
       <c r="I4" t="n">
         <v>4.63</v>
       </c>
       <c r="J4" t="n">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>155.43</v>
+        <v>155.79</v>
       </c>
       <c r="N4" t="n">
-        <v>153.8</v>
+        <v>153.93</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1013,29 +1013,29 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSIやや過熱、25日線上、+1σ、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>175.7</v>
+        <v>178.3</v>
       </c>
       <c r="X4" t="n">
-        <v>2.6</v>
+        <v>-1.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.48</v>
+        <v>-0.67</v>
       </c>
       <c r="Z4" t="n">
-        <v>17830</v>
+        <v>17710</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>2030</v>
+        <v>1910</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.85</v>
+        <v>12.09</v>
       </c>
     </row>
     <row r="5">
@@ -1056,22 +1056,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3025</v>
+        <v>3016</v>
       </c>
       <c r="F5" t="n">
-        <v>44.9</v>
+        <v>45.1</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.07</v>
+        <v>-1.41</v>
       </c>
       <c r="H5" t="n">
-        <v>0.92</v>
+        <v>0.42</v>
       </c>
       <c r="I5" t="n">
-        <v>5.09</v>
+        <v>2.27</v>
       </c>
       <c r="J5" t="n">
-        <v>22.72</v>
+        <v>18.63</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2933.13</v>
+        <v>2932.79</v>
       </c>
       <c r="N5" t="n">
-        <v>3164.74</v>
+        <v>3164.86</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1117,6 +1117,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
+・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -1129,25 +1130,25 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>3031</v>
+        <v>3025</v>
       </c>
       <c r="X5" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>39325</v>
+        <v>39208</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>2226</v>
+        <v>2109</v>
       </c>
       <c r="AC5" t="n">
-        <v>6</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="6">
@@ -1168,22 +1169,22 @@
         <v>4795</v>
       </c>
       <c r="E6" t="n">
-        <v>4991</v>
+        <v>4928</v>
       </c>
       <c r="F6" t="n">
-        <v>60.4</v>
+        <v>59.6</v>
       </c>
       <c r="G6" t="n">
-        <v>2.91</v>
+        <v>1.54</v>
       </c>
       <c r="H6" t="n">
-        <v>0.84</v>
+        <v>0.42</v>
       </c>
       <c r="I6" t="n">
-        <v>70.14</v>
+        <v>63.93</v>
       </c>
       <c r="J6" t="n">
-        <v>58.58</v>
+        <v>59.65</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1192,14 +1193,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4718.79</v>
+        <v>4716.96</v>
       </c>
       <c r="N6" t="n">
-        <v>4656.71</v>
+        <v>4663.56</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1229,7 +1230,8 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -1237,29 +1239,29 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+1σ、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>5005</v>
+        <v>4991</v>
       </c>
       <c r="X6" t="n">
-        <v>-14</v>
+        <v>-63</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.28</v>
+        <v>-1.26</v>
       </c>
       <c r="Z6" t="n">
-        <v>24955</v>
+        <v>24640</v>
       </c>
       <c r="AA6" t="n">
         <v>23975</v>
       </c>
       <c r="AB6" t="n">
-        <v>980</v>
+        <v>665</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.09</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="7">
@@ -1280,22 +1282,22 @@
         <v>7993</v>
       </c>
       <c r="E7" t="n">
-        <v>8268</v>
+        <v>8173</v>
       </c>
       <c r="F7" t="n">
-        <v>35.4</v>
+        <v>32.8</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.59</v>
+        <v>-5.65</v>
       </c>
       <c r="H7" t="n">
-        <v>0.93</v>
+        <v>0.42</v>
       </c>
       <c r="I7" t="n">
-        <v>56.08</v>
+        <v>26.29</v>
       </c>
       <c r="J7" t="n">
-        <v>195.58</v>
+        <v>161.72</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1308,10 +1310,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>7715.95</v>
+        <v>7729.61</v>
       </c>
       <c r="N7" t="n">
-        <v>8771.299999999999</v>
+        <v>8748.26</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1353,25 +1355,25 @@
         </is>
       </c>
       <c r="W7" t="n">
-        <v>8093</v>
+        <v>8268</v>
       </c>
       <c r="X7" t="n">
-        <v>175</v>
+        <v>-95</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.16</v>
+        <v>-1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>8268</v>
+        <v>8173</v>
       </c>
       <c r="AA7" t="n">
         <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>275</v>
+        <v>180</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.44</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="8">
@@ -1392,22 +1394,22 @@
         <v>55510</v>
       </c>
       <c r="E8" t="n">
-        <v>50590</v>
+        <v>51970</v>
       </c>
       <c r="F8" t="n">
-        <v>48.9</v>
+        <v>53.2</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.69</v>
+        <v>-2.38</v>
       </c>
       <c r="H8" t="n">
-        <v>0.95</v>
+        <v>0.61</v>
       </c>
       <c r="I8" t="n">
-        <v>-310.04</v>
+        <v>-452.35</v>
       </c>
       <c r="J8" t="n">
-        <v>-847.4299999999999</v>
+        <v>-768.41</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1420,10 +1422,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>66358.92999999999</v>
+        <v>66173.87</v>
       </c>
       <c r="N8" t="n">
-        <v>39393.76</v>
+        <v>39599.44</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1432,20 +1434,20 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1459,36 +1461,32 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>⚠️ 急落</t>
-        </is>
-      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>押し目、MACD買い、反発局面</t>
+          <t>RSI適正、押し目、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>54030</v>
+        <v>50590</v>
       </c>
       <c r="X8" t="n">
-        <v>-3440</v>
+        <v>1380</v>
       </c>
       <c r="Y8" t="n">
-        <v>-6.37</v>
+        <v>2.73</v>
       </c>
       <c r="Z8" t="n">
-        <v>50590</v>
+        <v>51970</v>
       </c>
       <c r="AA8" t="n">
         <v>55510</v>
       </c>
       <c r="AB8" t="n">
-        <v>-4920</v>
+        <v>-3540</v>
       </c>
       <c r="AC8" t="n">
-        <v>-8.859999999999999</v>
+        <v>-6.38</v>
       </c>
     </row>
     <row r="9">
@@ -1509,22 +1507,22 @@
         <v>10000</v>
       </c>
       <c r="E9" t="n">
-        <v>8714</v>
+        <v>9294</v>
       </c>
       <c r="F9" t="n">
-        <v>43.4</v>
+        <v>52.5</v>
       </c>
       <c r="G9" t="n">
-        <v>-8.49</v>
+        <v>-2.29</v>
       </c>
       <c r="H9" t="n">
-        <v>0.87</v>
+        <v>0.68</v>
       </c>
       <c r="I9" t="n">
-        <v>-511.08</v>
+        <v>-465.84</v>
       </c>
       <c r="J9" t="n">
-        <v>-619.89</v>
+        <v>-589.08</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1533,14 +1531,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>13218.04</v>
+        <v>13144.43</v>
       </c>
       <c r="N9" t="n">
-        <v>7863.9</v>
+        <v>7894.81</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1549,20 +1547,20 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1570,41 +1568,42 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>⚠️ 急落</t>
+          <t>🚀 急騰</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD買い、反発局面</t>
+          <t>RSI適正、押し目、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>9209</v>
+        <v>8714</v>
       </c>
       <c r="X9" t="n">
-        <v>-495</v>
+        <v>580</v>
       </c>
       <c r="Y9" t="n">
-        <v>-5.38</v>
+        <v>6.66</v>
       </c>
       <c r="Z9" t="n">
-        <v>8714</v>
+        <v>9294</v>
       </c>
       <c r="AA9" t="n">
         <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1286</v>
+        <v>-706</v>
       </c>
       <c r="AC9" t="n">
-        <v>-12.86</v>
+        <v>-7.06</v>
       </c>
     </row>
     <row r="10">
@@ -1634,7 +1633,7 @@
         <v>-1.67</v>
       </c>
       <c r="H10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="I10" t="n">
         <v>1.42</v>
@@ -1735,7 +1734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1394"/>
+  <dimension ref="A1:C1403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22647,6 +22646,141 @@
         </is>
       </c>
       <c r="C1394" t="n">
+        <v>36.74</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1395" t="n">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1396" t="n">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1397" t="n">
+        <v>177.1</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1398" t="n">
+        <v>3016</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1399" t="n">
+        <v>4928</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1400" t="n">
+        <v>8173</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1401" t="n">
+        <v>51970</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1402" t="n">
+        <v>9294</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1403" t="n">
         <v>36.74</v>
       </c>
     </row>
@@ -22661,7 +22795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F241"/>
+  <dimension ref="A1:F242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26963,19 +27097,29 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
+      <c r="A239" t="inlineStr"/>
+      <c r="B239" s="1" t="n">
+        <v>46280.5</v>
+      </c>
+      <c r="C239" t="n">
+        <v>212232</v>
+      </c>
+      <c r="D239" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E239" t="n">
+        <v>2942</v>
+      </c>
+      <c r="F239" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr"/>
-      <c r="C239" t="inlineStr"/>
-      <c r="D239" t="inlineStr"/>
-      <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr"/>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr"/>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr"/>
@@ -26983,16 +27127,24 @@
       <c r="F240" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A241" t="inlineStr"/>
       <c r="B241" t="inlineStr"/>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr"/>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27964,31 +28116,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>975</v>
+        <v>987</v>
       </c>
       <c r="F10" t="n">
-        <v>-6</v>
+        <v>12</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.61</v>
+        <v>1.23</v>
       </c>
       <c r="H10" t="n">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="I10" t="n">
-        <v>62.9</v>
+        <v>66</v>
       </c>
       <c r="J10" t="n">
-        <v>1.95</v>
+        <v>2.92</v>
       </c>
       <c r="K10" t="n">
-        <v>1.49</v>
+        <v>0.09</v>
       </c>
       <c r="L10" t="n">
-        <v>22.24</v>
+        <v>21.54</v>
       </c>
       <c r="M10" t="n">
-        <v>25.51</v>
+        <v>24.72</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -27997,14 +28149,14 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>866.24</v>
+        <v>869.17</v>
       </c>
       <c r="Q10" t="n">
-        <v>986.16</v>
+        <v>986.29</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -28012,16 +28164,16 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -28029,7 +28181,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
@@ -29496,31 +29648,31 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>51.16</v>
+        <v>46.59</v>
       </c>
       <c r="F25" t="n">
-        <v>2.54</v>
+        <v>-4.57</v>
       </c>
       <c r="G25" t="n">
-        <v>5.22</v>
+        <v>-8.93</v>
       </c>
       <c r="H25" t="n">
-        <v>1471000</v>
+        <v>1452306</v>
       </c>
       <c r="I25" t="n">
-        <v>46.2</v>
+        <v>40.6</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.14</v>
+        <v>-11.92</v>
       </c>
       <c r="K25" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.94</v>
+        <v>-2.12</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.19</v>
+        <v>-2.18</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -29529,14 +29681,14 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>59.67</v>
+        <v>59.56</v>
       </c>
       <c r="Q25" t="n">
-        <v>37.27</v>
+        <v>37.41</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -29544,16 +29696,16 @@
         </is>
       </c>
       <c r="S25" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -29561,8 +29713,8 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・25日線から大きく下に乖離しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>212,232円</t>
+          <t>211,595円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2,942円</t>
+          <t>2,305円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.1%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3375</v>
+        <v>3340</v>
       </c>
       <c r="F2" t="n">
-        <v>47.8</v>
+        <v>46.4</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.41</v>
+        <v>-2.39</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>2.53</v>
       </c>
       <c r="I2" t="n">
-        <v>32.95</v>
+        <v>30.16</v>
       </c>
       <c r="J2" t="n">
-        <v>74.27</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3007.96</v>
+        <v>3007.49</v>
       </c>
       <c r="N2" t="n">
-        <v>2718.03</v>
+        <v>2717.85</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -795,22 +795,22 @@
         <v>3345</v>
       </c>
       <c r="X2" t="n">
-        <v>30</v>
+        <v>-5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.9</v>
+        <v>-0.15</v>
       </c>
       <c r="Z2" t="n">
-        <v>13500</v>
+        <v>13360</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2700</v>
+        <v>2560</v>
       </c>
       <c r="AC2" t="n">
-        <v>25</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="3">
@@ -831,22 +831,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F3" t="n">
-        <v>54.4</v>
+        <v>53.9</v>
       </c>
       <c r="G3" t="n">
-        <v>3.17</v>
+        <v>2.75</v>
       </c>
       <c r="H3" t="n">
-        <v>0.97</v>
+        <v>1.71</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.64</v>
       </c>
       <c r="J3" t="n">
-        <v>6.28</v>
+        <v>6.25</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>432.79</v>
+        <v>432.76</v>
       </c>
       <c r="N3" t="n">
-        <v>412.09</v>
+        <v>412.08</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -893,6 +893,7 @@
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
+・出来高が増加しています。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -901,29 +902,29 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+          <t>RSI適正、25日線上、出来高微増、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W3" t="n">
         <v>475</v>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>47700</v>
+        <v>47500</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>5700</v>
+        <v>5500</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.57</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="4">
@@ -944,22 +945,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>177.1</v>
+        <v>178.1</v>
       </c>
       <c r="F4" t="n">
-        <v>64.3</v>
+        <v>66.8</v>
       </c>
       <c r="G4" t="n">
-        <v>4.89</v>
+        <v>5.46</v>
       </c>
       <c r="H4" t="n">
-        <v>0.41</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>4.63</v>
+        <v>4.71</v>
       </c>
       <c r="J4" t="n">
-        <v>4.55</v>
+        <v>4.57</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -972,10 +973,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>155.79</v>
+        <v>155.81</v>
       </c>
       <c r="N4" t="n">
-        <v>153.93</v>
+        <v>153.94</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1013,29 +1014,29 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+1σ、MACD買い、長期上昇</t>
+          <t>RSIやや過熱、25日線上、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>178.3</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2</v>
+        <v>-0.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.67</v>
+        <v>-0.11</v>
       </c>
       <c r="Z4" t="n">
-        <v>17710</v>
+        <v>17810</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1910</v>
+        <v>2010</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.09</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="5">
@@ -1056,22 +1057,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3016</v>
+        <v>3021</v>
       </c>
       <c r="F5" t="n">
-        <v>45.1</v>
+        <v>45.5</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.41</v>
+        <v>-1.26</v>
       </c>
       <c r="H5" t="n">
-        <v>0.42</v>
+        <v>0.88</v>
       </c>
       <c r="I5" t="n">
-        <v>2.27</v>
+        <v>2.67</v>
       </c>
       <c r="J5" t="n">
-        <v>18.63</v>
+        <v>18.71</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1084,10 +1085,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2932.79</v>
+        <v>2932.85</v>
       </c>
       <c r="N5" t="n">
-        <v>3164.86</v>
+        <v>3164.88</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1133,22 +1134,22 @@
         <v>3025</v>
       </c>
       <c r="X5" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.3</v>
+        <v>-0.13</v>
       </c>
       <c r="Z5" t="n">
-        <v>39208</v>
+        <v>39273</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>2109</v>
+        <v>2174</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.68</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="6">
@@ -1169,22 +1170,22 @@
         <v>4795</v>
       </c>
       <c r="E6" t="n">
-        <v>4928</v>
+        <v>4910</v>
       </c>
       <c r="F6" t="n">
-        <v>59.6</v>
+        <v>58.6</v>
       </c>
       <c r="G6" t="n">
-        <v>1.54</v>
+        <v>1.19</v>
       </c>
       <c r="H6" t="n">
-        <v>0.42</v>
+        <v>0.86</v>
       </c>
       <c r="I6" t="n">
-        <v>63.93</v>
+        <v>62.5</v>
       </c>
       <c r="J6" t="n">
-        <v>59.65</v>
+        <v>59.37</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1197,10 +1198,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4716.96</v>
+        <v>4716.72</v>
       </c>
       <c r="N6" t="n">
-        <v>4663.56</v>
+        <v>4663.47</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1246,22 +1247,22 @@
         <v>4991</v>
       </c>
       <c r="X6" t="n">
-        <v>-63</v>
+        <v>-81</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.26</v>
+        <v>-1.62</v>
       </c>
       <c r="Z6" t="n">
-        <v>24640</v>
+        <v>24550</v>
       </c>
       <c r="AA6" t="n">
         <v>23975</v>
       </c>
       <c r="AB6" t="n">
-        <v>665</v>
+        <v>575</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.77</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="7">
@@ -1282,22 +1283,22 @@
         <v>7993</v>
       </c>
       <c r="E7" t="n">
-        <v>8173</v>
+        <v>8118</v>
       </c>
       <c r="F7" t="n">
-        <v>32.8</v>
+        <v>31.9</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.65</v>
+        <v>-6.26</v>
       </c>
       <c r="H7" t="n">
-        <v>0.42</v>
+        <v>0.74</v>
       </c>
       <c r="I7" t="n">
-        <v>26.29</v>
+        <v>21.9</v>
       </c>
       <c r="J7" t="n">
-        <v>161.72</v>
+        <v>160.85</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1310,10 +1311,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>7729.61</v>
+        <v>7728.88</v>
       </c>
       <c r="N7" t="n">
-        <v>8748.26</v>
+        <v>8747.99</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1358,22 +1359,22 @@
         <v>8268</v>
       </c>
       <c r="X7" t="n">
-        <v>-95</v>
+        <v>-150</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.15</v>
+        <v>-1.81</v>
       </c>
       <c r="Z7" t="n">
-        <v>8173</v>
+        <v>8118</v>
       </c>
       <c r="AA7" t="n">
         <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>180</v>
+        <v>125</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.25</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="8">
@@ -1394,22 +1395,22 @@
         <v>55510</v>
       </c>
       <c r="E8" t="n">
-        <v>51970</v>
+        <v>51750</v>
       </c>
       <c r="F8" t="n">
-        <v>53.2</v>
+        <v>52.8</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.38</v>
+        <v>-2.78</v>
       </c>
       <c r="H8" t="n">
-        <v>0.61</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>-452.35</v>
+        <v>-469.9</v>
       </c>
       <c r="J8" t="n">
-        <v>-768.41</v>
+        <v>-771.92</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1422,10 +1423,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>66173.87</v>
+        <v>66170.92999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>39599.44</v>
+        <v>39598.34</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1471,22 +1472,22 @@
         <v>50590</v>
       </c>
       <c r="X8" t="n">
-        <v>1380</v>
+        <v>1160</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.73</v>
+        <v>2.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>51970</v>
+        <v>51750</v>
       </c>
       <c r="AA8" t="n">
         <v>55510</v>
       </c>
       <c r="AB8" t="n">
-        <v>-3540</v>
+        <v>-3760</v>
       </c>
       <c r="AC8" t="n">
-        <v>-6.38</v>
+        <v>-6.77</v>
       </c>
     </row>
     <row r="9">
@@ -1507,22 +1508,22 @@
         <v>10000</v>
       </c>
       <c r="E9" t="n">
-        <v>9294</v>
+        <v>9197</v>
       </c>
       <c r="F9" t="n">
-        <v>52.5</v>
+        <v>51.5</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.29</v>
+        <v>-3.27</v>
       </c>
       <c r="H9" t="n">
-        <v>0.68</v>
+        <v>1.1</v>
       </c>
       <c r="I9" t="n">
-        <v>-465.84</v>
+        <v>-473.58</v>
       </c>
       <c r="J9" t="n">
-        <v>-589.08</v>
+        <v>-590.63</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1535,10 +1536,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>13144.43</v>
+        <v>13143.13</v>
       </c>
       <c r="N9" t="n">
-        <v>7894.81</v>
+        <v>7894.33</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1588,22 +1589,22 @@
         <v>8714</v>
       </c>
       <c r="X9" t="n">
-        <v>580</v>
+        <v>483</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.66</v>
+        <v>5.54</v>
       </c>
       <c r="Z9" t="n">
-        <v>9294</v>
+        <v>9197</v>
       </c>
       <c r="AA9" t="n">
         <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-706</v>
+        <v>-803</v>
       </c>
       <c r="AC9" t="n">
-        <v>-7.06</v>
+        <v>-8.029999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1734,7 +1735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1403"/>
+  <dimension ref="A1:C1412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22781,6 +22782,141 @@
         </is>
       </c>
       <c r="C1403" t="n">
+        <v>36.74</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1404" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1405" t="n">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1406" t="n">
+        <v>178.1</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1407" t="n">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1408" t="n">
+        <v>4910</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1409" t="n">
+        <v>8118</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1410" t="n">
+        <v>51750</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1411" t="n">
+        <v>9197</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1412" t="n">
         <v>36.74</v>
       </c>
     </row>
@@ -22795,7 +22931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F242"/>
+  <dimension ref="A1:F243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27115,19 +27251,29 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
+      <c r="A240" t="inlineStr"/>
+      <c r="B240" s="1" t="n">
+        <v>46280.75</v>
+      </c>
+      <c r="C240" t="n">
+        <v>211595</v>
+      </c>
+      <c r="D240" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E240" t="n">
+        <v>2305</v>
+      </c>
+      <c r="F240" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr"/>
-      <c r="C240" t="inlineStr"/>
-      <c r="D240" t="inlineStr"/>
-      <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr"/>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr"/>
       <c r="B241" t="inlineStr"/>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr"/>
@@ -27135,16 +27281,24 @@
       <c r="F241" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr"/>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr"/>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27309,31 +27463,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1019</v>
+        <v>1003</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>-16</v>
       </c>
       <c r="G2" t="n">
-        <v>0.39</v>
+        <v>-1.57</v>
       </c>
       <c r="H2" t="n">
-        <v>902400</v>
+        <v>232800</v>
       </c>
       <c r="I2" t="n">
-        <v>60</v>
+        <v>56.5</v>
       </c>
       <c r="J2" t="n">
-        <v>4.26</v>
+        <v>1.97</v>
       </c>
       <c r="K2" t="n">
-        <v>1.04</v>
+        <v>0.32</v>
       </c>
       <c r="L2" t="n">
-        <v>41.89</v>
+        <v>37.53</v>
       </c>
       <c r="M2" t="n">
-        <v>46.74</v>
+        <v>44.9</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -27346,10 +27500,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>836.65</v>
+        <v>840.83</v>
       </c>
       <c r="Q2" t="n">
-        <v>1122.97</v>
+        <v>1121.17</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -27410,31 +27564,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3345</v>
+        <v>3375</v>
       </c>
       <c r="F3" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
-        <v>2.45</v>
+        <v>0.9</v>
       </c>
       <c r="H3" t="n">
-        <v>122100</v>
+        <v>205600</v>
       </c>
       <c r="I3" t="n">
-        <v>47.2</v>
+        <v>47.8</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.16</v>
+        <v>-1.41</v>
       </c>
       <c r="K3" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>38.37</v>
+        <v>32.95</v>
       </c>
       <c r="M3" t="n">
-        <v>84.59999999999999</v>
+        <v>74.27</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -27447,10 +27601,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2993.88</v>
+        <v>3007.96</v>
       </c>
       <c r="Q3" t="n">
-        <v>2714.59</v>
+        <v>2718.03</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -27458,7 +27612,7 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -27476,7 +27630,7 @@
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・出来高が増加しています。
+・出来高が急増しています。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -27512,31 +27666,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1355</v>
+        <v>1334</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>-21</v>
       </c>
       <c r="G4" t="n">
-        <v>2.19</v>
+        <v>-1.55</v>
       </c>
       <c r="H4" t="n">
-        <v>5400</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>64.7</v>
+        <v>62.9</v>
       </c>
       <c r="J4" t="n">
-        <v>6.02</v>
+        <v>3.74</v>
       </c>
       <c r="K4" t="n">
-        <v>0.51</v>
+        <v>0.05</v>
       </c>
       <c r="L4" t="n">
-        <v>42.2</v>
+        <v>39.03</v>
       </c>
       <c r="M4" t="n">
-        <v>42.42</v>
+        <v>41.74</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -27549,10 +27703,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1203.54</v>
+        <v>1203.81</v>
       </c>
       <c r="Q4" t="n">
-        <v>1642.25</v>
+        <v>1641.31</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -27612,67 +27766,775 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3465</v>
+        <v>3515</v>
       </c>
       <c r="F5" t="n">
+        <v>50</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I5" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L5" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="M5" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>3429.33</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3143.86</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは買いシグナルです。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3984.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ユーザーローカル</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AI解析・データ分析</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1548</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>25700</v>
+      </c>
+      <c r="I6" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-29.09</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-37.64</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1686.41</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1701.27</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>60</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4054.T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>日本情報クリエイト</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>不動産向けクラウド</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>520</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5400</v>
+      </c>
+      <c r="I7" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-6.74</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-7.73</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>537.26</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>584.03</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
         <v>30</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="H5" t="n">
-        <v>17300</v>
-      </c>
-      <c r="I5" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="L5" t="n">
-        <v>9.06</v>
-      </c>
-      <c r="M5" t="n">
-        <v>9.16</v>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7072.T</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>インティメート・マージャー</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>データマーケティング</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1070</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>200</v>
+      </c>
+      <c r="I8" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-5.61</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-5.58</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1054.08</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1021.87</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>70</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7033.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>マネジメントソリューションズ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PMO支援・DX案件増加</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1567</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-14</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="H9" t="n">
+        <v>10900</v>
+      </c>
+      <c r="I9" t="n">
+        <v>36</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-2.77</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L9" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="M9" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P5" t="n">
-        <v>3435.8</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3139.57</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P9" t="n">
+        <v>1449.35</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1379.65</v>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S5" t="n">
+      <c r="S9" t="n">
+        <v>65</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9342.T</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>スマサポ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>不動産DX</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>987</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>600</v>
+      </c>
+      <c r="I10" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L10" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="M10" t="n">
+        <v>23.93</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>871.96</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>986.41</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>75</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6971.T</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>京セラ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>自社株</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3546</v>
+      </c>
+      <c r="F11" t="n">
+        <v>26</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1213100</v>
+      </c>
+      <c r="I11" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-50.41</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-49.27</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>3662.63</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2926.54</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>45</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026/10/29</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>あと44日</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3778.T</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>さくらインターネット(株)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>3720</v>
+      </c>
+      <c r="F12" t="n">
+        <v>115</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="H12" t="n">
+        <v>188900</v>
+      </c>
+      <c r="I12" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="L12" t="n">
+        <v>78.87</v>
+      </c>
+      <c r="M12" t="n">
+        <v>102.58</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>3202.97</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3054.88</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
         <v>95</v>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -27683,704 +28545,718 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr">
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>3984.T</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ユーザーローカル</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5803.T</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>(株)フジクラ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>監視</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>AI解析・データ分析</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1548</v>
-      </c>
-      <c r="F6" t="n">
-        <v>19</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="H6" t="n">
-        <v>68000</v>
-      </c>
-      <c r="I6" t="n">
-        <v>51</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-31.94</v>
-      </c>
-      <c r="M6" t="n">
-        <v>-39.78</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>4822</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-12</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H13" t="n">
+        <v>16193300</v>
+      </c>
+      <c r="I13" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-9.470000000000001</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-46.44</v>
+      </c>
+      <c r="M13" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>5063.59</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4475.9</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2026/11/10</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>あと56日</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>166A.T</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>タスキホールディングス</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>何度も高値更新中の強トレンド</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1069</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="H14" t="n">
+        <v>46200</v>
+      </c>
+      <c r="I14" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-6.55</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-17.62</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1108.04</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>925.79</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>65</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・売られ過ぎ水準です。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5801.T</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>古河電気工業</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>半導体設備関連</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3824</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-21</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12376300</v>
+      </c>
+      <c r="I15" t="n">
+        <v>48</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-2.87</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L15" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="M15" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P6" t="n">
-        <v>1688.5</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1703.06</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
+      <c r="P15" t="n">
+        <v>4040.75</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3153.65</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
         <v>60</v>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>★★☆☆☆</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🔴 下降
-・MACDは買いシグナルです。
+・🟡 反発中
+・MACDは売りシグナルです。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>4054.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>日本情報クリエイト</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2026/11/09</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>あと55日</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3374.T</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>内外テック</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>監視</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>不動産向けクラウド</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>522</v>
-      </c>
-      <c r="F7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="H7" t="n">
-        <v>6200</v>
-      </c>
-      <c r="I7" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-7.1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-7.98</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>3915</v>
+      </c>
+      <c r="F16" t="n">
+        <v>85</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H16" t="n">
+        <v>7800</v>
+      </c>
+      <c r="I16" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-5.21</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L16" t="n">
+        <v>34.72</v>
+      </c>
+      <c r="M16" t="n">
+        <v>94.44</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>537.14</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>584.88</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>30</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7072.T</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>インティメート・マージャー</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>データマーケティング</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1076</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="H8" t="n">
-        <v>7200</v>
-      </c>
-      <c r="I8" t="n">
-        <v>31</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-5.23</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-2.64</v>
-      </c>
-      <c r="M8" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>-1S</t>
         </is>
       </c>
-      <c r="P8" t="n">
-        <v>1053.15</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1022.9</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P16" t="n">
+        <v>3554.36</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2829.47</v>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S8" t="n">
-        <v>75</v>
-      </c>
-      <c r="T8" t="inlineStr">
+      <c r="S16" t="n">
+        <v>70</v>
+      </c>
+      <c r="T16" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・出来高が増加しています。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
         <is>
           <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>7033.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>マネジメントソリューションズ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>7012.T</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>川崎重工業(株)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>監視</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PMO支援・DX案件増加</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1581</v>
-      </c>
-      <c r="F9" t="n">
-        <v>42</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="H9" t="n">
-        <v>41700</v>
-      </c>
-      <c r="I9" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-1.62</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L9" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>2318</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-33.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3665300</v>
+      </c>
+      <c r="I17" t="n">
+        <v>30</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-9.73</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-106.67</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-92.51000000000001</v>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>2752.49</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2825.86</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは売りシグナルです。
+・売られ過ぎ水準です。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>あと57日</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>トヨタ自動車(株)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4000円で売る予定</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3016</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-9</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>8678500</v>
+      </c>
+      <c r="I18" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="M18" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P9" t="n">
-        <v>1446.92</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1378.45</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>65</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9342.T</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>スマサポ</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>不動産DX</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>987</v>
-      </c>
-      <c r="F10" t="n">
-        <v>12</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="H10" t="n">
-        <v>100</v>
-      </c>
-      <c r="I10" t="n">
-        <v>66</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="L10" t="n">
-        <v>21.54</v>
-      </c>
-      <c r="M10" t="n">
-        <v>24.72</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>869.17</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>986.29</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P18" t="n">
+        <v>2932.79</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3164.86</v>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>🟢 上昇</t>
         </is>
       </c>
-      <c r="S10" t="n">
-        <v>75</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
+      <c r="S18" t="n">
+        <v>55</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>6971.T</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>京セラ</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2026/11/05</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>あと51日</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>8053.T</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>住友商事</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>保有中</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>自社株</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>3520</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-31</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4002900</v>
-      </c>
-      <c r="I11" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>-2.99</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-55.86</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-48.98</v>
-      </c>
-      <c r="N11" t="inlineStr">
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>1786</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-25</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3234800</v>
+      </c>
+      <c r="I19" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L19" t="n">
+        <v>30.08</v>
+      </c>
+      <c r="M19" t="n">
+        <v>36.99</v>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P11" t="n">
-        <v>3661.79</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2918.82</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>45</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2026/10/29</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>あと45日</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>3778.T</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>さくらインターネット(株)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="n">
-        <v>3605</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-55</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="H12" t="n">
-        <v>612300</v>
-      </c>
-      <c r="I12" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="L12" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="M12" t="n">
-        <v>108.51</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>3193.71</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3051.2</v>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="P19" t="n">
+        <v>1674.06</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1561.15</v>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S12" t="n">
+      <c r="S19" t="n">
         <v>85</v>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>★★★★☆</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -28391,302 +29267,202 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2026/10/29</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>あと44日</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
         <is>
           <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>5803.T</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>(株)フジクラ</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ブロードリーフ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>500円で売</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>477</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H20" t="n">
+        <v>843600</v>
+      </c>
+      <c r="I20" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M20" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>432.79</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>412.09</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>95</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>監視</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="n">
-        <v>4834</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-148</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-2.97</v>
-      </c>
-      <c r="H13" t="n">
-        <v>35382300</v>
-      </c>
-      <c r="I13" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-9.76</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-22.24</v>
-      </c>
-      <c r="M13" t="n">
-        <v>31.15</v>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>9294</v>
+      </c>
+      <c r="F21" t="n">
+        <v>580</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="H21" t="n">
+        <v>19310700</v>
+      </c>
+      <c r="I21" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-465.84</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-589.08</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>5062.91</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4466.59</v>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>13144.43</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>7894.81</v>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>🟡 反発中</t>
         </is>
       </c>
-      <c r="S13" t="n">
-        <v>50</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>2026/11/10</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>あと57日</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>166A.T</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>タスキホールディングス</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>何度も高値更新中の強トレンド</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1073</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H14" t="n">
-        <v>262500</v>
-      </c>
-      <c r="I14" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-6.36</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-15.44</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1106.35</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>924.1900000000001</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S14" t="n">
-        <v>65</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>5801.T</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>古河電気工業</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>半導体設備関連</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>3845</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-136</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-3.42</v>
-      </c>
-      <c r="H15" t="n">
-        <v>22796400</v>
-      </c>
-      <c r="I15" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-2.46</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="L15" t="n">
-        <v>22.75</v>
-      </c>
-      <c r="M15" t="n">
-        <v>19.59</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>4059.17</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3139.33</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S15" t="n">
-        <v>65</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
+      <c r="S21" t="n">
+        <v>85</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -28697,410 +29473,198 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>2026/11/09</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>あと56日</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2026/11/05</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>あと51日</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
         <is>
           <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>3374.T</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>内外テック</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="n">
-        <v>3830</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-70</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-1.79</v>
-      </c>
-      <c r="H16" t="n">
-        <v>21900</v>
-      </c>
-      <c r="I16" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="J16" t="n">
-        <v>-7.53</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="L16" t="n">
-        <v>46.27</v>
-      </c>
-      <c r="M16" t="n">
-        <v>109.37</v>
-      </c>
-      <c r="N16" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>キオクシアホールディングス</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>51970</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1380</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H22" t="n">
+        <v>16202200</v>
+      </c>
+      <c r="I22" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-452.35</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-768.41</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>3542.89</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2819.49</v>
-      </c>
-      <c r="R16" t="inlineStr">
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>66173.87</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>39599.44</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>85</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2026/10/30</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>あと45日</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>8729.T</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ソニーファイナンシャル</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>163.1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="H23" t="n">
+        <v>22982300</v>
+      </c>
+      <c r="I23" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>152.03</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>150.53</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S16" t="n">
-        <v>70</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>7012.T</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>川崎重工業(株)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="n">
-        <v>2351</v>
-      </c>
-      <c r="F17" t="n">
-        <v>32</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="H17" t="n">
-        <v>9038600</v>
-      </c>
-      <c r="I17" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-104.64</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-88.95999999999999</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>2763.41</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2824.41</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S17" t="n">
-        <v>30</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>あと58日</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>7203.T</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>トヨタ自動車(株)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4000円で売る予定</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>3025</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-6</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="H18" t="n">
-        <v>22994300</v>
-      </c>
-      <c r="I18" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="L18" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="M18" t="n">
-        <v>22.72</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>2933.13</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3164.74</v>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="S18" t="n">
-        <v>55</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>2026/11/05</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>あと52日</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>8053.T</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>住友商事</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="n">
-        <v>1811</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="H19" t="n">
-        <v>6826000</v>
-      </c>
-      <c r="I19" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="L19" t="n">
-        <v>34.84</v>
-      </c>
-      <c r="M19" t="n">
-        <v>38.72</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1673.91</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1558</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S19" t="n">
+      <c r="S23" t="n">
         <v>95</v>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -29111,202 +29675,97 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>2026/10/29</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>あと45日</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>2026/11/12</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>あと58日</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
         <is>
           <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>3673.T</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ブロードリーフ</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>500円で売</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>475</v>
-      </c>
-      <c r="F20" t="n">
-        <v>17</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="H20" t="n">
-        <v>510800</v>
-      </c>
-      <c r="I20" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="L20" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="M20" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="N20" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6723.T</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ルネサスエレクトロニクス</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>3205</v>
+      </c>
+      <c r="F24" t="n">
+        <v>29</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3436800</v>
+      </c>
+      <c r="I24" t="n">
+        <v>40</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-6.53</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-144.84</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-153.78</v>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>432.62</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>411.47</v>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S20" t="n">
-        <v>95</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="n">
-        <v>8714</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-495</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-5.38</v>
-      </c>
-      <c r="H21" t="n">
-        <v>25803500</v>
-      </c>
-      <c r="I21" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-8.49</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-511.08</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-619.89</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>-1S</t>
         </is>
       </c>
-      <c r="P21" t="n">
-        <v>13218.04</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>7863.9</v>
-      </c>
-      <c r="R21" t="inlineStr">
+      <c r="P24" t="n">
+        <v>4038.05</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3179.77</v>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>🟡 反発中</t>
         </is>
       </c>
-      <c r="S21" t="n">
+      <c r="S24" t="n">
         <v>70</v>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -29316,308 +29775,6 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>2026/11/05</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>あと52日</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>285A.T</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>キオクシアホールディングス</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="n">
-        <v>50590</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-3440</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-6.37</v>
-      </c>
-      <c r="H22" t="n">
-        <v>28534900</v>
-      </c>
-      <c r="I22" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="J22" t="n">
-        <v>-4.69</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-310.04</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-847.4299999999999</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>66358.92999999999</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>39393.76</v>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S22" t="n">
-        <v>65</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>2026/10/30</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>あと46日</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>8729.T</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ソニーファイナンシャル</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>163.8</v>
-      </c>
-      <c r="F23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="H23" t="n">
-        <v>53785200</v>
-      </c>
-      <c r="I23" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>151.72</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>150.43</v>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S23" t="n">
-        <v>95</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>2026/11/12</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>あと59日</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>6723.T</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>ルネサスエレクトロニクス</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="n">
-        <v>3176</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-16</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="H24" t="n">
-        <v>9810200</v>
-      </c>
-      <c r="I24" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="J24" t="n">
-        <v>-8.039999999999999</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="L24" t="n">
-        <v>-147.67</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-156.02</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>4055.32</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3172.7</v>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S24" t="n">
-        <v>70</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="W24" t="inlineStr">
         <is>
           <t>2026/10/28</t>
@@ -29625,7 +29782,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>あと44日</t>
+          <t>あと43日</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -29657,7 +29814,7 @@
         <v>-8.93</v>
       </c>
       <c r="H25" t="n">
-        <v>1452306</v>
+        <v>1464200</v>
       </c>
       <c r="I25" t="n">
         <v>40.6</v>
@@ -29666,7 +29823,7 @@
         <v>-11.92</v>
       </c>
       <c r="K25" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="L25" t="n">
         <v>-2.12</v>
@@ -29726,7 +29883,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>あと29日</t>
+          <t>あと28日</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -29749,31 +29906,31 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>8268</v>
+        <v>8173</v>
       </c>
       <c r="F26" t="n">
-        <v>175</v>
+        <v>-95</v>
       </c>
       <c r="G26" t="n">
-        <v>2.16</v>
+        <v>-1.15</v>
       </c>
       <c r="H26" t="n">
-        <v>9454300</v>
+        <v>4101900</v>
       </c>
       <c r="I26" t="n">
-        <v>35.4</v>
+        <v>32.8</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.59</v>
+        <v>-5.65</v>
       </c>
       <c r="K26" t="n">
-        <v>0.93</v>
+        <v>0.42</v>
       </c>
       <c r="L26" t="n">
-        <v>56.08</v>
+        <v>26.29</v>
       </c>
       <c r="M26" t="n">
-        <v>195.58</v>
+        <v>161.72</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -29786,10 +29943,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7715.95</v>
+        <v>7729.61</v>
       </c>
       <c r="Q26" t="n">
-        <v>8771.299999999999</v>
+        <v>8748.26</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -29826,7 +29983,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>あと50日</t>
+          <t>あと49日</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>211,595円</t>
+          <t>211,594円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2,305円</t>
+          <t>2,304円</t>
         </is>
       </c>
     </row>
@@ -1625,22 +1625,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>36.74</v>
+        <v>35.64</v>
       </c>
       <c r="F10" t="n">
-        <v>53.9</v>
+        <v>42.1</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.67</v>
+        <v>-5.04</v>
       </c>
       <c r="H10" t="n">
-        <v>1.07</v>
+        <v>0.78</v>
       </c>
       <c r="I10" t="n">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="J10" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.69</v>
+        <v>33.62</v>
       </c>
       <c r="N10" t="n">
-        <v>31.51</v>
+        <v>31.52</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1665,20 +1665,20 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1686,42 +1686,37 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>⚠️ 急落</t>
-        </is>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD売り、長期上昇</t>
+          <t>押し目、-1σ、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>40.1</v>
+        <v>36.74</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.36</v>
+        <v>-1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>-8.380000000000001</v>
+        <v>-2.99</v>
       </c>
       <c r="Z10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6076</v>
+        <v>-6077</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.40000000000001</v>
+        <v>-99.42</v>
       </c>
     </row>
   </sheetData>
@@ -1735,7 +1730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1412"/>
+  <dimension ref="A1:C1421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22918,6 +22913,141 @@
       </c>
       <c r="C1412" t="n">
         <v>36.74</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1413" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1414" t="n">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1415" t="n">
+        <v>178.1</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1416" t="n">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1417" t="n">
+        <v>4910</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1418" t="n">
+        <v>8118</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1419" t="n">
+        <v>51750</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1420" t="n">
+        <v>9197</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1421" t="n">
+        <v>35.64</v>
       </c>
     </row>
   </sheetData>
@@ -22931,7 +23061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F243"/>
+  <dimension ref="A1:F244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27269,19 +27399,29 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
+      <c r="A241" t="inlineStr"/>
+      <c r="B241" s="1" t="n">
+        <v>46281.29166666666</v>
+      </c>
+      <c r="C241" t="n">
+        <v>211594</v>
+      </c>
+      <c r="D241" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E241" t="n">
+        <v>2304</v>
+      </c>
+      <c r="F241" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr"/>
-      <c r="C241" t="inlineStr"/>
-      <c r="D241" t="inlineStr"/>
-      <c r="E241" t="inlineStr"/>
-      <c r="F241" t="inlineStr"/>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr"/>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr"/>
@@ -27289,16 +27429,24 @@
       <c r="F242" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A243" t="inlineStr"/>
       <c r="B243" t="inlineStr"/>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr"/>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27463,31 +27611,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="F2" t="n">
-        <v>-16</v>
+        <v>-18</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.57</v>
+        <v>-1.77</v>
       </c>
       <c r="H2" t="n">
-        <v>232800</v>
+        <v>463200</v>
       </c>
       <c r="I2" t="n">
-        <v>56.5</v>
+        <v>56.2</v>
       </c>
       <c r="J2" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="K2" t="n">
-        <v>0.32</v>
+        <v>0.59</v>
       </c>
       <c r="L2" t="n">
-        <v>37.53</v>
+        <v>37.37</v>
       </c>
       <c r="M2" t="n">
-        <v>44.9</v>
+        <v>44.87</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -27500,10 +27648,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>840.83</v>
+        <v>840.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>1121.17</v>
+        <v>1121.16</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -27564,31 +27712,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3375</v>
+        <v>3340</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>-5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9</v>
+        <v>-0.15</v>
       </c>
       <c r="H3" t="n">
-        <v>205600</v>
+        <v>317100</v>
       </c>
       <c r="I3" t="n">
-        <v>47.8</v>
+        <v>46.4</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.41</v>
+        <v>-2.39</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>2.53</v>
       </c>
       <c r="L3" t="n">
-        <v>32.95</v>
+        <v>30.16</v>
       </c>
       <c r="M3" t="n">
-        <v>74.27</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -27601,10 +27749,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3007.96</v>
+        <v>3007.49</v>
       </c>
       <c r="Q3" t="n">
-        <v>2718.03</v>
+        <v>2717.85</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -27666,31 +27814,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1334</v>
+        <v>1346</v>
       </c>
       <c r="F4" t="n">
-        <v>-21</v>
+        <v>-9</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.55</v>
+        <v>-0.66</v>
       </c>
       <c r="H4" t="n">
-        <v>400</v>
+        <v>4100</v>
       </c>
       <c r="I4" t="n">
-        <v>62.9</v>
+        <v>64.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.74</v>
+        <v>4.64</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05</v>
+        <v>0.49</v>
       </c>
       <c r="L4" t="n">
-        <v>39.03</v>
+        <v>39.98</v>
       </c>
       <c r="M4" t="n">
-        <v>41.74</v>
+        <v>41.93</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -27703,10 +27851,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1203.81</v>
+        <v>1203.97</v>
       </c>
       <c r="Q4" t="n">
-        <v>1641.31</v>
+        <v>1641.37</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -27766,31 +27914,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3515</v>
+        <v>3475</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>1.44</v>
+        <v>0.29</v>
       </c>
       <c r="H5" t="n">
-        <v>2800</v>
+        <v>9400</v>
       </c>
       <c r="I5" t="n">
-        <v>59.7</v>
+        <v>58.1</v>
       </c>
       <c r="J5" t="n">
-        <v>1.76</v>
+        <v>0.65</v>
       </c>
       <c r="K5" t="n">
-        <v>0.22</v>
+        <v>0.68</v>
       </c>
       <c r="L5" t="n">
-        <v>12.63</v>
+        <v>9.44</v>
       </c>
       <c r="M5" t="n">
-        <v>9.85</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -27803,10 +27951,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3429.33</v>
+        <v>3428.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>3143.86</v>
+        <v>3143.66</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -27868,31 +28016,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="H6" t="n">
-        <v>25700</v>
+        <v>60700</v>
       </c>
       <c r="I6" t="n">
-        <v>53.7</v>
+        <v>54</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01</v>
+        <v>0.13</v>
       </c>
       <c r="K6" t="n">
-        <v>0.34</v>
+        <v>0.73</v>
       </c>
       <c r="L6" t="n">
-        <v>-29.09</v>
+        <v>-28.93</v>
       </c>
       <c r="M6" t="n">
-        <v>-37.64</v>
+        <v>-37.61</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -27905,10 +28053,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1686.41</v>
+        <v>1686.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>1701.27</v>
+        <v>1701.28</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -27978,7 +28126,7 @@
         <v>-0.38</v>
       </c>
       <c r="H7" t="n">
-        <v>5400</v>
+        <v>7900</v>
       </c>
       <c r="I7" t="n">
         <v>48.5</v>
@@ -27987,7 +28135,7 @@
         <v>-1.25</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="L7" t="n">
         <v>-6.74</v>
@@ -28070,31 +28218,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="F8" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I8" t="n">
-        <v>31.6</v>
+        <v>32.4</v>
       </c>
       <c r="J8" t="n">
-        <v>-5.61</v>
+        <v>-5.1</v>
       </c>
       <c r="K8" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.58</v>
+        <v>-5.1</v>
       </c>
       <c r="M8" t="n">
-        <v>5.68</v>
+        <v>5.77</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -28107,10 +28255,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1054.08</v>
+        <v>1054.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>1021.87</v>
+        <v>1021.89</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -28170,31 +28318,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1567</v>
+        <v>1558</v>
       </c>
       <c r="F9" t="n">
-        <v>-14</v>
+        <v>-23</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.89</v>
+        <v>-1.45</v>
       </c>
       <c r="H9" t="n">
-        <v>10900</v>
+        <v>89000</v>
       </c>
       <c r="I9" t="n">
-        <v>36</v>
+        <v>35.2</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.77</v>
+        <v>-3.31</v>
       </c>
       <c r="K9" t="n">
-        <v>0.25</v>
+        <v>1.49</v>
       </c>
       <c r="L9" t="n">
-        <v>12.37</v>
+        <v>11.65</v>
       </c>
       <c r="M9" t="n">
-        <v>29.99</v>
+        <v>29.85</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -28207,10 +28355,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1449.35</v>
+        <v>1449.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>1379.65</v>
+        <v>1379.61</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -28370,31 +28518,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3546</v>
+        <v>3531</v>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>0.74</v>
+        <v>0.31</v>
       </c>
       <c r="H11" t="n">
-        <v>1213100</v>
+        <v>3497900</v>
       </c>
       <c r="I11" t="n">
-        <v>43.8</v>
+        <v>42.4</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.97</v>
+        <v>-2.37</v>
       </c>
       <c r="K11" t="n">
-        <v>0.25</v>
+        <v>0.66</v>
       </c>
       <c r="L11" t="n">
-        <v>-50.41</v>
+        <v>-51.61</v>
       </c>
       <c r="M11" t="n">
-        <v>-49.27</v>
+        <v>-49.51</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -28407,10 +28555,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3662.63</v>
+        <v>3662.43</v>
       </c>
       <c r="Q11" t="n">
-        <v>2926.54</v>
+        <v>2926.46</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -28474,67 +28622,790 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>3720</v>
+        <v>3580</v>
       </c>
       <c r="F12" t="n">
-        <v>115</v>
+        <v>-25</v>
       </c>
       <c r="G12" t="n">
-        <v>3.19</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>188900</v>
+        <v>642300</v>
       </c>
       <c r="I12" t="n">
-        <v>55.8</v>
+        <v>51.5</v>
       </c>
       <c r="J12" t="n">
-        <v>0.48</v>
+        <v>-3.15</v>
       </c>
       <c r="K12" t="n">
-        <v>0.31</v>
+        <v>0.91</v>
       </c>
       <c r="L12" t="n">
-        <v>78.87</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>102.58</v>
+        <v>100.35</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>3201.11</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3054.18</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>70</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>🟡 調整中押し目（段階的買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5803.T</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>(株)フジクラ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>4744</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-90</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="H13" t="n">
+        <v>31474800</v>
+      </c>
+      <c r="I13" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-10.89</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-52.66</v>
+      </c>
+      <c r="M13" t="n">
+        <v>14.39</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>5062.55</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4475.51</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>35</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・25日線から大きく下に乖離しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2026/11/10</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>あと56日</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>166A.T</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>タスキホールディングス</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>何度も高値更新中の強トレンド</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1069</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="H14" t="n">
+        <v>164200</v>
+      </c>
+      <c r="I14" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-6.55</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-17.62</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1108.04</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>925.79</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>65</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・売られ過ぎ水準です。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5801.T</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>古河電気工業</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>半導体設備関連</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3719</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-126</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-3.28</v>
+      </c>
+      <c r="H15" t="n">
+        <v>22958800</v>
+      </c>
+      <c r="I15" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-5.44</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L15" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="M15" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>4039.35</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3153.13</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>65</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
+・RSIは良好な水準です。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2026/11/09</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>あと55日</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3374.T</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>内外テック</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>3875</v>
+      </c>
+      <c r="F16" t="n">
+        <v>45</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H16" t="n">
+        <v>14200</v>
+      </c>
+      <c r="I16" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-6.14</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L16" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="M16" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>3553.83</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2829.27</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>70</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>7012.T</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>川崎重工業(株)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>2372</v>
+      </c>
+      <c r="F17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H17" t="n">
+        <v>17581900</v>
+      </c>
+      <c r="I17" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-7.68</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-102.33</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-91.64</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>2753.21</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2826.14</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは売りシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>あと57日</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>トヨタ自動車(株)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4000円で売る予定</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3021</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="H18" t="n">
+        <v>19958900</v>
+      </c>
+      <c r="I18" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="M18" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P12" t="n">
-        <v>3202.97</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3054.88</v>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="P18" t="n">
+        <v>2932.85</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3164.88</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>55</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2026/11/05</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>あと51日</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>8053.T</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>住友商事</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>1770</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-40.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8412000</v>
+      </c>
+      <c r="I19" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L19" t="n">
+        <v>28.84</v>
+      </c>
+      <c r="M19" t="n">
+        <v>36.74</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1673.85</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1561.07</v>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S12" t="n">
-        <v>95</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
+      <c r="S19" t="n">
+        <v>85</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -28545,718 +29416,405 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2026/10/29</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>あと44日</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ブロードリーフ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>500円で売</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>475</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1809000</v>
+      </c>
+      <c r="I20" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="M20" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>432.76</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>412.08</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>100</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・出来高が増加しています。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
         <is>
           <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>5803.T</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>(株)フジクラ</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>監視</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="n">
-        <v>4822</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-12</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="H13" t="n">
-        <v>16193300</v>
-      </c>
-      <c r="I13" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-9.470000000000001</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-46.44</v>
-      </c>
-      <c r="M13" t="n">
-        <v>15.63</v>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>9197</v>
+      </c>
+      <c r="F21" t="n">
+        <v>483</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="H21" t="n">
+        <v>34475900</v>
+      </c>
+      <c r="I21" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-3.27</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-473.58</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-590.63</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>5063.59</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4475.9</v>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>13143.13</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>7894.33</v>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>🟡 反発中</t>
         </is>
       </c>
-      <c r="S13" t="n">
-        <v>50</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
+      <c r="S21" t="n">
+        <v>85</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>2026/11/10</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>あと56日</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>166A.T</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>タスキホールディングス</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>何度も高値更新中の強トレンド</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1069</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-4</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="H14" t="n">
-        <v>46200</v>
-      </c>
-      <c r="I14" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-6.55</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-17.62</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1108.04</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>925.79</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S14" t="n">
-        <v>65</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>5801.T</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>古河電気工業</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>半導体設備関連</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>3824</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-21</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12376300</v>
-      </c>
-      <c r="I15" t="n">
-        <v>48</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-2.87</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="L15" t="n">
-        <v>15.32</v>
-      </c>
-      <c r="M15" t="n">
-        <v>18.74</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>4040.75</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3153.65</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S15" t="n">
-        <v>60</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
+・MACDは買いシグナルです。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>2026/11/09</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>あと55日</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2026/11/05</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>あと51日</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
         <is>
           <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>3374.T</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>内外テック</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="n">
-        <v>3915</v>
-      </c>
-      <c r="F16" t="n">
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>キオクシアホールディングス</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>51750</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1160</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H22" t="n">
+        <v>29060500</v>
+      </c>
+      <c r="I22" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-2.78</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-469.9</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-771.92</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>66170.92999999999</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>39598.34</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
         <v>85</v>
       </c>
-      <c r="G16" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="H16" t="n">
-        <v>7800</v>
-      </c>
-      <c r="I16" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>-5.21</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="L16" t="n">
-        <v>34.72</v>
-      </c>
-      <c r="M16" t="n">
-        <v>94.44</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>3554.36</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2829.47</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S16" t="n">
-        <v>70</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>7012.T</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>川崎重工業(株)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="n">
-        <v>2318</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-33.5</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-1.42</v>
-      </c>
-      <c r="H17" t="n">
-        <v>3665300</v>
-      </c>
-      <c r="I17" t="n">
-        <v>30</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-9.73</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-106.67</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-92.51000000000001</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>2752.49</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2825.86</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S17" t="n">
-        <v>15</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>あと57日</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>7203.T</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>トヨタ自動車(株)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4000円で売る予定</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>3016</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-9</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="H18" t="n">
-        <v>8678500</v>
-      </c>
-      <c r="I18" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-1.41</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="M18" t="n">
-        <v>18.63</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>2932.79</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3164.86</v>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="S18" t="n">
-        <v>55</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
+・🟡 反発中
+・MACDは買いシグナルです。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>2026/11/05</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>あと51日</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2026/10/30</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>あと45日</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
         <is>
           <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>8053.T</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>住友商事</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="n">
-        <v>1786</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-25</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="H19" t="n">
-        <v>3234800</v>
-      </c>
-      <c r="I19" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="L19" t="n">
-        <v>30.08</v>
-      </c>
-      <c r="M19" t="n">
-        <v>36.99</v>
-      </c>
-      <c r="N19" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>8729.T</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ソニーファイナンシャル</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>163</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="H23" t="n">
+        <v>48347000</v>
+      </c>
+      <c r="I23" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P19" t="n">
-        <v>1674.06</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1561.15</v>
-      </c>
-      <c r="R19" t="inlineStr">
+      <c r="P23" t="n">
+        <v>152.03</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>150.53</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S19" t="n">
-        <v>85</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
+      <c r="S23" t="n">
+        <v>95</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -29267,414 +29825,6 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>2026/10/29</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>あと44日</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>3673.T</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ブロードリーフ</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>500円で売</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>477</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H20" t="n">
-        <v>843600</v>
-      </c>
-      <c r="I20" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="L20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="M20" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>432.79</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>412.09</v>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S20" t="n">
-        <v>95</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="n">
-        <v>9294</v>
-      </c>
-      <c r="F21" t="n">
-        <v>580</v>
-      </c>
-      <c r="G21" t="n">
-        <v>6.66</v>
-      </c>
-      <c r="H21" t="n">
-        <v>19310700</v>
-      </c>
-      <c r="I21" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-2.29</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-465.84</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-589.08</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>13144.43</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>7894.81</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S21" t="n">
-        <v>85</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>2026/11/05</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>あと51日</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>285A.T</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>キオクシアホールディングス</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="n">
-        <v>51970</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1380</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="H22" t="n">
-        <v>16202200</v>
-      </c>
-      <c r="I22" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-452.35</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-768.41</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>66173.87</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>39599.44</v>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S22" t="n">
-        <v>85</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>2026/10/30</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>あと45日</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>8729.T</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ソニーファイナンシャル</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>163.1</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="H23" t="n">
-        <v>22982300</v>
-      </c>
-      <c r="I23" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>152.03</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>150.53</v>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S23" t="n">
-        <v>95</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
       <c r="W23" t="inlineStr">
         <is>
           <t>2026/11/12</t>
@@ -29705,31 +29855,31 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>3205</v>
+        <v>3155</v>
       </c>
       <c r="F24" t="n">
-        <v>29</v>
+        <v>-21</v>
       </c>
       <c r="G24" t="n">
-        <v>0.91</v>
+        <v>-0.66</v>
       </c>
       <c r="H24" t="n">
-        <v>3436800</v>
+        <v>7596000</v>
       </c>
       <c r="I24" t="n">
-        <v>40</v>
+        <v>36.9</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.53</v>
+        <v>-7.93</v>
       </c>
       <c r="K24" t="n">
-        <v>0.43</v>
+        <v>0.86</v>
       </c>
       <c r="L24" t="n">
-        <v>-144.84</v>
+        <v>-148.83</v>
       </c>
       <c r="M24" t="n">
-        <v>-153.78</v>
+        <v>-154.58</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -29742,37 +29892,37 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>4038.05</v>
+        <v>4037.39</v>
       </c>
       <c r="Q24" t="n">
-        <v>3179.77</v>
+        <v>3179.52</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>🟡 反発中</t>
+          <t>🔴 下降</t>
         </is>
       </c>
       <c r="S24" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟡 反発中
+・🔴 下降
 ・MACDは買いシグナルです。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -29787,7 +29937,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
         </is>
       </c>
     </row>
@@ -29906,31 +30056,31 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>8173</v>
+        <v>8118</v>
       </c>
       <c r="F26" t="n">
-        <v>-95</v>
+        <v>-150</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.15</v>
+        <v>-1.81</v>
       </c>
       <c r="H26" t="n">
-        <v>4101900</v>
+        <v>7686000</v>
       </c>
       <c r="I26" t="n">
-        <v>32.8</v>
+        <v>31.9</v>
       </c>
       <c r="J26" t="n">
-        <v>-5.65</v>
+        <v>-6.26</v>
       </c>
       <c r="K26" t="n">
-        <v>0.42</v>
+        <v>0.74</v>
       </c>
       <c r="L26" t="n">
-        <v>26.29</v>
+        <v>21.9</v>
       </c>
       <c r="M26" t="n">
-        <v>161.72</v>
+        <v>160.85</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -29943,10 +30093,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7729.61</v>
+        <v>7728.88</v>
       </c>
       <c r="Q26" t="n">
-        <v>8748.26</v>
+        <v>8747.99</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>211,594円</t>
+          <t>210,007円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2,304円</t>
+          <t>717円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>0.34%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3340</v>
+        <v>3285</v>
       </c>
       <c r="F2" t="n">
-        <v>46.4</v>
+        <v>39.5</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.39</v>
+        <v>-4</v>
       </c>
       <c r="H2" t="n">
-        <v>2.53</v>
+        <v>0.58</v>
       </c>
       <c r="I2" t="n">
-        <v>30.16</v>
+        <v>18.99</v>
       </c>
       <c r="J2" t="n">
-        <v>73.70999999999999</v>
+        <v>62.77</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3007.49</v>
+        <v>3018.6</v>
       </c>
       <c r="N2" t="n">
-        <v>2717.85</v>
+        <v>2720.5</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -757,11 +757,11 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -778,8 +778,6 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・出来高が急増しています。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -788,29 +786,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>押し目、出来高増加、MACD売り、長期上昇</t>
+          <t>押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3345</v>
+        <v>3340</v>
       </c>
       <c r="X2" t="n">
-        <v>-5</v>
+        <v>-55</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.15</v>
+        <v>-1.65</v>
       </c>
       <c r="Z2" t="n">
-        <v>13360</v>
+        <v>13140</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2560</v>
+        <v>2340</v>
       </c>
       <c r="AC2" t="n">
-        <v>23.7</v>
+        <v>21.67</v>
       </c>
     </row>
     <row r="3">
@@ -831,26 +829,26 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="F3" t="n">
-        <v>53.9</v>
+        <v>49.4</v>
       </c>
       <c r="G3" t="n">
-        <v>2.75</v>
+        <v>3.21</v>
       </c>
       <c r="H3" t="n">
-        <v>1.71</v>
+        <v>0.22</v>
       </c>
       <c r="I3" t="n">
-        <v>4.64</v>
+        <v>5.31</v>
       </c>
       <c r="J3" t="n">
-        <v>6.25</v>
+        <v>6.06</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -859,10 +857,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>432.76</v>
+        <v>433.13</v>
       </c>
       <c r="N3" t="n">
-        <v>412.08</v>
+        <v>412.71</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -875,7 +873,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -892,8 +890,8 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・RSIは良好な水準です。
-・出来高が増加しています。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -902,29 +900,29 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、出来高微増、MACD売り、長期上昇</t>
+          <t>25日線上、ゴールデンクロス、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W3" t="n">
         <v>475</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="Z3" t="n">
-        <v>47500</v>
+        <v>47800</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>5500</v>
+        <v>5800</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.1</v>
+        <v>13.81</v>
       </c>
     </row>
     <row r="4">
@@ -945,22 +943,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>178.1</v>
+        <v>176.8</v>
       </c>
       <c r="F4" t="n">
-        <v>66.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>5.46</v>
+        <v>4.24</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="I4" t="n">
-        <v>4.71</v>
+        <v>4.61</v>
       </c>
       <c r="J4" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -973,10 +971,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>155.81</v>
+        <v>156.19</v>
       </c>
       <c r="N4" t="n">
-        <v>153.94</v>
+        <v>154.07</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1018,25 +1016,25 @@
         </is>
       </c>
       <c r="W4" t="n">
-        <v>178.3</v>
+        <v>178.1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2</v>
+        <v>-1.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.11</v>
+        <v>-0.73</v>
       </c>
       <c r="Z4" t="n">
-        <v>17810</v>
+        <v>17680</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>2010</v>
+        <v>1880</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.72</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="5">
@@ -1057,22 +1055,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3021</v>
+        <v>3041</v>
       </c>
       <c r="F5" t="n">
-        <v>45.5</v>
+        <v>46.8</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.26</v>
+        <v>-0.66</v>
       </c>
       <c r="H5" t="n">
-        <v>0.88</v>
+        <v>0.4</v>
       </c>
       <c r="I5" t="n">
-        <v>2.67</v>
+        <v>2.34</v>
       </c>
       <c r="J5" t="n">
-        <v>18.71</v>
+        <v>15.44</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1085,10 +1083,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2932.85</v>
+        <v>2934.66</v>
       </c>
       <c r="N5" t="n">
-        <v>3164.88</v>
+        <v>3165.09</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1131,25 +1129,25 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>3025</v>
+        <v>3021</v>
       </c>
       <c r="X5" t="n">
-        <v>-4</v>
+        <v>20</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.13</v>
+        <v>0.66</v>
       </c>
       <c r="Z5" t="n">
-        <v>39273</v>
+        <v>39533</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>2174</v>
+        <v>2434</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.86</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="6">
@@ -1170,22 +1168,22 @@
         <v>4795</v>
       </c>
       <c r="E6" t="n">
-        <v>4910</v>
+        <v>4968</v>
       </c>
       <c r="F6" t="n">
-        <v>58.6</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>1.19</v>
+        <v>2.29</v>
       </c>
       <c r="H6" t="n">
-        <v>0.86</v>
+        <v>0.51</v>
       </c>
       <c r="I6" t="n">
-        <v>62.5</v>
+        <v>60.42</v>
       </c>
       <c r="J6" t="n">
-        <v>59.37</v>
+        <v>59.58</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1198,10 +1196,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4716.72</v>
+        <v>4717.35</v>
       </c>
       <c r="N6" t="n">
-        <v>4663.47</v>
+        <v>4670.4</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1244,25 +1242,25 @@
         </is>
       </c>
       <c r="W6" t="n">
-        <v>4991</v>
+        <v>4910</v>
       </c>
       <c r="X6" t="n">
-        <v>-81</v>
+        <v>58</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.62</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>24550</v>
+        <v>24840</v>
       </c>
       <c r="AA6" t="n">
         <v>23975</v>
       </c>
       <c r="AB6" t="n">
-        <v>575</v>
+        <v>865</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.4</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="7">
@@ -1283,22 +1281,22 @@
         <v>7993</v>
       </c>
       <c r="E7" t="n">
-        <v>8118</v>
+        <v>8131</v>
       </c>
       <c r="F7" t="n">
-        <v>31.9</v>
+        <v>35.1</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.26</v>
+        <v>-5.95</v>
       </c>
       <c r="H7" t="n">
-        <v>0.74</v>
+        <v>0.29</v>
       </c>
       <c r="I7" t="n">
-        <v>21.9</v>
+        <v>-4.08</v>
       </c>
       <c r="J7" t="n">
-        <v>160.85</v>
+        <v>127.86</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1311,10 +1309,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>7728.88</v>
+        <v>7741.79</v>
       </c>
       <c r="N7" t="n">
-        <v>8747.99</v>
+        <v>8723.540000000001</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1356,61 +1354,61 @@
         </is>
       </c>
       <c r="W7" t="n">
-        <v>8268</v>
+        <v>8118</v>
       </c>
       <c r="X7" t="n">
-        <v>-150</v>
+        <v>13</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.81</v>
+        <v>0.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>8118</v>
+        <v>8131</v>
       </c>
       <c r="AA7" t="n">
         <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>285A.T</t>
+          <t>6976.T</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>キオクシアホールディングス</t>
+          <t>太陽誘電</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>55510</v>
+        <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>51750</v>
+        <v>9157</v>
       </c>
       <c r="F8" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.78</v>
+        <v>-3.24</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="I8" t="n">
-        <v>-469.9</v>
+        <v>-441.99</v>
       </c>
       <c r="J8" t="n">
-        <v>-771.92</v>
+        <v>-560.9</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1423,10 +1421,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>66170.92999999999</v>
+        <v>13051.09</v>
       </c>
       <c r="N8" t="n">
-        <v>39598.34</v>
+        <v>7923.97</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1469,77 +1467,77 @@
         </is>
       </c>
       <c r="W8" t="n">
-        <v>50590</v>
+        <v>9197</v>
       </c>
       <c r="X8" t="n">
-        <v>1160</v>
+        <v>-40</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.29</v>
+        <v>-0.43</v>
       </c>
       <c r="Z8" t="n">
-        <v>51750</v>
+        <v>9157</v>
       </c>
       <c r="AA8" t="n">
-        <v>55510</v>
+        <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-3760</v>
+        <v>-843</v>
       </c>
       <c r="AC8" t="n">
-        <v>-6.77</v>
+        <v>-8.43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6976.T</t>
+          <t>285A.T</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>太陽誘電</t>
+          <t>キオクシアホールディングス</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>10000</v>
+        <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>9197</v>
+        <v>49690</v>
       </c>
       <c r="F9" t="n">
-        <v>51.5</v>
+        <v>45.4</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.27</v>
+        <v>-6.64</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1</v>
+        <v>0.59</v>
       </c>
       <c r="I9" t="n">
-        <v>-473.58</v>
+        <v>-754.13</v>
       </c>
       <c r="J9" t="n">
-        <v>-590.63</v>
+        <v>-768.36</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>13143.13</v>
+        <v>65866.8</v>
       </c>
       <c r="N9" t="n">
-        <v>7894.33</v>
+        <v>39790.11</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1548,20 +1546,20 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1569,42 +1567,39 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD買い、反発局面</t>
+          <t>押し目、デッドクロス、-1σ、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>8714</v>
+        <v>51750</v>
       </c>
       <c r="X9" t="n">
-        <v>483</v>
+        <v>-2060</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.54</v>
+        <v>-3.98</v>
       </c>
       <c r="Z9" t="n">
-        <v>9197</v>
+        <v>49690</v>
       </c>
       <c r="AA9" t="n">
-        <v>10000</v>
+        <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-803</v>
+        <v>-5820</v>
       </c>
       <c r="AC9" t="n">
-        <v>-8.029999999999999</v>
+        <v>-10.48</v>
       </c>
     </row>
     <row r="10">
@@ -1730,7 +1725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1421"/>
+  <dimension ref="A1:C1430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23047,6 +23042,141 @@
         </is>
       </c>
       <c r="C1421" t="n">
+        <v>35.64</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1422" t="n">
+        <v>3285</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1423" t="n">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1424" t="n">
+        <v>176.8</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1425" t="n">
+        <v>3041</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1426" t="n">
+        <v>4968</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1427" t="n">
+        <v>8131</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1428" t="n">
+        <v>9157</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1429" t="n">
+        <v>49690</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1430" t="n">
         <v>35.64</v>
       </c>
     </row>
@@ -23061,7 +23191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F244"/>
+  <dimension ref="A1:F245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27417,19 +27547,29 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
+      <c r="A242" t="inlineStr"/>
+      <c r="B242" s="1" t="n">
+        <v>46281.5</v>
+      </c>
+      <c r="C242" t="n">
+        <v>210007</v>
+      </c>
+      <c r="D242" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E242" t="n">
+        <v>717</v>
+      </c>
+      <c r="F242" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr"/>
-      <c r="C242" t="inlineStr"/>
-      <c r="D242" t="inlineStr"/>
-      <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr"/>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr"/>
       <c r="B243" t="inlineStr"/>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr"/>
@@ -27437,16 +27577,24 @@
       <c r="F243" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A244" t="inlineStr"/>
       <c r="B244" t="inlineStr"/>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr"/>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -29955,31 +30103,31 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>46.59</v>
+        <v>47.5</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.57</v>
+        <v>0.91</v>
       </c>
       <c r="G25" t="n">
-        <v>-8.93</v>
+        <v>1.95</v>
       </c>
       <c r="H25" t="n">
-        <v>1464200</v>
+        <v>1000313</v>
       </c>
       <c r="I25" t="n">
-        <v>40.6</v>
+        <v>43.5</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.92</v>
+        <v>-9.67</v>
       </c>
       <c r="K25" t="n">
-        <v>1.2</v>
+        <v>0.85</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.12</v>
+        <v>-2.17</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.18</v>
+        <v>-2.17</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -29992,10 +30140,10 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>59.56</v>
+        <v>59.48</v>
       </c>
       <c r="Q25" t="n">
-        <v>37.41</v>
+        <v>37.55</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -30003,7 +30151,7 @@
         </is>
       </c>
       <c r="S25" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -30019,8 +30167,7 @@
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
-・MACDは買いシグナルです。
-・25日線から大きく下に乖離しています。
+・MACDは売りシグナルです。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>210,007円</t>
+          <t>210,784円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>717円</t>
+          <t>1,494円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3285</v>
+        <v>3310</v>
       </c>
       <c r="F2" t="n">
-        <v>39.5</v>
+        <v>40.3</v>
       </c>
       <c r="G2" t="n">
-        <v>-4</v>
+        <v>-3.3</v>
       </c>
       <c r="H2" t="n">
-        <v>0.58</v>
+        <v>0.92</v>
       </c>
       <c r="I2" t="n">
-        <v>18.99</v>
+        <v>20.98</v>
       </c>
       <c r="J2" t="n">
-        <v>62.77</v>
+        <v>63.17</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3018.6</v>
+        <v>3018.93</v>
       </c>
       <c r="N2" t="n">
-        <v>2720.5</v>
+        <v>2720.63</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -793,22 +793,22 @@
         <v>3340</v>
       </c>
       <c r="X2" t="n">
-        <v>-55</v>
+        <v>-30</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.65</v>
+        <v>-0.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>13140</v>
+        <v>13240</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2340</v>
+        <v>2440</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.67</v>
+        <v>22.59</v>
       </c>
     </row>
     <row r="3">
@@ -829,22 +829,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F3" t="n">
-        <v>49.4</v>
+        <v>48.8</v>
       </c>
       <c r="G3" t="n">
-        <v>3.21</v>
+        <v>2.8</v>
       </c>
       <c r="H3" t="n">
-        <v>0.22</v>
+        <v>0.6</v>
       </c>
       <c r="I3" t="n">
-        <v>5.31</v>
+        <v>5.15</v>
       </c>
       <c r="J3" t="n">
-        <v>6.06</v>
+        <v>6.03</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>433.13</v>
+        <v>433.1</v>
       </c>
       <c r="N3" t="n">
-        <v>412.71</v>
+        <v>412.7</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -907,22 +907,22 @@
         <v>475</v>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.63</v>
+        <v>0.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>47800</v>
+        <v>47600</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>5800</v>
+        <v>5600</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.81</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="4">
@@ -943,19 +943,19 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>176.8</v>
+        <v>177.1</v>
       </c>
       <c r="F4" t="n">
-        <v>67.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>4.24</v>
+        <v>4.41</v>
       </c>
       <c r="H4" t="n">
-        <v>0.43</v>
+        <v>0.82</v>
       </c>
       <c r="I4" t="n">
-        <v>4.61</v>
+        <v>4.63</v>
       </c>
       <c r="J4" t="n">
         <v>4.58</v>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>156.19</v>
+        <v>156.2</v>
       </c>
       <c r="N4" t="n">
         <v>154.07</v>
@@ -1019,22 +1019,22 @@
         <v>178.1</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.73</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="Z4" t="n">
-        <v>17680</v>
+        <v>17710</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1880</v>
+        <v>1910</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.9</v>
+        <v>12.09</v>
       </c>
     </row>
     <row r="5">
@@ -1055,22 +1055,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3041</v>
+        <v>3016</v>
       </c>
       <c r="F5" t="n">
-        <v>46.8</v>
+        <v>44.4</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.66</v>
+        <v>-1.44</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4</v>
+        <v>0.82</v>
       </c>
       <c r="I5" t="n">
-        <v>2.34</v>
+        <v>0.34</v>
       </c>
       <c r="J5" t="n">
-        <v>15.44</v>
+        <v>15.04</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2934.66</v>
+        <v>2934.33</v>
       </c>
       <c r="N5" t="n">
-        <v>3165.09</v>
+        <v>3164.96</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1116,7 +1116,6 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
-・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -1132,22 +1131,22 @@
         <v>3021</v>
       </c>
       <c r="X5" t="n">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.66</v>
+        <v>-0.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>39533</v>
+        <v>39208</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>2434</v>
+        <v>2109</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.56</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="6">
@@ -1168,22 +1167,22 @@
         <v>4795</v>
       </c>
       <c r="E6" t="n">
-        <v>4968</v>
+        <v>4944</v>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>59.2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.29</v>
+        <v>1.81</v>
       </c>
       <c r="H6" t="n">
-        <v>0.51</v>
+        <v>0.88</v>
       </c>
       <c r="I6" t="n">
-        <v>60.42</v>
+        <v>58.51</v>
       </c>
       <c r="J6" t="n">
-        <v>59.58</v>
+        <v>59.2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1196,10 +1195,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4717.35</v>
+        <v>4717.03</v>
       </c>
       <c r="N6" t="n">
-        <v>4670.4</v>
+        <v>4670.28</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1212,7 +1211,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1228,7 +1227,7 @@
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
-・MACDは買いシグナルです。
+・MACDは売りシグナルです。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
@@ -1238,29 +1237,29 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>4910</v>
       </c>
       <c r="X6" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z6" t="n">
-        <v>24840</v>
+        <v>24720</v>
       </c>
       <c r="AA6" t="n">
         <v>23975</v>
       </c>
       <c r="AB6" t="n">
-        <v>865</v>
+        <v>745</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.61</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="7">
@@ -1281,22 +1280,22 @@
         <v>7993</v>
       </c>
       <c r="E7" t="n">
-        <v>8131</v>
+        <v>8126</v>
       </c>
       <c r="F7" t="n">
-        <v>35.1</v>
+        <v>34.9</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.95</v>
+        <v>-6.01</v>
       </c>
       <c r="H7" t="n">
-        <v>0.29</v>
+        <v>0.49</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.08</v>
+        <v>-4.48</v>
       </c>
       <c r="J7" t="n">
-        <v>127.86</v>
+        <v>127.78</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1309,10 +1308,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>7741.79</v>
+        <v>7741.72</v>
       </c>
       <c r="N7" t="n">
-        <v>8723.540000000001</v>
+        <v>8723.52</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1357,22 +1356,22 @@
         <v>8118</v>
       </c>
       <c r="X7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>8131</v>
+        <v>8126</v>
       </c>
       <c r="AA7" t="n">
         <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="8">
@@ -1393,22 +1392,22 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>9157</v>
+        <v>9364</v>
       </c>
       <c r="F8" t="n">
-        <v>52.9</v>
+        <v>55.1</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.24</v>
+        <v>-1.14</v>
       </c>
       <c r="H8" t="n">
-        <v>0.54</v>
+        <v>0.93</v>
       </c>
       <c r="I8" t="n">
-        <v>-441.99</v>
+        <v>-425.48</v>
       </c>
       <c r="J8" t="n">
-        <v>-560.9</v>
+        <v>-557.6</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1421,10 +1420,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>13051.09</v>
+        <v>13053.85</v>
       </c>
       <c r="N8" t="n">
-        <v>7923.97</v>
+        <v>7925</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1470,22 +1469,22 @@
         <v>9197</v>
       </c>
       <c r="X8" t="n">
-        <v>-40</v>
+        <v>167</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.43</v>
+        <v>1.82</v>
       </c>
       <c r="Z8" t="n">
-        <v>9157</v>
+        <v>9364</v>
       </c>
       <c r="AA8" t="n">
         <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-843</v>
+        <v>-636</v>
       </c>
       <c r="AC8" t="n">
-        <v>-8.43</v>
+        <v>-6.36</v>
       </c>
     </row>
     <row r="9">
@@ -1506,22 +1505,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>49690</v>
+        <v>50780</v>
       </c>
       <c r="F9" t="n">
-        <v>45.4</v>
+        <v>47.1</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.64</v>
+        <v>-4.67</v>
       </c>
       <c r="H9" t="n">
-        <v>0.59</v>
+        <v>0.96</v>
       </c>
       <c r="I9" t="n">
-        <v>-754.13</v>
+        <v>-667.1799999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-768.36</v>
+        <v>-750.97</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1530,14 +1529,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>65866.8</v>
+        <v>65881.33</v>
       </c>
       <c r="N9" t="n">
-        <v>39790.11</v>
+        <v>39795.57</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1546,11 +1545,11 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟠 利益確定検討</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1569,7 +1568,7 @@
 ・MACDは買いシグナルです。
 ・デッドクロスが発生し、短期的な下落に注意が必要です。
 ・RSIは良好な水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
@@ -1577,29 +1576,29 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>押し目、デッドクロス、-1σ、MACD買い、反発局面</t>
+          <t>押し目、デッドクロス、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
         <v>51750</v>
       </c>
       <c r="X9" t="n">
-        <v>-2060</v>
+        <v>-970</v>
       </c>
       <c r="Y9" t="n">
-        <v>-3.98</v>
+        <v>-1.87</v>
       </c>
       <c r="Z9" t="n">
-        <v>49690</v>
+        <v>50780</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-5820</v>
+        <v>-4730</v>
       </c>
       <c r="AC9" t="n">
-        <v>-10.48</v>
+        <v>-8.52</v>
       </c>
     </row>
     <row r="10">
@@ -1725,7 +1724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1430"/>
+  <dimension ref="A1:C1439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23177,6 +23176,141 @@
         </is>
       </c>
       <c r="C1430" t="n">
+        <v>35.64</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1431" t="n">
+        <v>3310</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1432" t="n">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1433" t="n">
+        <v>177.1</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1434" t="n">
+        <v>3016</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1435" t="n">
+        <v>4944</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1436" t="n">
+        <v>8126</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1437" t="n">
+        <v>9364</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1438" t="n">
+        <v>50780</v>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1439" t="n">
         <v>35.64</v>
       </c>
     </row>
@@ -23191,7 +23325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F245"/>
+  <dimension ref="A1:F246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27565,19 +27699,29 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
+      <c r="A243" t="inlineStr"/>
+      <c r="B243" s="1" t="n">
+        <v>46281.75</v>
+      </c>
+      <c r="C243" t="n">
+        <v>210784</v>
+      </c>
+      <c r="D243" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E243" t="n">
+        <v>1494</v>
+      </c>
+      <c r="F243" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr"/>
-      <c r="C243" t="inlineStr"/>
-      <c r="D243" t="inlineStr"/>
-      <c r="E243" t="inlineStr"/>
-      <c r="F243" t="inlineStr"/>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr"/>
       <c r="B244" t="inlineStr"/>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr"/>
@@ -27585,16 +27729,24 @@
       <c r="F244" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A245" t="inlineStr"/>
       <c r="B245" t="inlineStr"/>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr"/>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27759,31 +27911,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1001</v>
+        <v>977</v>
       </c>
       <c r="F2" t="n">
-        <v>-18</v>
+        <v>-24</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.77</v>
+        <v>-2.4</v>
       </c>
       <c r="H2" t="n">
-        <v>463200</v>
+        <v>335300</v>
       </c>
       <c r="I2" t="n">
-        <v>56.2</v>
+        <v>49.8</v>
       </c>
       <c r="J2" t="n">
-        <v>1.78</v>
+        <v>-1.21</v>
       </c>
       <c r="K2" t="n">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
       <c r="L2" t="n">
-        <v>37.37</v>
+        <v>31.49</v>
       </c>
       <c r="M2" t="n">
-        <v>44.87</v>
+        <v>42.19</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -27796,10 +27948,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>840.8</v>
+        <v>844.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>1121.16</v>
+        <v>1119.47</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -27807,16 +27959,16 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -27834,7 +27986,7 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>⚪ 様子見（押し目ではない）</t>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -27860,31 +28012,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3340</v>
+        <v>3285</v>
       </c>
       <c r="F3" t="n">
-        <v>-5</v>
+        <v>-55</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.15</v>
+        <v>-1.65</v>
       </c>
       <c r="H3" t="n">
-        <v>317100</v>
+        <v>72200</v>
       </c>
       <c r="I3" t="n">
-        <v>46.4</v>
+        <v>39.5</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.39</v>
+        <v>-4</v>
       </c>
       <c r="K3" t="n">
-        <v>2.53</v>
+        <v>0.58</v>
       </c>
       <c r="L3" t="n">
-        <v>30.16</v>
+        <v>18.99</v>
       </c>
       <c r="M3" t="n">
-        <v>73.70999999999999</v>
+        <v>62.77</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -27897,10 +28049,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3007.49</v>
+        <v>3018.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2717.85</v>
+        <v>2720.5</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -27908,7 +28060,7 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -27925,8 +28077,6 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・出来高が急増しています。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -27962,31 +28112,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1346</v>
+        <v>1334</v>
       </c>
       <c r="F4" t="n">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.66</v>
+        <v>-0.89</v>
       </c>
       <c r="H4" t="n">
-        <v>4100</v>
+        <v>3600</v>
       </c>
       <c r="I4" t="n">
-        <v>64.7</v>
+        <v>62.3</v>
       </c>
       <c r="J4" t="n">
-        <v>4.64</v>
+        <v>3.14</v>
       </c>
       <c r="K4" t="n">
-        <v>0.49</v>
+        <v>0.59</v>
       </c>
       <c r="L4" t="n">
-        <v>39.98</v>
+        <v>36.84</v>
       </c>
       <c r="M4" t="n">
-        <v>41.93</v>
+        <v>40.91</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -27999,10 +28149,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1203.97</v>
+        <v>1205.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1641.37</v>
+        <v>1640.76</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -28062,35 +28212,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3475</v>
+        <v>3480</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.29</v>
+        <v>0.14</v>
       </c>
       <c r="H5" t="n">
-        <v>9400</v>
+        <v>4200</v>
       </c>
       <c r="I5" t="n">
-        <v>58.1</v>
+        <v>58.6</v>
       </c>
       <c r="J5" t="n">
-        <v>0.65</v>
+        <v>0.76</v>
       </c>
       <c r="K5" t="n">
-        <v>0.68</v>
+        <v>0.38</v>
       </c>
       <c r="L5" t="n">
-        <v>9.44</v>
+        <v>10.03</v>
       </c>
       <c r="M5" t="n">
-        <v>9.210000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -28099,10 +28249,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3428.8</v>
+        <v>3425</v>
       </c>
       <c r="Q5" t="n">
-        <v>3143.66</v>
+        <v>3147.73</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -28127,7 +28277,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
@@ -28164,31 +28314,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1550</v>
+        <v>1524</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>-26</v>
       </c>
       <c r="G6" t="n">
-        <v>0.13</v>
+        <v>-1.68</v>
       </c>
       <c r="H6" t="n">
-        <v>60700</v>
+        <v>15500</v>
       </c>
       <c r="I6" t="n">
-        <v>54</v>
+        <v>48.4</v>
       </c>
       <c r="J6" t="n">
-        <v>0.13</v>
+        <v>-1.52</v>
       </c>
       <c r="K6" t="n">
-        <v>0.73</v>
+        <v>0.22</v>
       </c>
       <c r="L6" t="n">
-        <v>-28.93</v>
+        <v>-28.32</v>
       </c>
       <c r="M6" t="n">
-        <v>-37.61</v>
+        <v>-35.75</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -28201,10 +28351,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1686.44</v>
+        <v>1682.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>1701.28</v>
+        <v>1699.27</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -28212,16 +28362,16 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -28265,31 +28415,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F7" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.38</v>
+        <v>-0.19</v>
       </c>
       <c r="H7" t="n">
-        <v>7900</v>
+        <v>5900</v>
       </c>
       <c r="I7" t="n">
-        <v>48.5</v>
+        <v>53.3</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.25</v>
+        <v>-1.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="L7" t="n">
-        <v>-6.74</v>
+        <v>-6.46</v>
       </c>
       <c r="M7" t="n">
-        <v>-7.73</v>
+        <v>-7.48</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -28302,10 +28452,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>537.26</v>
+        <v>537.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>584.03</v>
+        <v>583.08</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -28313,16 +28463,16 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -28366,31 +28516,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1076</v>
+        <v>1060</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-1.49</v>
       </c>
       <c r="H8" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="I8" t="n">
-        <v>32.4</v>
+        <v>32.1</v>
       </c>
       <c r="J8" t="n">
-        <v>-5.1</v>
+        <v>-6.34</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08</v>
+        <v>0.28</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.1</v>
+        <v>-8.24</v>
       </c>
       <c r="M8" t="n">
-        <v>5.77</v>
+        <v>2.97</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -28403,10 +28553,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1054.16</v>
+        <v>1054.59</v>
       </c>
       <c r="Q8" t="n">
-        <v>1021.89</v>
+        <v>1020.65</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -28466,31 +28616,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1558</v>
+        <v>1550</v>
       </c>
       <c r="F9" t="n">
-        <v>-23</v>
+        <v>-8</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.45</v>
+        <v>-0.51</v>
       </c>
       <c r="H9" t="n">
-        <v>89000</v>
+        <v>16200</v>
       </c>
       <c r="I9" t="n">
-        <v>35.2</v>
+        <v>35.7</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.31</v>
+        <v>-4.02</v>
       </c>
       <c r="K9" t="n">
-        <v>1.49</v>
+        <v>0.32</v>
       </c>
       <c r="L9" t="n">
-        <v>11.65</v>
+        <v>8.1</v>
       </c>
       <c r="M9" t="n">
-        <v>29.85</v>
+        <v>25.5</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -28503,10 +28653,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1449.23</v>
+        <v>1451.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>1379.61</v>
+        <v>1380.72</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -28566,31 +28716,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>987</v>
+        <v>949</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-38</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-3.85</v>
       </c>
       <c r="H10" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="I10" t="n">
-        <v>66.40000000000001</v>
+        <v>31.7</v>
       </c>
       <c r="J10" t="n">
-        <v>2.66</v>
+        <v>-1.32</v>
       </c>
       <c r="K10" t="n">
-        <v>0.62</v>
+        <v>0.47</v>
       </c>
       <c r="L10" t="n">
-        <v>20.75</v>
+        <v>16.87</v>
       </c>
       <c r="M10" t="n">
-        <v>23.93</v>
+        <v>22.52</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -28603,10 +28753,10 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>871.96</v>
+        <v>874.49</v>
       </c>
       <c r="Q10" t="n">
-        <v>986.41</v>
+        <v>986.46</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -28614,16 +28764,16 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -28640,7 +28790,7 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>⚪ 様子見（押し目ではない）</t>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -28666,31 +28816,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3531</v>
+        <v>3565</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="G11" t="n">
-        <v>0.31</v>
+        <v>0.96</v>
       </c>
       <c r="H11" t="n">
-        <v>3497900</v>
+        <v>900300</v>
       </c>
       <c r="I11" t="n">
-        <v>42.4</v>
+        <v>43.3</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.37</v>
+        <v>-1.19</v>
       </c>
       <c r="K11" t="n">
-        <v>0.66</v>
+        <v>0.21</v>
       </c>
       <c r="L11" t="n">
-        <v>-51.61</v>
+        <v>-44.98</v>
       </c>
       <c r="M11" t="n">
-        <v>-49.51</v>
+        <v>-48.6</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -28703,10 +28853,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3662.43</v>
+        <v>3662.79</v>
       </c>
       <c r="Q11" t="n">
-        <v>2926.46</v>
+        <v>2934.22</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -28714,23 +28864,23 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
-・MACDは売りシグナルです。
+・MACDは買いシグナルです。
 ・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
@@ -28743,7 +28893,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>あと44日</t>
+          <t>あと43日</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -28770,35 +28920,35 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>3580</v>
+        <v>3520</v>
       </c>
       <c r="F12" t="n">
-        <v>-25</v>
+        <v>-60</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.68</v>
       </c>
       <c r="H12" t="n">
-        <v>642300</v>
+        <v>244600</v>
       </c>
       <c r="I12" t="n">
-        <v>51.5</v>
+        <v>45.3</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.15</v>
+        <v>-4.86</v>
       </c>
       <c r="K12" t="n">
-        <v>0.91</v>
+        <v>0.39</v>
       </c>
       <c r="L12" t="n">
-        <v>67.70999999999999</v>
+        <v>51.03</v>
       </c>
       <c r="M12" t="n">
-        <v>100.35</v>
+        <v>90.48</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -28807,10 +28957,10 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3201.11</v>
+        <v>3208.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>3054.18</v>
+        <v>3056.68</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -28818,7 +28968,7 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -28835,7 +28985,6 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
@@ -28846,7 +28995,7 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>🟡 調整中押し目（段階的買い足し検討）</t>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -28868,31 +29017,31 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>4744</v>
+        <v>4797</v>
       </c>
       <c r="F13" t="n">
-        <v>-90</v>
+        <v>53</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.86</v>
+        <v>1.12</v>
       </c>
       <c r="H13" t="n">
-        <v>31474800</v>
+        <v>15031600</v>
       </c>
       <c r="I13" t="n">
-        <v>39.5</v>
+        <v>36.1</v>
       </c>
       <c r="J13" t="n">
-        <v>-10.89</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.83</v>
+        <v>0.48</v>
       </c>
       <c r="L13" t="n">
-        <v>-52.66</v>
+        <v>-71.67</v>
       </c>
       <c r="M13" t="n">
-        <v>14.39</v>
+        <v>-2.82</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -28905,10 +29054,10 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5062.55</v>
+        <v>5064.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>4475.51</v>
+        <v>4483.83</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -28916,16 +29065,16 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -28933,7 +29082,6 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは売りシグナルです。
-・25日線から大きく下に乖離しています。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
@@ -28946,7 +29094,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>あと56日</t>
+          <t>あと55日</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -28980,28 +29128,28 @@
         <v>1069</v>
       </c>
       <c r="F14" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.37</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>164200</v>
+        <v>65500</v>
       </c>
       <c r="I14" t="n">
-        <v>25.7</v>
+        <v>24.8</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.55</v>
+        <v>-6.4</v>
       </c>
       <c r="K14" t="n">
-        <v>0.59</v>
+        <v>0.32</v>
       </c>
       <c r="L14" t="n">
-        <v>-17.62</v>
+        <v>-19.12</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.2</v>
+        <v>-7.19</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -29014,10 +29162,10 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1108.04</v>
+        <v>1109.72</v>
       </c>
       <c r="Q14" t="n">
-        <v>925.79</v>
+        <v>927.34</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -29078,47 +29226,47 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3719</v>
+        <v>3747</v>
       </c>
       <c r="F15" t="n">
-        <v>-126</v>
+        <v>28</v>
       </c>
       <c r="G15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H15" t="n">
+        <v>9251200</v>
+      </c>
+      <c r="I15" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-4.26</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L15" t="n">
         <v>-3.28</v>
       </c>
-      <c r="H15" t="n">
-        <v>22958800</v>
-      </c>
-      <c r="I15" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-5.44</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L15" t="n">
-        <v>6.95</v>
-      </c>
       <c r="M15" t="n">
-        <v>17.06</v>
+        <v>13</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>4039.35</v>
+        <v>4019.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>3153.13</v>
+        <v>3166.95</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -29126,16 +29274,16 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -29143,9 +29291,8 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは売りシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
-・RSIは良好な水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
+・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
@@ -29157,12 +29304,12 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>あと55日</t>
+          <t>あと54日</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
+          <t>🟡 調整中押し目（段階的買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -29184,31 +29331,31 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>3875</v>
+        <v>3880</v>
       </c>
       <c r="F16" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>1.17</v>
+        <v>0.13</v>
       </c>
       <c r="H16" t="n">
-        <v>14200</v>
+        <v>10500</v>
       </c>
       <c r="I16" t="n">
-        <v>39.6</v>
+        <v>32.3</v>
       </c>
       <c r="J16" t="n">
-        <v>-6.14</v>
+        <v>-5.52</v>
       </c>
       <c r="K16" t="n">
-        <v>0.86</v>
+        <v>0.7</v>
       </c>
       <c r="L16" t="n">
-        <v>31.53</v>
+        <v>20.03</v>
       </c>
       <c r="M16" t="n">
-        <v>93.8</v>
+        <v>79.05</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -29221,10 +29368,10 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3553.83</v>
+        <v>3565.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>2829.27</v>
+        <v>2838.81</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -29280,31 +29427,31 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>2372</v>
+        <v>2401</v>
       </c>
       <c r="F17" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="G17" t="n">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="H17" t="n">
-        <v>17581900</v>
+        <v>6360500</v>
       </c>
       <c r="I17" t="n">
-        <v>33.9</v>
+        <v>31.4</v>
       </c>
       <c r="J17" t="n">
-        <v>-7.68</v>
+        <v>-6.01</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4</v>
+        <v>0.54</v>
       </c>
       <c r="L17" t="n">
-        <v>-102.33</v>
+        <v>-97.03</v>
       </c>
       <c r="M17" t="n">
-        <v>-91.64</v>
+        <v>-92.72</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -29313,14 +29460,14 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2753.21</v>
+        <v>2745.77</v>
       </c>
       <c r="Q17" t="n">
-        <v>2826.14</v>
+        <v>2827.97</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -29328,7 +29475,7 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -29345,7 +29492,7 @@
           <t>【AI分析レポート】
 ・🔴 下降
 ・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド中心付近で推移しています。
 ⚠️ 下落トレンドです。
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
@@ -29357,7 +29504,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>あと57日</t>
+          <t>あと56日</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -29388,31 +29535,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3021</v>
+        <v>3041</v>
       </c>
       <c r="F18" t="n">
-        <v>-4</v>
+        <v>20</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.13</v>
+        <v>0.66</v>
       </c>
       <c r="H18" t="n">
-        <v>19958900</v>
+        <v>7787000</v>
       </c>
       <c r="I18" t="n">
-        <v>45.5</v>
+        <v>46.8</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.26</v>
+        <v>-0.66</v>
       </c>
       <c r="K18" t="n">
-        <v>0.88</v>
+        <v>0.4</v>
       </c>
       <c r="L18" t="n">
-        <v>2.67</v>
+        <v>2.34</v>
       </c>
       <c r="M18" t="n">
-        <v>18.71</v>
+        <v>15.44</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -29425,10 +29572,10 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2932.85</v>
+        <v>2934.66</v>
       </c>
       <c r="Q18" t="n">
-        <v>3164.88</v>
+        <v>3165.09</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -29466,7 +29613,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>あと51日</t>
+          <t>あと50日</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -29493,31 +29640,31 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>1770</v>
+        <v>1781</v>
       </c>
       <c r="F19" t="n">
-        <v>-40.5</v>
+        <v>10.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.24</v>
+        <v>0.59</v>
       </c>
       <c r="H19" t="n">
-        <v>8412000</v>
+        <v>2720000</v>
       </c>
       <c r="I19" t="n">
-        <v>50.9</v>
+        <v>53.6</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.85</v>
+        <v>-0.26</v>
       </c>
       <c r="K19" t="n">
-        <v>0.88</v>
+        <v>0.34</v>
       </c>
       <c r="L19" t="n">
-        <v>28.84</v>
+        <v>24.65</v>
       </c>
       <c r="M19" t="n">
-        <v>36.74</v>
+        <v>34.32</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -29530,10 +29677,10 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1673.85</v>
+        <v>1674.32</v>
       </c>
       <c r="Q19" t="n">
-        <v>1561.07</v>
+        <v>1564.14</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -29571,7 +29718,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>あと44日</t>
+          <t>あと43日</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -29602,35 +29749,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="H20" t="n">
-        <v>1809000</v>
+        <v>184900</v>
       </c>
       <c r="I20" t="n">
-        <v>53.9</v>
+        <v>49.4</v>
       </c>
       <c r="J20" t="n">
-        <v>2.75</v>
+        <v>3.21</v>
       </c>
       <c r="K20" t="n">
-        <v>1.71</v>
+        <v>0.22</v>
       </c>
       <c r="L20" t="n">
-        <v>4.64</v>
+        <v>5.31</v>
       </c>
       <c r="M20" t="n">
-        <v>6.25</v>
+        <v>6.06</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -29639,10 +29786,10 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>432.76</v>
+        <v>433.13</v>
       </c>
       <c r="Q20" t="n">
-        <v>412.08</v>
+        <v>412.71</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -29650,7 +29797,7 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -29667,8 +29814,8 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・RSIは良好な水準です。
-・出来高が増加しています。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -29700,31 +29847,31 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>9197</v>
+        <v>9157</v>
       </c>
       <c r="F21" t="n">
-        <v>483</v>
+        <v>-40</v>
       </c>
       <c r="G21" t="n">
-        <v>5.54</v>
+        <v>-0.43</v>
       </c>
       <c r="H21" t="n">
-        <v>34475900</v>
+        <v>15334100</v>
       </c>
       <c r="I21" t="n">
-        <v>51.5</v>
+        <v>52.9</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.27</v>
+        <v>-3.24</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1</v>
+        <v>0.54</v>
       </c>
       <c r="L21" t="n">
-        <v>-473.58</v>
+        <v>-441.99</v>
       </c>
       <c r="M21" t="n">
-        <v>-590.63</v>
+        <v>-560.9</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -29737,10 +29884,10 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>13143.13</v>
+        <v>13051.09</v>
       </c>
       <c r="Q21" t="n">
-        <v>7894.33</v>
+        <v>7923.97</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -29778,7 +29925,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>あと51日</t>
+          <t>あと50日</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -29801,47 +29948,47 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>51750</v>
+        <v>49690</v>
       </c>
       <c r="F22" t="n">
-        <v>1160</v>
+        <v>-2060</v>
       </c>
       <c r="G22" t="n">
-        <v>2.29</v>
+        <v>-3.98</v>
       </c>
       <c r="H22" t="n">
-        <v>29060500</v>
+        <v>15179600</v>
       </c>
       <c r="I22" t="n">
-        <v>52.8</v>
+        <v>45.4</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.78</v>
+        <v>-6.64</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0.59</v>
       </c>
       <c r="L22" t="n">
-        <v>-469.9</v>
+        <v>-754.13</v>
       </c>
       <c r="M22" t="n">
-        <v>-771.92</v>
+        <v>-768.36</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>66170.92999999999</v>
+        <v>65866.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>39598.34</v>
+        <v>39790.11</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -29849,16 +29996,16 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -29866,8 +30013,9 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
@@ -29879,12 +30027,12 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>あと45日</t>
+          <t>あと44日</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
+          <t>🟡 調整中押し目（段階的買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -29902,31 +30050,31 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>163</v>
+        <v>161.4</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8</v>
+        <v>-1.6</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.49</v>
+        <v>-0.98</v>
       </c>
       <c r="H23" t="n">
-        <v>48347000</v>
+        <v>22479800</v>
       </c>
       <c r="I23" t="n">
-        <v>50.4</v>
+        <v>48.5</v>
       </c>
       <c r="J23" t="n">
-        <v>1.94</v>
+        <v>0.76</v>
       </c>
       <c r="K23" t="n">
-        <v>0.95</v>
+        <v>0.51</v>
       </c>
       <c r="L23" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="M23" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -29939,10 +30087,10 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>152.03</v>
+        <v>152.33</v>
       </c>
       <c r="Q23" t="n">
-        <v>150.53</v>
+        <v>150.63</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -29950,16 +30098,16 @@
         </is>
       </c>
       <c r="S23" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -29980,7 +30128,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>あと58日</t>
+          <t>あと57日</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -30003,31 +30151,31 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>3155</v>
+        <v>3187</v>
       </c>
       <c r="F24" t="n">
-        <v>-21</v>
+        <v>32</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.66</v>
+        <v>1.01</v>
       </c>
       <c r="H24" t="n">
-        <v>7596000</v>
+        <v>2775400</v>
       </c>
       <c r="I24" t="n">
-        <v>36.9</v>
+        <v>38.7</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.93</v>
+        <v>-6.32</v>
       </c>
       <c r="K24" t="n">
-        <v>0.86</v>
+        <v>0.37</v>
       </c>
       <c r="L24" t="n">
-        <v>-148.83</v>
+        <v>-145.48</v>
       </c>
       <c r="M24" t="n">
-        <v>-154.58</v>
+        <v>-152.76</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -30040,37 +30188,37 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>4037.39</v>
+        <v>4020.99</v>
       </c>
       <c r="Q24" t="n">
-        <v>3179.52</v>
+        <v>3186.34</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>🔴 下降</t>
+          <t>🟡 反発中</t>
         </is>
       </c>
       <c r="S24" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🔴 下降
+・🟡 反発中
 ・MACDは買いシグナルです。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -30080,12 +30228,12 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>あと43日</t>
+          <t>あと42日</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -30112,7 +30260,7 @@
         <v>1.95</v>
       </c>
       <c r="H25" t="n">
-        <v>1000313</v>
+        <v>1018600</v>
       </c>
       <c r="I25" t="n">
         <v>43.5</v>
@@ -30121,7 +30269,7 @@
         <v>-9.67</v>
       </c>
       <c r="K25" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="L25" t="n">
         <v>-2.17</v>
@@ -30175,12 +30323,12 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>2026/10/13</t>
+          <t>2026/10/06</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>あと28日</t>
+          <t>あと20日</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -30203,31 +30351,31 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>8118</v>
+        <v>8131</v>
       </c>
       <c r="F26" t="n">
-        <v>-150</v>
+        <v>13</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.81</v>
+        <v>0.16</v>
       </c>
       <c r="H26" t="n">
-        <v>7686000</v>
+        <v>2557900</v>
       </c>
       <c r="I26" t="n">
-        <v>31.9</v>
+        <v>35.1</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.26</v>
+        <v>-5.95</v>
       </c>
       <c r="K26" t="n">
-        <v>0.74</v>
+        <v>0.29</v>
       </c>
       <c r="L26" t="n">
-        <v>21.9</v>
+        <v>-4.08</v>
       </c>
       <c r="M26" t="n">
-        <v>160.85</v>
+        <v>127.86</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -30240,10 +30388,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7728.88</v>
+        <v>7741.79</v>
       </c>
       <c r="Q26" t="n">
-        <v>8747.99</v>
+        <v>8723.540000000001</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -30280,7 +30428,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>あと49日</t>
+          <t>あと48日</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>210,784円</t>
+          <t>210,785円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1,494円</t>
+          <t>1,495円</t>
         </is>
       </c>
     </row>
@@ -1619,38 +1619,38 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>35.64</v>
+        <v>36.85</v>
       </c>
       <c r="F10" t="n">
-        <v>42.1</v>
+        <v>48.5</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.04</v>
+        <v>-2.36</v>
       </c>
       <c r="H10" t="n">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="I10" t="n">
-        <v>1.13</v>
+        <v>0.98</v>
       </c>
       <c r="J10" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.62</v>
+        <v>33.49</v>
       </c>
       <c r="N10" t="n">
-        <v>31.52</v>
+        <v>31.54</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1659,20 +1659,20 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟠 利益確定検討</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1680,7 +1680,9 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -1688,29 +1690,29 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、長期上昇</t>
+          <t>押し目、デッドクロス、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>36.74</v>
+        <v>35.64</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1</v>
+        <v>1.21</v>
       </c>
       <c r="Y10" t="n">
-        <v>-2.99</v>
+        <v>3.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6077</v>
+        <v>-6076</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.42</v>
+        <v>-99.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1724,7 +1726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1439"/>
+  <dimension ref="A1:C1448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23312,6 +23314,141 @@
       </c>
       <c r="C1439" t="n">
         <v>35.64</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1440" t="n">
+        <v>3310</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1441" t="n">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1442" t="n">
+        <v>177.1</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1443" t="n">
+        <v>3016</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1444" t="n">
+        <v>4944</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1445" t="n">
+        <v>8126</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1446" t="n">
+        <v>9364</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1447" t="n">
+        <v>50780</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1448" t="n">
+        <v>36.85</v>
       </c>
     </row>
   </sheetData>
@@ -23325,7 +23462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F246"/>
+  <dimension ref="A1:F247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27717,19 +27854,29 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
+      <c r="A244" t="inlineStr"/>
+      <c r="B244" s="1" t="n">
+        <v>46282.29166666666</v>
+      </c>
+      <c r="C244" t="n">
+        <v>210785</v>
+      </c>
+      <c r="D244" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E244" t="n">
+        <v>1495</v>
+      </c>
+      <c r="F244" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr"/>
-      <c r="C244" t="inlineStr"/>
-      <c r="D244" t="inlineStr"/>
-      <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr"/>
       <c r="B245" t="inlineStr"/>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr"/>
@@ -27737,16 +27884,24 @@
       <c r="F245" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A246" t="inlineStr"/>
       <c r="B246" t="inlineStr"/>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27911,31 +28066,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>977</v>
+        <v>991</v>
       </c>
       <c r="F2" t="n">
-        <v>-24</v>
+        <v>-10</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.4</v>
+        <v>-1</v>
       </c>
       <c r="H2" t="n">
-        <v>335300</v>
+        <v>595200</v>
       </c>
       <c r="I2" t="n">
-        <v>49.8</v>
+        <v>51.5</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.21</v>
+        <v>0.15</v>
       </c>
       <c r="K2" t="n">
-        <v>0.51</v>
+        <v>0.83</v>
       </c>
       <c r="L2" t="n">
-        <v>31.49</v>
+        <v>32.61</v>
       </c>
       <c r="M2" t="n">
-        <v>42.19</v>
+        <v>42.41</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -27948,10 +28103,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>844.84</v>
+        <v>845.03</v>
       </c>
       <c r="Q2" t="n">
-        <v>1119.47</v>
+        <v>1119.55</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -27959,16 +28114,16 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -27986,7 +28141,7 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
+          <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
@@ -28012,31 +28167,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3285</v>
+        <v>3310</v>
       </c>
       <c r="F3" t="n">
-        <v>-55</v>
+        <v>-30</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.65</v>
+        <v>-0.9</v>
       </c>
       <c r="H3" t="n">
-        <v>72200</v>
+        <v>122400</v>
       </c>
       <c r="I3" t="n">
-        <v>39.5</v>
+        <v>40.3</v>
       </c>
       <c r="J3" t="n">
-        <v>-4</v>
+        <v>-3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>0.58</v>
+        <v>0.92</v>
       </c>
       <c r="L3" t="n">
-        <v>18.99</v>
+        <v>20.98</v>
       </c>
       <c r="M3" t="n">
-        <v>62.77</v>
+        <v>63.17</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -28049,10 +28204,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3018.6</v>
+        <v>3018.93</v>
       </c>
       <c r="Q3" t="n">
-        <v>2720.5</v>
+        <v>2720.63</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -28112,31 +28267,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1334</v>
+        <v>1325</v>
       </c>
       <c r="F4" t="n">
-        <v>-12</v>
+        <v>-21</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.89</v>
+        <v>-1.56</v>
       </c>
       <c r="H4" t="n">
-        <v>3600</v>
+        <v>11800</v>
       </c>
       <c r="I4" t="n">
-        <v>62.3</v>
+        <v>61</v>
       </c>
       <c r="J4" t="n">
-        <v>3.14</v>
+        <v>2.47</v>
       </c>
       <c r="K4" t="n">
-        <v>0.59</v>
+        <v>1.53</v>
       </c>
       <c r="L4" t="n">
-        <v>36.84</v>
+        <v>36.12</v>
       </c>
       <c r="M4" t="n">
-        <v>40.91</v>
+        <v>40.77</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -28149,10 +28304,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1205.08</v>
+        <v>1204.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>1640.76</v>
+        <v>1640.72</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -28160,16 +28315,16 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -28177,6 +28332,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
+・出来高が増加しています。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -28212,35 +28368,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3480</v>
+        <v>3430</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>-45</v>
       </c>
       <c r="G5" t="n">
-        <v>0.14</v>
+        <v>-1.29</v>
       </c>
       <c r="H5" t="n">
-        <v>4200</v>
+        <v>12000</v>
       </c>
       <c r="I5" t="n">
-        <v>58.6</v>
+        <v>55.9</v>
       </c>
       <c r="J5" t="n">
-        <v>0.76</v>
+        <v>-0.63</v>
       </c>
       <c r="K5" t="n">
-        <v>0.38</v>
+        <v>0.95</v>
       </c>
       <c r="L5" t="n">
-        <v>10.03</v>
+        <v>6.04</v>
       </c>
       <c r="M5" t="n">
-        <v>9.380000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -28249,10 +28405,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3425</v>
+        <v>3424.33</v>
       </c>
       <c r="Q5" t="n">
-        <v>3147.73</v>
+        <v>3147.48</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -28260,24 +28416,23 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
-・MACDは買いシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
+・MACDは売りシグナルです。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
@@ -28288,7 +28443,7 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>⚪ 様子見（押し目ではない）</t>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -28314,31 +28469,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1524</v>
+        <v>1544</v>
       </c>
       <c r="F6" t="n">
-        <v>-26</v>
+        <v>-6</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.68</v>
+        <v>-0.39</v>
       </c>
       <c r="H6" t="n">
-        <v>15500</v>
+        <v>31800</v>
       </c>
       <c r="I6" t="n">
-        <v>48.4</v>
+        <v>51.4</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.52</v>
+        <v>-0.28</v>
       </c>
       <c r="K6" t="n">
-        <v>0.22</v>
+        <v>0.43</v>
       </c>
       <c r="L6" t="n">
-        <v>-28.32</v>
+        <v>-26.73</v>
       </c>
       <c r="M6" t="n">
-        <v>-35.75</v>
+        <v>-35.43</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -28351,10 +28506,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1682.81</v>
+        <v>1683.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1699.27</v>
+        <v>1699.37</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -28362,16 +28517,16 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -28415,31 +28570,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F7" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.19</v>
+        <v>-0.38</v>
       </c>
       <c r="H7" t="n">
-        <v>5900</v>
+        <v>15800</v>
       </c>
       <c r="I7" t="n">
-        <v>53.3</v>
+        <v>51.6</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.1</v>
+        <v>-1.28</v>
       </c>
       <c r="K7" t="n">
-        <v>0.97</v>
+        <v>1.96</v>
       </c>
       <c r="L7" t="n">
-        <v>-6.46</v>
+        <v>-6.54</v>
       </c>
       <c r="M7" t="n">
-        <v>-7.48</v>
+        <v>-7.49</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -28452,10 +28607,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>537.45</v>
+        <v>537.4299999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>583.08</v>
+        <v>583.0700000000001</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -28463,7 +28618,7 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -28481,6 +28636,7 @@
 ・🔴 下降
 ・MACDは買いシグナルです。
 ・RSIは良好な水準です。
+・出来高が増加しています。
 ・ボリンジャーバンド中心付近で推移しています。
 ⚠️ 下落トレンドです。
 無理な買いは避け、反転サインを待ちましょう。</t>
@@ -28516,31 +28672,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1060</v>
+        <v>1079</v>
       </c>
       <c r="F8" t="n">
-        <v>-16</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.49</v>
+        <v>0.28</v>
       </c>
       <c r="H8" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="I8" t="n">
-        <v>32.1</v>
+        <v>35.5</v>
       </c>
       <c r="J8" t="n">
-        <v>-6.34</v>
+        <v>-4.72</v>
       </c>
       <c r="K8" t="n">
-        <v>0.28</v>
+        <v>0.48</v>
       </c>
       <c r="L8" t="n">
-        <v>-8.24</v>
+        <v>-6.72</v>
       </c>
       <c r="M8" t="n">
-        <v>2.97</v>
+        <v>3.27</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -28553,10 +28709,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1054.59</v>
+        <v>1054.84</v>
       </c>
       <c r="Q8" t="n">
-        <v>1020.65</v>
+        <v>1020.75</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -28616,31 +28772,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="F9" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.51</v>
+        <v>-0.45</v>
       </c>
       <c r="H9" t="n">
-        <v>16200</v>
+        <v>47100</v>
       </c>
       <c r="I9" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.02</v>
+        <v>-3.96</v>
       </c>
       <c r="K9" t="n">
-        <v>0.32</v>
+        <v>0.84</v>
       </c>
       <c r="L9" t="n">
-        <v>8.1</v>
+        <v>8.18</v>
       </c>
       <c r="M9" t="n">
-        <v>25.5</v>
+        <v>25.52</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -28653,7 +28809,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1451.53</v>
+        <v>1451.55</v>
       </c>
       <c r="Q9" t="n">
         <v>1380.72</v>
@@ -28716,31 +28872,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>949</v>
+        <v>980</v>
       </c>
       <c r="F10" t="n">
-        <v>-38</v>
+        <v>-7</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.85</v>
+        <v>-0.71</v>
       </c>
       <c r="H10" t="n">
-        <v>300</v>
+        <v>1200</v>
       </c>
       <c r="I10" t="n">
-        <v>31.7</v>
+        <v>42.1</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.32</v>
+        <v>1.77</v>
       </c>
       <c r="K10" t="n">
-        <v>0.47</v>
+        <v>1.46</v>
       </c>
       <c r="L10" t="n">
-        <v>16.87</v>
+        <v>19.34</v>
       </c>
       <c r="M10" t="n">
-        <v>22.52</v>
+        <v>23.01</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -28753,10 +28909,10 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>874.49</v>
+        <v>874.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>986.46</v>
+        <v>986.62</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -28764,16 +28920,16 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -28790,7 +28946,7 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
+          <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
@@ -28816,31 +28972,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3565</v>
+        <v>3600</v>
       </c>
       <c r="F11" t="n">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="G11" t="n">
-        <v>0.96</v>
+        <v>1.95</v>
       </c>
       <c r="H11" t="n">
-        <v>900300</v>
+        <v>3086100</v>
       </c>
       <c r="I11" t="n">
-        <v>43.3</v>
+        <v>46.3</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.19</v>
+        <v>-0.25</v>
       </c>
       <c r="K11" t="n">
-        <v>0.21</v>
+        <v>0.65</v>
       </c>
       <c r="L11" t="n">
-        <v>-44.98</v>
+        <v>-42.19</v>
       </c>
       <c r="M11" t="n">
-        <v>-48.6</v>
+        <v>-48.04</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -28853,10 +29009,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3662.79</v>
+        <v>3663.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2934.22</v>
+        <v>2934.39</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -28881,6 +29037,7 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
+・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
@@ -28929,7 +29086,7 @@
         <v>-1.68</v>
       </c>
       <c r="H12" t="n">
-        <v>244600</v>
+        <v>450300</v>
       </c>
       <c r="I12" t="n">
         <v>45.3</v>
@@ -28938,7 +29095,7 @@
         <v>-4.86</v>
       </c>
       <c r="K12" t="n">
-        <v>0.39</v>
+        <v>0.67</v>
       </c>
       <c r="L12" t="n">
         <v>51.03</v>
@@ -29017,31 +29174,31 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>4797</v>
+        <v>4839</v>
       </c>
       <c r="F13" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="G13" t="n">
-        <v>1.12</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>15031600</v>
+        <v>26196900</v>
       </c>
       <c r="I13" t="n">
-        <v>36.1</v>
+        <v>37.2</v>
       </c>
       <c r="J13" t="n">
-        <v>-9.210000000000001</v>
+        <v>-8.44</v>
       </c>
       <c r="K13" t="n">
-        <v>0.48</v>
+        <v>0.79</v>
       </c>
       <c r="L13" t="n">
-        <v>-71.67</v>
+        <v>-68.31999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.82</v>
+        <v>-2.15</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -29054,10 +29211,10 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5064.15</v>
+        <v>5064.71</v>
       </c>
       <c r="Q13" t="n">
-        <v>4483.83</v>
+        <v>4484.04</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -29125,31 +29282,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
       <c r="H14" t="n">
-        <v>65500</v>
+        <v>146100</v>
       </c>
       <c r="I14" t="n">
-        <v>24.8</v>
+        <v>24.4</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.4</v>
+        <v>-6.73</v>
       </c>
       <c r="K14" t="n">
-        <v>0.32</v>
+        <v>0.65</v>
       </c>
       <c r="L14" t="n">
-        <v>-19.12</v>
+        <v>-19.44</v>
       </c>
       <c r="M14" t="n">
-        <v>-7.19</v>
+        <v>-7.25</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -29162,10 +29319,10 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1109.72</v>
+        <v>1109.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>927.34</v>
+        <v>927.3200000000001</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -29226,31 +29383,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3747</v>
+        <v>3812</v>
       </c>
       <c r="F15" t="n">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="G15" t="n">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="H15" t="n">
-        <v>9251200</v>
+        <v>17118100</v>
       </c>
       <c r="I15" t="n">
-        <v>41.5</v>
+        <v>43.4</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.26</v>
+        <v>-2.67</v>
       </c>
       <c r="K15" t="n">
-        <v>0.46</v>
+        <v>0.79</v>
       </c>
       <c r="L15" t="n">
-        <v>-3.28</v>
+        <v>1.91</v>
       </c>
       <c r="M15" t="n">
-        <v>13</v>
+        <v>14.03</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -29263,10 +29420,10 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>4019.8</v>
+        <v>4020.67</v>
       </c>
       <c r="Q15" t="n">
-        <v>3166.95</v>
+        <v>3167.27</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -29331,31 +29488,31 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>3880</v>
+        <v>3940</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="G16" t="n">
-        <v>0.13</v>
+        <v>1.68</v>
       </c>
       <c r="H16" t="n">
-        <v>10500</v>
+        <v>34400</v>
       </c>
       <c r="I16" t="n">
-        <v>32.3</v>
+        <v>35.4</v>
       </c>
       <c r="J16" t="n">
-        <v>-5.52</v>
+        <v>-4.12</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7</v>
+        <v>1.74</v>
       </c>
       <c r="L16" t="n">
-        <v>20.03</v>
+        <v>24.81</v>
       </c>
       <c r="M16" t="n">
-        <v>79.05</v>
+        <v>80</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -29364,14 +29521,14 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3565.43</v>
+        <v>3566.23</v>
       </c>
       <c r="Q16" t="n">
-        <v>2838.81</v>
+        <v>2839.11</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -29396,7 +29553,8 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・出来高が増加しています。
+・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -29427,31 +29585,31 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>2401</v>
+        <v>2389</v>
       </c>
       <c r="F17" t="n">
-        <v>29</v>
+        <v>16.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1.22</v>
+        <v>0.7</v>
       </c>
       <c r="H17" t="n">
-        <v>6360500</v>
+        <v>11167200</v>
       </c>
       <c r="I17" t="n">
-        <v>31.4</v>
+        <v>30</v>
       </c>
       <c r="J17" t="n">
-        <v>-6.01</v>
+        <v>-6.48</v>
       </c>
       <c r="K17" t="n">
-        <v>0.54</v>
+        <v>0.88</v>
       </c>
       <c r="L17" t="n">
-        <v>-97.03</v>
+        <v>-98.03</v>
       </c>
       <c r="M17" t="n">
-        <v>-92.72</v>
+        <v>-92.92</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -29464,10 +29622,10 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2745.77</v>
+        <v>2745.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>2827.97</v>
+        <v>2827.91</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -29492,6 +29650,7 @@
           <t>【AI分析レポート】
 ・🔴 下降
 ・MACDは売りシグナルです。
+・売られ過ぎ水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 ⚠️ 下落トレンドです。
 無理な買いは避け、反転サインを待ちましょう。</t>
@@ -29535,31 +29694,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3041</v>
+        <v>3016</v>
       </c>
       <c r="F18" t="n">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="G18" t="n">
-        <v>0.66</v>
+        <v>-0.17</v>
       </c>
       <c r="H18" t="n">
-        <v>7787000</v>
+        <v>17508600</v>
       </c>
       <c r="I18" t="n">
-        <v>46.8</v>
+        <v>44.4</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.66</v>
+        <v>-1.44</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4</v>
+        <v>0.82</v>
       </c>
       <c r="L18" t="n">
-        <v>2.34</v>
+        <v>0.34</v>
       </c>
       <c r="M18" t="n">
-        <v>15.44</v>
+        <v>15.04</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -29572,10 +29731,10 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2934.66</v>
+        <v>2934.33</v>
       </c>
       <c r="Q18" t="n">
-        <v>3165.09</v>
+        <v>3164.96</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -29600,7 +29759,6 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
-・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -29640,31 +29798,31 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>1781</v>
+        <v>1786</v>
       </c>
       <c r="F19" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>0.59</v>
+        <v>0.9</v>
       </c>
       <c r="H19" t="n">
-        <v>2720000</v>
+        <v>6261600</v>
       </c>
       <c r="I19" t="n">
-        <v>53.6</v>
+        <v>54.2</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.26</v>
+        <v>0.03</v>
       </c>
       <c r="K19" t="n">
-        <v>0.34</v>
+        <v>0.71</v>
       </c>
       <c r="L19" t="n">
-        <v>24.65</v>
+        <v>25.09</v>
       </c>
       <c r="M19" t="n">
-        <v>34.32</v>
+        <v>34.41</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -29677,10 +29835,10 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1674.32</v>
+        <v>1674.39</v>
       </c>
       <c r="Q19" t="n">
-        <v>1564.14</v>
+        <v>1564.16</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -29688,16 +29846,16 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -29723,7 +29881,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
+          <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
@@ -29749,31 +29907,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0.63</v>
+        <v>0.21</v>
       </c>
       <c r="H20" t="n">
-        <v>184900</v>
+        <v>543300</v>
       </c>
       <c r="I20" t="n">
-        <v>49.4</v>
+        <v>48.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.21</v>
+        <v>2.8</v>
       </c>
       <c r="K20" t="n">
-        <v>0.22</v>
+        <v>0.6</v>
       </c>
       <c r="L20" t="n">
-        <v>5.31</v>
+        <v>5.15</v>
       </c>
       <c r="M20" t="n">
-        <v>6.06</v>
+        <v>6.03</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -29786,10 +29944,10 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>433.13</v>
+        <v>433.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>412.71</v>
+        <v>412.7</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -29847,31 +30005,31 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>9157</v>
+        <v>9364</v>
       </c>
       <c r="F21" t="n">
-        <v>-40</v>
+        <v>167</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.43</v>
+        <v>1.82</v>
       </c>
       <c r="H21" t="n">
-        <v>15334100</v>
+        <v>28604300</v>
       </c>
       <c r="I21" t="n">
-        <v>52.9</v>
+        <v>55.1</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.24</v>
+        <v>-1.14</v>
       </c>
       <c r="K21" t="n">
-        <v>0.54</v>
+        <v>0.93</v>
       </c>
       <c r="L21" t="n">
-        <v>-441.99</v>
+        <v>-425.48</v>
       </c>
       <c r="M21" t="n">
-        <v>-560.9</v>
+        <v>-557.6</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -29884,10 +30042,10 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>13051.09</v>
+        <v>13053.85</v>
       </c>
       <c r="Q21" t="n">
-        <v>7923.97</v>
+        <v>7925</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -29948,31 +30106,31 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>49690</v>
+        <v>50780</v>
       </c>
       <c r="F22" t="n">
-        <v>-2060</v>
+        <v>-970</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.98</v>
+        <v>-1.87</v>
       </c>
       <c r="H22" t="n">
-        <v>15179600</v>
+        <v>27253000</v>
       </c>
       <c r="I22" t="n">
-        <v>45.4</v>
+        <v>47.1</v>
       </c>
       <c r="J22" t="n">
-        <v>-6.64</v>
+        <v>-4.67</v>
       </c>
       <c r="K22" t="n">
-        <v>0.59</v>
+        <v>0.96</v>
       </c>
       <c r="L22" t="n">
-        <v>-754.13</v>
+        <v>-667.1799999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-768.36</v>
+        <v>-750.97</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -29981,14 +30139,14 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>65866.8</v>
+        <v>65881.33</v>
       </c>
       <c r="Q22" t="n">
-        <v>39790.11</v>
+        <v>39795.57</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -29996,7 +30154,7 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -30015,7 +30173,7 @@
 ・MACDは買いシグナルです。
 ・デッドクロスが発生し、短期的な下落に注意が必要です。
 ・RSIは良好な水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
@@ -30050,31 +30208,31 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>161.4</v>
+        <v>163.2</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6</v>
+        <v>0.2</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.98</v>
+        <v>0.12</v>
       </c>
       <c r="H23" t="n">
-        <v>22479800</v>
+        <v>47625700</v>
       </c>
       <c r="I23" t="n">
-        <v>48.5</v>
+        <v>51</v>
       </c>
       <c r="J23" t="n">
-        <v>0.76</v>
+        <v>1.84</v>
       </c>
       <c r="K23" t="n">
-        <v>0.51</v>
+        <v>0.96</v>
       </c>
       <c r="L23" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="M23" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -30087,10 +30245,10 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>152.33</v>
+        <v>152.35</v>
       </c>
       <c r="Q23" t="n">
-        <v>150.63</v>
+        <v>150.64</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -30098,16 +30256,16 @@
         </is>
       </c>
       <c r="S23" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -30151,31 +30309,31 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>3187</v>
+        <v>3240</v>
       </c>
       <c r="F24" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="G24" t="n">
-        <v>1.01</v>
+        <v>2.69</v>
       </c>
       <c r="H24" t="n">
-        <v>2775400</v>
+        <v>5824500</v>
       </c>
       <c r="I24" t="n">
-        <v>38.7</v>
+        <v>42.3</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.32</v>
+        <v>-4.82</v>
       </c>
       <c r="K24" t="n">
-        <v>0.37</v>
+        <v>0.71</v>
       </c>
       <c r="L24" t="n">
-        <v>-145.48</v>
+        <v>-141.26</v>
       </c>
       <c r="M24" t="n">
-        <v>-152.76</v>
+        <v>-151.91</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -30184,14 +30342,14 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>4020.99</v>
+        <v>4021.69</v>
       </c>
       <c r="Q24" t="n">
-        <v>3186.34</v>
+        <v>3186.6</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -30199,7 +30357,7 @@
         </is>
       </c>
       <c r="S24" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -30216,7 +30374,7 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
@@ -30351,31 +30509,31 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>8131</v>
+        <v>8126</v>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="H26" t="n">
-        <v>2557900</v>
+        <v>4574300</v>
       </c>
       <c r="I26" t="n">
-        <v>35.1</v>
+        <v>34.9</v>
       </c>
       <c r="J26" t="n">
-        <v>-5.95</v>
+        <v>-6.01</v>
       </c>
       <c r="K26" t="n">
-        <v>0.29</v>
+        <v>0.49</v>
       </c>
       <c r="L26" t="n">
-        <v>-4.08</v>
+        <v>-4.48</v>
       </c>
       <c r="M26" t="n">
-        <v>127.86</v>
+        <v>127.78</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -30388,10 +30546,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7741.79</v>
+        <v>7741.72</v>
       </c>
       <c r="Q26" t="n">
-        <v>8723.540000000001</v>
+        <v>8723.52</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>210,785円</t>
+          <t>212,129円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1,495円</t>
+          <t>2,839円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3310</v>
+        <v>3455</v>
       </c>
       <c r="F2" t="n">
-        <v>40.3</v>
+        <v>37.4</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.3</v>
+        <v>0.66</v>
       </c>
       <c r="H2" t="n">
-        <v>0.92</v>
+        <v>0.35</v>
       </c>
       <c r="I2" t="n">
-        <v>20.98</v>
+        <v>25.12</v>
       </c>
       <c r="J2" t="n">
-        <v>63.17</v>
+        <v>55.56</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3018.93</v>
+        <v>3031.87</v>
       </c>
       <c r="N2" t="n">
-        <v>2720.63</v>
+        <v>2723.95</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -757,11 +757,11 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -786,29 +786,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3340</v>
+        <v>3310</v>
       </c>
       <c r="X2" t="n">
-        <v>-30</v>
+        <v>145</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.9</v>
+        <v>4.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>13240</v>
+        <v>13820</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2440</v>
+        <v>3020</v>
       </c>
       <c r="AC2" t="n">
-        <v>22.59</v>
+        <v>27.96</v>
       </c>
     </row>
     <row r="3">
@@ -829,38 +829,38 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="F3" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8</v>
+        <v>5.19</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6</v>
+        <v>0.36</v>
       </c>
       <c r="I3" t="n">
-        <v>5.15</v>
+        <v>6.61</v>
       </c>
       <c r="J3" t="n">
-        <v>6.03</v>
+        <v>6.15</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>433.1</v>
+        <v>433.58</v>
       </c>
       <c r="N3" t="n">
-        <v>412.7</v>
+        <v>413.29</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -889,10 +889,9 @@
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
-・MACDは売りシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
+・MACDは買いシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -900,29 +899,29 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25日線上、ゴールデンクロス、MACD売り、長期上昇</t>
+          <t>25日線上、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.21</v>
+        <v>2.94</v>
       </c>
       <c r="Z3" t="n">
-        <v>47600</v>
+        <v>49000</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>5600</v>
+        <v>7000</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.33</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="4">
@@ -943,22 +942,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>177.1</v>
+        <v>179.2</v>
       </c>
       <c r="F4" t="n">
-        <v>67.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>4.41</v>
+        <v>5.18</v>
       </c>
       <c r="H4" t="n">
-        <v>0.82</v>
+        <v>0.48</v>
       </c>
       <c r="I4" t="n">
-        <v>4.63</v>
+        <v>4.69</v>
       </c>
       <c r="J4" t="n">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -971,10 +970,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>156.2</v>
+        <v>156.61</v>
       </c>
       <c r="N4" t="n">
-        <v>154.07</v>
+        <v>154.21</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1016,25 +1015,25 @@
         </is>
       </c>
       <c r="W4" t="n">
-        <v>178.1</v>
+        <v>177.1</v>
       </c>
       <c r="X4" t="n">
-        <v>-1</v>
+        <v>2.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.5600000000000001</v>
+        <v>1.19</v>
       </c>
       <c r="Z4" t="n">
-        <v>17710</v>
+        <v>17920</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1910</v>
+        <v>2120</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.09</v>
+        <v>13.42</v>
       </c>
     </row>
     <row r="5">
@@ -1055,22 +1054,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3016</v>
+        <v>3035</v>
       </c>
       <c r="F5" t="n">
-        <v>44.4</v>
+        <v>42.3</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.44</v>
+        <v>-0.88</v>
       </c>
       <c r="H5" t="n">
-        <v>0.82</v>
+        <v>0.51</v>
       </c>
       <c r="I5" t="n">
-        <v>0.34</v>
+        <v>0.03</v>
       </c>
       <c r="J5" t="n">
-        <v>15.04</v>
+        <v>12.04</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1083,10 +1082,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2934.33</v>
+        <v>2936.87</v>
       </c>
       <c r="N5" t="n">
-        <v>3164.96</v>
+        <v>3164.88</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1128,102 +1127,214 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>3021</v>
+        <v>3016</v>
       </c>
       <c r="X5" t="n">
-        <v>-5</v>
+        <v>19</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.17</v>
+        <v>0.63</v>
       </c>
       <c r="Z5" t="n">
-        <v>39208</v>
+        <v>39455</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>2109</v>
+        <v>2356</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.68</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7993</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8455</v>
+      </c>
+      <c r="F6" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="J6" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>7755.44</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8700.57</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>55</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>押し目、MACD売り、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>8126</v>
+      </c>
+      <c r="X6" t="n">
+        <v>329</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>8455</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7993</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>462</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.78</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>8058.T</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>三菱商事</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C7" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>4795</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E7" t="n">
         <v>4944</v>
       </c>
-      <c r="F6" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="I6" t="n">
-        <v>58.51</v>
-      </c>
-      <c r="J6" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="F7" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I7" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="J7" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>4717.03</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4670.28</v>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="M7" t="n">
+        <v>4717.29</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4676.88</v>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>🟢 強い買い</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q7" t="n">
         <v>95</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -1234,221 +1345,222 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>4910</v>
-      </c>
-      <c r="X6" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>24720</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>23975</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>745</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.11</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7993</v>
-      </c>
-      <c r="E7" t="n">
-        <v>8126</v>
-      </c>
-      <c r="F7" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-6.01</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-4.48</v>
-      </c>
-      <c r="J7" t="n">
-        <v>127.78</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>7741.72</v>
-      </c>
-      <c r="N7" t="n">
-        <v>8723.52</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>60</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
+          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>8118</v>
+        <v>4944</v>
       </c>
       <c r="X7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>8126</v>
+        <v>24720</v>
       </c>
       <c r="AA7" t="n">
-        <v>7993</v>
+        <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>133</v>
+        <v>745</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.66</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6976.T</t>
+          <t>285A.T</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>太陽誘電</t>
+          <t>キオクシアホールディングス</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
+        <v>55510</v>
+      </c>
+      <c r="E8" t="n">
+        <v>49760</v>
+      </c>
+      <c r="F8" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-6.44</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-895.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-779.88</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>65510.93</v>
+      </c>
+      <c r="N8" t="n">
+        <v>39994.21</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>65</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>RSI適正、押し目、MACD売り、反発局面</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>50780</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-1020</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>49760</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>55510</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-5750</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-10.36</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
         <v>10000</v>
       </c>
-      <c r="E8" t="n">
-        <v>9364</v>
-      </c>
-      <c r="F8" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-1.14</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-425.48</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-557.6</v>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="E9" t="n">
+        <v>8962</v>
+      </c>
+      <c r="F9" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-4.59</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-415.02</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-529.08</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="M8" t="n">
-        <v>13053.85</v>
-      </c>
-      <c r="N8" t="n">
-        <v>7925</v>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="M9" t="n">
+        <v>12957.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7954.19</v>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>🟡 反発中</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>85</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>65</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -1459,146 +1571,32 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>RSI適正、押し目、MACD買い、反発局面</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>9197</v>
-      </c>
-      <c r="X8" t="n">
-        <v>167</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>9364</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-636</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-6.36</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>285A.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>キオクシアホールディングス</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>55510</v>
-      </c>
-      <c r="E9" t="n">
-        <v>50780</v>
-      </c>
-      <c r="F9" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-4.67</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-667.1799999999999</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-750.97</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>DC</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>65881.33</v>
-      </c>
-      <c r="N9" t="n">
-        <v>39795.57</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>🟠 利益確定検討</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>50</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>押し目、デッドクロス、MACD買い、反発局面</t>
+          <t>押し目、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>51750</v>
+        <v>9364</v>
       </c>
       <c r="X9" t="n">
-        <v>-970</v>
+        <v>-402</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.87</v>
+        <v>-4.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>50780</v>
+        <v>8962</v>
       </c>
       <c r="AA9" t="n">
-        <v>55510</v>
+        <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-4730</v>
+        <v>-1038</v>
       </c>
       <c r="AC9" t="n">
-        <v>-8.52</v>
+        <v>-10.38</v>
       </c>
     </row>
     <row r="10">
@@ -1726,7 +1724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1448"/>
+  <dimension ref="A1:C1457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23448,6 +23446,141 @@
         </is>
       </c>
       <c r="C1448" t="n">
+        <v>36.85</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1449" t="n">
+        <v>3455</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1450" t="n">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1451" t="n">
+        <v>179.2</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1452" t="n">
+        <v>3035</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1453" t="n">
+        <v>8455</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1454" t="n">
+        <v>4944</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1455" t="n">
+        <v>49760</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1456" t="n">
+        <v>8962</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1457" t="n">
         <v>36.85</v>
       </c>
     </row>
@@ -23462,7 +23595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F247"/>
+  <dimension ref="A1:F248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27872,19 +28005,29 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
+      <c r="A245" t="inlineStr"/>
+      <c r="B245" s="1" t="n">
+        <v>46282.5</v>
+      </c>
+      <c r="C245" t="n">
+        <v>212129</v>
+      </c>
+      <c r="D245" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E245" t="n">
+        <v>2839</v>
+      </c>
+      <c r="F245" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr"/>
-      <c r="C245" t="inlineStr"/>
-      <c r="D245" t="inlineStr"/>
-      <c r="E245" t="inlineStr"/>
-      <c r="F245" t="inlineStr"/>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr"/>
       <c r="B246" t="inlineStr"/>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr"/>
@@ -27892,16 +28035,24 @@
       <c r="F246" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A247" t="inlineStr"/>
       <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr"/>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -30409,31 +30560,31 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>47.5</v>
+        <v>48.24</v>
       </c>
       <c r="F25" t="n">
-        <v>0.91</v>
+        <v>0.74</v>
       </c>
       <c r="G25" t="n">
-        <v>1.95</v>
+        <v>1.56</v>
       </c>
       <c r="H25" t="n">
-        <v>1018600</v>
+        <v>1074462</v>
       </c>
       <c r="I25" t="n">
-        <v>43.5</v>
+        <v>41.6</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.67</v>
+        <v>-7.63</v>
       </c>
       <c r="K25" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.17</v>
+        <v>-2.13</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.17</v>
+        <v>-2.16</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -30442,14 +30593,14 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>59.48</v>
+        <v>59.37</v>
       </c>
       <c r="Q25" t="n">
-        <v>37.55</v>
+        <v>37.69</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -30457,24 +30608,24 @@
         </is>
       </c>
       <c r="S25" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・MACDは買いシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
@@ -30581,12 +30732,12 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>2026/11/03</t>
+          <t>2026/11/05</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>あと48日</t>
+          <t>あと50日</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>212,129円</t>
+          <t>212,409円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2,839円</t>
+          <t>3,119円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3455</v>
+        <v>3445</v>
       </c>
       <c r="F2" t="n">
-        <v>37.4</v>
+        <v>36.8</v>
       </c>
       <c r="G2" t="n">
-        <v>0.66</v>
+        <v>0.38</v>
       </c>
       <c r="H2" t="n">
-        <v>0.35</v>
+        <v>0.62</v>
       </c>
       <c r="I2" t="n">
-        <v>25.12</v>
+        <v>24.32</v>
       </c>
       <c r="J2" t="n">
-        <v>55.56</v>
+        <v>55.4</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3031.87</v>
+        <v>3031.73</v>
       </c>
       <c r="N2" t="n">
-        <v>2723.95</v>
+        <v>2723.9</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -793,22 +793,22 @@
         <v>3310</v>
       </c>
       <c r="X2" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.38</v>
+        <v>4.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>13820</v>
+        <v>13780</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>3020</v>
+        <v>2980</v>
       </c>
       <c r="AC2" t="n">
-        <v>27.96</v>
+        <v>27.59</v>
       </c>
     </row>
     <row r="3">
@@ -829,22 +829,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F3" t="n">
-        <v>49.1</v>
+        <v>48.8</v>
       </c>
       <c r="G3" t="n">
-        <v>5.19</v>
+        <v>4.98</v>
       </c>
       <c r="H3" t="n">
-        <v>0.36</v>
+        <v>0.72</v>
       </c>
       <c r="I3" t="n">
-        <v>6.61</v>
+        <v>6.53</v>
       </c>
       <c r="J3" t="n">
-        <v>6.15</v>
+        <v>6.13</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>433.58</v>
+        <v>433.56</v>
       </c>
       <c r="N3" t="n">
         <v>413.29</v>
@@ -906,22 +906,22 @@
         <v>476</v>
       </c>
       <c r="X3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.94</v>
+        <v>2.73</v>
       </c>
       <c r="Z3" t="n">
-        <v>49000</v>
+        <v>48900</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7000</v>
+        <v>6900</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.67</v>
+        <v>16.43</v>
       </c>
     </row>
     <row r="4">
@@ -942,22 +942,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>179.2</v>
+        <v>180</v>
       </c>
       <c r="F4" t="n">
-        <v>69.90000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="G4" t="n">
-        <v>5.18</v>
+        <v>5.63</v>
       </c>
       <c r="H4" t="n">
-        <v>0.48</v>
+        <v>0.96</v>
       </c>
       <c r="I4" t="n">
-        <v>4.69</v>
+        <v>4.76</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>156.61</v>
+        <v>156.62</v>
       </c>
       <c r="N4" t="n">
         <v>154.21</v>
@@ -1003,6 +1003,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
+・買われ過ぎ水準です。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -1018,22 +1019,22 @@
         <v>177.1</v>
       </c>
       <c r="X4" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.19</v>
+        <v>1.64</v>
       </c>
       <c r="Z4" t="n">
-        <v>17920</v>
+        <v>18000</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>2120</v>
+        <v>2200</v>
       </c>
       <c r="AC4" t="n">
-        <v>13.42</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="5">
@@ -1054,22 +1055,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="F5" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.88</v>
+        <v>-0.92</v>
       </c>
       <c r="H5" t="n">
-        <v>0.51</v>
+        <v>0.96</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="J5" t="n">
-        <v>12.04</v>
+        <v>12.02</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1082,7 +1083,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2936.87</v>
+        <v>2936.86</v>
       </c>
       <c r="N5" t="n">
         <v>3164.88</v>
@@ -1130,22 +1131,22 @@
         <v>3016</v>
       </c>
       <c r="X5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>39455</v>
+        <v>39442</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>2356</v>
+        <v>2343</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.35</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="6">
@@ -1166,22 +1167,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>8455</v>
+        <v>8475</v>
       </c>
       <c r="F6" t="n">
-        <v>36.9</v>
+        <v>37.5</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.26</v>
+        <v>-2.04</v>
       </c>
       <c r="H6" t="n">
-        <v>0.59</v>
+        <v>0.97</v>
       </c>
       <c r="I6" t="n">
-        <v>1.14</v>
+        <v>2.74</v>
       </c>
       <c r="J6" t="n">
-        <v>102.45</v>
+        <v>102.77</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1194,10 +1195,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>7755.44</v>
+        <v>7755.71</v>
       </c>
       <c r="N6" t="n">
-        <v>8700.57</v>
+        <v>8700.67</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1242,22 +1243,22 @@
         <v>8126</v>
       </c>
       <c r="X6" t="n">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.05</v>
+        <v>4.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>8455</v>
+        <v>8475</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.78</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="7">
@@ -1278,22 +1279,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4944</v>
+        <v>4979</v>
       </c>
       <c r="F7" t="n">
-        <v>57.3</v>
+        <v>58.6</v>
       </c>
       <c r="G7" t="n">
-        <v>1.72</v>
+        <v>2.41</v>
       </c>
       <c r="H7" t="n">
-        <v>0.44</v>
+        <v>0.86</v>
       </c>
       <c r="I7" t="n">
-        <v>54.72</v>
+        <v>57.51</v>
       </c>
       <c r="J7" t="n">
-        <v>58.3</v>
+        <v>58.86</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1306,10 +1307,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4717.29</v>
+        <v>4717.76</v>
       </c>
       <c r="N7" t="n">
-        <v>4676.88</v>
+        <v>4677.05</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1355,58 +1356,58 @@
         <v>4944</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="Z7" t="n">
-        <v>24720</v>
+        <v>24895</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>745</v>
+        <v>920</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.11</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>285A.T</t>
+          <t>6976.T</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>キオクシアホールディングス</t>
+          <t>太陽誘電</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>55510</v>
+        <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>49760</v>
+        <v>9000</v>
       </c>
       <c r="F8" t="n">
-        <v>53.6</v>
+        <v>47.3</v>
       </c>
       <c r="G8" t="n">
-        <v>-6.44</v>
+        <v>-4.2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.54</v>
+        <v>0.89</v>
       </c>
       <c r="I8" t="n">
-        <v>-895.5</v>
+        <v>-411.98</v>
       </c>
       <c r="J8" t="n">
-        <v>-779.88</v>
+        <v>-528.48</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1419,10 +1420,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>65510.93</v>
+        <v>12957.52</v>
       </c>
       <c r="N8" t="n">
-        <v>39994.21</v>
+        <v>7954.38</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1448,6 +1449,119 @@
         </is>
       </c>
       <c r="T8" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>押し目、MACD買い、反発局面</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>9364</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-364</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-3.89</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>キオクシアホールディングス</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>55510</v>
+      </c>
+      <c r="E9" t="n">
+        <v>49880</v>
+      </c>
+      <c r="F9" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-6.22</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-885.9299999999999</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-777.96</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>65512.53</v>
+      </c>
+      <c r="N9" t="n">
+        <v>39994.82</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>65</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -1458,145 +1572,32 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>RSI適正、押し目、MACD売り、反発局面</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>50780</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-1020</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-2.01</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>49760</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>55510</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-5750</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-10.36</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E9" t="n">
-        <v>8962</v>
-      </c>
-      <c r="F9" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-4.59</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-415.02</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-529.08</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>12957.01</v>
-      </c>
-      <c r="N9" t="n">
-        <v>7954.19</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>65</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>押し目、MACD買い、反発局面</t>
+          <t>RSI適正、押し目、MACD売り、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>9364</v>
+        <v>50780</v>
       </c>
       <c r="X9" t="n">
-        <v>-402</v>
+        <v>-900</v>
       </c>
       <c r="Y9" t="n">
-        <v>-4.29</v>
+        <v>-1.77</v>
       </c>
       <c r="Z9" t="n">
-        <v>8962</v>
+        <v>49880</v>
       </c>
       <c r="AA9" t="n">
-        <v>10000</v>
+        <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1038</v>
+        <v>-5630</v>
       </c>
       <c r="AC9" t="n">
-        <v>-10.38</v>
+        <v>-10.14</v>
       </c>
     </row>
     <row r="10">
@@ -1724,7 +1725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1457"/>
+  <dimension ref="A1:C1466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23581,6 +23582,141 @@
         </is>
       </c>
       <c r="C1457" t="n">
+        <v>36.85</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1458" t="n">
+        <v>3445</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1459" t="n">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1460" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1461" t="n">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1462" t="n">
+        <v>8475</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1463" t="n">
+        <v>4979</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1464" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1465" t="n">
+        <v>49880</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1466" t="n">
         <v>36.85</v>
       </c>
     </row>
@@ -23595,7 +23731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F248"/>
+  <dimension ref="A1:F249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28023,19 +28159,29 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
+      <c r="A246" t="inlineStr"/>
+      <c r="B246" s="1" t="n">
+        <v>46282.75</v>
+      </c>
+      <c r="C246" t="n">
+        <v>212409</v>
+      </c>
+      <c r="D246" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E246" t="n">
+        <v>3119</v>
+      </c>
+      <c r="F246" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr"/>
-      <c r="C246" t="inlineStr"/>
-      <c r="D246" t="inlineStr"/>
-      <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr"/>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr"/>
       <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr"/>
@@ -28043,16 +28189,24 @@
       <c r="F247" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A248" t="inlineStr"/>
       <c r="B248" t="inlineStr"/>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr"/>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -28217,31 +28371,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>991</v>
+        <v>1020</v>
       </c>
       <c r="F2" t="n">
-        <v>-10</v>
+        <v>29</v>
       </c>
       <c r="G2" t="n">
-        <v>-1</v>
+        <v>2.93</v>
       </c>
       <c r="H2" t="n">
-        <v>595200</v>
+        <v>441300</v>
       </c>
       <c r="I2" t="n">
-        <v>51.5</v>
+        <v>41</v>
       </c>
       <c r="J2" t="n">
-        <v>0.15</v>
+        <v>2.28</v>
       </c>
       <c r="K2" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="L2" t="n">
-        <v>32.61</v>
+        <v>30.82</v>
       </c>
       <c r="M2" t="n">
-        <v>42.41</v>
+        <v>40.1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -28254,10 +28408,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>845.03</v>
+        <v>849.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>1119.55</v>
+        <v>1118.06</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -28265,16 +28419,16 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -28282,7 +28436,6 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
-・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -28318,31 +28471,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3310</v>
+        <v>3455</v>
       </c>
       <c r="F3" t="n">
-        <v>-30</v>
+        <v>145</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9</v>
+        <v>4.38</v>
       </c>
       <c r="H3" t="n">
-        <v>122400</v>
+        <v>46900</v>
       </c>
       <c r="I3" t="n">
-        <v>40.3</v>
+        <v>37.4</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.3</v>
+        <v>0.66</v>
       </c>
       <c r="K3" t="n">
-        <v>0.92</v>
+        <v>0.35</v>
       </c>
       <c r="L3" t="n">
-        <v>20.98</v>
+        <v>25.12</v>
       </c>
       <c r="M3" t="n">
-        <v>63.17</v>
+        <v>55.56</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -28355,10 +28508,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3018.93</v>
+        <v>3031.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>2720.63</v>
+        <v>2723.95</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -28366,7 +28519,7 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -28392,7 +28545,7 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
+          <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
@@ -28418,31 +28571,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1325</v>
+        <v>1340</v>
       </c>
       <c r="F4" t="n">
-        <v>-21</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.56</v>
+        <v>1.13</v>
       </c>
       <c r="H4" t="n">
-        <v>11800</v>
+        <v>20000</v>
       </c>
       <c r="I4" t="n">
-        <v>61</v>
+        <v>57.3</v>
       </c>
       <c r="J4" t="n">
-        <v>2.47</v>
+        <v>3.03</v>
       </c>
       <c r="K4" t="n">
-        <v>1.53</v>
+        <v>1.94</v>
       </c>
       <c r="L4" t="n">
-        <v>36.12</v>
+        <v>33.88</v>
       </c>
       <c r="M4" t="n">
-        <v>40.77</v>
+        <v>39.39</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -28455,10 +28608,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1204.96</v>
+        <v>1206.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>1640.72</v>
+        <v>1639.77</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -28483,6 +28636,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
+・RSIは良好な水準です。
 ・出来高が増加しています。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
@@ -28519,67 +28673,1493 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3430</v>
+        <v>3500</v>
       </c>
       <c r="F5" t="n">
-        <v>-45</v>
+        <v>70</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.29</v>
+        <v>2.04</v>
       </c>
       <c r="H5" t="n">
-        <v>12000</v>
+        <v>2100</v>
       </c>
       <c r="I5" t="n">
-        <v>55.9</v>
+        <v>56.3</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.63</v>
+        <v>1.29</v>
       </c>
       <c r="K5" t="n">
-        <v>0.95</v>
+        <v>0.2</v>
       </c>
       <c r="L5" t="n">
-        <v>6.04</v>
+        <v>8.9</v>
       </c>
       <c r="M5" t="n">
-        <v>8.58</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>3421.73</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3151.62</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは買いシグナルです。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3984.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ユーザーローカル</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AI解析・データ分析</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1546</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H6" t="n">
+        <v>26600</v>
+      </c>
+      <c r="I6" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-24.53</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-33.25</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P5" t="n">
-        <v>3424.33</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3147.48</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P6" t="n">
+        <v>1679.64</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1697.42</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>30</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4054.T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>日本情報クリエイト</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>不動産向けクラウド</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>520</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I7" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-6.15</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-7.22</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>537.7</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>582.11</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>30</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは買いシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7072.T</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>インティメート・マージャー</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>データマーケティング</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1094</v>
+      </c>
+      <c r="F8" t="n">
+        <v>15</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H8" t="n">
+        <v>800</v>
+      </c>
+      <c r="I8" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-3.21</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-6.73</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1056.08</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1019.65</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S5" t="n">
-        <v>85</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
+      <c r="S8" t="n">
+        <v>65</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7033.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>マネジメントソリューションズ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PMO支援・DX案件増加</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1559</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I9" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-3.71</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1454.37</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1381.81</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>65</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9342.T</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>スマサポ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>不動産DX</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>980</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I10" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L10" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="M10" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>874.91</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>986.62</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>65</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6971.T</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>京セラ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>自社株</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3591</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-9</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1410700</v>
+      </c>
+      <c r="I11" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-35.04</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-45.44</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>3663.88</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2942.07</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>65</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026/10/29</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>あと42日</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3778.T</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>さくらインターネット(株)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>3675</v>
+      </c>
+      <c r="F12" t="n">
+        <v>155</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>704400</v>
+      </c>
+      <c r="I12" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>49.74</v>
+      </c>
+      <c r="M12" t="n">
+        <v>82.34</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>3218.39</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3060.03</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>65</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5803.T</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>(株)フジクラ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>4877</v>
+      </c>
+      <c r="F13" t="n">
+        <v>38</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H13" t="n">
+        <v>20060900</v>
+      </c>
+      <c r="I13" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-76.77</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-17.08</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>5068.75</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4494.05</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2026/11/10</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>あと54日</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>166A.T</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>タスキホールディングス</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>何度も高値更新中の強トレンド</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1085</v>
+      </c>
+      <c r="F14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H14" t="n">
+        <v>102700</v>
+      </c>
+      <c r="I14" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-4.74</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-19.05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-9.609999999999999</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1111.56</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>928.9</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>65</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・売られ過ぎ水準です。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5801.T</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>古河電気工業</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>半導体設備関連</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3785</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-27</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="H15" t="n">
+        <v>15049000</v>
+      </c>
+      <c r="I15" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-3.03</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-4.22</v>
+      </c>
+      <c r="M15" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>4003.25</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3181.79</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>45</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2026/11/09</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>あと53日</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3374.T</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>内外テック</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>3955</v>
+      </c>
+      <c r="F16" t="n">
+        <v>15</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H16" t="n">
+        <v>9100</v>
+      </c>
+      <c r="I16" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L16" t="n">
+        <v>20.46</v>
+      </c>
+      <c r="M16" t="n">
+        <v>68.09</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>3579.57</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2849.02</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>65</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>7012.T</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>川崎重工業(株)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>2421</v>
+      </c>
+      <c r="F17" t="n">
+        <v>32</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5543200</v>
+      </c>
+      <c r="I17" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-4.63</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-91</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-92.53</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>2740.23</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2830.08</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは買いシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>あと55日</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>トヨタ自動車(株)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4000円で売る予定</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3035</v>
+      </c>
+      <c r="F18" t="n">
+        <v>19</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H18" t="n">
+        <v>9888000</v>
+      </c>
+      <c r="I18" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M18" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>2936.87</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3164.88</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>55</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2026/11/05</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>あと49日</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>8053.T</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>住友商事</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>1824</v>
+      </c>
+      <c r="F19" t="n">
+        <v>38</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3089500</v>
+      </c>
+      <c r="I19" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L19" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="M19" t="n">
+        <v>32.51</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1675.98</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1567.44</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>95</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -28590,600 +30170,202 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>3984.T</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ユーザーローカル</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>AI解析・データ分析</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1544</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="H6" t="n">
-        <v>31800</v>
-      </c>
-      <c r="I6" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-26.73</v>
-      </c>
-      <c r="M6" t="n">
-        <v>-35.43</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2026/10/29</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>あと42日</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ブロードリーフ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>500円で売</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>490</v>
+      </c>
+      <c r="F20" t="n">
+        <v>14</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H20" t="n">
+        <v>286800</v>
+      </c>
+      <c r="I20" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L20" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="M20" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>1683.08</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1699.37</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v>50</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>433.58</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>413.29</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>95</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🔴 下降
+・🟢 強い上昇
 ・MACDは買いシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>4054.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>日本情報クリエイト</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>不動産向けクラウド</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>518</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="H7" t="n">
-        <v>15800</v>
-      </c>
-      <c r="I7" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-1.28</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-6.54</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-7.49</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>537.4299999999999</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>583.0700000000001</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>55</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・出来高が増加しています。
-・ボリンジャーバンド中心付近で推移しています。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7072.T</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>インティメート・マージャー</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>データマーケティング</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1079</v>
-      </c>
-      <c r="F8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="I8" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-4.72</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-6.72</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>1054.84</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1020.75</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v>70</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>7033.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>マネジメントソリューションズ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>監視</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PMO支援・DX案件増加</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1551</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-7</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="H9" t="n">
-        <v>47100</v>
-      </c>
-      <c r="I9" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-3.96</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="L9" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="M9" t="n">
-        <v>25.52</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>8962</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-402</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-4.29</v>
+      </c>
+      <c r="H21" t="n">
+        <v>15635500</v>
+      </c>
+      <c r="I21" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-4.59</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-415.02</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-529.08</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P9" t="n">
-        <v>1451.55</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1380.72</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
+      <c r="P21" t="n">
+        <v>12957.01</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>7954.19</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
         <v>65</v>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9342.T</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>スマサポ</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>不動産DX</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>980</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-7</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-0.71</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I10" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="L10" t="n">
-        <v>19.34</v>
-      </c>
-      <c r="M10" t="n">
-        <v>23.01</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>874.91</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>986.62</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>65</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>6971.T</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>京セラ</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>自社株</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>3600</v>
-      </c>
-      <c r="F11" t="n">
-        <v>69</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3086100</v>
-      </c>
-      <c r="I11" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-42.19</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-48.04</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>3663.25</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2934.39</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>65</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -29194,718 +30376,499 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2026/10/29</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2026/11/05</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>あと49日</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>キオクシアホールディングス</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>49760</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-1020</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="H22" t="n">
+        <v>13782800</v>
+      </c>
+      <c r="I22" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-6.44</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-895.5</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-779.88</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>65510.93</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>39994.21</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>65</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2026/10/30</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
         <is>
           <t>あと43日</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>3778.T</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>さくらインターネット(株)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="n">
-        <v>3520</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-60</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-1.68</v>
-      </c>
-      <c r="H12" t="n">
-        <v>450300</v>
-      </c>
-      <c r="I12" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-4.86</v>
-      </c>
-      <c r="K12" t="n">
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>8729.T</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ソニーファイナンシャル</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>164.3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G23" t="n">
         <v>0.67</v>
       </c>
-      <c r="L12" t="n">
-        <v>51.03</v>
-      </c>
-      <c r="M12" t="n">
-        <v>90.48</v>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="H23" t="n">
+        <v>28531900</v>
+      </c>
+      <c r="I23" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>3208.25</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3056.68</v>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>152.7</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>150.74</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S12" t="n">
-        <v>65</v>
-      </c>
-      <c r="T12" t="inlineStr">
+      <c r="S23" t="n">
+        <v>75</v>
+      </c>
+      <c r="T23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>5803.T</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>(株)フジクラ</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="n">
-        <v>4839</v>
-      </c>
-      <c r="F13" t="n">
-        <v>95</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" t="n">
-        <v>26196900</v>
-      </c>
-      <c r="I13" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-8.44</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-68.31999999999999</v>
-      </c>
-      <c r="M13" t="n">
-        <v>-2.15</v>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>2026/11/12</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>あと56日</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6723.T</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ルネサスエレクトロニクス</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>3182</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-58</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4272400</v>
+      </c>
+      <c r="I24" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-138.34</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-149.2</v>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>-1S</t>
         </is>
       </c>
-      <c r="P13" t="n">
-        <v>5064.71</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4484.04</v>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="P24" t="n">
+        <v>4004.72</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3193.64</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>35</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは買いシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>2026/10/28</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>あと41日</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PENG</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ペンギン・ソリューションズ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>48.24</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1098100</v>
+      </c>
+      <c r="I25" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-7.63</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>59.37</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>37.69</v>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>🟡 反発中</t>
         </is>
       </c>
-      <c r="S13" t="n">
-        <v>50</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
+      <c r="S25" t="n">
+        <v>65</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>2026/11/10</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>あと55日</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>166A.T</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>タスキホールディングス</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>何度も高値更新中の強トレンド</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1065</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-4</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="H14" t="n">
-        <v>146100</v>
-      </c>
-      <c r="I14" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-6.73</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-19.44</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-7.25</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1109.67</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>927.3200000000001</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S14" t="n">
-        <v>65</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>5801.T</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>古河電気工業</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>半導体設備関連</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>3812</v>
-      </c>
-      <c r="F15" t="n">
-        <v>93</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H15" t="n">
-        <v>17118100</v>
-      </c>
-      <c r="I15" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-2.67</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="M15" t="n">
-        <v>14.03</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>DC</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>4020.67</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3167.27</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S15" t="n">
-        <v>30</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
+・MACDは買いシグナルです。
 ・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>2026/11/09</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>あと54日</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>🟡 調整中押し目（段階的買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>3374.T</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>内外テック</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="n">
-        <v>3940</v>
-      </c>
-      <c r="F16" t="n">
-        <v>65</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H16" t="n">
-        <v>34400</v>
-      </c>
-      <c r="I16" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>-4.12</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="L16" t="n">
-        <v>24.81</v>
-      </c>
-      <c r="M16" t="n">
-        <v>80</v>
-      </c>
-      <c r="N16" t="inlineStr">
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>2026/10/06</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>あと19日</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>8455</v>
+      </c>
+      <c r="F26" t="n">
+        <v>329</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4244100</v>
+      </c>
+      <c r="I26" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M26" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P16" t="n">
-        <v>3566.23</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2839.11</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S16" t="n">
-        <v>70</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・出来高が増加しています。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>7012.T</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>川崎重工業(株)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="n">
-        <v>2389</v>
-      </c>
-      <c r="F17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H17" t="n">
-        <v>11167200</v>
-      </c>
-      <c r="I17" t="n">
-        <v>30</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-6.48</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-98.03</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-92.92</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>2745.6</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2827.91</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・ボリンジャーバンド中心付近で推移しています。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>あと56日</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>7203.T</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>トヨタ自動車(株)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4000円で売る予定</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>3016</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-5</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="H18" t="n">
-        <v>17508600</v>
-      </c>
-      <c r="I18" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="M18" t="n">
-        <v>15.04</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>2934.33</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3164.96</v>
-      </c>
-      <c r="R18" t="inlineStr">
+      <c r="P26" t="n">
+        <v>7755.44</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>8700.57</v>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>🟢 上昇</t>
         </is>
       </c>
-      <c r="S18" t="n">
+      <c r="S26" t="n">
         <v>55</v>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>★★☆☆☆</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 上昇
@@ -29915,829 +30878,14 @@
 順張りが有利な局面です。</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>2026/11/05</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>あと50日</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>8053.T</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>住友商事</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="n">
-        <v>1786</v>
-      </c>
-      <c r="F19" t="n">
-        <v>16</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H19" t="n">
-        <v>6261600</v>
-      </c>
-      <c r="I19" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="L19" t="n">
-        <v>25.09</v>
-      </c>
-      <c r="M19" t="n">
-        <v>34.41</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1674.39</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1564.16</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S19" t="n">
-        <v>95</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>2026/10/29</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>あと43日</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>3673.T</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ブロードリーフ</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>500円で売</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>476</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H20" t="n">
-        <v>543300</v>
-      </c>
-      <c r="I20" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L20" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="M20" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>433.1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>412.7</v>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S20" t="n">
-        <v>90</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="n">
-        <v>9364</v>
-      </c>
-      <c r="F21" t="n">
-        <v>167</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="H21" t="n">
-        <v>28604300</v>
-      </c>
-      <c r="I21" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-1.14</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-425.48</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-557.6</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>13053.85</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>7925</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S21" t="n">
-        <v>85</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>2026/11/05</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>あと50日</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>285A.T</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>キオクシアホールディングス</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="n">
-        <v>50780</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-970</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-1.87</v>
-      </c>
-      <c r="H22" t="n">
-        <v>27253000</v>
-      </c>
-      <c r="I22" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>-4.67</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-667.1799999999999</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-750.97</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>DC</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>65881.33</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>39795.57</v>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S22" t="n">
-        <v>50</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>2026/10/30</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>あと44日</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>🟡 調整中押し目（段階的買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>8729.T</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ソニーファイナンシャル</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>163.2</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H23" t="n">
-        <v>47625700</v>
-      </c>
-      <c r="I23" t="n">
-        <v>51</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>152.35</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>150.64</v>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S23" t="n">
-        <v>95</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>2026/11/12</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>あと57日</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>6723.T</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>ルネサスエレクトロニクス</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="n">
-        <v>3240</v>
-      </c>
-      <c r="F24" t="n">
-        <v>85</v>
-      </c>
-      <c r="G24" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="H24" t="n">
-        <v>5824500</v>
-      </c>
-      <c r="I24" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="J24" t="n">
-        <v>-4.82</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="L24" t="n">
-        <v>-141.26</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-151.91</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>4021.69</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3186.6</v>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S24" t="n">
-        <v>65</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>2026/10/28</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>あと42日</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>PENG</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ペンギン・ソリューションズ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="n">
-        <v>48.24</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1074462</v>
-      </c>
-      <c r="I25" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-7.63</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="L25" t="n">
-        <v>-2.13</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-2.16</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>59.37</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>37.69</v>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S25" t="n">
-        <v>65</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>2026/10/06</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>あと20日</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="n">
-        <v>8126</v>
-      </c>
-      <c r="F26" t="n">
-        <v>8</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H26" t="n">
-        <v>4574300</v>
-      </c>
-      <c r="I26" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="J26" t="n">
-        <v>-6.01</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="L26" t="n">
-        <v>-4.48</v>
-      </c>
-      <c r="M26" t="n">
-        <v>127.78</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P26" t="n">
-        <v>7741.72</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>8723.52</v>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="S26" t="n">
-        <v>60</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>2026/11/05</t>
-        </is>
-      </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>あと50日</t>
+          <t>あと49日</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>212,409円</t>
+          <t>212,412円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3,119円</t>
+          <t>3,122円</t>
         </is>
       </c>
     </row>
@@ -1618,38 +1618,38 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>36.85</v>
+        <v>40.35</v>
       </c>
       <c r="F10" t="n">
-        <v>48.5</v>
+        <v>54.6</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.36</v>
+        <v>6.6</v>
       </c>
       <c r="H10" t="n">
-        <v>0.91</v>
+        <v>1.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0.98</v>
+        <v>1.14</v>
       </c>
       <c r="J10" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.49</v>
+        <v>33.41</v>
       </c>
       <c r="N10" t="n">
-        <v>31.54</v>
+        <v>31.58</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1658,20 +1658,20 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>🟠 利益確定検討</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1679,39 +1679,44 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・出来高が増加しています。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>🚀 急騰</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>押し目、デッドクロス、MACD売り、長期上昇</t>
+          <t>RSI適正、25日線上、出来高微増、ゴールデンクロス、+1σ、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>35.64</v>
+        <v>36.85</v>
       </c>
       <c r="X10" t="n">
-        <v>1.21</v>
+        <v>3.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.4</v>
+        <v>9.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6076</v>
+        <v>-6073</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.40000000000001</v>
+        <v>-99.34</v>
       </c>
     </row>
   </sheetData>
@@ -1725,7 +1730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1466"/>
+  <dimension ref="A1:C1475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23718,6 +23723,141 @@
       </c>
       <c r="C1466" t="n">
         <v>36.85</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1467" t="n">
+        <v>3445</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1468" t="n">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1469" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1470" t="n">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1471" t="n">
+        <v>8475</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1472" t="n">
+        <v>4979</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1473" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1474" t="n">
+        <v>49880</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1475" t="n">
+        <v>40.35</v>
       </c>
     </row>
   </sheetData>
@@ -23731,7 +23871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F249"/>
+  <dimension ref="A1:F250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28177,19 +28317,29 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
+      <c r="A247" t="inlineStr"/>
+      <c r="B247" s="1" t="n">
+        <v>46283.29166666666</v>
+      </c>
+      <c r="C247" t="n">
+        <v>212412</v>
+      </c>
+      <c r="D247" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E247" t="n">
+        <v>3122</v>
+      </c>
+      <c r="F247" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr"/>
-      <c r="C247" t="inlineStr"/>
-      <c r="D247" t="inlineStr"/>
-      <c r="E247" t="inlineStr"/>
-      <c r="F247" t="inlineStr"/>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr"/>
       <c r="B248" t="inlineStr"/>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr"/>
@@ -28197,16 +28347,24 @@
       <c r="F248" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A249" t="inlineStr"/>
       <c r="B249" t="inlineStr"/>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr"/>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -28371,31 +28529,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1020</v>
+        <v>1001</v>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>2.93</v>
+        <v>1.01</v>
       </c>
       <c r="H2" t="n">
-        <v>441300</v>
+        <v>742700</v>
       </c>
       <c r="I2" t="n">
-        <v>41</v>
+        <v>37.4</v>
       </c>
       <c r="J2" t="n">
-        <v>2.28</v>
+        <v>0.45</v>
       </c>
       <c r="K2" t="n">
-        <v>0.71</v>
+        <v>1.09</v>
       </c>
       <c r="L2" t="n">
-        <v>30.82</v>
+        <v>29.3</v>
       </c>
       <c r="M2" t="n">
-        <v>40.1</v>
+        <v>39.79</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -28408,10 +28566,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>849.84</v>
+        <v>849.59</v>
       </c>
       <c r="Q2" t="n">
-        <v>1118.06</v>
+        <v>1117.96</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -28471,31 +28629,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3455</v>
+        <v>3445</v>
       </c>
       <c r="F3" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="G3" t="n">
-        <v>4.38</v>
+        <v>4.08</v>
       </c>
       <c r="H3" t="n">
-        <v>46900</v>
+        <v>89400</v>
       </c>
       <c r="I3" t="n">
-        <v>37.4</v>
+        <v>36.8</v>
       </c>
       <c r="J3" t="n">
-        <v>0.66</v>
+        <v>0.38</v>
       </c>
       <c r="K3" t="n">
-        <v>0.35</v>
+        <v>0.62</v>
       </c>
       <c r="L3" t="n">
-        <v>25.12</v>
+        <v>24.32</v>
       </c>
       <c r="M3" t="n">
-        <v>55.56</v>
+        <v>55.4</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -28508,10 +28666,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3031.87</v>
+        <v>3031.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>2723.95</v>
+        <v>2723.9</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -28571,31 +28729,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1340</v>
+        <v>1347</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>1.13</v>
+        <v>1.66</v>
       </c>
       <c r="H4" t="n">
-        <v>20000</v>
+        <v>29800</v>
       </c>
       <c r="I4" t="n">
-        <v>57.3</v>
+        <v>58</v>
       </c>
       <c r="J4" t="n">
-        <v>3.03</v>
+        <v>3.54</v>
       </c>
       <c r="K4" t="n">
-        <v>1.94</v>
+        <v>2.43</v>
       </c>
       <c r="L4" t="n">
-        <v>33.88</v>
+        <v>34.43</v>
       </c>
       <c r="M4" t="n">
-        <v>39.39</v>
+        <v>39.5</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -28608,10 +28766,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1206.48</v>
+        <v>1206.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>1639.77</v>
+        <v>1639.81</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -28619,7 +28777,7 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -28637,7 +28795,7 @@
 ・🟢 上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・出来高が増加しています。
+・出来高が急増しています。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -28673,31 +28831,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3500</v>
+        <v>3475</v>
       </c>
       <c r="F5" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="G5" t="n">
-        <v>2.04</v>
+        <v>1.31</v>
       </c>
       <c r="H5" t="n">
-        <v>2100</v>
+        <v>3900</v>
       </c>
       <c r="I5" t="n">
-        <v>56.3</v>
+        <v>55.3</v>
       </c>
       <c r="J5" t="n">
-        <v>1.29</v>
+        <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="L5" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
       <c r="M5" t="n">
-        <v>8.640000000000001</v>
+        <v>8.24</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -28710,10 +28868,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3421.73</v>
+        <v>3421.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>3151.62</v>
+        <v>3151.5</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -28737,7 +28895,7 @@
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
-・MACDは買いシグナルです。
+・MACDは売りシグナルです。
 ・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
@@ -28775,31 +28933,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1546</v>
+        <v>1552</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>0.13</v>
+        <v>0.52</v>
       </c>
       <c r="H6" t="n">
-        <v>26600</v>
+        <v>64500</v>
       </c>
       <c r="I6" t="n">
-        <v>46.6</v>
+        <v>47.7</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.22</v>
+        <v>0.15</v>
       </c>
       <c r="K6" t="n">
-        <v>0.45</v>
+        <v>0.96</v>
       </c>
       <c r="L6" t="n">
-        <v>-24.53</v>
+        <v>-24.05</v>
       </c>
       <c r="M6" t="n">
-        <v>-33.25</v>
+        <v>-33.16</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -28812,10 +28970,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1679.64</v>
+        <v>1679.72</v>
       </c>
       <c r="Q6" t="n">
-        <v>1697.42</v>
+        <v>1697.45</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -28823,7 +28981,7 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -28876,31 +29034,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>0.39</v>
+        <v>0.58</v>
       </c>
       <c r="H7" t="n">
-        <v>2500</v>
+        <v>15500</v>
       </c>
       <c r="I7" t="n">
-        <v>42.3</v>
+        <v>44.4</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.49</v>
+        <v>-0.31</v>
       </c>
       <c r="K7" t="n">
-        <v>0.32</v>
+        <v>1.5</v>
       </c>
       <c r="L7" t="n">
-        <v>-6.15</v>
+        <v>-6.07</v>
       </c>
       <c r="M7" t="n">
-        <v>-7.22</v>
+        <v>-7.21</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -28913,7 +29071,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>537.7</v>
+        <v>537.71</v>
       </c>
       <c r="Q7" t="n">
         <v>582.11</v>
@@ -28924,7 +29082,7 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -28941,6 +29099,7 @@
           <t>【AI分析レポート】
 ・🔴 下降
 ・MACDは買いシグナルです。
+・出来高が増加しています。
 ・ボリンジャーバンド中心付近で推移しています。
 ⚠️ 下落トレンドです。
 無理な買いは避け、反転サインを待ちましょう。</t>
@@ -28976,31 +29135,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1094</v>
+        <v>1082</v>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>1.39</v>
+        <v>0.28</v>
       </c>
       <c r="H8" t="n">
-        <v>800</v>
+        <v>2400</v>
       </c>
       <c r="I8" t="n">
-        <v>44.6</v>
+        <v>41.1</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.21</v>
+        <v>-4.23</v>
       </c>
       <c r="K8" t="n">
-        <v>0.29</v>
+        <v>0.79</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.73</v>
+        <v>-7.68</v>
       </c>
       <c r="M8" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -29009,34 +29168,134 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1055.92</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1019.6</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>70</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7033.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>マネジメントソリューションズ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PMO支援・DX案件増加</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1577</v>
+      </c>
+      <c r="F9" t="n">
+        <v>26</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H9" t="n">
+        <v>49200</v>
+      </c>
+      <c r="I9" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L9" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="M9" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P8" t="n">
-        <v>1056.08</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1019.65</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P9" t="n">
+        <v>1454.61</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1381.9</v>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S8" t="n">
+      <c r="S9" t="n">
         <v>65</v>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -29046,106 +29305,6 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>7033.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>マネジメントソリューションズ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PMO支援・DX案件増加</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1559</v>
-      </c>
-      <c r="F9" t="n">
-        <v>8</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H9" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I9" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-3.71</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>21.61</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>1454.37</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1381.81</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>65</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
@@ -29176,31 +29335,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="F10" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.71</v>
+        <v>0.1</v>
       </c>
       <c r="H10" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="I10" t="n">
-        <v>42.1</v>
+        <v>45.1</v>
       </c>
       <c r="J10" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="K10" t="n">
-        <v>1.46</v>
+        <v>0.67</v>
       </c>
       <c r="L10" t="n">
-        <v>19.34</v>
+        <v>18.09</v>
       </c>
       <c r="M10" t="n">
-        <v>23.01</v>
+        <v>22.03</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -29213,10 +29372,10 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>874.91</v>
+        <v>877.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>986.62</v>
+        <v>986.73</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -29241,6 +29400,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
+・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -29276,31 +29436,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3591</v>
+        <v>3559</v>
       </c>
       <c r="F11" t="n">
-        <v>-9</v>
+        <v>-41</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.25</v>
+        <v>-1.14</v>
       </c>
       <c r="H11" t="n">
-        <v>1410700</v>
+        <v>3985100</v>
       </c>
       <c r="I11" t="n">
-        <v>47.4</v>
+        <v>45.1</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.16</v>
+        <v>-1.01</v>
       </c>
       <c r="K11" t="n">
-        <v>0.36</v>
+        <v>0.89</v>
       </c>
       <c r="L11" t="n">
-        <v>-35.04</v>
+        <v>-37.6</v>
       </c>
       <c r="M11" t="n">
-        <v>-45.44</v>
+        <v>-45.95</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -29313,10 +29473,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3663.88</v>
+        <v>3663.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>2942.07</v>
+        <v>2941.91</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -29381,31 +29541,31 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>3675</v>
+        <v>3695</v>
       </c>
       <c r="F12" t="n">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="G12" t="n">
-        <v>4.4</v>
+        <v>4.97</v>
       </c>
       <c r="H12" t="n">
-        <v>704400</v>
+        <v>1143400</v>
       </c>
       <c r="I12" t="n">
-        <v>43.2</v>
+        <v>44</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.66</v>
+        <v>-0.14</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1</v>
+        <v>1.57</v>
       </c>
       <c r="L12" t="n">
-        <v>49.74</v>
+        <v>51.34</v>
       </c>
       <c r="M12" t="n">
-        <v>82.34</v>
+        <v>82.66</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -29418,10 +29578,10 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3218.39</v>
+        <v>3218.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>3060.03</v>
+        <v>3060.13</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -29429,7 +29589,7 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -29446,6 +29606,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
+・出来高が増加しています。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -29477,31 +29638,31 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>4877</v>
+        <v>4867</v>
       </c>
       <c r="F13" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>0.79</v>
+        <v>0.58</v>
       </c>
       <c r="H13" t="n">
-        <v>20060900</v>
+        <v>30234600</v>
       </c>
       <c r="I13" t="n">
-        <v>40.6</v>
+        <v>40.3</v>
       </c>
       <c r="J13" t="n">
-        <v>-7.1</v>
+        <v>-7.28</v>
       </c>
       <c r="K13" t="n">
-        <v>0.66</v>
+        <v>0.93</v>
       </c>
       <c r="L13" t="n">
-        <v>-76.77</v>
+        <v>-77.56999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-17.08</v>
+        <v>-17.24</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -29514,10 +29675,10 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5068.75</v>
+        <v>5068.61</v>
       </c>
       <c r="Q13" t="n">
-        <v>4494.05</v>
+        <v>4494</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -29585,31 +29746,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="F14" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G14" t="n">
-        <v>1.88</v>
+        <v>1.69</v>
       </c>
       <c r="H14" t="n">
-        <v>102700</v>
+        <v>269300</v>
       </c>
       <c r="I14" t="n">
-        <v>27.9</v>
+        <v>27.4</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.74</v>
+        <v>-4.91</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.24</v>
       </c>
       <c r="L14" t="n">
-        <v>-19.05</v>
+        <v>-19.21</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.609999999999999</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -29622,10 +29783,10 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1111.56</v>
+        <v>1111.53</v>
       </c>
       <c r="Q14" t="n">
-        <v>928.9</v>
+        <v>928.89</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -29686,31 +29847,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3785</v>
+        <v>3763</v>
       </c>
       <c r="F15" t="n">
-        <v>-27</v>
+        <v>-49</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.71</v>
+        <v>-1.29</v>
       </c>
       <c r="H15" t="n">
-        <v>15049000</v>
+        <v>23256200</v>
       </c>
       <c r="I15" t="n">
-        <v>46.9</v>
+        <v>46.4</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.03</v>
+        <v>-3.58</v>
       </c>
       <c r="K15" t="n">
-        <v>0.74</v>
+        <v>1.06</v>
       </c>
       <c r="L15" t="n">
-        <v>-4.22</v>
+        <v>-5.97</v>
       </c>
       <c r="M15" t="n">
-        <v>10.38</v>
+        <v>10.03</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -29723,10 +29884,10 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>4003.25</v>
+        <v>4002.96</v>
       </c>
       <c r="Q15" t="n">
-        <v>3181.79</v>
+        <v>3181.68</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -29791,31 +29952,31 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>3955</v>
+        <v>4025</v>
       </c>
       <c r="F16" t="n">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="G16" t="n">
-        <v>0.38</v>
+        <v>2.16</v>
       </c>
       <c r="H16" t="n">
-        <v>9100</v>
+        <v>21800</v>
       </c>
       <c r="I16" t="n">
-        <v>35.9</v>
+        <v>39.1</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.25</v>
+        <v>-1.61</v>
       </c>
       <c r="K16" t="n">
-        <v>0.46</v>
+        <v>0.98</v>
       </c>
       <c r="L16" t="n">
-        <v>20.46</v>
+        <v>26.05</v>
       </c>
       <c r="M16" t="n">
-        <v>68.09</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -29828,10 +29989,10 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3579.57</v>
+        <v>3580.51</v>
       </c>
       <c r="Q16" t="n">
-        <v>2849.02</v>
+        <v>2849.37</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -29890,28 +30051,28 @@
         <v>2421</v>
       </c>
       <c r="F17" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="H17" t="n">
-        <v>5543200</v>
+        <v>11028700</v>
       </c>
       <c r="I17" t="n">
         <v>33.8</v>
       </c>
       <c r="J17" t="n">
-        <v>-4.63</v>
+        <v>-4.61</v>
       </c>
       <c r="K17" t="n">
-        <v>0.51</v>
+        <v>0.91</v>
       </c>
       <c r="L17" t="n">
-        <v>-91</v>
+        <v>-90.95999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-92.53</v>
+        <v>-92.52</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -29924,7 +30085,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2740.23</v>
+        <v>2740.24</v>
       </c>
       <c r="Q17" t="n">
         <v>2830.08</v>
@@ -29995,31 +30156,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="F18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="H18" t="n">
-        <v>9888000</v>
+        <v>20929600</v>
       </c>
       <c r="I18" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.88</v>
+        <v>-0.92</v>
       </c>
       <c r="K18" t="n">
-        <v>0.51</v>
+        <v>0.96</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="M18" t="n">
-        <v>12.04</v>
+        <v>12.02</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -30032,7 +30193,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2936.87</v>
+        <v>2936.86</v>
       </c>
       <c r="Q18" t="n">
         <v>3164.88</v>
@@ -30099,31 +30260,31 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>1824</v>
+        <v>1845</v>
       </c>
       <c r="F19" t="n">
-        <v>38</v>
+        <v>58.5</v>
       </c>
       <c r="G19" t="n">
-        <v>2.13</v>
+        <v>3.28</v>
       </c>
       <c r="H19" t="n">
-        <v>3089500</v>
+        <v>9541700</v>
       </c>
       <c r="I19" t="n">
-        <v>55.5</v>
+        <v>57.5</v>
       </c>
       <c r="J19" t="n">
-        <v>2.06</v>
+        <v>3.16</v>
       </c>
       <c r="K19" t="n">
-        <v>0.41</v>
+        <v>1.08</v>
       </c>
       <c r="L19" t="n">
-        <v>24.9</v>
+        <v>26.53</v>
       </c>
       <c r="M19" t="n">
-        <v>32.51</v>
+        <v>32.84</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -30132,14 +30293,14 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1675.98</v>
+        <v>1676.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>1567.44</v>
+        <v>1567.54</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -30165,7 +30326,7 @@
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -30208,31 +30369,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>2.94</v>
+        <v>2.73</v>
       </c>
       <c r="H20" t="n">
-        <v>286800</v>
+        <v>635100</v>
       </c>
       <c r="I20" t="n">
-        <v>49.1</v>
+        <v>48.8</v>
       </c>
       <c r="J20" t="n">
-        <v>5.19</v>
+        <v>4.98</v>
       </c>
       <c r="K20" t="n">
-        <v>0.36</v>
+        <v>0.72</v>
       </c>
       <c r="L20" t="n">
-        <v>6.61</v>
+        <v>6.53</v>
       </c>
       <c r="M20" t="n">
-        <v>6.15</v>
+        <v>6.13</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -30245,7 +30406,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>433.58</v>
+        <v>433.56</v>
       </c>
       <c r="Q20" t="n">
         <v>413.29</v>
@@ -30305,31 +30466,31 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>8962</v>
+        <v>9000</v>
       </c>
       <c r="F21" t="n">
-        <v>-402</v>
+        <v>-364</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.29</v>
+        <v>-3.89</v>
       </c>
       <c r="H21" t="n">
-        <v>15635500</v>
+        <v>26019400</v>
       </c>
       <c r="I21" t="n">
-        <v>46.9</v>
+        <v>47.3</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.59</v>
+        <v>-4.2</v>
       </c>
       <c r="K21" t="n">
-        <v>0.57</v>
+        <v>0.89</v>
       </c>
       <c r="L21" t="n">
-        <v>-415.02</v>
+        <v>-411.98</v>
       </c>
       <c r="M21" t="n">
-        <v>-529.08</v>
+        <v>-528.48</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -30342,10 +30503,10 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>12957.01</v>
+        <v>12957.52</v>
       </c>
       <c r="Q21" t="n">
-        <v>7954.19</v>
+        <v>7954.38</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -30406,31 +30567,31 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>49760</v>
+        <v>49880</v>
       </c>
       <c r="F22" t="n">
-        <v>-1020</v>
+        <v>-900</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.01</v>
+        <v>-1.77</v>
       </c>
       <c r="H22" t="n">
-        <v>13782800</v>
+        <v>25108400</v>
       </c>
       <c r="I22" t="n">
-        <v>53.6</v>
+        <v>53.8</v>
       </c>
       <c r="J22" t="n">
-        <v>-6.44</v>
+        <v>-6.22</v>
       </c>
       <c r="K22" t="n">
-        <v>0.54</v>
+        <v>0.91</v>
       </c>
       <c r="L22" t="n">
-        <v>-895.5</v>
+        <v>-885.9299999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-779.88</v>
+        <v>-777.96</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -30443,10 +30604,10 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>65510.93</v>
+        <v>65512.53</v>
       </c>
       <c r="Q22" t="n">
-        <v>39994.21</v>
+        <v>39994.82</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -30507,28 +30668,28 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>164.3</v>
+        <v>164</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="G23" t="n">
-        <v>0.67</v>
+        <v>0.49</v>
       </c>
       <c r="H23" t="n">
-        <v>28531900</v>
+        <v>50330300</v>
       </c>
       <c r="I23" t="n">
-        <v>47.8</v>
+        <v>47.3</v>
       </c>
       <c r="J23" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="K23" t="n">
-        <v>0.63</v>
+        <v>1.01</v>
       </c>
       <c r="L23" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="M23" t="n">
         <v>1.76</v>
@@ -30547,7 +30708,7 @@
         <v>152.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>150.74</v>
+        <v>150.73</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -30608,31 +30769,31 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>3182</v>
+        <v>3168</v>
       </c>
       <c r="F24" t="n">
-        <v>-58</v>
+        <v>-72</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.79</v>
+        <v>-2.22</v>
       </c>
       <c r="H24" t="n">
-        <v>4272400</v>
+        <v>9206600</v>
       </c>
       <c r="I24" t="n">
-        <v>37.3</v>
+        <v>36.7</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.9</v>
+        <v>-6.29</v>
       </c>
       <c r="K24" t="n">
-        <v>0.57</v>
+        <v>1.08</v>
       </c>
       <c r="L24" t="n">
-        <v>-138.34</v>
+        <v>-139.46</v>
       </c>
       <c r="M24" t="n">
-        <v>-149.2</v>
+        <v>-149.42</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -30645,10 +30806,10 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>4004.72</v>
+        <v>4004.53</v>
       </c>
       <c r="Q24" t="n">
-        <v>3193.64</v>
+        <v>3193.57</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -30808,31 +30969,31 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>8455</v>
+        <v>8475</v>
       </c>
       <c r="F26" t="n">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="G26" t="n">
-        <v>4.05</v>
+        <v>4.29</v>
       </c>
       <c r="H26" t="n">
-        <v>4244100</v>
+        <v>7644500</v>
       </c>
       <c r="I26" t="n">
-        <v>36.9</v>
+        <v>37.5</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.26</v>
+        <v>-2.04</v>
       </c>
       <c r="K26" t="n">
-        <v>0.59</v>
+        <v>0.97</v>
       </c>
       <c r="L26" t="n">
-        <v>1.14</v>
+        <v>2.74</v>
       </c>
       <c r="M26" t="n">
-        <v>102.45</v>
+        <v>102.77</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -30845,10 +31006,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7755.44</v>
+        <v>7755.71</v>
       </c>
       <c r="Q26" t="n">
-        <v>8700.57</v>
+        <v>8700.67</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>212,412円</t>
+          <t>214,233円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3,122円</t>
+          <t>4,943円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3445</v>
+        <v>3395</v>
       </c>
       <c r="F2" t="n">
-        <v>36.8</v>
+        <v>31</v>
       </c>
       <c r="G2" t="n">
-        <v>0.38</v>
+        <v>-1.03</v>
       </c>
       <c r="H2" t="n">
-        <v>0.62</v>
+        <v>0.31</v>
       </c>
       <c r="I2" t="n">
-        <v>24.32</v>
+        <v>22.68</v>
       </c>
       <c r="J2" t="n">
-        <v>55.4</v>
+        <v>48.85</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3031.73</v>
+        <v>3044.6</v>
       </c>
       <c r="N2" t="n">
-        <v>2723.9</v>
+        <v>2726.83</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -757,11 +757,11 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -786,29 +786,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>25日線上、MACD売り、長期上昇</t>
+          <t>押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3310</v>
+        <v>3445</v>
       </c>
       <c r="X2" t="n">
-        <v>135</v>
+        <v>-50</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.08</v>
+        <v>-1.45</v>
       </c>
       <c r="Z2" t="n">
-        <v>13780</v>
+        <v>13580</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2980</v>
+        <v>2780</v>
       </c>
       <c r="AC2" t="n">
-        <v>27.59</v>
+        <v>25.74</v>
       </c>
     </row>
     <row r="3">
@@ -829,22 +829,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="F3" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="G3" t="n">
-        <v>4.98</v>
+        <v>6.1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.72</v>
+        <v>0.23</v>
       </c>
       <c r="I3" t="n">
-        <v>6.53</v>
+        <v>8.18</v>
       </c>
       <c r="J3" t="n">
-        <v>6.13</v>
+        <v>6.54</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>433.56</v>
+        <v>434.33</v>
       </c>
       <c r="N3" t="n">
-        <v>413.29</v>
+        <v>414</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -903,25 +903,25 @@
         </is>
       </c>
       <c r="W3" t="n">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="X3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.73</v>
+        <v>1.64</v>
       </c>
       <c r="Z3" t="n">
-        <v>48900</v>
+        <v>49700</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6900</v>
+        <v>7700</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.43</v>
+        <v>18.33</v>
       </c>
     </row>
     <row r="4">
@@ -942,22 +942,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>180</v>
+        <v>177.3</v>
       </c>
       <c r="F4" t="n">
-        <v>70.8</v>
+        <v>59.2</v>
       </c>
       <c r="G4" t="n">
-        <v>5.63</v>
+        <v>3.69</v>
       </c>
       <c r="H4" t="n">
-        <v>0.96</v>
+        <v>0.52</v>
       </c>
       <c r="I4" t="n">
-        <v>4.76</v>
+        <v>4.58</v>
       </c>
       <c r="J4" t="n">
-        <v>4.62</v>
+        <v>4.61</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>156.62</v>
+        <v>157.02</v>
       </c>
       <c r="N4" t="n">
-        <v>154.21</v>
+        <v>154.35</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1002,8 +1002,8 @@
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
-・MACDは買いシグナルです。
-・買われ過ぎ水準です。
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -1012,29 +1012,29 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSIやや過熱、25日線上、+1σ、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、+1σ、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>177.1</v>
+        <v>180</v>
       </c>
       <c r="X4" t="n">
-        <v>2.9</v>
+        <v>-2.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.64</v>
+        <v>-1.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>18000</v>
+        <v>17730</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>2200</v>
+        <v>1930</v>
       </c>
       <c r="AC4" t="n">
-        <v>13.92</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="5">
@@ -1055,22 +1055,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3034</v>
+        <v>3003</v>
       </c>
       <c r="F5" t="n">
-        <v>42.2</v>
+        <v>35.2</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.92</v>
+        <v>-1.91</v>
       </c>
       <c r="H5" t="n">
-        <v>0.96</v>
+        <v>0.59</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05</v>
+        <v>-2.83</v>
       </c>
       <c r="J5" t="n">
-        <v>12.02</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2936.86</v>
+        <v>2938.49</v>
       </c>
       <c r="N5" t="n">
-        <v>3164.88</v>
+        <v>3164.73</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1128,25 +1128,25 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>3016</v>
+        <v>3034</v>
       </c>
       <c r="X5" t="n">
-        <v>18</v>
+        <v>-31</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6</v>
+        <v>-1.02</v>
       </c>
       <c r="Z5" t="n">
-        <v>39442</v>
+        <v>39039</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>2343</v>
+        <v>1940</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.32</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="6">
@@ -1167,22 +1167,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>8475</v>
+        <v>8307</v>
       </c>
       <c r="F6" t="n">
-        <v>37.5</v>
+        <v>33.2</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.04</v>
+        <v>-3.72</v>
       </c>
       <c r="H6" t="n">
-        <v>0.97</v>
+        <v>0.39</v>
       </c>
       <c r="I6" t="n">
-        <v>2.74</v>
+        <v>-5.04</v>
       </c>
       <c r="J6" t="n">
-        <v>102.77</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1191,14 +1191,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>7755.71</v>
+        <v>7767.04</v>
       </c>
       <c r="N6" t="n">
-        <v>8700.67</v>
+        <v>8677.870000000001</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
@@ -1236,29 +1236,29 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、上昇トレンド</t>
+          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>8126</v>
+        <v>8475</v>
       </c>
       <c r="X6" t="n">
-        <v>349</v>
+        <v>-168</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.29</v>
+        <v>-1.98</v>
       </c>
       <c r="Z6" t="n">
-        <v>8475</v>
+        <v>8307</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>482</v>
+        <v>314</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.03</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="7">
@@ -1279,22 +1279,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4979</v>
+        <v>4944</v>
       </c>
       <c r="F7" t="n">
-        <v>58.6</v>
+        <v>56.2</v>
       </c>
       <c r="G7" t="n">
-        <v>2.41</v>
+        <v>1.54</v>
       </c>
       <c r="H7" t="n">
-        <v>0.86</v>
+        <v>0.38</v>
       </c>
       <c r="I7" t="n">
-        <v>57.51</v>
+        <v>53.28</v>
       </c>
       <c r="J7" t="n">
-        <v>58.86</v>
+        <v>57.74</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4717.76</v>
+        <v>4717.29</v>
       </c>
       <c r="N7" t="n">
-        <v>4677.05</v>
+        <v>4683.76</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1353,61 +1353,61 @@
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4944</v>
+        <v>4979</v>
       </c>
       <c r="X7" t="n">
-        <v>35</v>
+        <v>-35</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.71</v>
+        <v>-0.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>24895</v>
+        <v>24720</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>920</v>
+        <v>745</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.84</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6976.T</t>
+          <t>285A.T</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>太陽誘電</t>
+          <t>キオクシアホールディングス</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>10000</v>
+        <v>55510</v>
       </c>
       <c r="E8" t="n">
-        <v>9000</v>
+        <v>51960</v>
       </c>
       <c r="F8" t="n">
-        <v>47.3</v>
+        <v>53.8</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.2</v>
+        <v>-2.18</v>
       </c>
       <c r="H8" t="n">
-        <v>0.89</v>
+        <v>0.59</v>
       </c>
       <c r="I8" t="n">
-        <v>-411.98</v>
+        <v>-881.3</v>
       </c>
       <c r="J8" t="n">
-        <v>-528.48</v>
+        <v>-798.63</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>12957.52</v>
+        <v>65164.27</v>
       </c>
       <c r="N8" t="n">
-        <v>7954.38</v>
+        <v>40205.35</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1449,6 +1449,119 @@
         </is>
       </c>
       <c r="T8" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>RSI適正、押し目、MACD売り、反発局面</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>49880</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2080</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>51960</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>55510</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-3550</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-6.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9157</v>
+      </c>
+      <c r="F9" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-384.19</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-499.62</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>12856.28</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7984.31</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>65</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -1459,145 +1572,32 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>押し目、MACD買い、反発局面</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>9364</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-364</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-3.89</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>9000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>285A.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>キオクシアホールディングス</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>55510</v>
-      </c>
-      <c r="E9" t="n">
-        <v>49880</v>
-      </c>
-      <c r="F9" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-6.22</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-885.9299999999999</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-777.96</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>65512.53</v>
-      </c>
-      <c r="N9" t="n">
-        <v>39994.82</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>65</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD売り、反発局面</t>
+          <t>押し目、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>50780</v>
+        <v>9000</v>
       </c>
       <c r="X9" t="n">
-        <v>-900</v>
+        <v>157</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.77</v>
+        <v>1.74</v>
       </c>
       <c r="Z9" t="n">
-        <v>49880</v>
+        <v>9157</v>
       </c>
       <c r="AA9" t="n">
-        <v>55510</v>
+        <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-5630</v>
+        <v>-843</v>
       </c>
       <c r="AC9" t="n">
-        <v>-10.14</v>
+        <v>-8.43</v>
       </c>
     </row>
     <row r="10">
@@ -1627,7 +1627,7 @@
         <v>6.6</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="I10" t="n">
         <v>1.14</v>
@@ -1730,7 +1730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1475"/>
+  <dimension ref="A1:C1484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23857,6 +23857,141 @@
         </is>
       </c>
       <c r="C1475" t="n">
+        <v>40.35</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1476" t="n">
+        <v>3395</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1477" t="n">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1478" t="n">
+        <v>177.3</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1479" t="n">
+        <v>3003</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1480" t="n">
+        <v>8307</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1481" t="n">
+        <v>4944</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1482" t="n">
+        <v>51960</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1483" t="n">
+        <v>9157</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1484" t="n">
         <v>40.35</v>
       </c>
     </row>
@@ -23871,7 +24006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F250"/>
+  <dimension ref="A1:F251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28335,19 +28470,29 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
+      <c r="A248" t="inlineStr"/>
+      <c r="B248" s="1" t="n">
+        <v>46283.5</v>
+      </c>
+      <c r="C248" t="n">
+        <v>214233</v>
+      </c>
+      <c r="D248" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E248" t="n">
+        <v>4943</v>
+      </c>
+      <c r="F248" t="n">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr"/>
-      <c r="C248" t="inlineStr"/>
-      <c r="D248" t="inlineStr"/>
-      <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr"/>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr"/>
       <c r="B249" t="inlineStr"/>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr"/>
@@ -28355,16 +28500,24 @@
       <c r="F249" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A250" t="inlineStr"/>
       <c r="B250" t="inlineStr"/>
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr"/>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -30869,31 +31022,31 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>48.24</v>
+        <v>52.55</v>
       </c>
       <c r="F25" t="n">
-        <v>0.74</v>
+        <v>4.31</v>
       </c>
       <c r="G25" t="n">
-        <v>1.56</v>
+        <v>8.93</v>
       </c>
       <c r="H25" t="n">
-        <v>1098100</v>
+        <v>1395762</v>
       </c>
       <c r="I25" t="n">
-        <v>41.6</v>
+        <v>50.2</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.63</v>
+        <v>1.1</v>
       </c>
       <c r="K25" t="n">
-        <v>0.9</v>
+        <v>1.08</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.13</v>
+        <v>-1.72</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.16</v>
+        <v>-2.08</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -30906,10 +31059,10 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>59.37</v>
+        <v>59.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>37.69</v>
+        <v>37.85</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -30917,16 +31070,16 @@
         </is>
       </c>
       <c r="S25" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -30934,6 +31087,7 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
+・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
@@ -30951,7 +31105,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
+          <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>214,233円</t>
+          <t>216,574円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4,943円</t>
+          <t>7,284円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>3.48%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3395</v>
+        <v>3340</v>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>29.5</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.03</v>
+        <v>-2.57</v>
       </c>
       <c r="H2" t="n">
-        <v>0.31</v>
+        <v>0.58</v>
       </c>
       <c r="I2" t="n">
-        <v>22.68</v>
+        <v>18.29</v>
       </c>
       <c r="J2" t="n">
-        <v>48.85</v>
+        <v>47.98</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3044.6</v>
+        <v>3043.87</v>
       </c>
       <c r="N2" t="n">
-        <v>2726.83</v>
+        <v>2726.56</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -757,20 +757,20 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -778,6 +778,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
+・売られ過ぎ水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -786,29 +787,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>RSI売られすぎ、押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>3445</v>
       </c>
       <c r="X2" t="n">
-        <v>-50</v>
+        <v>-105</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.45</v>
+        <v>-3.05</v>
       </c>
       <c r="Z2" t="n">
-        <v>13580</v>
+        <v>13360</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2780</v>
+        <v>2560</v>
       </c>
       <c r="AC2" t="n">
-        <v>25.74</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="3">
@@ -829,22 +830,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="F3" t="n">
-        <v>49.1</v>
+        <v>47.1</v>
       </c>
       <c r="G3" t="n">
-        <v>6.1</v>
+        <v>4.87</v>
       </c>
       <c r="H3" t="n">
-        <v>0.23</v>
+        <v>0.65</v>
       </c>
       <c r="I3" t="n">
-        <v>8.18</v>
+        <v>7.7</v>
       </c>
       <c r="J3" t="n">
-        <v>6.54</v>
+        <v>6.45</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -857,10 +858,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>434.33</v>
+        <v>434.25</v>
       </c>
       <c r="N3" t="n">
-        <v>414</v>
+        <v>413.97</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -906,22 +907,22 @@
         <v>489</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.64</v>
+        <v>0.41</v>
       </c>
       <c r="Z3" t="n">
-        <v>49700</v>
+        <v>49100</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7700</v>
+        <v>7100</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.33</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="4">
@@ -951,7 +952,7 @@
         <v>3.69</v>
       </c>
       <c r="H4" t="n">
-        <v>0.52</v>
+        <v>1.35</v>
       </c>
       <c r="I4" t="n">
         <v>4.58</v>
@@ -1055,22 +1056,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3003</v>
+        <v>3025</v>
       </c>
       <c r="F5" t="n">
-        <v>35.2</v>
+        <v>36.8</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.91</v>
+        <v>-1.22</v>
       </c>
       <c r="H5" t="n">
-        <v>0.59</v>
+        <v>1.82</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.83</v>
+        <v>-1.07</v>
       </c>
       <c r="J5" t="n">
-        <v>9.050000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1083,10 +1084,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2938.49</v>
+        <v>2938.78</v>
       </c>
       <c r="N5" t="n">
-        <v>3164.73</v>
+        <v>3164.84</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1099,19 +1100,132 @@
         </is>
       </c>
       <c r="Q5" t="n">
+        <v>60</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・出来高が増加しています。
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>押し目、出来高微増、MACD売り、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>3034</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-9</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>39325</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>37099</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2226</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7993</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8339</v>
+      </c>
+      <c r="F6" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-3.36</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="J6" t="n">
+        <v>81.72</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>7767.47</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8678.030000000001</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
         <v>55</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>★★☆☆☆</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 上昇
@@ -1121,144 +1235,32 @@
 順張りが有利な局面です。</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>押し目、MACD売り、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>3034</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-31</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>39039</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>37099</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1940</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.23</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>7993</v>
-      </c>
-      <c r="E6" t="n">
-        <v>8307</v>
-      </c>
-      <c r="F6" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-3.72</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-5.04</v>
-      </c>
-      <c r="J6" t="n">
-        <v>81.20999999999999</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>7767.04</v>
-      </c>
-      <c r="N6" t="n">
-        <v>8677.870000000001</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>60</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
+          <t>押し目、MACD売り、上昇トレンド</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>8475</v>
       </c>
       <c r="X6" t="n">
-        <v>-168</v>
+        <v>-136</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.98</v>
+        <v>-1.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>8307</v>
+        <v>8339</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>314</v>
+        <v>346</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.93</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="7">
@@ -1279,22 +1281,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4944</v>
+        <v>4947</v>
       </c>
       <c r="F7" t="n">
-        <v>56.2</v>
+        <v>56.3</v>
       </c>
       <c r="G7" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="H7" t="n">
-        <v>0.38</v>
+        <v>1.39</v>
       </c>
       <c r="I7" t="n">
-        <v>53.28</v>
+        <v>53.52</v>
       </c>
       <c r="J7" t="n">
-        <v>57.74</v>
+        <v>57.79</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1307,10 +1309,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4717.29</v>
+        <v>4717.33</v>
       </c>
       <c r="N7" t="n">
-        <v>4683.76</v>
+        <v>4683.77</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1356,22 +1358,22 @@
         <v>4979</v>
       </c>
       <c r="X7" t="n">
-        <v>-35</v>
+        <v>-32</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.7</v>
+        <v>-0.64</v>
       </c>
       <c r="Z7" t="n">
-        <v>24720</v>
+        <v>24735</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.11</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="8">
@@ -1392,22 +1394,22 @@
         <v>55510</v>
       </c>
       <c r="E8" t="n">
-        <v>51960</v>
+        <v>54570</v>
       </c>
       <c r="F8" t="n">
-        <v>53.8</v>
+        <v>58.1</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.18</v>
+        <v>2.53</v>
       </c>
       <c r="H8" t="n">
-        <v>0.59</v>
+        <v>1.19</v>
       </c>
       <c r="I8" t="n">
-        <v>-881.3</v>
+        <v>-673.09</v>
       </c>
       <c r="J8" t="n">
-        <v>-798.63</v>
+        <v>-756.99</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1420,10 +1422,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>65164.27</v>
+        <v>65199.07</v>
       </c>
       <c r="N8" t="n">
-        <v>40205.35</v>
+        <v>40218.4</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1432,136 +1434,23 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>RSI適正、押し目、MACD売り、反発局面</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>49880</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2080</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>51960</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>55510</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-3550</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-6.4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E9" t="n">
-        <v>9157</v>
-      </c>
-      <c r="F9" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-384.19</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-499.62</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>12856.28</v>
-      </c>
-      <c r="N9" t="n">
-        <v>7984.31</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>65</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -1572,32 +1461,149 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>🚀 急騰</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>RSI適正、25日線上、MACD買い、反発局面</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>49880</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4690</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>54570</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>55510</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-940</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-1.69</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9375</v>
+      </c>
+      <c r="F9" t="n">
+        <v>52</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-366.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-496.14</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>12859.19</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7985.4</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>🟢 強い買い</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>95</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>押し目、MACD買い、反発局面</t>
+          <t>RSI適正、25日線上、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
         <v>9000</v>
       </c>
       <c r="X9" t="n">
-        <v>157</v>
+        <v>375</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.74</v>
+        <v>4.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>9157</v>
+        <v>9375</v>
       </c>
       <c r="AA9" t="n">
         <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-843</v>
+        <v>-625</v>
       </c>
       <c r="AC9" t="n">
-        <v>-8.43</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="10">
@@ -1730,7 +1736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1484"/>
+  <dimension ref="A1:C1493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23992,6 +23998,141 @@
         </is>
       </c>
       <c r="C1484" t="n">
+        <v>40.35</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1485" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1486" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1487" t="n">
+        <v>177.3</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1488" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1489" t="n">
+        <v>8339</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1490" t="n">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1491" t="n">
+        <v>54570</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1492" t="n">
+        <v>9375</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1493" t="n">
         <v>40.35</v>
       </c>
     </row>
@@ -24006,7 +24147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F251"/>
+  <dimension ref="A1:F252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28488,19 +28629,29 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
+      <c r="A249" t="inlineStr"/>
+      <c r="B249" s="1" t="n">
+        <v>46283.75</v>
+      </c>
+      <c r="C249" t="n">
+        <v>216574</v>
+      </c>
+      <c r="D249" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E249" t="n">
+        <v>7284</v>
+      </c>
+      <c r="F249" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr"/>
-      <c r="C249" t="inlineStr"/>
-      <c r="D249" t="inlineStr"/>
-      <c r="E249" t="inlineStr"/>
-      <c r="F249" t="inlineStr"/>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr"/>
       <c r="B250" t="inlineStr"/>
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr"/>
@@ -28508,16 +28659,24 @@
       <c r="F250" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A251" t="inlineStr"/>
       <c r="B251" t="inlineStr"/>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -28685,28 +28844,28 @@
         <v>1001</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>742700</v>
+        <v>365300</v>
       </c>
       <c r="I2" t="n">
-        <v>37.4</v>
+        <v>40.6</v>
       </c>
       <c r="J2" t="n">
-        <v>0.45</v>
+        <v>-0.09</v>
       </c>
       <c r="K2" t="n">
-        <v>1.09</v>
+        <v>0.6</v>
       </c>
       <c r="L2" t="n">
-        <v>29.3</v>
+        <v>26.38</v>
       </c>
       <c r="M2" t="n">
-        <v>39.79</v>
+        <v>37.11</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -28719,10 +28878,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>849.59</v>
+        <v>853.9299999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>1117.96</v>
+        <v>1116.07</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -28730,16 +28889,16 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -28756,7 +28915,7 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>⚪ 様子見（押し目ではない）</t>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -28782,31 +28941,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3445</v>
+        <v>3395</v>
       </c>
       <c r="F3" t="n">
-        <v>135</v>
+        <v>-50</v>
       </c>
       <c r="G3" t="n">
-        <v>4.08</v>
+        <v>-1.45</v>
       </c>
       <c r="H3" t="n">
-        <v>89400</v>
+        <v>43700</v>
       </c>
       <c r="I3" t="n">
-        <v>36.8</v>
+        <v>31</v>
       </c>
       <c r="J3" t="n">
-        <v>0.38</v>
+        <v>-1.03</v>
       </c>
       <c r="K3" t="n">
-        <v>0.62</v>
+        <v>0.31</v>
       </c>
       <c r="L3" t="n">
-        <v>24.32</v>
+        <v>22.68</v>
       </c>
       <c r="M3" t="n">
-        <v>55.4</v>
+        <v>48.85</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -28819,10 +28978,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3031.73</v>
+        <v>3044.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2723.9</v>
+        <v>2726.83</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -28830,7 +28989,7 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -28856,7 +29015,7 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>⚪ 様子見（押し目ではない）</t>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -28882,31 +29041,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1347</v>
+        <v>1333</v>
       </c>
       <c r="F4" t="n">
-        <v>22</v>
+        <v>-14</v>
       </c>
       <c r="G4" t="n">
-        <v>1.66</v>
+        <v>-1.04</v>
       </c>
       <c r="H4" t="n">
-        <v>29800</v>
+        <v>3800</v>
       </c>
       <c r="I4" t="n">
-        <v>58</v>
+        <v>52.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.54</v>
+        <v>2.11</v>
       </c>
       <c r="K4" t="n">
-        <v>2.43</v>
+        <v>0.35</v>
       </c>
       <c r="L4" t="n">
-        <v>34.43</v>
+        <v>31.6</v>
       </c>
       <c r="M4" t="n">
-        <v>39.5</v>
+        <v>37.92</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -28919,10 +29078,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1206.57</v>
+        <v>1208.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>1639.81</v>
+        <v>1638.78</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -28930,625 +29089,19 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・出来高が急増しています。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>5532.T</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>リアルゲイト</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>オフィス再生</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>3475</v>
-      </c>
-      <c r="F5" t="n">
-        <v>45</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3900</v>
-      </c>
-      <c r="I5" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="M5" t="n">
-        <v>8.24</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>3421.4</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3151.5</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>100</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>3984.T</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ユーザーローカル</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>AI解析・データ分析</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1552</v>
-      </c>
-      <c r="F6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H6" t="n">
-        <v>64500</v>
-      </c>
-      <c r="I6" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-24.05</v>
-      </c>
-      <c r="M6" t="n">
-        <v>-33.16</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>1679.72</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1697.45</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v>40</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>4054.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>日本情報クリエイト</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>不動産向けクラウド</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>521</v>
-      </c>
-      <c r="F7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="H7" t="n">
-        <v>15500</v>
-      </c>
-      <c r="I7" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-6.07</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-7.21</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>537.71</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>582.11</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>35</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは買いシグナルです。
-・出来高が増加しています。
-・ボリンジャーバンド中心付近で推移しています。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7072.T</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>インティメート・マージャー</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>データマーケティング</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1082</v>
-      </c>
-      <c r="F8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2400</v>
-      </c>
-      <c r="I8" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-4.23</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-7.68</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>1055.92</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1019.6</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v>70</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>7033.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>マネジメントソリューションズ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PMO支援・DX案件増加</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1577</v>
-      </c>
-      <c r="F9" t="n">
-        <v>26</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H9" t="n">
-        <v>49200</v>
-      </c>
-      <c r="I9" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-2.64</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="L9" t="n">
-        <v>7.44</v>
-      </c>
-      <c r="M9" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>1454.61</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1381.9</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>65</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9342.T</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>スマサポ</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>不動産DX</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>981</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>600</v>
-      </c>
-      <c r="I10" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="L10" t="n">
-        <v>18.09</v>
-      </c>
-      <c r="M10" t="n">
-        <v>22.03</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>877.87</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>986.73</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>65</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 上昇
@@ -29559,11 +29112,616 @@
 順張りが有利な局面です。</t>
         </is>
       </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5532.T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>リアルゲイト</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>オフィス再生</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3495</v>
+      </c>
+      <c r="F5" t="n">
+        <v>20</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5200</v>
+      </c>
+      <c r="I5" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L5" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="M5" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>3421.2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3156.01</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>95</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3984.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ユーザーローカル</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AI解析・データ分析</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1558</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H6" t="n">
+        <v>23000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-21.21</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-30.77</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1676.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1695.75</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>55</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは買いシグナルです。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4054.T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>日本情報クリエイト</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>不動産向けクラウド</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>520</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12900</v>
+      </c>
+      <c r="I7" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-5.71</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-6.91</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>537.99</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>581.1799999999999</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>30</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは買いシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7072.T</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>インティメート・マージャー</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>データマーケティング</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1090</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I8" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-3.28</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-7.71</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1056.96</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1018.62</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>80</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・売られ過ぎ水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7033.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>マネジメントソリューションズ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PMO支援・DX案件増加</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1584</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H9" t="n">
+        <v>22500</v>
+      </c>
+      <c r="I9" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L9" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="M9" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1458.05</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1383.31</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>65</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9342.T</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>スマサポ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>不動産DX</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>961</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-20</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I10" t="n">
+        <v>38</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>880.52</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>986.75</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>65</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・出来高が急増しています。
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>⚪ 様子見（押し目ではない）</t>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -29589,31 +29747,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3559</v>
+        <v>3592</v>
       </c>
       <c r="F11" t="n">
-        <v>-41</v>
+        <v>33</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.14</v>
+        <v>0.93</v>
       </c>
       <c r="H11" t="n">
-        <v>3985100</v>
+        <v>1744200</v>
       </c>
       <c r="I11" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.01</v>
+        <v>0.26</v>
       </c>
       <c r="K11" t="n">
-        <v>0.89</v>
+        <v>0.53</v>
       </c>
       <c r="L11" t="n">
-        <v>-37.6</v>
+        <v>-30.94</v>
       </c>
       <c r="M11" t="n">
-        <v>-45.95</v>
+        <v>-42.95</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -29626,10 +29784,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3663.45</v>
+        <v>3660.51</v>
       </c>
       <c r="Q11" t="n">
-        <v>2941.91</v>
+        <v>2949.54</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -29637,7 +29795,7 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -29667,12 +29825,12 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>あと42日</t>
+          <t>あと41日</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
+          <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
@@ -29694,31 +29852,31 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>3695</v>
+        <v>3810</v>
       </c>
       <c r="F12" t="n">
-        <v>175</v>
+        <v>115</v>
       </c>
       <c r="G12" t="n">
-        <v>4.97</v>
+        <v>3.11</v>
       </c>
       <c r="H12" t="n">
-        <v>1143400</v>
+        <v>485700</v>
       </c>
       <c r="I12" t="n">
-        <v>44</v>
+        <v>46.4</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.14</v>
+        <v>3.03</v>
       </c>
       <c r="K12" t="n">
-        <v>1.57</v>
+        <v>0.73</v>
       </c>
       <c r="L12" t="n">
-        <v>51.34</v>
+        <v>60.17</v>
       </c>
       <c r="M12" t="n">
-        <v>82.66</v>
+        <v>78.16</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -29731,10 +29889,10 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3218.65</v>
+        <v>3230.27</v>
       </c>
       <c r="Q12" t="n">
-        <v>3060.13</v>
+        <v>3063.94</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -29742,7 +29900,7 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -29759,7 +29917,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・出来高が増加しています。
+・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -29769,7 +29927,7 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
+          <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
@@ -29791,31 +29949,31 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>4867</v>
+        <v>4926</v>
       </c>
       <c r="F13" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="G13" t="n">
-        <v>0.58</v>
+        <v>1.21</v>
       </c>
       <c r="H13" t="n">
-        <v>30234600</v>
+        <v>19898100</v>
       </c>
       <c r="I13" t="n">
-        <v>40.3</v>
+        <v>37.7</v>
       </c>
       <c r="J13" t="n">
-        <v>-7.28</v>
+        <v>-5.63</v>
       </c>
       <c r="K13" t="n">
-        <v>0.93</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-77.56999999999999</v>
+        <v>-79.23</v>
       </c>
       <c r="M13" t="n">
-        <v>-17.24</v>
+        <v>-29.64</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -29824,14 +29982,14 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5068.61</v>
+        <v>5067.61</v>
       </c>
       <c r="Q13" t="n">
-        <v>4494</v>
+        <v>4504.22</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -29839,16 +29997,16 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -29856,7 +30014,7 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
@@ -29868,7 +30026,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>あと54日</t>
+          <t>あと53日</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -29899,31 +30057,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1083</v>
+        <v>1099</v>
       </c>
       <c r="F14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="H14" t="n">
-        <v>269300</v>
+        <v>116200</v>
       </c>
       <c r="I14" t="n">
-        <v>27.4</v>
+        <v>34.4</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.91</v>
+        <v>-3.35</v>
       </c>
       <c r="K14" t="n">
-        <v>1.24</v>
+        <v>0.61</v>
       </c>
       <c r="L14" t="n">
-        <v>-19.21</v>
+        <v>-17.54</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.640000000000001</v>
+        <v>-11.22</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -29932,14 +30090,14 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1111.53</v>
+        <v>1113.44</v>
       </c>
       <c r="Q14" t="n">
-        <v>928.89</v>
+        <v>930.64</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -29947,16 +30105,16 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -29964,8 +30122,7 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
@@ -30000,31 +30157,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3763</v>
+        <v>3840</v>
       </c>
       <c r="F15" t="n">
-        <v>-49</v>
+        <v>77</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.29</v>
+        <v>2.05</v>
       </c>
       <c r="H15" t="n">
-        <v>23256200</v>
+        <v>11036900</v>
       </c>
       <c r="I15" t="n">
-        <v>46.4</v>
+        <v>45.3</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.58</v>
+        <v>-1.38</v>
       </c>
       <c r="K15" t="n">
-        <v>1.06</v>
+        <v>0.57</v>
       </c>
       <c r="L15" t="n">
-        <v>-5.97</v>
+        <v>-5.94</v>
       </c>
       <c r="M15" t="n">
-        <v>10.03</v>
+        <v>6.84</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -30037,10 +30194,10 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>4002.96</v>
+        <v>3983.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>3181.68</v>
+        <v>3196.41</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -30078,7 +30235,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>あと53日</t>
+          <t>あと52日</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -30105,31 +30262,31 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>4025</v>
+        <v>4050</v>
       </c>
       <c r="F16" t="n">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="G16" t="n">
-        <v>2.16</v>
+        <v>0.62</v>
       </c>
       <c r="H16" t="n">
-        <v>21800</v>
+        <v>5100</v>
       </c>
       <c r="I16" t="n">
-        <v>39.1</v>
+        <v>42.5</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.61</v>
+        <v>-0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>0.98</v>
+        <v>0.26</v>
       </c>
       <c r="L16" t="n">
-        <v>26.05</v>
+        <v>28.71</v>
       </c>
       <c r="M16" t="n">
-        <v>69.20999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -30142,10 +30299,10 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3580.51</v>
+        <v>3593.77</v>
       </c>
       <c r="Q16" t="n">
-        <v>2849.37</v>
+        <v>2859.73</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -30201,31 +30358,31 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>2421</v>
+        <v>2388</v>
       </c>
       <c r="F17" t="n">
-        <v>32.5</v>
+        <v>-33.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1.36</v>
+        <v>-1.38</v>
       </c>
       <c r="H17" t="n">
-        <v>11028700</v>
+        <v>4713600</v>
       </c>
       <c r="I17" t="n">
-        <v>33.8</v>
+        <v>34.3</v>
       </c>
       <c r="J17" t="n">
-        <v>-4.61</v>
+        <v>-5.24</v>
       </c>
       <c r="K17" t="n">
-        <v>0.91</v>
+        <v>0.44</v>
       </c>
       <c r="L17" t="n">
-        <v>-90.95999999999999</v>
+        <v>-87.05</v>
       </c>
       <c r="M17" t="n">
-        <v>-92.52</v>
+        <v>-91.43000000000001</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -30238,10 +30395,10 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2740.24</v>
+        <v>2734.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>2830.08</v>
+        <v>2832.27</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -30278,7 +30435,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>あと55日</t>
+          <t>あと54日</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -30309,31 +30466,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3034</v>
+        <v>3003</v>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
+        <v>-31</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6</v>
+        <v>-1.02</v>
       </c>
       <c r="H18" t="n">
-        <v>20929600</v>
+        <v>10836000</v>
       </c>
       <c r="I18" t="n">
-        <v>42.2</v>
+        <v>35.2</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.92</v>
+        <v>-1.91</v>
       </c>
       <c r="K18" t="n">
-        <v>0.96</v>
+        <v>0.59</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.05</v>
+        <v>-2.83</v>
       </c>
       <c r="M18" t="n">
-        <v>12.02</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -30346,10 +30503,10 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2936.86</v>
+        <v>2938.49</v>
       </c>
       <c r="Q18" t="n">
-        <v>3164.88</v>
+        <v>3164.73</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -30386,7 +30543,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>あと49日</t>
+          <t>あと48日</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -30413,31 +30570,31 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>1845</v>
+        <v>1812</v>
       </c>
       <c r="F19" t="n">
-        <v>58.5</v>
+        <v>-32.5</v>
       </c>
       <c r="G19" t="n">
-        <v>3.28</v>
+        <v>-1.76</v>
       </c>
       <c r="H19" t="n">
-        <v>9541700</v>
+        <v>3167000</v>
       </c>
       <c r="I19" t="n">
-        <v>57.5</v>
+        <v>52.1</v>
       </c>
       <c r="J19" t="n">
-        <v>3.16</v>
+        <v>1.29</v>
       </c>
       <c r="K19" t="n">
-        <v>1.08</v>
+        <v>0.46</v>
       </c>
       <c r="L19" t="n">
-        <v>26.53</v>
+        <v>24.77</v>
       </c>
       <c r="M19" t="n">
-        <v>32.84</v>
+        <v>31.22</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -30446,14 +30603,14 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1676.25</v>
+        <v>1677.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>1567.54</v>
+        <v>1570.74</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -30479,7 +30636,7 @@
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -30491,7 +30648,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>あと42日</t>
+          <t>あと41日</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -30522,31 +30679,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="F20" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>2.73</v>
+        <v>1.64</v>
       </c>
       <c r="H20" t="n">
-        <v>635100</v>
+        <v>168800</v>
       </c>
       <c r="I20" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="J20" t="n">
-        <v>4.98</v>
+        <v>6.1</v>
       </c>
       <c r="K20" t="n">
-        <v>0.72</v>
+        <v>0.23</v>
       </c>
       <c r="L20" t="n">
-        <v>6.53</v>
+        <v>8.18</v>
       </c>
       <c r="M20" t="n">
-        <v>6.13</v>
+        <v>6.54</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -30559,10 +30716,10 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>433.56</v>
+        <v>434.33</v>
       </c>
       <c r="Q20" t="n">
-        <v>413.29</v>
+        <v>414</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -30619,31 +30776,31 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>9000</v>
+        <v>9157</v>
       </c>
       <c r="F21" t="n">
-        <v>-364</v>
+        <v>157</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.89</v>
+        <v>1.74</v>
       </c>
       <c r="H21" t="n">
-        <v>26019400</v>
+        <v>12798500</v>
       </c>
       <c r="I21" t="n">
-        <v>47.3</v>
+        <v>49.7</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.2</v>
+        <v>-1.75</v>
       </c>
       <c r="K21" t="n">
-        <v>0.89</v>
+        <v>0.5</v>
       </c>
       <c r="L21" t="n">
-        <v>-411.98</v>
+        <v>-384.19</v>
       </c>
       <c r="M21" t="n">
-        <v>-528.48</v>
+        <v>-499.62</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -30656,10 +30813,10 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>12957.52</v>
+        <v>12856.28</v>
       </c>
       <c r="Q21" t="n">
-        <v>7954.38</v>
+        <v>7984.31</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -30697,7 +30854,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>あと49日</t>
+          <t>あと48日</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -30720,31 +30877,31 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>49880</v>
+        <v>51960</v>
       </c>
       <c r="F22" t="n">
-        <v>-900</v>
+        <v>2080</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.77</v>
+        <v>4.17</v>
       </c>
       <c r="H22" t="n">
-        <v>25108400</v>
+        <v>14725400</v>
       </c>
       <c r="I22" t="n">
         <v>53.8</v>
       </c>
       <c r="J22" t="n">
-        <v>-6.22</v>
+        <v>-2.18</v>
       </c>
       <c r="K22" t="n">
-        <v>0.91</v>
+        <v>0.59</v>
       </c>
       <c r="L22" t="n">
-        <v>-885.9299999999999</v>
+        <v>-881.3</v>
       </c>
       <c r="M22" t="n">
-        <v>-777.96</v>
+        <v>-798.63</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -30757,10 +30914,10 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>65512.53</v>
+        <v>65164.27</v>
       </c>
       <c r="Q22" t="n">
-        <v>39994.82</v>
+        <v>40205.35</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -30798,7 +30955,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>あと43日</t>
+          <t>あと42日</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -30821,31 +30978,31 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8</v>
+        <v>-2</v>
       </c>
       <c r="G23" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="H23" t="n">
+        <v>21739700</v>
+      </c>
+      <c r="I23" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K23" t="n">
         <v>0.49</v>
       </c>
-      <c r="H23" t="n">
-        <v>50330300</v>
-      </c>
-      <c r="I23" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1.01</v>
-      </c>
       <c r="L23" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="M23" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -30854,14 +31011,14 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>152.7</v>
+        <v>152.99</v>
       </c>
       <c r="Q23" t="n">
-        <v>150.73</v>
+        <v>150.84</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -30869,16 +31026,16 @@
         </is>
       </c>
       <c r="S23" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -30887,7 +31044,7 @@
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -30899,7 +31056,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>あと56日</t>
+          <t>あと55日</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -30922,31 +31079,31 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>3168</v>
+        <v>3228</v>
       </c>
       <c r="F24" t="n">
-        <v>-72</v>
+        <v>60</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.22</v>
+        <v>1.89</v>
       </c>
       <c r="H24" t="n">
-        <v>9206600</v>
+        <v>5098600</v>
       </c>
       <c r="I24" t="n">
-        <v>36.7</v>
+        <v>41.6</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.29</v>
+        <v>-3.93</v>
       </c>
       <c r="K24" t="n">
-        <v>1.08</v>
+        <v>0.68</v>
       </c>
       <c r="L24" t="n">
-        <v>-139.46</v>
+        <v>-131.67</v>
       </c>
       <c r="M24" t="n">
-        <v>-149.42</v>
+        <v>-145.87</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -30955,41 +31112,41 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>4004.53</v>
+        <v>3983.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>3193.57</v>
+        <v>3200.93</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>🔴 下降</t>
+          <t>🟡 反発中</t>
         </is>
       </c>
       <c r="S24" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🔴 下降
+・🟡 反発中
 ・MACDは買いシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -30999,12 +31156,12 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>あと41日</t>
+          <t>あと40日</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -31031,7 +31188,7 @@
         <v>8.93</v>
       </c>
       <c r="H25" t="n">
-        <v>1395762</v>
+        <v>1511000</v>
       </c>
       <c r="I25" t="n">
         <v>50.2</v>
@@ -31040,7 +31197,7 @@
         <v>1.1</v>
       </c>
       <c r="K25" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="L25" t="n">
         <v>-1.72</v>
@@ -31100,7 +31257,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>あと19日</t>
+          <t>あと18日</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -31123,31 +31280,31 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>8475</v>
+        <v>8307</v>
       </c>
       <c r="F26" t="n">
-        <v>349</v>
+        <v>-168</v>
       </c>
       <c r="G26" t="n">
-        <v>4.29</v>
+        <v>-1.98</v>
       </c>
       <c r="H26" t="n">
-        <v>7644500</v>
+        <v>2507300</v>
       </c>
       <c r="I26" t="n">
-        <v>37.5</v>
+        <v>33.2</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.04</v>
+        <v>-3.72</v>
       </c>
       <c r="K26" t="n">
-        <v>0.97</v>
+        <v>0.39</v>
       </c>
       <c r="L26" t="n">
-        <v>2.74</v>
+        <v>-5.04</v>
       </c>
       <c r="M26" t="n">
-        <v>102.77</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -31156,14 +31313,14 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7755.71</v>
+        <v>7767.04</v>
       </c>
       <c r="Q26" t="n">
-        <v>8700.67</v>
+        <v>8677.870000000001</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -31171,7 +31328,7 @@
         </is>
       </c>
       <c r="S26" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -31188,7 +31345,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
@@ -31200,7 +31357,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>あと49日</t>
+          <t>あと48日</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>216,574円</t>
+          <t>216,573円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7,284円</t>
+          <t>7,283円</t>
         </is>
       </c>
     </row>
@@ -1624,38 +1624,38 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>40.35</v>
+        <v>39.09</v>
       </c>
       <c r="F10" t="n">
-        <v>54.6</v>
+        <v>54.9</v>
       </c>
       <c r="G10" t="n">
-        <v>6.6</v>
+        <v>3.28</v>
       </c>
       <c r="H10" t="n">
-        <v>1.51</v>
+        <v>1.15</v>
       </c>
       <c r="I10" t="n">
         <v>1.14</v>
       </c>
       <c r="J10" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.41</v>
+        <v>33.26</v>
       </c>
       <c r="N10" t="n">
-        <v>31.58</v>
+        <v>31.6</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1664,20 +1664,20 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1685,44 +1685,39 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
 ・RSIは良好な水準です。
-・出来高が増加しています。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、出来高微増、ゴールデンクロス、+1σ、MACD売り、長期上昇</t>
+          <t>RSI適正、25日線上、デッドクロス、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>36.85</v>
+        <v>40.35</v>
       </c>
       <c r="X10" t="n">
-        <v>3.5</v>
+        <v>-1.26</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.5</v>
+        <v>-3.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6073</v>
+        <v>-6074</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.34</v>
+        <v>-99.36</v>
       </c>
     </row>
   </sheetData>
@@ -1736,7 +1731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1493"/>
+  <dimension ref="A1:C1502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24134,6 +24129,141 @@
       </c>
       <c r="C1493" t="n">
         <v>40.35</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1494" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1495" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1496" t="n">
+        <v>177.3</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1497" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1498" t="n">
+        <v>8339</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1499" t="n">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1500" t="n">
+        <v>54570</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1501" t="n">
+        <v>9375</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1502" t="n">
+        <v>39.09</v>
       </c>
     </row>
   </sheetData>
@@ -24147,7 +24277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F252"/>
+  <dimension ref="A1:F253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28647,19 +28777,29 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
+      <c r="A250" t="inlineStr"/>
+      <c r="B250" s="1" t="n">
+        <v>46286.29166666666</v>
+      </c>
+      <c r="C250" t="n">
+        <v>216573</v>
+      </c>
+      <c r="D250" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E250" t="n">
+        <v>7283</v>
+      </c>
+      <c r="F250" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr"/>
-      <c r="C250" t="inlineStr"/>
-      <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr"/>
-      <c r="F250" t="inlineStr"/>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr"/>
       <c r="B251" t="inlineStr"/>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr"/>
@@ -28667,16 +28807,24 @@
       <c r="F251" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A252" t="inlineStr"/>
       <c r="B252" t="inlineStr"/>
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr"/>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -28841,35 +28989,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="H2" t="n">
-        <v>365300</v>
+        <v>801400</v>
       </c>
       <c r="I2" t="n">
-        <v>40.6</v>
+        <v>39.9</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.09</v>
+        <v>-0.57</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6</v>
+        <v>1.14</v>
       </c>
       <c r="L2" t="n">
-        <v>26.38</v>
+        <v>25.98</v>
       </c>
       <c r="M2" t="n">
-        <v>37.11</v>
+        <v>37.03</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -28878,10 +29026,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>853.9299999999999</v>
+        <v>853.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>1116.07</v>
+        <v>1116.05</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -28889,16 +29037,16 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -28906,6 +29054,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -28915,7 +29064,7 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
+          <t>🟡 調整中押し目（段階的買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -28941,31 +29090,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3395</v>
+        <v>3340</v>
       </c>
       <c r="F3" t="n">
-        <v>-50</v>
+        <v>-105</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.45</v>
+        <v>-3.05</v>
       </c>
       <c r="H3" t="n">
-        <v>43700</v>
+        <v>84600</v>
       </c>
       <c r="I3" t="n">
-        <v>31</v>
+        <v>29.5</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.03</v>
+        <v>-2.57</v>
       </c>
       <c r="K3" t="n">
-        <v>0.31</v>
+        <v>0.58</v>
       </c>
       <c r="L3" t="n">
-        <v>22.68</v>
+        <v>18.29</v>
       </c>
       <c r="M3" t="n">
-        <v>48.85</v>
+        <v>47.98</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -28978,10 +29127,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3044.6</v>
+        <v>3043.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>2726.83</v>
+        <v>2726.56</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -28989,16 +29138,16 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -29006,6 +29155,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
+・売られ過ぎ水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -29041,31 +29191,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1333</v>
+        <v>1355</v>
       </c>
       <c r="F4" t="n">
-        <v>-14</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.04</v>
+        <v>0.59</v>
       </c>
       <c r="H4" t="n">
-        <v>3800</v>
+        <v>5500</v>
       </c>
       <c r="I4" t="n">
-        <v>52.2</v>
+        <v>55.2</v>
       </c>
       <c r="J4" t="n">
-        <v>2.11</v>
+        <v>3.72</v>
       </c>
       <c r="K4" t="n">
-        <v>0.35</v>
+        <v>0.49</v>
       </c>
       <c r="L4" t="n">
-        <v>31.6</v>
+        <v>33.36</v>
       </c>
       <c r="M4" t="n">
-        <v>37.92</v>
+        <v>38.27</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -29078,10 +29228,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1208.85</v>
+        <v>1209.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>1638.78</v>
+        <v>1638.89</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -29142,31 +29292,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3495</v>
+        <v>3490</v>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.58</v>
+        <v>0.43</v>
       </c>
       <c r="H5" t="n">
-        <v>5200</v>
+        <v>8100</v>
       </c>
       <c r="I5" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1.08</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.54</v>
+        <v>0.8</v>
       </c>
       <c r="L5" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>8.41</v>
+        <v>8.33</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -29179,10 +29329,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3421.2</v>
+        <v>3421.13</v>
       </c>
       <c r="Q5" t="n">
-        <v>3156.01</v>
+        <v>3155.98</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -29243,31 +29393,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1558</v>
+        <v>1567</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>0.39</v>
+        <v>0.97</v>
       </c>
       <c r="H6" t="n">
-        <v>23000</v>
+        <v>53700</v>
       </c>
       <c r="I6" t="n">
-        <v>46.9</v>
+        <v>48.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.63</v>
+        <v>1.19</v>
       </c>
       <c r="K6" t="n">
-        <v>0.46</v>
+        <v>0.96</v>
       </c>
       <c r="L6" t="n">
-        <v>-21.21</v>
+        <v>-20.49</v>
       </c>
       <c r="M6" t="n">
-        <v>-30.77</v>
+        <v>-30.62</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -29280,10 +29430,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1676.5</v>
+        <v>1676.62</v>
       </c>
       <c r="Q6" t="n">
-        <v>1695.75</v>
+        <v>1695.79</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -29345,31 +29495,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.19</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>12900</v>
+        <v>23600</v>
       </c>
       <c r="I7" t="n">
-        <v>42.9</v>
+        <v>44.4</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4</v>
+        <v>-0.21</v>
       </c>
       <c r="K7" t="n">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="L7" t="n">
-        <v>-5.71</v>
+        <v>-5.63</v>
       </c>
       <c r="M7" t="n">
-        <v>-6.91</v>
+        <v>-6.89</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -29382,7 +29532,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>537.99</v>
+        <v>538</v>
       </c>
       <c r="Q7" t="n">
         <v>581.1799999999999</v>
@@ -29393,7 +29543,7 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -29410,6 +29560,7 @@
           <t>【AI分析レポート】
 ・🔴 下降
 ・MACDは買いシグナルです。
+・出来高が増加しています。
 ・ボリンジャーバンド中心付近で推移しています。
 ⚠️ 下落トレンドです。
 無理な買いは避け、反転サインを待ちましょう。</t>
@@ -29454,7 +29605,7 @@
         <v>0.74</v>
       </c>
       <c r="H8" t="n">
-        <v>3000</v>
+        <v>4200</v>
       </c>
       <c r="I8" t="n">
         <v>27.7</v>
@@ -29463,7 +29614,7 @@
         <v>-3.28</v>
       </c>
       <c r="K8" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="L8" t="n">
         <v>-7.71</v>
@@ -29546,31 +29697,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1584</v>
+        <v>1596</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G9" t="n">
-        <v>0.44</v>
+        <v>1.2</v>
       </c>
       <c r="H9" t="n">
-        <v>22500</v>
+        <v>383900</v>
       </c>
       <c r="I9" t="n">
-        <v>38.6</v>
+        <v>40.5</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.37</v>
+        <v>-1.66</v>
       </c>
       <c r="K9" t="n">
-        <v>0.45</v>
+        <v>3.14</v>
       </c>
       <c r="L9" t="n">
-        <v>7.34</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>18.99</v>
+        <v>19.18</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -29583,10 +29734,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1458.05</v>
+        <v>1458.21</v>
       </c>
       <c r="Q9" t="n">
-        <v>1383.31</v>
+        <v>1383.37</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -29594,16 +29745,16 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -29611,6 +29762,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
+・出来高が急増しています。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -29646,31 +29798,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="F10" t="n">
-        <v>-20</v>
+        <v>-16</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.04</v>
+        <v>-1.63</v>
       </c>
       <c r="H10" t="n">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="I10" t="n">
-        <v>38</v>
+        <v>39.4</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.59</v>
+        <v>-0.19</v>
       </c>
       <c r="K10" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="L10" t="n">
-        <v>15.31</v>
+        <v>15.63</v>
       </c>
       <c r="M10" t="n">
-        <v>20.68</v>
+        <v>20.75</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -29683,10 +29835,10 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>880.52</v>
+        <v>880.5700000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>986.75</v>
+        <v>986.77</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -29747,31 +29899,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3592</v>
+        <v>3637</v>
       </c>
       <c r="F11" t="n">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="G11" t="n">
-        <v>0.93</v>
+        <v>2.19</v>
       </c>
       <c r="H11" t="n">
-        <v>1744200</v>
+        <v>8509000</v>
       </c>
       <c r="I11" t="n">
-        <v>45.2</v>
+        <v>48.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.26</v>
+        <v>1.47</v>
       </c>
       <c r="K11" t="n">
-        <v>0.53</v>
+        <v>1.84</v>
       </c>
       <c r="L11" t="n">
-        <v>-30.94</v>
+        <v>-27.35</v>
       </c>
       <c r="M11" t="n">
-        <v>-42.95</v>
+        <v>-42.23</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -29784,10 +29936,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3660.51</v>
+        <v>3661.11</v>
       </c>
       <c r="Q11" t="n">
-        <v>2949.54</v>
+        <v>2949.76</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -29795,19 +29947,1051 @@
         </is>
       </c>
       <c r="S11" t="n">
+        <v>80</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・出来高が増加しています。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026/10/29</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>あと41日</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3778.T</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>さくらインターネット(株)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>3840</v>
+      </c>
+      <c r="F12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H12" t="n">
+        <v>941900</v>
+      </c>
+      <c r="I12" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="L12" t="n">
+        <v>62.56</v>
+      </c>
+      <c r="M12" t="n">
+        <v>78.64</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>3230.67</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3064.09</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
         <v>75</v>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5803.T</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>(株)フジクラ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>4952</v>
+      </c>
+      <c r="F13" t="n">
+        <v>85</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H13" t="n">
+        <v>37410000</v>
+      </c>
+      <c r="I13" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-5.15</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-77.16</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-29.22</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>5067.96</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4504.35</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>45</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2026/11/10</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>あと53日</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>166A.T</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>タスキホールディングス</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>何度も高値更新中の強トレンド</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1087</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H14" t="n">
+        <v>338500</v>
+      </c>
+      <c r="I14" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-4.36</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-18.49</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-11.41</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1113.28</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>930.58</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>45</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5801.T</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>古河電気工業</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>半導体設備関連</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3901</v>
+      </c>
+      <c r="F15" t="n">
+        <v>138</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H15" t="n">
+        <v>21047200</v>
+      </c>
+      <c r="I15" t="n">
+        <v>47</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="M15" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>3984.17</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3196.71</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>55</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2026/11/09</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>あと52日</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3374.T</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>内外テック</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>4080</v>
+      </c>
+      <c r="F16" t="n">
+        <v>55</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H16" t="n">
+        <v>14700</v>
+      </c>
+      <c r="I16" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L16" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>61.59</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>3594.17</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2859.88</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>75</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>7012.T</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>川崎重工業(株)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="H17" t="n">
+        <v>10860700</v>
+      </c>
+      <c r="I17" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-4.59</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-85.69</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-91.16</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>2734.48</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2832.35</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは買いシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>あと54日</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>トヨタ自動車(株)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4000円で売る予定</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3025</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-9</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>46568200</v>
+      </c>
+      <c r="I18" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="M18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>2938.78</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3164.84</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>60</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・出来高が増加しています。
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2026/11/05</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>あと48日</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>8053.T</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>住友商事</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>1796</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-48.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="H19" t="n">
+        <v>19454100</v>
+      </c>
+      <c r="I19" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="L19" t="n">
+        <v>23.49</v>
+      </c>
+      <c r="M19" t="n">
+        <v>30.97</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1677.39</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1570.66</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>100</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・出来高が増加しています。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2026/10/29</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>あと41日</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ブロードリーフ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>500円で売</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>491</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H20" t="n">
+        <v>524400</v>
+      </c>
+      <c r="I20" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L20" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M20" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>434.25</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>413.97</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>95</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>9375</v>
+      </c>
+      <c r="F21" t="n">
+        <v>375</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="H21" t="n">
+        <v>25919200</v>
+      </c>
+      <c r="I21" t="n">
+        <v>52</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-366.8</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-496.14</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>12859.19</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>7985.4</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>95</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -29818,101 +31002,198 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2026/10/29</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>あと41日</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2026/11/05</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>あと48日</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
         <is>
           <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>3778.T</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>さくらインターネット(株)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="n">
-        <v>3810</v>
-      </c>
-      <c r="F12" t="n">
-        <v>115</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="H12" t="n">
-        <v>485700</v>
-      </c>
-      <c r="I12" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="L12" t="n">
-        <v>60.17</v>
-      </c>
-      <c r="M12" t="n">
-        <v>78.16</v>
-      </c>
-      <c r="N12" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>キオクシアホールディングス</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>54570</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4690</v>
+      </c>
+      <c r="G22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>34475500</v>
+      </c>
+      <c r="I22" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-673.09</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-756.99</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P12" t="n">
-        <v>3230.27</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3063.94</v>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="P22" t="n">
+        <v>65199.07</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>40218.4</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>95</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2026/10/30</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>あと42日</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>8729.T</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ソニーファイナンシャル</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="H23" t="n">
+        <v>57685000</v>
+      </c>
+      <c r="I23" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>153</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>150.85</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S12" t="n">
-        <v>75</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
+      <c r="S23" t="n">
+        <v>95</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -29923,920 +31204,199 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>2026/11/12</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>あと55日</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
         <is>
           <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>5803.T</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>(株)フジクラ</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="n">
-        <v>4926</v>
-      </c>
-      <c r="F13" t="n">
-        <v>59</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="H13" t="n">
-        <v>19898100</v>
-      </c>
-      <c r="I13" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-5.63</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-79.23</v>
-      </c>
-      <c r="M13" t="n">
-        <v>-29.64</v>
-      </c>
-      <c r="N13" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6723.T</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ルネサスエレクトロニクス</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>3309</v>
+      </c>
+      <c r="F24" t="n">
+        <v>141</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="H24" t="n">
+        <v>15511700</v>
+      </c>
+      <c r="I24" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-125.21</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-144.58</v>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P13" t="n">
-        <v>5067.61</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4504.22</v>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="P24" t="n">
+        <v>3984.33</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3201.34</v>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>🟡 反発中</t>
         </is>
       </c>
-      <c r="S13" t="n">
-        <v>45</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
+      <c r="S24" t="n">
+        <v>70</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
-・MACDは売りシグナルです。
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・出来高が増加しています。
 ・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>2026/11/10</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>あと53日</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>2026/10/28</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>あと40日</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
         <is>
           <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>166A.T</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>タスキホールディングス</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>何度も高値更新中の強トレンド</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1099</v>
-      </c>
-      <c r="F14" t="n">
-        <v>16</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="H14" t="n">
-        <v>116200</v>
-      </c>
-      <c r="I14" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-3.35</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-17.54</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-11.22</v>
-      </c>
-      <c r="N14" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PENG</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ペンギン・ソリューションズ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>52.55</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1511000</v>
+      </c>
+      <c r="I25" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P14" t="n">
-        <v>1113.44</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>930.64</v>
-      </c>
-      <c r="R14" t="inlineStr">
+      <c r="P25" t="n">
+        <v>59.28</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>37.85</v>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>🟡 反発中</t>
         </is>
       </c>
-      <c r="S14" t="n">
-        <v>45</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>5801.T</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>古河電気工業</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>半導体設備関連</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>3840</v>
-      </c>
-      <c r="F15" t="n">
-        <v>77</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="H15" t="n">
-        <v>11036900</v>
-      </c>
-      <c r="I15" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-5.94</v>
-      </c>
-      <c r="M15" t="n">
-        <v>6.84</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>3983.36</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3196.41</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S15" t="n">
-        <v>45</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>2026/11/09</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>あと52日</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>3374.T</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>内外テック</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="n">
-        <v>4050</v>
-      </c>
-      <c r="F16" t="n">
-        <v>25</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="H16" t="n">
-        <v>5100</v>
-      </c>
-      <c r="I16" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="L16" t="n">
-        <v>28.71</v>
-      </c>
-      <c r="M16" t="n">
-        <v>61.11</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>3593.77</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2859.73</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S16" t="n">
-        <v>65</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>7012.T</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>川崎重工業(株)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="n">
-        <v>2388</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-33.5</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="H17" t="n">
-        <v>4713600</v>
-      </c>
-      <c r="I17" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-5.24</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-87.05</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-91.43000000000001</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>2734.25</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2832.27</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S17" t="n">
-        <v>30</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは買いシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>あと54日</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>7203.T</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>トヨタ自動車(株)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4000円で売る予定</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>3003</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-31</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="H18" t="n">
-        <v>10836000</v>
-      </c>
-      <c r="I18" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-1.91</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-2.83</v>
-      </c>
-      <c r="M18" t="n">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>2938.49</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3164.73</v>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="S18" t="n">
-        <v>55</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>2026/11/05</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>あと48日</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>8053.T</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>住友商事</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="n">
-        <v>1812</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-32.5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-1.76</v>
-      </c>
-      <c r="H19" t="n">
-        <v>3167000</v>
-      </c>
-      <c r="I19" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="L19" t="n">
-        <v>24.77</v>
-      </c>
-      <c r="M19" t="n">
-        <v>31.22</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1677.6</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1570.74</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S19" t="n">
+      <c r="S25" t="n">
         <v>95</v>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>2026/10/29</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>あと41日</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>3673.T</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ブロードリーフ</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>500円で売</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>497</v>
-      </c>
-      <c r="F20" t="n">
-        <v>8</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="H20" t="n">
-        <v>168800</v>
-      </c>
-      <c r="I20" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="L20" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="M20" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>434.33</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>414</v>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S20" t="n">
-        <v>95</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="n">
-        <v>9157</v>
-      </c>
-      <c r="F21" t="n">
-        <v>157</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="H21" t="n">
-        <v>12798500</v>
-      </c>
-      <c r="I21" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-384.19</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-499.62</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>12856.28</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>7984.31</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S21" t="n">
-        <v>65</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -30847,409 +31407,6 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>2026/11/05</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>あと48日</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>285A.T</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>キオクシアホールディングス</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="n">
-        <v>51960</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2080</v>
-      </c>
-      <c r="G22" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="H22" t="n">
-        <v>14725400</v>
-      </c>
-      <c r="I22" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="J22" t="n">
-        <v>-2.18</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-881.3</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-798.63</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>65164.27</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>40205.35</v>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S22" t="n">
-        <v>65</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>2026/10/30</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>あと42日</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>8729.T</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ソニーファイナンシャル</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>162</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-2</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="H23" t="n">
-        <v>21739700</v>
-      </c>
-      <c r="I23" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>152.99</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>150.84</v>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S23" t="n">
-        <v>95</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>2026/11/12</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>あと55日</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>6723.T</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>ルネサスエレクトロニクス</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="n">
-        <v>3228</v>
-      </c>
-      <c r="F24" t="n">
-        <v>60</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="H24" t="n">
-        <v>5098600</v>
-      </c>
-      <c r="I24" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="J24" t="n">
-        <v>-3.93</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="L24" t="n">
-        <v>-131.67</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-145.87</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>3983.25</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3200.93</v>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S24" t="n">
-        <v>65</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>2026/10/28</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>あと40日</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>PENG</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ペンギン・ソリューションズ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="n">
-        <v>52.55</v>
-      </c>
-      <c r="F25" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="G25" t="n">
-        <v>8.93</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1511000</v>
-      </c>
-      <c r="I25" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="L25" t="n">
-        <v>-1.72</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-2.08</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>59.28</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>37.85</v>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S25" t="n">
-        <v>95</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="W25" t="inlineStr">
         <is>
           <t>2026/10/06</t>
@@ -31280,31 +31437,31 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>8307</v>
+        <v>8339</v>
       </c>
       <c r="F26" t="n">
-        <v>-168</v>
+        <v>-136</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.98</v>
+        <v>-1.6</v>
       </c>
       <c r="H26" t="n">
-        <v>2507300</v>
+        <v>6274100</v>
       </c>
       <c r="I26" t="n">
-        <v>33.2</v>
+        <v>33.7</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.72</v>
+        <v>-3.36</v>
       </c>
       <c r="K26" t="n">
-        <v>0.39</v>
+        <v>0.88</v>
       </c>
       <c r="L26" t="n">
-        <v>-5.04</v>
+        <v>-2.49</v>
       </c>
       <c r="M26" t="n">
-        <v>81.20999999999999</v>
+        <v>81.72</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -31313,14 +31470,14 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7767.04</v>
+        <v>7767.47</v>
       </c>
       <c r="Q26" t="n">
-        <v>8677.870000000001</v>
+        <v>8678.030000000001</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -31328,7 +31485,7 @@
         </is>
       </c>
       <c r="S26" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -31345,7 +31502,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -1731,7 +1731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1502"/>
+  <dimension ref="A1:C1511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24263,6 +24263,141 @@
         </is>
       </c>
       <c r="C1502" t="n">
+        <v>39.09</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1503" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1504" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1505" t="n">
+        <v>177.3</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1506" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1507" t="n">
+        <v>8339</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1508" t="n">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1509" t="n">
+        <v>54570</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1510" t="n">
+        <v>9375</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1511" t="n">
         <v>39.09</v>
       </c>
     </row>
@@ -24277,7 +24412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F253"/>
+  <dimension ref="A1:F254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28795,19 +28930,29 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
+      <c r="A251" t="inlineStr"/>
+      <c r="B251" s="1" t="n">
+        <v>46286.5</v>
+      </c>
+      <c r="C251" t="n">
+        <v>216573</v>
+      </c>
+      <c r="D251" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E251" t="n">
+        <v>7283</v>
+      </c>
+      <c r="F251" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr"/>
-      <c r="C251" t="inlineStr"/>
-      <c r="D251" t="inlineStr"/>
-      <c r="E251" t="inlineStr"/>
-      <c r="F251" t="inlineStr"/>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr"/>
       <c r="B252" t="inlineStr"/>
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr"/>
@@ -28815,16 +28960,24 @@
       <c r="F252" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A253" t="inlineStr"/>
       <c r="B253" t="inlineStr"/>
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr"/>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -29978,7 +30131,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>あと41日</t>
+          <t>あと39日</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -30179,7 +30332,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>あと53日</t>
+          <t>あと51日</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -30388,7 +30541,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>あと52日</t>
+          <t>あと50日</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -30588,7 +30741,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>あと54日</t>
+          <t>あと52日</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -30697,7 +30850,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>あと48日</t>
+          <t>あと46日</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -30803,7 +30956,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>あと41日</t>
+          <t>あと39日</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -31009,7 +31162,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>あと48日</t>
+          <t>あと46日</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -31110,7 +31263,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>あと42日</t>
+          <t>あと40日</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -31211,7 +31364,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>あと55日</t>
+          <t>あと53日</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -31313,7 +31466,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>あと40日</t>
+          <t>あと38日</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -31336,31 +31489,31 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>52.55</v>
+        <v>53.3</v>
       </c>
       <c r="F25" t="n">
-        <v>4.31</v>
+        <v>0.75</v>
       </c>
       <c r="G25" t="n">
-        <v>8.93</v>
+        <v>1.43</v>
       </c>
       <c r="H25" t="n">
-        <v>1511000</v>
+        <v>2289100</v>
       </c>
       <c r="I25" t="n">
-        <v>50.2</v>
+        <v>58.2</v>
       </c>
       <c r="J25" t="n">
-        <v>1.1</v>
+        <v>3.15</v>
       </c>
       <c r="K25" t="n">
-        <v>1.15</v>
+        <v>1.55</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.72</v>
+        <v>-1.33</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.08</v>
+        <v>-1.93</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -31373,10 +31526,10 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>59.28</v>
+        <v>59.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>37.85</v>
+        <v>38.02</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -31384,7 +31537,7 @@
         </is>
       </c>
       <c r="S25" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -31402,6 +31555,7 @@
 ・🟡 反発中
 ・MACDは買いシグナルです。
 ・RSIは良好な水準です。
+・出来高が増加しています。
 ・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
@@ -31414,7 +31568,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>あと18日</t>
+          <t>あと16日</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -31514,7 +31668,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>あと48日</t>
+          <t>あと46日</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -1731,7 +1731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1511"/>
+  <dimension ref="A1:C1520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24398,6 +24398,141 @@
         </is>
       </c>
       <c r="C1511" t="n">
+        <v>39.09</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1512" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1513" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1514" t="n">
+        <v>177.3</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1515" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1516" t="n">
+        <v>8339</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1517" t="n">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1518" t="n">
+        <v>54570</v>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1519" t="n">
+        <v>9375</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1520" t="n">
         <v>39.09</v>
       </c>
     </row>
@@ -24412,7 +24547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F254"/>
+  <dimension ref="A1:F255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28948,19 +29083,29 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
+      <c r="A252" t="inlineStr"/>
+      <c r="B252" s="1" t="n">
+        <v>46286.75</v>
+      </c>
+      <c r="C252" t="n">
+        <v>216573</v>
+      </c>
+      <c r="D252" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E252" t="n">
+        <v>7283</v>
+      </c>
+      <c r="F252" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr"/>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
-      <c r="F252" t="inlineStr"/>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr"/>
       <c r="B253" t="inlineStr"/>
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr"/>
@@ -28968,16 +29113,24 @@
       <c r="F253" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A254" t="inlineStr"/>
       <c r="B254" t="inlineStr"/>
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr"/>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -30131,7 +30284,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>あと39日</t>
+          <t>あと38日</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -30332,7 +30485,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>あと51日</t>
+          <t>あと50日</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -30541,7 +30694,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>あと50日</t>
+          <t>あと49日</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -30741,7 +30894,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>あと52日</t>
+          <t>あと51日</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -30850,7 +31003,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>あと46日</t>
+          <t>あと45日</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -30956,7 +31109,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>あと39日</t>
+          <t>あと38日</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -31162,7 +31315,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>あと46日</t>
+          <t>あと45日</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -31263,7 +31416,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>あと40日</t>
+          <t>あと39日</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -31364,7 +31517,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>あと53日</t>
+          <t>あと52日</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -31466,7 +31619,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>あと38日</t>
+          <t>あと37日</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -31568,7 +31721,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>あと16日</t>
+          <t>あと15日</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -31668,7 +31821,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>あと46日</t>
+          <t>あと45日</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>216,573円</t>
+          <t>216,575円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7,283円</t>
+          <t>7,285円</t>
         </is>
       </c>
     </row>
@@ -1624,38 +1624,38 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>39.09</v>
+        <v>41.2</v>
       </c>
       <c r="F10" t="n">
-        <v>54.9</v>
+        <v>58.8</v>
       </c>
       <c r="G10" t="n">
-        <v>3.28</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="I10" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="J10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+2S</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.26</v>
+        <v>33.18</v>
       </c>
       <c r="N10" t="n">
-        <v>31.6</v>
+        <v>31.64</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1664,20 +1664,20 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1685,39 +1685,43 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>🚀 急騰</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、デッドクロス、MACD売り、長期上昇</t>
+          <t>RSI適正、25日線上、ゴールデンクロス、+2σ、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>40.35</v>
+        <v>39.09</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.26</v>
+        <v>2.11</v>
       </c>
       <c r="Y10" t="n">
-        <v>-3.12</v>
+        <v>5.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6074</v>
+        <v>-6072</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.36</v>
+        <v>-99.33</v>
       </c>
     </row>
   </sheetData>
@@ -1731,7 +1735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1520"/>
+  <dimension ref="A1:C1529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24534,6 +24538,141 @@
       </c>
       <c r="C1520" t="n">
         <v>39.09</v>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1521" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1522" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1523" t="n">
+        <v>177.3</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1524" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1525" t="n">
+        <v>8339</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1526" t="n">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1527" t="n">
+        <v>54570</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1528" t="n">
+        <v>9375</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1529" t="n">
+        <v>41.2</v>
       </c>
     </row>
   </sheetData>
@@ -24547,7 +24686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F255"/>
+  <dimension ref="A1:F256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29101,19 +29240,29 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
+      <c r="A253" t="inlineStr"/>
+      <c r="B253" s="1" t="n">
+        <v>46287.29166666666</v>
+      </c>
+      <c r="C253" t="n">
+        <v>216575</v>
+      </c>
+      <c r="D253" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E253" t="n">
+        <v>7285</v>
+      </c>
+      <c r="F253" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr"/>
-      <c r="C253" t="inlineStr"/>
-      <c r="D253" t="inlineStr"/>
-      <c r="E253" t="inlineStr"/>
-      <c r="F253" t="inlineStr"/>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr"/>
       <c r="B254" t="inlineStr"/>
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr"/>
@@ -29121,16 +29270,24 @@
       <c r="F254" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A255" t="inlineStr"/>
       <c r="B255" t="inlineStr"/>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr"/>
+      <c r="C256" t="inlineStr"/>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -1633,7 +1633,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="I10" t="n">
         <v>1.31</v>
@@ -1735,7 +1735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1529"/>
+  <dimension ref="A1:C1538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24672,6 +24672,141 @@
         </is>
       </c>
       <c r="C1529" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1530" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1531" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1532" t="n">
+        <v>177.3</v>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1533" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1534" t="n">
+        <v>8339</v>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1535" t="n">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1536" t="n">
+        <v>54570</v>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1537" t="n">
+        <v>9375</v>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1538" t="n">
         <v>41.2</v>
       </c>
     </row>
@@ -24686,7 +24821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F256"/>
+  <dimension ref="A1:F257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29258,19 +29393,29 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
+      <c r="A254" t="inlineStr"/>
+      <c r="B254" s="1" t="n">
+        <v>46287.5</v>
+      </c>
+      <c r="C254" t="n">
+        <v>216575</v>
+      </c>
+      <c r="D254" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E254" t="n">
+        <v>7285</v>
+      </c>
+      <c r="F254" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr"/>
-      <c r="C254" t="inlineStr"/>
-      <c r="D254" t="inlineStr"/>
-      <c r="E254" t="inlineStr"/>
-      <c r="F254" t="inlineStr"/>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr"/>
       <c r="B255" t="inlineStr"/>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr"/>
@@ -29278,16 +29423,24 @@
       <c r="F255" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A256" t="inlineStr"/>
       <c r="B256" t="inlineStr"/>
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr"/>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -31799,31 +31952,31 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>53.3</v>
+        <v>54.91</v>
       </c>
       <c r="F25" t="n">
-        <v>0.75</v>
+        <v>1.61</v>
       </c>
       <c r="G25" t="n">
-        <v>1.43</v>
+        <v>3.02</v>
       </c>
       <c r="H25" t="n">
-        <v>2289100</v>
+        <v>1271587</v>
       </c>
       <c r="I25" t="n">
-        <v>58.2</v>
+        <v>62</v>
       </c>
       <c r="J25" t="n">
-        <v>3.15</v>
+        <v>7</v>
       </c>
       <c r="K25" t="n">
-        <v>1.55</v>
+        <v>0.88</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.33</v>
+        <v>-0.87</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.93</v>
+        <v>-1.72</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -31836,10 +31989,10 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>59.05</v>
+        <v>58.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>38.02</v>
+        <v>38.19</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -31847,7 +32000,7 @@
         </is>
       </c>
       <c r="S25" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -31864,8 +32017,6 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・出来高が増加しています。
 ・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -1735,7 +1735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1538"/>
+  <dimension ref="A1:C1547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24807,6 +24807,141 @@
         </is>
       </c>
       <c r="C1538" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1539" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1540" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1541" t="n">
+        <v>177.3</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1542" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1543" t="n">
+        <v>8339</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1544" t="n">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1545" t="n">
+        <v>54570</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1546" t="n">
+        <v>9375</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1547" t="n">
         <v>41.2</v>
       </c>
     </row>
@@ -24821,7 +24956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F257"/>
+  <dimension ref="A1:F258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29411,19 +29546,29 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
+      <c r="A255" t="inlineStr"/>
+      <c r="B255" s="1" t="n">
+        <v>46287.75</v>
+      </c>
+      <c r="C255" t="n">
+        <v>216575</v>
+      </c>
+      <c r="D255" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E255" t="n">
+        <v>7285</v>
+      </c>
+      <c r="F255" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr"/>
-      <c r="C255" t="inlineStr"/>
-      <c r="D255" t="inlineStr"/>
-      <c r="E255" t="inlineStr"/>
-      <c r="F255" t="inlineStr"/>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr"/>
       <c r="B256" t="inlineStr"/>
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr"/>
@@ -29431,16 +29576,24 @@
       <c r="F256" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A257" t="inlineStr"/>
       <c r="B257" t="inlineStr"/>
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr"/>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -30594,7 +30747,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>あと38日</t>
+          <t>あと37日</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -30795,7 +30948,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>あと50日</t>
+          <t>あと49日</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -31004,7 +31157,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>あと49日</t>
+          <t>あと48日</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -31204,7 +31357,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>あと51日</t>
+          <t>あと50日</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -31313,7 +31466,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>あと45日</t>
+          <t>あと44日</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -31419,7 +31572,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>あと38日</t>
+          <t>あと37日</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -31625,7 +31778,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>あと45日</t>
+          <t>あと44日</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -31726,7 +31879,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>あと39日</t>
+          <t>あと38日</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -31827,7 +31980,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>あと52日</t>
+          <t>あと51日</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -31929,7 +32082,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>あと37日</t>
+          <t>あと36日</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -31961,7 +32114,7 @@
         <v>3.02</v>
       </c>
       <c r="H25" t="n">
-        <v>1271587</v>
+        <v>1342000</v>
       </c>
       <c r="I25" t="n">
         <v>62</v>
@@ -31970,7 +32123,7 @@
         <v>7</v>
       </c>
       <c r="K25" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="L25" t="n">
         <v>-0.87</v>
@@ -32029,7 +32182,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>あと15日</t>
+          <t>あと14日</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -32129,7 +32282,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>あと45日</t>
+          <t>あと44日</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>216,575円</t>
+          <t>216,576円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7,285円</t>
+          <t>7,286円</t>
         </is>
       </c>
     </row>
@@ -1624,26 +1624,26 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>41.2</v>
+        <v>41.54</v>
       </c>
       <c r="F10" t="n">
-        <v>58.8</v>
+        <v>61</v>
       </c>
       <c r="G10" t="n">
-        <v>8.699999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>1.11</v>
+        <v>0.68</v>
       </c>
       <c r="I10" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="J10" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.18</v>
+        <v>33.1</v>
       </c>
       <c r="N10" t="n">
-        <v>31.64</v>
+        <v>31.68</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1684,44 +1684,38 @@
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
-・MACDは売りシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
-・RSIは良好な水準です。
+・MACDは買いシグナルです。
 ・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、ゴールデンクロス、+2σ、MACD売り、長期上昇</t>
+          <t>RSI適正、25日線上、+2σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>39.09</v>
+        <v>41.2</v>
       </c>
       <c r="X10" t="n">
-        <v>2.11</v>
+        <v>0.34</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.4</v>
+        <v>0.83</v>
       </c>
       <c r="Z10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6072</v>
+        <v>-6071</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.33</v>
+        <v>-99.31999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1735,7 +1729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1547"/>
+  <dimension ref="A1:C1556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24943,6 +24937,141 @@
       </c>
       <c r="C1547" t="n">
         <v>41.2</v>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1548" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1549" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1550" t="n">
+        <v>177.3</v>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1551" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1552" t="n">
+        <v>8339</v>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1553" t="n">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1554" t="n">
+        <v>54570</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1555" t="n">
+        <v>9375</v>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1556" t="n">
+        <v>41.54</v>
       </c>
     </row>
   </sheetData>
@@ -24956,7 +25085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F258"/>
+  <dimension ref="A1:F259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29564,19 +29693,29 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr">
+      <c r="A256" t="inlineStr"/>
+      <c r="B256" s="1" t="n">
+        <v>46288.29166666666</v>
+      </c>
+      <c r="C256" t="n">
+        <v>216576</v>
+      </c>
+      <c r="D256" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E256" t="n">
+        <v>7286</v>
+      </c>
+      <c r="F256" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr"/>
-      <c r="C256" t="inlineStr"/>
-      <c r="D256" t="inlineStr"/>
-      <c r="E256" t="inlineStr"/>
-      <c r="F256" t="inlineStr"/>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr"/>
       <c r="B257" t="inlineStr"/>
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr"/>
@@ -29584,16 +29723,24 @@
       <c r="F257" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A258" t="inlineStr"/>
       <c r="B258" t="inlineStr"/>
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr"/>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>216,576円</t>
+          <t>216,575円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7,286円</t>
+          <t>7,285円</t>
         </is>
       </c>
     </row>
@@ -1624,22 +1624,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>41.54</v>
+        <v>41.44</v>
       </c>
       <c r="F10" t="n">
-        <v>61</v>
+        <v>60.2</v>
       </c>
       <c r="G10" t="n">
-        <v>9.220000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.68</v>
+        <v>0.89</v>
       </c>
       <c r="I10" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="J10" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1648,14 +1648,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+2S</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>33.1</v>
       </c>
       <c r="N10" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -1693,26 +1693,26 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+2σ、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>41.2</v>
+        <v>41.54</v>
       </c>
       <c r="X10" t="n">
-        <v>0.34</v>
+        <v>-0.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.83</v>
+        <v>-0.24</v>
       </c>
       <c r="Z10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6071</v>
+        <v>-6072</v>
       </c>
       <c r="AC10" t="n">
         <v>-99.31999999999999</v>
@@ -1729,7 +1729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1556"/>
+  <dimension ref="A1:C1565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25072,6 +25072,141 @@
       </c>
       <c r="C1556" t="n">
         <v>41.54</v>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1557" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1558" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1559" t="n">
+        <v>177.3</v>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1560" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1561" t="n">
+        <v>8339</v>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1562" t="n">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1563" t="n">
+        <v>54570</v>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1564" t="n">
+        <v>9375</v>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1565" t="n">
+        <v>41.44</v>
       </c>
     </row>
   </sheetData>
@@ -25085,7 +25220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F259"/>
+  <dimension ref="A1:F260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29711,19 +29846,29 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
+      <c r="A257" t="inlineStr"/>
+      <c r="B257" s="1" t="n">
+        <v>46289.29166666666</v>
+      </c>
+      <c r="C257" t="n">
+        <v>216575</v>
+      </c>
+      <c r="D257" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E257" t="n">
+        <v>7285</v>
+      </c>
+      <c r="F257" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr"/>
-      <c r="C257" t="inlineStr"/>
-      <c r="D257" t="inlineStr"/>
-      <c r="E257" t="inlineStr"/>
-      <c r="F257" t="inlineStr"/>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr"/>
       <c r="B258" t="inlineStr"/>
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr"/>
@@ -29731,16 +29876,24 @@
       <c r="F258" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A259" t="inlineStr"/>
       <c r="B259" t="inlineStr"/>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr"/>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -32252,47 +32405,47 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>54.91</v>
+        <v>56.58</v>
       </c>
       <c r="F25" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="G25" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="H25" t="n">
-        <v>1342000</v>
+        <v>1634883</v>
       </c>
       <c r="I25" t="n">
-        <v>62</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>7</v>
+        <v>10.82</v>
       </c>
       <c r="K25" t="n">
-        <v>0.92</v>
+        <v>1.04</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.87</v>
+        <v>-0.37</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.72</v>
+        <v>-1.45</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>58.83</v>
+        <v>58.63</v>
       </c>
       <c r="Q25" t="n">
-        <v>38.19</v>
+        <v>38.37</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -32300,7 +32453,7 @@
         </is>
       </c>
       <c r="S25" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -32317,7 +32470,9 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
+・25日線から大きく上に乖離しています。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>216,575円</t>
+          <t>215,599円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7,285円</t>
+          <t>6,308円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3340</v>
+        <v>3375</v>
       </c>
       <c r="F2" t="n">
-        <v>29.5</v>
+        <v>36.8</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.57</v>
+        <v>-1.57</v>
       </c>
       <c r="H2" t="n">
-        <v>0.58</v>
+        <v>0.18</v>
       </c>
       <c r="I2" t="n">
-        <v>18.29</v>
+        <v>16.14</v>
       </c>
       <c r="J2" t="n">
-        <v>47.98</v>
+        <v>41.61</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3043.87</v>
+        <v>3056.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2726.56</v>
+        <v>2729.36</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -757,20 +757,20 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -778,7 +778,6 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・売られ過ぎ水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -787,29 +786,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>RSI売られすぎ、押し目、MACD売り、長期上昇</t>
+          <t>押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3445</v>
+        <v>3340</v>
       </c>
       <c r="X2" t="n">
-        <v>-105</v>
+        <v>35</v>
       </c>
       <c r="Y2" t="n">
-        <v>-3.05</v>
+        <v>1.05</v>
       </c>
       <c r="Z2" t="n">
-        <v>13360</v>
+        <v>13500</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2560</v>
+        <v>2700</v>
       </c>
       <c r="AC2" t="n">
-        <v>23.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -833,19 +832,19 @@
         <v>491</v>
       </c>
       <c r="F3" t="n">
-        <v>47.1</v>
+        <v>54.1</v>
       </c>
       <c r="G3" t="n">
-        <v>4.87</v>
+        <v>4.38</v>
       </c>
       <c r="H3" t="n">
-        <v>0.65</v>
+        <v>0.4</v>
       </c>
       <c r="I3" t="n">
-        <v>7.7</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>6.45</v>
+        <v>6.86</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -858,10 +857,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>434.25</v>
+        <v>435.12</v>
       </c>
       <c r="N3" t="n">
-        <v>413.97</v>
+        <v>414.62</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -874,7 +873,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -900,17 +899,17 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25日線上、+1σ、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
         <v>49100</v>
@@ -943,22 +942,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>177.3</v>
+        <v>175.3</v>
       </c>
       <c r="F4" t="n">
-        <v>59.2</v>
+        <v>49.4</v>
       </c>
       <c r="G4" t="n">
-        <v>3.69</v>
+        <v>2.19</v>
       </c>
       <c r="H4" t="n">
-        <v>1.35</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>4.58</v>
+        <v>4.23</v>
       </c>
       <c r="J4" t="n">
-        <v>4.61</v>
+        <v>4.53</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -967,14 +966,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>157.02</v>
+        <v>157.4</v>
       </c>
       <c r="N4" t="n">
-        <v>154.35</v>
+        <v>154.46</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -983,361 +982,23 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>RSI適正、25日線上、+1σ、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>180</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>17730</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>15800</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1930</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>12.22</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>7203.T</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>トヨタ自動車</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>13</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2853.77</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3025</v>
-      </c>
-      <c r="F5" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="J5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>2938.78</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3164.84</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>60</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・出来高が増加しています。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>押し目、出来高微増、MACD売り、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>3034</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-9</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>39325</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>37099</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2226</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>7993</v>
-      </c>
-      <c r="E6" t="n">
-        <v>8339</v>
-      </c>
-      <c r="F6" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-3.36</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-2.49</v>
-      </c>
-      <c r="J6" t="n">
-        <v>81.72</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>7767.47</v>
-      </c>
-      <c r="N6" t="n">
-        <v>8678.030000000001</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>55</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>押し目、MACD売り、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>8475</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-136</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>8339</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>7993</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>346</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>8058.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>三菱商事</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4795</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4947</v>
-      </c>
-      <c r="F7" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="I7" t="n">
-        <v>53.52</v>
-      </c>
-      <c r="J7" t="n">
-        <v>57.79</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>4717.33</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4683.77</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>🟢 強い買い</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>95</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -1348,32 +1009,370 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>25日線上、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>177.3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>17530</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>15800</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1730</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>10.95</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>トヨタ自動車</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2853.77</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2971.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-6.13</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>2940.55</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3164.23</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>75</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・売られ過ぎ水準です。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>RSI売られすぎ、押し目、-1σ、MACD売り、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>3025</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-53.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>38630</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>37099</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1530</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7993</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8235</v>
+      </c>
+      <c r="F6" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-4.33</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-14.85</v>
+      </c>
+      <c r="J6" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>7780.31</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8654.299999999999</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>60</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>8339</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-104</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>8235</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7993</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>242</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>三菱商事</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4795</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4863</v>
+      </c>
+      <c r="F7" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="I7" t="n">
+        <v>43.09</v>
+      </c>
+      <c r="J7" t="n">
+        <v>54.85</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>4716.89</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4689.84</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>65</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+          <t>押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4979</v>
+        <v>4947</v>
       </c>
       <c r="X7" t="n">
-        <v>-32</v>
+        <v>-84</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.64</v>
+        <v>-1.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>24735</v>
+        <v>24315</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>760</v>
+        <v>340</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.17</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="8">
@@ -1394,22 +1393,22 @@
         <v>55510</v>
       </c>
       <c r="E8" t="n">
-        <v>54570</v>
+        <v>54980</v>
       </c>
       <c r="F8" t="n">
-        <v>58.1</v>
+        <v>57.2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.53</v>
+        <v>3.84</v>
       </c>
       <c r="H8" t="n">
-        <v>1.19</v>
+        <v>0.65</v>
       </c>
       <c r="I8" t="n">
-        <v>-673.09</v>
+        <v>-465.96</v>
       </c>
       <c r="J8" t="n">
-        <v>-756.99</v>
+        <v>-698.78</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1422,10 +1421,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>65199.07</v>
+        <v>64906.53</v>
       </c>
       <c r="N8" t="n">
-        <v>40218.4</v>
+        <v>40451.37</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1461,36 +1460,32 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>RSI適正、25日線上、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>49880</v>
+        <v>54570</v>
       </c>
       <c r="X8" t="n">
-        <v>4690</v>
+        <v>410</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.4</v>
+        <v>0.75</v>
       </c>
       <c r="Z8" t="n">
-        <v>54570</v>
+        <v>54980</v>
       </c>
       <c r="AA8" t="n">
         <v>55510</v>
       </c>
       <c r="AB8" t="n">
-        <v>-940</v>
+        <v>-530</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.69</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="9">
@@ -1511,22 +1506,22 @@
         <v>10000</v>
       </c>
       <c r="E9" t="n">
-        <v>9375</v>
+        <v>9268</v>
       </c>
       <c r="F9" t="n">
-        <v>52</v>
+        <v>49.8</v>
       </c>
       <c r="G9" t="n">
-        <v>0.49</v>
+        <v>0.21</v>
       </c>
       <c r="H9" t="n">
-        <v>0.92</v>
+        <v>0.58</v>
       </c>
       <c r="I9" t="n">
-        <v>-366.8</v>
+        <v>-335.75</v>
       </c>
       <c r="J9" t="n">
-        <v>-496.14</v>
+        <v>-464.06</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1539,10 +1534,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>12859.19</v>
+        <v>12768.16</v>
       </c>
       <c r="N9" t="n">
-        <v>7985.4</v>
+        <v>8015.78</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1551,20 +1546,20 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1581,29 +1576,29 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD買い、反発局面</t>
+          <t>25日線上、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>9000</v>
+        <v>9375</v>
       </c>
       <c r="X9" t="n">
-        <v>375</v>
+        <v>-107</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.17</v>
+        <v>-1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>9375</v>
+        <v>9268</v>
       </c>
       <c r="AA9" t="n">
         <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-625</v>
+        <v>-732</v>
       </c>
       <c r="AC9" t="n">
-        <v>-6.25</v>
+        <v>-7.32</v>
       </c>
     </row>
     <row r="10">
@@ -1729,7 +1724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1565"/>
+  <dimension ref="A1:C1574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25206,6 +25201,141 @@
         </is>
       </c>
       <c r="C1565" t="n">
+        <v>41.44</v>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1566" t="n">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1567" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1568" t="n">
+        <v>175.3</v>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1569" t="n">
+        <v>2971.5</v>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1570" t="n">
+        <v>8235</v>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1571" t="n">
+        <v>4863</v>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1572" t="n">
+        <v>54980</v>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1573" t="n">
+        <v>9268</v>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1574" t="n">
         <v>41.44</v>
       </c>
     </row>
@@ -25220,7 +25350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F260"/>
+  <dimension ref="A1:F261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29864,19 +29994,29 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr">
+      <c r="A258" t="inlineStr"/>
+      <c r="B258" s="1" t="n">
+        <v>46289.5</v>
+      </c>
+      <c r="C258" t="n">
+        <v>215599</v>
+      </c>
+      <c r="D258" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E258" t="n">
+        <v>6308</v>
+      </c>
+      <c r="F258" t="n">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr"/>
-      <c r="C258" t="inlineStr"/>
-      <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr"/>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr"/>
       <c r="B259" t="inlineStr"/>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr"/>
@@ -29884,16 +30024,24 @@
       <c r="F259" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A260" t="inlineStr"/>
       <c r="B260" t="inlineStr"/>
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr"/>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -31047,7 +31195,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>あと37日</t>
+          <t>あと36日</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -31248,7 +31396,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>あと49日</t>
+          <t>あと48日</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -31457,7 +31605,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>あと48日</t>
+          <t>あと47日</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -31657,7 +31805,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>あと50日</t>
+          <t>あと49日</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -31766,7 +31914,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>あと44日</t>
+          <t>あと43日</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -31872,7 +32020,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>あと37日</t>
+          <t>あと36日</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -32078,7 +32226,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>あと44日</t>
+          <t>あと43日</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -32179,7 +32327,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>あと38日</t>
+          <t>あと37日</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -32280,7 +32428,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>あと51日</t>
+          <t>あと50日</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -32382,7 +32530,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>あと36日</t>
+          <t>あと35日</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -32405,31 +32553,31 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>56.58</v>
+        <v>53.88</v>
       </c>
       <c r="F25" t="n">
-        <v>1.67</v>
+        <v>-1.03</v>
       </c>
       <c r="G25" t="n">
-        <v>3.04</v>
+        <v>-1.88</v>
       </c>
       <c r="H25" t="n">
-        <v>1634883</v>
+        <v>1518193</v>
       </c>
       <c r="I25" t="n">
-        <v>68.40000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="J25" t="n">
-        <v>10.82</v>
+        <v>5.75</v>
       </c>
       <c r="K25" t="n">
-        <v>1.04</v>
+        <v>0.98</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.37</v>
+        <v>-0.59</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.45</v>
+        <v>-1.49</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -32442,10 +32590,10 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>58.63</v>
+        <v>58.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>38.37</v>
+        <v>38.35</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -32453,7 +32601,7 @@
         </is>
       </c>
       <c r="S25" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -32471,7 +32619,6 @@
 ・🟡 反発中
 ・MACDは買いシグナルです。
 ・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
-・25日線から大きく上に乖離しています。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
@@ -32484,7 +32631,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>あと14日</t>
+          <t>あと13日</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -32584,7 +32731,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>あと44日</t>
+          <t>あと43日</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>215,599円</t>
+          <t>214,014円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6,308円</t>
+          <t>4,724円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3375</v>
+        <v>3330</v>
       </c>
       <c r="F2" t="n">
-        <v>36.8</v>
+        <v>34.2</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.57</v>
+        <v>-2.84</v>
       </c>
       <c r="H2" t="n">
-        <v>0.18</v>
+        <v>0.34</v>
       </c>
       <c r="I2" t="n">
-        <v>16.14</v>
+        <v>12.56</v>
       </c>
       <c r="J2" t="n">
-        <v>41.61</v>
+        <v>40.89</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3056.11</v>
+        <v>3055.51</v>
       </c>
       <c r="N2" t="n">
-        <v>2729.36</v>
+        <v>2729.13</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -793,22 +793,22 @@
         <v>3340</v>
       </c>
       <c r="X2" t="n">
-        <v>35</v>
+        <v>-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.05</v>
+        <v>-0.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>13500</v>
+        <v>13320</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2700</v>
+        <v>2520</v>
       </c>
       <c r="AC2" t="n">
-        <v>25</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="3">
@@ -829,22 +829,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F3" t="n">
-        <v>54.1</v>
+        <v>52.9</v>
       </c>
       <c r="G3" t="n">
-        <v>4.38</v>
+        <v>3.77</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4</v>
+        <v>0.98</v>
       </c>
       <c r="I3" t="n">
-        <v>8.529999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>6.86</v>
+        <v>6.81</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>435.12</v>
+        <v>435.08</v>
       </c>
       <c r="N3" t="n">
-        <v>414.62</v>
+        <v>414.6</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -906,22 +906,22 @@
         <v>491</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0.61</v>
       </c>
       <c r="Z3" t="n">
-        <v>49100</v>
+        <v>48800</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7100</v>
+        <v>6800</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.9</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="4">
@@ -942,19 +942,19 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>175.3</v>
+        <v>174.9</v>
       </c>
       <c r="F4" t="n">
-        <v>49.4</v>
+        <v>48.6</v>
       </c>
       <c r="G4" t="n">
-        <v>2.19</v>
+        <v>1.97</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="I4" t="n">
-        <v>4.23</v>
+        <v>4.2</v>
       </c>
       <c r="J4" t="n">
         <v>4.53</v>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>157.4</v>
+        <v>157.39</v>
       </c>
       <c r="N4" t="n">
         <v>154.46</v>
@@ -1019,22 +1019,22 @@
         <v>177.3</v>
       </c>
       <c r="X4" t="n">
-        <v>-2</v>
+        <v>-2.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1.13</v>
+        <v>-1.35</v>
       </c>
       <c r="Z4" t="n">
-        <v>17530</v>
+        <v>17490</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1730</v>
+        <v>1690</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.95</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="5">
@@ -1055,22 +1055,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>2971.5</v>
+        <v>2969</v>
       </c>
       <c r="F5" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.91</v>
+        <v>-2.99</v>
       </c>
       <c r="H5" t="n">
-        <v>0.73</v>
+        <v>1.22</v>
       </c>
       <c r="I5" t="n">
-        <v>-6.13</v>
+        <v>-6.33</v>
       </c>
       <c r="J5" t="n">
-        <v>6.3</v>
+        <v>6.26</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2940.55</v>
+        <v>2940.52</v>
       </c>
       <c r="N5" t="n">
-        <v>3164.23</v>
+        <v>3164.21</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1132,22 +1132,22 @@
         <v>3025</v>
       </c>
       <c r="X5" t="n">
-        <v>-53.5</v>
+        <v>-56</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.77</v>
+        <v>-1.85</v>
       </c>
       <c r="Z5" t="n">
-        <v>38630</v>
+        <v>38597</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>1530</v>
+        <v>1498</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.13</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="6">
@@ -1168,22 +1168,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>8235</v>
+        <v>8196</v>
       </c>
       <c r="F6" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.33</v>
+        <v>-4.77</v>
       </c>
       <c r="H6" t="n">
-        <v>0.62</v>
+        <v>1.01</v>
       </c>
       <c r="I6" t="n">
-        <v>-14.85</v>
+        <v>-17.96</v>
       </c>
       <c r="J6" t="n">
-        <v>62.4</v>
+        <v>61.78</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>7780.31</v>
+        <v>7779.79</v>
       </c>
       <c r="N6" t="n">
-        <v>8654.299999999999</v>
+        <v>8654.1</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1208,20 +1208,20 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1229,6 +1229,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
+・売られ過ぎ水準です。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -1237,29 +1238,29 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
+          <t>RSI売られすぎ、押し目、-1σ、MACD売り、上昇トレンド</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>8339</v>
       </c>
       <c r="X6" t="n">
-        <v>-104</v>
+        <v>-143</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.25</v>
+        <v>-1.71</v>
       </c>
       <c r="Z6" t="n">
-        <v>8235</v>
+        <v>8196</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>242</v>
+        <v>203</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.03</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="7">
@@ -1280,22 +1281,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4863</v>
+        <v>4811</v>
       </c>
       <c r="F7" t="n">
-        <v>45.6</v>
+        <v>43.5</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.25</v>
+        <v>-1.27</v>
       </c>
       <c r="H7" t="n">
-        <v>0.66</v>
+        <v>1.32</v>
       </c>
       <c r="I7" t="n">
-        <v>43.09</v>
+        <v>38.94</v>
       </c>
       <c r="J7" t="n">
-        <v>54.85</v>
+        <v>54.02</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1308,10 +1309,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4716.89</v>
+        <v>4716.2</v>
       </c>
       <c r="N7" t="n">
-        <v>4689.84</v>
+        <v>4689.58</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1341,7 +1342,6 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -1357,22 +1357,22 @@
         <v>4947</v>
       </c>
       <c r="X7" t="n">
-        <v>-84</v>
+        <v>-136</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.7</v>
+        <v>-2.75</v>
       </c>
       <c r="Z7" t="n">
-        <v>24315</v>
+        <v>24055</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>340</v>
+        <v>80</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.42</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="8">
@@ -1393,22 +1393,22 @@
         <v>55510</v>
       </c>
       <c r="E8" t="n">
-        <v>54980</v>
+        <v>54580</v>
       </c>
       <c r="F8" t="n">
-        <v>57.2</v>
+        <v>56.5</v>
       </c>
       <c r="G8" t="n">
-        <v>3.84</v>
+        <v>3.11</v>
       </c>
       <c r="H8" t="n">
-        <v>0.65</v>
+        <v>0.97</v>
       </c>
       <c r="I8" t="n">
-        <v>-465.96</v>
+        <v>-497.87</v>
       </c>
       <c r="J8" t="n">
-        <v>-698.78</v>
+        <v>-705.17</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>64906.53</v>
+        <v>64901.2</v>
       </c>
       <c r="N8" t="n">
-        <v>40451.37</v>
+        <v>40449.37</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1470,22 +1470,22 @@
         <v>54570</v>
       </c>
       <c r="X8" t="n">
-        <v>410</v>
+        <v>10</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.75</v>
+        <v>0.02</v>
       </c>
       <c r="Z8" t="n">
-        <v>54980</v>
+        <v>54580</v>
       </c>
       <c r="AA8" t="n">
         <v>55510</v>
       </c>
       <c r="AB8" t="n">
-        <v>-530</v>
+        <v>-930</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.95</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="9">
@@ -1506,22 +1506,22 @@
         <v>10000</v>
       </c>
       <c r="E9" t="n">
-        <v>9268</v>
+        <v>8935</v>
       </c>
       <c r="F9" t="n">
-        <v>49.8</v>
+        <v>46.6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.21</v>
+        <v>-3.25</v>
       </c>
       <c r="H9" t="n">
-        <v>0.58</v>
+        <v>0.96</v>
       </c>
       <c r="I9" t="n">
-        <v>-335.75</v>
+        <v>-362.32</v>
       </c>
       <c r="J9" t="n">
-        <v>-464.06</v>
+        <v>-469.38</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>12768.16</v>
+        <v>12763.72</v>
       </c>
       <c r="N9" t="n">
-        <v>8015.78</v>
+        <v>8014.11</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1546,11 +1546,11 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1576,29 +1576,29 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>25日線上、MACD買い、反発局面</t>
+          <t>押し目、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
         <v>9375</v>
       </c>
       <c r="X9" t="n">
-        <v>-107</v>
+        <v>-440</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.14</v>
+        <v>-4.69</v>
       </c>
       <c r="Z9" t="n">
-        <v>9268</v>
+        <v>8935</v>
       </c>
       <c r="AA9" t="n">
         <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-732</v>
+        <v>-1065</v>
       </c>
       <c r="AC9" t="n">
-        <v>-7.32</v>
+        <v>-10.65</v>
       </c>
     </row>
     <row r="10">
@@ -1724,7 +1724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1574"/>
+  <dimension ref="A1:C1583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25336,6 +25336,141 @@
         </is>
       </c>
       <c r="C1574" t="n">
+        <v>41.44</v>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1575" t="n">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1576" t="n">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1577" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1578" t="n">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1579" t="n">
+        <v>8196</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1580" t="n">
+        <v>4811</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1581" t="n">
+        <v>54580</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1582" t="n">
+        <v>8935</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1583" t="n">
         <v>41.44</v>
       </c>
     </row>
@@ -25350,7 +25485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F261"/>
+  <dimension ref="A1:F262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30012,19 +30147,29 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr">
+      <c r="A259" t="inlineStr"/>
+      <c r="B259" s="1" t="n">
+        <v>46289.75069444445</v>
+      </c>
+      <c r="C259" t="n">
+        <v>214014</v>
+      </c>
+      <c r="D259" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E259" t="n">
+        <v>4724</v>
+      </c>
+      <c r="F259" t="n">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr"/>
-      <c r="C259" t="inlineStr"/>
-      <c r="D259" t="inlineStr"/>
-      <c r="E259" t="inlineStr"/>
-      <c r="F259" t="inlineStr"/>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr"/>
       <c r="B260" t="inlineStr"/>
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr"/>
@@ -30032,16 +30177,24 @@
       <c r="F260" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A261" t="inlineStr"/>
       <c r="B261" t="inlineStr"/>
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr"/>
+      <c r="C262" t="inlineStr"/>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -30206,35 +30359,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H2" t="n">
-        <v>801400</v>
+        <v>371000</v>
       </c>
       <c r="I2" t="n">
-        <v>39.9</v>
+        <v>47.1</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.57</v>
+        <v>-0.17</v>
       </c>
       <c r="K2" t="n">
-        <v>1.14</v>
+        <v>0.62</v>
       </c>
       <c r="L2" t="n">
-        <v>25.98</v>
+        <v>23.4</v>
       </c>
       <c r="M2" t="n">
-        <v>37.03</v>
+        <v>34.3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -30243,10 +30396,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>853.87</v>
+        <v>858.27</v>
       </c>
       <c r="Q2" t="n">
-        <v>1116.05</v>
+        <v>1113.71</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -30254,221 +30407,19 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>🟡 調整中押し目（段階的買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>4431.T</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>スマレジ</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>POSレジSaaS</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>3340</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-105</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-3.05</v>
-      </c>
-      <c r="H3" t="n">
-        <v>84600</v>
-      </c>
-      <c r="I3" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-2.57</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="L3" t="n">
-        <v>18.29</v>
-      </c>
-      <c r="M3" t="n">
-        <v>47.98</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>3043.87</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2726.56</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>80</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>4412.T</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>サイエンスアーツ</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>現場向けコミュニケーション</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1355</v>
-      </c>
-      <c r="F4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="H4" t="n">
-        <v>5500</v>
-      </c>
-      <c r="I4" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="L4" t="n">
-        <v>33.36</v>
-      </c>
-      <c r="M4" t="n">
-        <v>38.27</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>1209.14</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1638.89</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>85</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 上昇
@@ -30479,6 +30430,207 @@
 順張りが有利な局面です。</t>
         </is>
       </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>スマレジ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>POSレジSaaS</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3375</v>
+      </c>
+      <c r="F3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H3" t="n">
+        <v>22800</v>
+      </c>
+      <c r="I3" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L3" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="M3" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>3056.11</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2729.36</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>65</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>4412.T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>サイエンスアーツ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>現場向けコミュニケーション</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1398</v>
+      </c>
+      <c r="F4" t="n">
+        <v>43</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="H4" t="n">
+        <v>13600</v>
+      </c>
+      <c r="I4" t="n">
+        <v>52</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>35.57</v>
+      </c>
+      <c r="M4" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1212.84</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1638.17</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>85</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
@@ -30509,31 +30661,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3490</v>
+        <v>3530</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.43</v>
+        <v>1.15</v>
       </c>
       <c r="H5" t="n">
-        <v>8100</v>
+        <v>2600</v>
       </c>
       <c r="I5" t="n">
-        <v>49.5</v>
+        <v>47.8</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.19</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8</v>
+        <v>0.36</v>
       </c>
       <c r="L5" t="n">
-        <v>8.699999999999999</v>
+        <v>13.19</v>
       </c>
       <c r="M5" t="n">
-        <v>8.33</v>
+        <v>9.31</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -30546,10 +30698,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3421.13</v>
+        <v>3423</v>
       </c>
       <c r="Q5" t="n">
-        <v>3155.98</v>
+        <v>3160.03</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -30610,47 +30762,47 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1567</v>
+        <v>1600</v>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="G6" t="n">
-        <v>0.97</v>
+        <v>2.11</v>
       </c>
       <c r="H6" t="n">
-        <v>53700</v>
+        <v>43600</v>
       </c>
       <c r="I6" t="n">
-        <v>48.5</v>
+        <v>62.7</v>
       </c>
       <c r="J6" t="n">
-        <v>1.19</v>
+        <v>3.24</v>
       </c>
       <c r="K6" t="n">
-        <v>0.96</v>
+        <v>0.86</v>
       </c>
       <c r="L6" t="n">
-        <v>-20.49</v>
+        <v>-14.83</v>
       </c>
       <c r="M6" t="n">
-        <v>-30.62</v>
+        <v>-27.47</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1676.62</v>
+        <v>1674.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1695.79</v>
+        <v>1693.98</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -30658,7 +30810,7 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -30675,114 +30827,112 @@
           <t>【AI分析レポート】
 ・🔴 下降
 ・MACDは買いシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4054.T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>日本情報クリエイト</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>不動産向けクラウド</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>521</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4300</v>
+      </c>
+      <c r="I7" t="n">
+        <v>48</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-5.22</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-6.56</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>538.24</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>580.12</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>30</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは買いシグナルです。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 ⚠️ 下落トレンドです。
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>4054.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>日本情報クリエイト</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>不動産向けクラウド</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>521</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>23600</v>
-      </c>
-      <c r="I7" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-5.63</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-6.89</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>538</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>581.1799999999999</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>35</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは買いシグナルです。
-・出来高が増加しています。
-・ボリンジャーバンド中心付近で推移しています。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
@@ -30813,31 +30963,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1090</v>
+        <v>1109</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>0.74</v>
+        <v>1.74</v>
       </c>
       <c r="H8" t="n">
-        <v>4200</v>
+        <v>2900</v>
       </c>
       <c r="I8" t="n">
-        <v>27.7</v>
+        <v>37.6</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.28</v>
+        <v>-1.26</v>
       </c>
       <c r="K8" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="L8" t="n">
-        <v>-7.71</v>
+        <v>-6.13</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.68</v>
+        <v>-1.77</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -30850,10 +31000,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1056.96</v>
+        <v>1058.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>1018.62</v>
+        <v>1017.8</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -30861,16 +31011,16 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -30878,7 +31028,6 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・売られ過ぎ水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -30914,31 +31063,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1596</v>
+        <v>1616</v>
       </c>
       <c r="F9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="H9" t="n">
-        <v>383900</v>
+        <v>44700</v>
       </c>
       <c r="I9" t="n">
-        <v>40.5</v>
+        <v>47.5</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.66</v>
+        <v>-0.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.14</v>
+        <v>0.36</v>
       </c>
       <c r="L9" t="n">
-        <v>8.289999999999999</v>
+        <v>10.46</v>
       </c>
       <c r="M9" t="n">
-        <v>19.18</v>
+        <v>17.44</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -30951,10 +31100,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1458.21</v>
+        <v>1462.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1383.37</v>
+        <v>1384.85</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -30962,327 +31111,19 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・出来高が急増しています。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9342.T</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>スマサポ</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>不動産DX</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>965</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-16</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-1.63</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3500</v>
-      </c>
-      <c r="I10" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="L10" t="n">
-        <v>15.63</v>
-      </c>
-      <c r="M10" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>880.5700000000001</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>986.77</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>65</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・出来高が急増しています。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>6971.T</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>京セラ</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>自社株</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>3637</v>
-      </c>
-      <c r="F11" t="n">
-        <v>78</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8509000</v>
-      </c>
-      <c r="I11" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-27.35</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-42.23</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>3661.11</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2949.76</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>80</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・出来高が増加しています。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2026/10/29</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>あと36日</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>3778.T</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>さくらインターネット(株)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="n">
-        <v>3840</v>
-      </c>
-      <c r="F12" t="n">
-        <v>145</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="H12" t="n">
-        <v>941900</v>
-      </c>
-      <c r="I12" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="L12" t="n">
-        <v>62.56</v>
-      </c>
-      <c r="M12" t="n">
-        <v>78.64</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>3230.67</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3064.09</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S12" t="n">
-        <v>75</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -31293,6 +31134,313 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9342.T</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>スマサポ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>不動産DX</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>966</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I10" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L10" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="M10" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>883.39</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>986.8099999999999</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>55</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6971.T</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>京セラ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>自社株</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3653</v>
+      </c>
+      <c r="F11" t="n">
+        <v>16</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1972000</v>
+      </c>
+      <c r="I11" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-17.73</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-37.33</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>3657.64</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2957.58</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>100</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026/10/29</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>あと35日</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3778.T</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>さくらインターネット(株)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>3850</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H12" t="n">
+        <v>287300</v>
+      </c>
+      <c r="I12" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L12" t="n">
+        <v>71.44</v>
+      </c>
+      <c r="M12" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>3243</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3067.77</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>95</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
@@ -31319,31 +31467,31 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>4952</v>
+        <v>5018</v>
       </c>
       <c r="F13" t="n">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="G13" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="H13" t="n">
-        <v>37410000</v>
+        <v>21419300</v>
       </c>
       <c r="I13" t="n">
-        <v>38.3</v>
+        <v>43.7</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.15</v>
+        <v>-3.1</v>
       </c>
       <c r="K13" t="n">
-        <v>1.16</v>
+        <v>0.73</v>
       </c>
       <c r="L13" t="n">
-        <v>-77.16</v>
+        <v>-70.69</v>
       </c>
       <c r="M13" t="n">
-        <v>-29.22</v>
+        <v>-37.51</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -31356,10 +31504,10 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5067.96</v>
+        <v>5070.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>4504.35</v>
+        <v>4514.48</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -31396,7 +31544,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>あと48日</t>
+          <t>あと47日</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -31427,31 +31575,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>0.37</v>
+        <v>0.55</v>
       </c>
       <c r="H14" t="n">
-        <v>338500</v>
+        <v>88300</v>
       </c>
       <c r="I14" t="n">
-        <v>31.4</v>
+        <v>26.9</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.36</v>
+        <v>-3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>1.43</v>
+        <v>0.44</v>
       </c>
       <c r="L14" t="n">
-        <v>-18.49</v>
+        <v>-17.24</v>
       </c>
       <c r="M14" t="n">
-        <v>-11.41</v>
+        <v>-12.58</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -31464,10 +31612,10 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1113.28</v>
+        <v>1115.32</v>
       </c>
       <c r="Q14" t="n">
-        <v>930.58</v>
+        <v>932.27</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -31475,16 +31623,16 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -31492,6 +31640,7 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは売りシグナルです。
+・売られ過ぎ水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
@@ -31527,31 +31676,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3901</v>
+        <v>3846</v>
       </c>
       <c r="F15" t="n">
-        <v>138</v>
+        <v>-55</v>
       </c>
       <c r="G15" t="n">
-        <v>3.67</v>
+        <v>-1.41</v>
       </c>
       <c r="H15" t="n">
-        <v>21047200</v>
+        <v>12558600</v>
       </c>
       <c r="I15" t="n">
-        <v>47</v>
+        <v>49.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0.12</v>
+        <v>-0.83</v>
       </c>
       <c r="K15" t="n">
-        <v>0.98</v>
+        <v>0.65</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.07</v>
+        <v>-1.6</v>
       </c>
       <c r="M15" t="n">
-        <v>7.81</v>
+        <v>5.93</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -31564,10 +31713,10 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3984.17</v>
+        <v>3967.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>3196.71</v>
+        <v>3211.36</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -31575,16 +31724,16 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -31605,12 +31754,12 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>あと47日</t>
+          <t>あと46日</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>⚪ 様子見（押し目ではない）</t>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -31632,31 +31781,31 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>4080</v>
+        <v>4330</v>
       </c>
       <c r="F16" t="n">
-        <v>55</v>
+        <v>250</v>
       </c>
       <c r="G16" t="n">
-        <v>1.37</v>
+        <v>6.13</v>
       </c>
       <c r="H16" t="n">
-        <v>14700</v>
+        <v>35900</v>
       </c>
       <c r="I16" t="n">
-        <v>43.8</v>
+        <v>52.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1</v>
+        <v>6.23</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.48</v>
       </c>
       <c r="L16" t="n">
-        <v>31.1</v>
+        <v>54.65</v>
       </c>
       <c r="M16" t="n">
-        <v>61.59</v>
+        <v>60.2</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -31665,34 +31814,344 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>3612.07</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2871.62</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>95</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>7012.T</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>川崎重工業(株)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>2436</v>
+      </c>
+      <c r="F17" t="n">
+        <v>31</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4767500</v>
+      </c>
+      <c r="I17" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-78.12</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-88.55</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P16" t="n">
-        <v>3594.17</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2859.88</v>
-      </c>
-      <c r="R16" t="inlineStr">
+      <c r="P17" t="n">
+        <v>2729.02</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2834.6</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは買いシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>あと48日</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>トヨタ自動車(株)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4000円で売る予定</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2972</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-53.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="H18" t="n">
+        <v>17846300</v>
+      </c>
+      <c r="I18" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-6.13</v>
+      </c>
+      <c r="M18" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>2940.55</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3164.23</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>75</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・売られ過ぎ水準です。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2026/11/05</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>あと42日</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>8053.T</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>住友商事</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>1788</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4157400</v>
+      </c>
+      <c r="I19" t="n">
+        <v>43</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L19" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="M19" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1678.64</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1573.73</v>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S16" t="n">
-        <v>75</v>
-      </c>
-      <c r="T16" t="inlineStr">
+      <c r="S19" t="n">
+        <v>65</v>
+      </c>
+      <c r="T19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -31702,330 +32161,19 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>7012.T</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>川崎重工業(株)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="n">
-        <v>2405</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-0.68</v>
-      </c>
-      <c r="H17" t="n">
-        <v>10860700</v>
-      </c>
-      <c r="I17" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-4.59</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-85.69</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-91.16</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>2734.48</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2832.35</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S17" t="n">
-        <v>30</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは買いシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>あと49日</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>7203.T</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>トヨタ自動車(株)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4000円で売る予定</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>3025</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-9</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="H18" t="n">
-        <v>46568200</v>
-      </c>
-      <c r="I18" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="M18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>2938.78</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3164.84</v>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="S18" t="n">
-        <v>60</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・出来高が増加しています。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>2026/11/05</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>あと43日</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2026/10/29</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>あと35日</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
         <is>
           <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>8053.T</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>住友商事</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="n">
-        <v>1796</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-48.5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-2.63</v>
-      </c>
-      <c r="H19" t="n">
-        <v>19454100</v>
-      </c>
-      <c r="I19" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="L19" t="n">
-        <v>23.49</v>
-      </c>
-      <c r="M19" t="n">
-        <v>30.97</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1677.39</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1570.66</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S19" t="n">
-        <v>100</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・出来高が増加しています。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>2026/10/29</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>あと36日</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
@@ -32054,28 +32202,28 @@
         <v>491</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>524400</v>
+        <v>301700</v>
       </c>
       <c r="I20" t="n">
-        <v>47.1</v>
+        <v>54.1</v>
       </c>
       <c r="J20" t="n">
-        <v>4.87</v>
+        <v>4.38</v>
       </c>
       <c r="K20" t="n">
-        <v>0.65</v>
+        <v>0.4</v>
       </c>
       <c r="L20" t="n">
-        <v>7.7</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>6.45</v>
+        <v>6.86</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -32088,10 +32236,10 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>434.25</v>
+        <v>435.12</v>
       </c>
       <c r="Q20" t="n">
-        <v>413.97</v>
+        <v>414.62</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -32099,7 +32247,7 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -32148,31 +32296,31 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>9375</v>
+        <v>9268</v>
       </c>
       <c r="F21" t="n">
-        <v>375</v>
+        <v>-107</v>
       </c>
       <c r="G21" t="n">
-        <v>4.17</v>
+        <v>-1.14</v>
       </c>
       <c r="H21" t="n">
-        <v>25919200</v>
+        <v>15158900</v>
       </c>
       <c r="I21" t="n">
-        <v>52</v>
+        <v>49.8</v>
       </c>
       <c r="J21" t="n">
-        <v>0.49</v>
+        <v>0.21</v>
       </c>
       <c r="K21" t="n">
-        <v>0.92</v>
+        <v>0.58</v>
       </c>
       <c r="L21" t="n">
-        <v>-366.8</v>
+        <v>-335.75</v>
       </c>
       <c r="M21" t="n">
-        <v>-496.14</v>
+        <v>-464.06</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -32185,10 +32333,10 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>12859.19</v>
+        <v>12768.16</v>
       </c>
       <c r="Q21" t="n">
-        <v>7985.4</v>
+        <v>8015.78</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -32196,16 +32344,16 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -32226,7 +32374,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>あと43日</t>
+          <t>あと42日</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -32249,31 +32397,31 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>54570</v>
+        <v>54980</v>
       </c>
       <c r="F22" t="n">
-        <v>4690</v>
+        <v>410</v>
       </c>
       <c r="G22" t="n">
-        <v>9.4</v>
+        <v>0.75</v>
       </c>
       <c r="H22" t="n">
-        <v>34475500</v>
+        <v>17207400</v>
       </c>
       <c r="I22" t="n">
-        <v>58.1</v>
+        <v>57.2</v>
       </c>
       <c r="J22" t="n">
-        <v>2.53</v>
+        <v>3.84</v>
       </c>
       <c r="K22" t="n">
-        <v>1.19</v>
+        <v>0.65</v>
       </c>
       <c r="L22" t="n">
-        <v>-673.09</v>
+        <v>-465.96</v>
       </c>
       <c r="M22" t="n">
-        <v>-756.99</v>
+        <v>-698.78</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -32286,10 +32434,10 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>65199.07</v>
+        <v>64906.53</v>
       </c>
       <c r="Q22" t="n">
-        <v>40218.4</v>
+        <v>40451.37</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -32327,7 +32475,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>あと37日</t>
+          <t>あと36日</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -32350,31 +32498,31 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>162.5</v>
+        <v>159.3</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5</v>
+        <v>-3.2</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.91</v>
+        <v>-1.97</v>
       </c>
       <c r="H23" t="n">
-        <v>57685000</v>
+        <v>39520300</v>
       </c>
       <c r="I23" t="n">
-        <v>57.7</v>
+        <v>46</v>
       </c>
       <c r="J23" t="n">
-        <v>0.98</v>
+        <v>-1.1</v>
       </c>
       <c r="K23" t="n">
-        <v>1.12</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="M23" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -32387,10 +32535,10 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>153</v>
+        <v>153.23</v>
       </c>
       <c r="Q23" t="n">
-        <v>150.85</v>
+        <v>150.94</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -32398,16 +32546,16 @@
         </is>
       </c>
       <c r="S23" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -32428,12 +32576,12 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>あと50日</t>
+          <t>あと49日</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>⚪ 様子見（押し目ではない）</t>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -32451,31 +32599,31 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>3309</v>
+        <v>3475</v>
       </c>
       <c r="F24" t="n">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="G24" t="n">
-        <v>4.45</v>
+        <v>5.02</v>
       </c>
       <c r="H24" t="n">
-        <v>15511700</v>
+        <v>10473600</v>
       </c>
       <c r="I24" t="n">
-        <v>46.1</v>
+        <v>57</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.62</v>
+        <v>3.81</v>
       </c>
       <c r="K24" t="n">
-        <v>1.62</v>
+        <v>1.08</v>
       </c>
       <c r="L24" t="n">
-        <v>-125.21</v>
+        <v>-99.38</v>
       </c>
       <c r="M24" t="n">
-        <v>-144.58</v>
+        <v>-135.54</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -32488,10 +32636,10 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3984.33</v>
+        <v>3966.16</v>
       </c>
       <c r="Q24" t="n">
-        <v>3201.34</v>
+        <v>3209.66</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -32499,16 +32647,16 @@
         </is>
       </c>
       <c r="S24" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -32517,7 +32665,6 @@
 ・🟡 反発中
 ・MACDは買いシグナルです。
 ・RSIは良好な水準です。
-・出来高が増加しています。
 ・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
@@ -32530,12 +32677,12 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>あと35日</t>
+          <t>あと34日</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
+          <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
@@ -32562,7 +32709,7 @@
         <v>-1.88</v>
       </c>
       <c r="H25" t="n">
-        <v>1518193</v>
+        <v>1518600</v>
       </c>
       <c r="I25" t="n">
         <v>63.2</v>
@@ -32631,7 +32778,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>あと13日</t>
+          <t>あと12日</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -32654,31 +32801,31 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>8339</v>
+        <v>8235</v>
       </c>
       <c r="F26" t="n">
-        <v>-136</v>
+        <v>-104</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.6</v>
+        <v>-1.25</v>
       </c>
       <c r="H26" t="n">
-        <v>6274100</v>
+        <v>3701400</v>
       </c>
       <c r="I26" t="n">
-        <v>33.7</v>
+        <v>30.3</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.36</v>
+        <v>-4.33</v>
       </c>
       <c r="K26" t="n">
-        <v>0.88</v>
+        <v>0.62</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.49</v>
+        <v>-14.85</v>
       </c>
       <c r="M26" t="n">
-        <v>81.72</v>
+        <v>62.4</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -32687,14 +32834,14 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7767.47</v>
+        <v>7780.31</v>
       </c>
       <c r="Q26" t="n">
-        <v>8678.030000000001</v>
+        <v>8654.299999999999</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -32702,7 +32849,7 @@
         </is>
       </c>
       <c r="S26" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -32719,7 +32866,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
@@ -32731,7 +32878,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>あと43日</t>
+          <t>あと42日</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>214,014円</t>
+          <t>214,015円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4,724円</t>
+          <t>4,725円</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>41.44</v>
+        <v>41.51</v>
       </c>
       <c r="F10" t="n">
-        <v>60.2</v>
+        <v>58.7</v>
       </c>
       <c r="G10" t="n">
-        <v>8.5</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="I10" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="J10" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.1</v>
+        <v>33.07</v>
       </c>
       <c r="N10" t="n">
-        <v>31.72</v>
+        <v>31.75</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1680,6 +1680,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
+・RSIは良好な水準です。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -1692,22 +1693,22 @@
         </is>
       </c>
       <c r="W10" t="n">
-        <v>41.54</v>
+        <v>41.44</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.24</v>
+        <v>0.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6072</v>
+        <v>-6071</v>
       </c>
       <c r="AC10" t="n">
         <v>-99.31999999999999</v>
@@ -1724,7 +1725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1583"/>
+  <dimension ref="A1:C1592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25472,6 +25473,141 @@
       </c>
       <c r="C1583" t="n">
         <v>41.44</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1584" t="n">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1585" t="n">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1586" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1587" t="n">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1588" t="n">
+        <v>8196</v>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1589" t="n">
+        <v>4811</v>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1590" t="n">
+        <v>54580</v>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1591" t="n">
+        <v>8935</v>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1592" t="n">
+        <v>41.51</v>
       </c>
     </row>
   </sheetData>
@@ -25485,7 +25621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F262"/>
+  <dimension ref="A1:F263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30165,19 +30301,29 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr">
+      <c r="A260" t="inlineStr"/>
+      <c r="B260" s="1" t="n">
+        <v>46290.22152777778</v>
+      </c>
+      <c r="C260" t="n">
+        <v>214015</v>
+      </c>
+      <c r="D260" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E260" t="n">
+        <v>4725</v>
+      </c>
+      <c r="F260" t="n">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr"/>
-      <c r="C260" t="inlineStr"/>
-      <c r="D260" t="inlineStr"/>
-      <c r="E260" t="inlineStr"/>
-      <c r="F260" t="inlineStr"/>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr"/>
       <c r="B261" t="inlineStr"/>
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr"/>
@@ -30185,16 +30331,24 @@
       <c r="F261" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A262" t="inlineStr"/>
       <c r="B262" t="inlineStr"/>
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr"/>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -30359,31 +30513,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1000</v>
+        <v>986</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>-10</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4</v>
+        <v>-1</v>
       </c>
       <c r="H2" t="n">
-        <v>371000</v>
+        <v>644200</v>
       </c>
       <c r="I2" t="n">
-        <v>47.1</v>
+        <v>44.5</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.17</v>
+        <v>-1.51</v>
       </c>
       <c r="K2" t="n">
-        <v>0.62</v>
+        <v>0.99</v>
       </c>
       <c r="L2" t="n">
-        <v>23.4</v>
+        <v>22.28</v>
       </c>
       <c r="M2" t="n">
-        <v>34.3</v>
+        <v>34.08</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -30396,10 +30550,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>858.27</v>
+        <v>858.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1113.71</v>
+        <v>1113.64</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -30424,7 +30578,6 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
-・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -30460,31 +30613,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3375</v>
+        <v>3330</v>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>-10</v>
       </c>
       <c r="G3" t="n">
-        <v>1.05</v>
+        <v>-0.3</v>
       </c>
       <c r="H3" t="n">
-        <v>22800</v>
+        <v>45200</v>
       </c>
       <c r="I3" t="n">
-        <v>36.8</v>
+        <v>34.2</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.57</v>
+        <v>-2.84</v>
       </c>
       <c r="K3" t="n">
-        <v>0.18</v>
+        <v>0.34</v>
       </c>
       <c r="L3" t="n">
-        <v>16.14</v>
+        <v>12.56</v>
       </c>
       <c r="M3" t="n">
-        <v>41.61</v>
+        <v>40.89</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -30497,10 +30650,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3056.11</v>
+        <v>3055.51</v>
       </c>
       <c r="Q3" t="n">
-        <v>2729.36</v>
+        <v>2729.13</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -30560,31 +30713,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1398</v>
+        <v>1381</v>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>3.17</v>
+        <v>1.92</v>
       </c>
       <c r="H4" t="n">
-        <v>13600</v>
+        <v>22000</v>
       </c>
       <c r="I4" t="n">
-        <v>52</v>
+        <v>49.5</v>
       </c>
       <c r="J4" t="n">
-        <v>6.47</v>
+        <v>5.23</v>
       </c>
       <c r="K4" t="n">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="L4" t="n">
-        <v>35.57</v>
+        <v>34.21</v>
       </c>
       <c r="M4" t="n">
-        <v>37.73</v>
+        <v>37.46</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -30597,10 +30750,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1212.84</v>
+        <v>1212.61</v>
       </c>
       <c r="Q4" t="n">
-        <v>1638.17</v>
+        <v>1638.09</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -30608,16 +30761,16 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -30626,6 +30779,7 @@
 ・🟢 上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
+・出来高が増加しています。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -30661,31 +30815,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3530</v>
+        <v>3545</v>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>1.15</v>
+        <v>1.58</v>
       </c>
       <c r="H5" t="n">
-        <v>2600</v>
+        <v>7600</v>
       </c>
       <c r="I5" t="n">
-        <v>47.8</v>
+        <v>48.6</v>
       </c>
       <c r="J5" t="n">
-        <v>2.19</v>
+        <v>2.61</v>
       </c>
       <c r="K5" t="n">
-        <v>0.36</v>
+        <v>0.93</v>
       </c>
       <c r="L5" t="n">
-        <v>13.19</v>
+        <v>14.39</v>
       </c>
       <c r="M5" t="n">
-        <v>9.31</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -30694,14 +30848,14 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3423</v>
+        <v>3423.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3160.03</v>
+        <v>3160.11</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -30727,7 +30881,7 @@
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -30762,31 +30916,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1600</v>
+        <v>1586</v>
       </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G6" t="n">
-        <v>2.11</v>
+        <v>1.21</v>
       </c>
       <c r="H6" t="n">
-        <v>43600</v>
+        <v>87500</v>
       </c>
       <c r="I6" t="n">
-        <v>62.7</v>
+        <v>60.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.24</v>
+        <v>2.38</v>
       </c>
       <c r="K6" t="n">
-        <v>0.86</v>
+        <v>1.47</v>
       </c>
       <c r="L6" t="n">
-        <v>-14.83</v>
+        <v>-15.95</v>
       </c>
       <c r="M6" t="n">
-        <v>-27.47</v>
+        <v>-27.69</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -30799,10 +30953,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1674.08</v>
+        <v>1673.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>1693.98</v>
+        <v>1693.91</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -30862,31 +31016,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="H7" t="n">
-        <v>4300</v>
+        <v>14600</v>
       </c>
       <c r="I7" t="n">
-        <v>48</v>
+        <v>51.9</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.15</v>
+        <v>0.21</v>
       </c>
       <c r="K7" t="n">
-        <v>0.32</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>-5.22</v>
+        <v>-5.06</v>
       </c>
       <c r="M7" t="n">
-        <v>-6.56</v>
+        <v>-6.53</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -30899,10 +31053,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>538.24</v>
+        <v>538.27</v>
       </c>
       <c r="Q7" t="n">
-        <v>580.12</v>
+        <v>580.13</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -30910,16 +31064,16 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -30963,31 +31117,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1109</v>
+        <v>1100</v>
       </c>
       <c r="F8" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>1.74</v>
+        <v>0.92</v>
       </c>
       <c r="H8" t="n">
-        <v>2900</v>
+        <v>4700</v>
       </c>
       <c r="I8" t="n">
-        <v>37.6</v>
+        <v>34</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.26</v>
+        <v>-2.03</v>
       </c>
       <c r="K8" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.13</v>
+        <v>-6.84</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.77</v>
+        <v>-1.91</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -31000,10 +31154,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1058.85</v>
+        <v>1058.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>1017.8</v>
+        <v>1017.75</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -31011,19 +31165,120 @@
         </is>
       </c>
       <c r="S8" t="n">
+        <v>70</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・出来高が増加しています。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7033.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>マネジメントソリューションズ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PMO支援・DX案件増加</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1575</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-21</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="H9" t="n">
+        <v>103500</v>
+      </c>
+      <c r="I9" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L9" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="M9" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1461.65</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1384.64</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
         <v>65</v>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -31033,107 +31288,6 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>7033.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>マネジメントソリューションズ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PMO支援・DX案件増加</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1616</v>
-      </c>
-      <c r="F9" t="n">
-        <v>20</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H9" t="n">
-        <v>44700</v>
-      </c>
-      <c r="I9" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="L9" t="n">
-        <v>10.46</v>
-      </c>
-      <c r="M9" t="n">
-        <v>17.44</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>1462.2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1384.85</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>65</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
@@ -31164,31 +31318,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1000</v>
+        <v>3600</v>
       </c>
       <c r="I10" t="n">
-        <v>40.8</v>
+        <v>40.2</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.28</v>
+        <v>-0.38</v>
       </c>
       <c r="K10" t="n">
-        <v>0.72</v>
+        <v>1.89</v>
       </c>
       <c r="L10" t="n">
-        <v>13.6</v>
+        <v>13.52</v>
       </c>
       <c r="M10" t="n">
-        <v>19.32</v>
+        <v>19.3</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -31201,10 +31355,10 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>883.39</v>
+        <v>883.37</v>
       </c>
       <c r="Q10" t="n">
-        <v>986.8099999999999</v>
+        <v>986.8</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -31212,7 +31366,7 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -31229,6 +31383,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
+・出来高が増加しています。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -31264,31 +31419,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3653</v>
+        <v>3650</v>
       </c>
       <c r="F11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>0.44</v>
+        <v>0.36</v>
       </c>
       <c r="H11" t="n">
-        <v>1972000</v>
+        <v>4843900</v>
       </c>
       <c r="I11" t="n">
-        <v>50.3</v>
+        <v>50.1</v>
       </c>
       <c r="J11" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="K11" t="n">
-        <v>0.47</v>
+        <v>1.01</v>
       </c>
       <c r="L11" t="n">
-        <v>-17.73</v>
+        <v>-17.97</v>
       </c>
       <c r="M11" t="n">
-        <v>-37.33</v>
+        <v>-37.38</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -31301,10 +31456,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3657.64</v>
+        <v>3657.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>2957.58</v>
+        <v>2957.57</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -31370,31 +31525,31 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>3850</v>
+        <v>3830</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="G12" t="n">
-        <v>0.26</v>
+        <v>-0.26</v>
       </c>
       <c r="H12" t="n">
-        <v>287300</v>
+        <v>542100</v>
       </c>
       <c r="I12" t="n">
-        <v>52.2</v>
+        <v>51.4</v>
       </c>
       <c r="J12" t="n">
-        <v>4.03</v>
+        <v>3.51</v>
       </c>
       <c r="K12" t="n">
-        <v>0.41</v>
+        <v>0.73</v>
       </c>
       <c r="L12" t="n">
-        <v>71.44</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>77.2</v>
+        <v>76.88</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -31407,10 +31562,10 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3243</v>
+        <v>3242.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>3067.77</v>
+        <v>3067.67</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -31467,31 +31622,31 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>5018</v>
+        <v>4911</v>
       </c>
       <c r="F13" t="n">
-        <v>66</v>
+        <v>-41</v>
       </c>
       <c r="G13" t="n">
-        <v>1.33</v>
+        <v>-0.83</v>
       </c>
       <c r="H13" t="n">
-        <v>21419300</v>
+        <v>34159800</v>
       </c>
       <c r="I13" t="n">
-        <v>43.7</v>
+        <v>41.2</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.1</v>
+        <v>-5.09</v>
       </c>
       <c r="K13" t="n">
-        <v>0.73</v>
+        <v>1.07</v>
       </c>
       <c r="L13" t="n">
-        <v>-70.69</v>
+        <v>-79.22</v>
       </c>
       <c r="M13" t="n">
-        <v>-37.51</v>
+        <v>-39.22</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -31504,10 +31659,10 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5070.8</v>
+        <v>5069.37</v>
       </c>
       <c r="Q13" t="n">
-        <v>4514.48</v>
+        <v>4513.95</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -31575,31 +31730,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0.55</v>
+        <v>0.09</v>
       </c>
       <c r="H14" t="n">
-        <v>88300</v>
+        <v>238300</v>
       </c>
       <c r="I14" t="n">
-        <v>26.9</v>
+        <v>25.3</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.5</v>
+        <v>-3.92</v>
       </c>
       <c r="K14" t="n">
-        <v>0.44</v>
+        <v>1.03</v>
       </c>
       <c r="L14" t="n">
-        <v>-17.24</v>
+        <v>-17.64</v>
       </c>
       <c r="M14" t="n">
-        <v>-12.58</v>
+        <v>-12.66</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -31612,10 +31767,10 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1115.32</v>
+        <v>1115.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>932.27</v>
+        <v>932.24</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -31676,31 +31831,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3846</v>
+        <v>3807</v>
       </c>
       <c r="F15" t="n">
-        <v>-55</v>
+        <v>-94</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.41</v>
+        <v>-2.41</v>
       </c>
       <c r="H15" t="n">
-        <v>12558600</v>
+        <v>19858900</v>
       </c>
       <c r="I15" t="n">
-        <v>49.7</v>
+        <v>48.7</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.83</v>
+        <v>-1.8</v>
       </c>
       <c r="K15" t="n">
-        <v>0.65</v>
+        <v>0.95</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.6</v>
+        <v>-4.71</v>
       </c>
       <c r="M15" t="n">
-        <v>5.93</v>
+        <v>5.31</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -31713,10 +31868,10 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3967.32</v>
+        <v>3966.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>3211.36</v>
+        <v>3211.17</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -31781,31 +31936,31 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>4330</v>
+        <v>4445</v>
       </c>
       <c r="F16" t="n">
-        <v>250</v>
+        <v>365</v>
       </c>
       <c r="G16" t="n">
-        <v>6.13</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>35900</v>
+        <v>58000</v>
       </c>
       <c r="I16" t="n">
-        <v>52.8</v>
+        <v>56</v>
       </c>
       <c r="J16" t="n">
-        <v>6.23</v>
+        <v>8.92</v>
       </c>
       <c r="K16" t="n">
-        <v>1.48</v>
+        <v>2.03</v>
       </c>
       <c r="L16" t="n">
-        <v>54.65</v>
+        <v>63.83</v>
       </c>
       <c r="M16" t="n">
-        <v>60.2</v>
+        <v>62.04</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -31814,14 +31969,14 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>+2S</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3612.07</v>
+        <v>3613.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>2871.62</v>
+        <v>2872.19</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -31829,7 +31984,7 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -31845,9 +32000,10 @@
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
-・MACDは売りシグナルです。
+・MACDは買いシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・出来高が急増しています。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -31878,31 +32034,31 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>2436</v>
+        <v>2400</v>
       </c>
       <c r="F17" t="n">
-        <v>31</v>
+        <v>-4.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1.29</v>
+        <v>-0.19</v>
       </c>
       <c r="H17" t="n">
-        <v>4767500</v>
+        <v>9020900</v>
       </c>
       <c r="I17" t="n">
-        <v>42.3</v>
+        <v>38.7</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.71</v>
+        <v>-4.08</v>
       </c>
       <c r="K17" t="n">
-        <v>0.43</v>
+        <v>0.76</v>
       </c>
       <c r="L17" t="n">
-        <v>-78.12</v>
+        <v>-80.95</v>
       </c>
       <c r="M17" t="n">
-        <v>-88.55</v>
+        <v>-89.12</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -31915,10 +32071,10 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2729.02</v>
+        <v>2728.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>2834.6</v>
+        <v>2834.42</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -31986,31 +32142,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2972</v>
+        <v>2969</v>
       </c>
       <c r="F18" t="n">
-        <v>-53.5</v>
+        <v>-56</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.77</v>
+        <v>-1.85</v>
       </c>
       <c r="H18" t="n">
-        <v>17846300</v>
+        <v>33817300</v>
       </c>
       <c r="I18" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.91</v>
+        <v>-2.99</v>
       </c>
       <c r="K18" t="n">
-        <v>0.73</v>
+        <v>1.22</v>
       </c>
       <c r="L18" t="n">
-        <v>-6.13</v>
+        <v>-6.33</v>
       </c>
       <c r="M18" t="n">
-        <v>6.3</v>
+        <v>6.26</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -32023,10 +32179,10 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2940.55</v>
+        <v>2940.52</v>
       </c>
       <c r="Q18" t="n">
-        <v>3164.23</v>
+        <v>3164.21</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -32091,31 +32247,31 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>1788</v>
+        <v>1769</v>
       </c>
       <c r="F19" t="n">
-        <v>-8.5</v>
+        <v>-27.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.47</v>
+        <v>-1.53</v>
       </c>
       <c r="H19" t="n">
-        <v>4157400</v>
+        <v>11285900</v>
       </c>
       <c r="I19" t="n">
-        <v>43</v>
+        <v>41.3</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.12</v>
+        <v>-1.14</v>
       </c>
       <c r="K19" t="n">
-        <v>0.43</v>
+        <v>1.03</v>
       </c>
       <c r="L19" t="n">
-        <v>20.16</v>
+        <v>18.65</v>
       </c>
       <c r="M19" t="n">
-        <v>28.81</v>
+        <v>28.5</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -32128,10 +32284,10 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1678.64</v>
+        <v>1678.39</v>
       </c>
       <c r="Q19" t="n">
-        <v>1573.73</v>
+        <v>1573.63</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -32199,31 +32355,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.61</v>
       </c>
       <c r="H20" t="n">
-        <v>301700</v>
+        <v>853500</v>
       </c>
       <c r="I20" t="n">
-        <v>54.1</v>
+        <v>52.9</v>
       </c>
       <c r="J20" t="n">
-        <v>4.38</v>
+        <v>3.77</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4</v>
+        <v>0.98</v>
       </c>
       <c r="L20" t="n">
-        <v>8.529999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>6.86</v>
+        <v>6.81</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -32236,10 +32392,10 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>435.12</v>
+        <v>435.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>414.62</v>
+        <v>414.6</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -32296,31 +32452,31 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>9268</v>
+        <v>8935</v>
       </c>
       <c r="F21" t="n">
-        <v>-107</v>
+        <v>-440</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.14</v>
+        <v>-4.69</v>
       </c>
       <c r="H21" t="n">
-        <v>15158900</v>
+        <v>27368700</v>
       </c>
       <c r="I21" t="n">
-        <v>49.8</v>
+        <v>46.6</v>
       </c>
       <c r="J21" t="n">
-        <v>0.21</v>
+        <v>-3.25</v>
       </c>
       <c r="K21" t="n">
-        <v>0.58</v>
+        <v>0.96</v>
       </c>
       <c r="L21" t="n">
-        <v>-335.75</v>
+        <v>-362.32</v>
       </c>
       <c r="M21" t="n">
-        <v>-464.06</v>
+        <v>-469.38</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -32333,10 +32489,10 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>12768.16</v>
+        <v>12763.72</v>
       </c>
       <c r="Q21" t="n">
-        <v>8015.78</v>
+        <v>8014.11</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -32344,7 +32500,7 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -32379,7 +32535,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>⚪ 様子見（押し目ではない）</t>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -32397,31 +32553,31 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>54980</v>
+        <v>54580</v>
       </c>
       <c r="F22" t="n">
-        <v>410</v>
+        <v>10</v>
       </c>
       <c r="G22" t="n">
-        <v>0.75</v>
+        <v>0.02</v>
       </c>
       <c r="H22" t="n">
-        <v>17207400</v>
+        <v>27809600</v>
       </c>
       <c r="I22" t="n">
-        <v>57.2</v>
+        <v>56.5</v>
       </c>
       <c r="J22" t="n">
-        <v>3.84</v>
+        <v>3.11</v>
       </c>
       <c r="K22" t="n">
-        <v>0.65</v>
+        <v>0.97</v>
       </c>
       <c r="L22" t="n">
-        <v>-465.96</v>
+        <v>-497.87</v>
       </c>
       <c r="M22" t="n">
-        <v>-698.78</v>
+        <v>-705.17</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -32434,10 +32590,10 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>64906.53</v>
+        <v>64901.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>40451.37</v>
+        <v>40449.37</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -32498,31 +32654,31 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>159.3</v>
+        <v>158.9</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.2</v>
+        <v>-3.6</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.97</v>
+        <v>-2.22</v>
       </c>
       <c r="H23" t="n">
-        <v>39520300</v>
+        <v>79200300</v>
       </c>
       <c r="I23" t="n">
-        <v>46</v>
+        <v>45.3</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1</v>
+        <v>-1.34</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="M23" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -32538,7 +32694,7 @@
         <v>153.23</v>
       </c>
       <c r="Q23" t="n">
-        <v>150.94</v>
+        <v>150.93</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -32599,31 +32755,31 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>3475</v>
+        <v>3490</v>
       </c>
       <c r="F24" t="n">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="G24" t="n">
-        <v>5.02</v>
+        <v>5.47</v>
       </c>
       <c r="H24" t="n">
-        <v>10473600</v>
+        <v>16601300</v>
       </c>
       <c r="I24" t="n">
-        <v>57</v>
+        <v>57.6</v>
       </c>
       <c r="J24" t="n">
-        <v>3.81</v>
+        <v>4.24</v>
       </c>
       <c r="K24" t="n">
-        <v>1.08</v>
+        <v>1.52</v>
       </c>
       <c r="L24" t="n">
-        <v>-99.38</v>
+        <v>-98.18000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-135.54</v>
+        <v>-135.3</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -32632,14 +32788,14 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3966.16</v>
+        <v>3966.36</v>
       </c>
       <c r="Q24" t="n">
-        <v>3209.66</v>
+        <v>3209.74</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -32647,7 +32803,7 @@
         </is>
       </c>
       <c r="S24" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -32665,7 +32821,8 @@
 ・🟡 反発中
 ・MACDは買いシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・出来高が増加しています。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
@@ -32801,31 +32958,31 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>8235</v>
+        <v>8196</v>
       </c>
       <c r="F26" t="n">
-        <v>-104</v>
+        <v>-143</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.25</v>
+        <v>-1.71</v>
       </c>
       <c r="H26" t="n">
-        <v>3701400</v>
+        <v>6609600</v>
       </c>
       <c r="I26" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.33</v>
+        <v>-4.77</v>
       </c>
       <c r="K26" t="n">
-        <v>0.62</v>
+        <v>1.01</v>
       </c>
       <c r="L26" t="n">
-        <v>-14.85</v>
+        <v>-17.96</v>
       </c>
       <c r="M26" t="n">
-        <v>62.4</v>
+        <v>61.78</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -32838,10 +32995,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7780.31</v>
+        <v>7779.79</v>
       </c>
       <c r="Q26" t="n">
-        <v>8654.299999999999</v>
+        <v>8654.1</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -32849,16 +33006,16 @@
         </is>
       </c>
       <c r="S26" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -32866,6 +33023,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
+・売られ過ぎ水準です。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -1628,7 +1628,7 @@
         <v>8.119999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="I10" t="n">
         <v>1.58</v>
@@ -1725,7 +1725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1592"/>
+  <dimension ref="A1:C1601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25607,6 +25607,141 @@
         </is>
       </c>
       <c r="C1592" t="n">
+        <v>41.51</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1593" t="n">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1594" t="n">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1595" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1596" t="n">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1597" t="n">
+        <v>8196</v>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1598" t="n">
+        <v>4811</v>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1599" t="n">
+        <v>54580</v>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1600" t="n">
+        <v>8935</v>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1601" t="n">
         <v>41.51</v>
       </c>
     </row>
@@ -25621,7 +25756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F263"/>
+  <dimension ref="A1:F264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30319,19 +30454,29 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr">
+      <c r="A261" t="inlineStr"/>
+      <c r="B261" s="1" t="n">
+        <v>46290.29166666666</v>
+      </c>
+      <c r="C261" t="n">
+        <v>214015</v>
+      </c>
+      <c r="D261" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E261" t="n">
+        <v>4725</v>
+      </c>
+      <c r="F261" t="n">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr"/>
-      <c r="C261" t="inlineStr"/>
-      <c r="D261" t="inlineStr"/>
-      <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr"/>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr"/>
       <c r="B262" t="inlineStr"/>
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr"/>
@@ -30339,16 +30484,24 @@
       <c r="F262" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A263" t="inlineStr"/>
       <c r="B263" t="inlineStr"/>
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr"/>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -32857,35 +33010,35 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>53.88</v>
+        <v>53.08</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.03</v>
+        <v>-0.8</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.88</v>
+        <v>-1.48</v>
       </c>
       <c r="H25" t="n">
-        <v>1518600</v>
+        <v>1574766</v>
       </c>
       <c r="I25" t="n">
-        <v>63.2</v>
+        <v>61.2</v>
       </c>
       <c r="J25" t="n">
-        <v>5.75</v>
+        <v>4.62</v>
       </c>
       <c r="K25" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.59</v>
+        <v>-0.42</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.49</v>
+        <v>-1.28</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -32894,10 +33047,10 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>58.6</v>
+        <v>58.51</v>
       </c>
       <c r="Q25" t="n">
-        <v>38.35</v>
+        <v>38.51</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -32905,7 +33058,7 @@
         </is>
       </c>
       <c r="S25" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -32922,7 +33075,6 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>214,015円</t>
+          <t>215,623円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4,725円</t>
+          <t>6,333円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -717,22 +717,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3330</v>
+        <v>3355</v>
       </c>
       <c r="F2" t="n">
-        <v>34.2</v>
+        <v>41.6</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.84</v>
+        <v>-2.2</v>
       </c>
       <c r="H2" t="n">
-        <v>0.34</v>
+        <v>0.71</v>
       </c>
       <c r="I2" t="n">
-        <v>12.56</v>
+        <v>9.91</v>
       </c>
       <c r="J2" t="n">
-        <v>40.89</v>
+        <v>34.7</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3055.51</v>
+        <v>3067.01</v>
       </c>
       <c r="N2" t="n">
-        <v>2729.13</v>
+        <v>2731.7</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -790,25 +790,25 @@
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3340</v>
+        <v>3330</v>
       </c>
       <c r="X2" t="n">
-        <v>-10</v>
+        <v>25</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.3</v>
+        <v>0.75</v>
       </c>
       <c r="Z2" t="n">
-        <v>13320</v>
+        <v>13420</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2520</v>
+        <v>2620</v>
       </c>
       <c r="AC2" t="n">
-        <v>23.33</v>
+        <v>24.26</v>
       </c>
     </row>
     <row r="3">
@@ -829,22 +829,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="F3" t="n">
-        <v>52.9</v>
+        <v>53.7</v>
       </c>
       <c r="G3" t="n">
-        <v>3.77</v>
+        <v>1.88</v>
       </c>
       <c r="H3" t="n">
-        <v>0.98</v>
+        <v>0.35</v>
       </c>
       <c r="I3" t="n">
-        <v>8.289999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J3" t="n">
-        <v>6.81</v>
+        <v>7.07</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -853,14 +853,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>435.08</v>
+        <v>435.93</v>
       </c>
       <c r="N3" t="n">
-        <v>414.6</v>
+        <v>415.2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -899,29 +899,29 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+1σ、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="X3" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.61</v>
+        <v>-1.43</v>
       </c>
       <c r="Z3" t="n">
-        <v>48800</v>
+        <v>48100</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6800</v>
+        <v>6100</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.19</v>
+        <v>14.52</v>
       </c>
     </row>
     <row r="4">
@@ -942,22 +942,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>174.9</v>
+        <v>175.7</v>
       </c>
       <c r="F4" t="n">
-        <v>48.6</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.11</v>
+        <v>0.36</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="J4" t="n">
-        <v>4.53</v>
+        <v>4.41</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>157.39</v>
+        <v>157.79</v>
       </c>
       <c r="N4" t="n">
-        <v>154.46</v>
+        <v>154.58</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,20 +982,20 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,29 +1012,29 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>25日線上、MACD売り、長期上昇</t>
+          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>177.3</v>
+        <v>174.9</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.4</v>
+        <v>0.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1.35</v>
+        <v>0.46</v>
       </c>
       <c r="Z4" t="n">
-        <v>17490</v>
+        <v>17570</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1690</v>
+        <v>1770</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.7</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="5">
@@ -1055,22 +1055,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>2969</v>
+        <v>2988</v>
       </c>
       <c r="F5" t="n">
-        <v>20.5</v>
+        <v>30.6</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.99</v>
+        <v>-2.32</v>
       </c>
       <c r="H5" t="n">
-        <v>1.22</v>
+        <v>0.33</v>
       </c>
       <c r="I5" t="n">
-        <v>-6.33</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>6.26</v>
+        <v>3.23</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1079,14 +1079,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2940.52</v>
+        <v>2942.36</v>
       </c>
       <c r="N5" t="n">
-        <v>3164.21</v>
+        <v>3163.69</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1095,20 +1095,20 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1116,151 +1116,149 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
-・売られ過ぎ水準です。
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>押し目、MACD売り、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>2969</v>
+      </c>
+      <c r="X5" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>38844</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>37099</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1745</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7993</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8181</v>
+      </c>
+      <c r="F6" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-4.69</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-31.08</v>
+      </c>
+      <c r="J6" t="n">
+        <v>43.21</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>7788.55</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8630.42</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>60</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>RSI売られすぎ、押し目、-1σ、MACD売り、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>3025</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-56</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-1.85</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>38597</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>37099</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1498</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>4.04</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>7993</v>
-      </c>
-      <c r="E6" t="n">
-        <v>8196</v>
-      </c>
-      <c r="F6" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-4.77</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-17.96</v>
-      </c>
-      <c r="J6" t="n">
-        <v>61.78</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>7779.79</v>
-      </c>
-      <c r="N6" t="n">
-        <v>8654.1</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>75</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>RSI売られすぎ、押し目、-1σ、MACD売り、上昇トレンド</t>
+          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>8339</v>
+        <v>8196</v>
       </c>
       <c r="X6" t="n">
-        <v>-143</v>
+        <v>-15</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.71</v>
+        <v>-0.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>8196</v>
+        <v>8181</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.54</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="7">
@@ -1281,22 +1279,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4811</v>
+        <v>4857</v>
       </c>
       <c r="F7" t="n">
-        <v>43.5</v>
+        <v>49.9</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.27</v>
+        <v>-0.39</v>
       </c>
       <c r="H7" t="n">
-        <v>1.32</v>
+        <v>0.37</v>
       </c>
       <c r="I7" t="n">
-        <v>38.94</v>
+        <v>30.74</v>
       </c>
       <c r="J7" t="n">
-        <v>54.02</v>
+        <v>49.36</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1309,10 +1307,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4716.2</v>
+        <v>4716.17</v>
       </c>
       <c r="N7" t="n">
-        <v>4689.58</v>
+        <v>4695.67</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1342,6 +1340,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
+・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -1354,25 +1353,25 @@
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4947</v>
+        <v>4811</v>
       </c>
       <c r="X7" t="n">
-        <v>-136</v>
+        <v>46</v>
       </c>
       <c r="Y7" t="n">
-        <v>-2.75</v>
+        <v>0.96</v>
       </c>
       <c r="Z7" t="n">
-        <v>24055</v>
+        <v>24285</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>80</v>
+        <v>310</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.33</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="8">
@@ -1393,63 +1392,177 @@
         <v>55510</v>
       </c>
       <c r="E8" t="n">
+        <v>55880</v>
+      </c>
+      <c r="F8" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-251.21</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-614.37</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>64604.4</v>
+      </c>
+      <c r="N8" t="n">
+        <v>40683.53</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>🟢 強い買い</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>100</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
+・RSIは良好な水準です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>RSI適正、25日線上、ゴールデンクロス、+1σ、MACD買い、反発局面</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
         <v>54580</v>
       </c>
-      <c r="F8" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-497.87</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-705.17</v>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="X8" t="n">
+        <v>1300</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>55880</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>55510</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>370</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9301</v>
+      </c>
+      <c r="F9" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-325.48</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-440.6</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="M8" t="n">
-        <v>64901.2</v>
-      </c>
-      <c r="N8" t="n">
-        <v>40449.37</v>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="M9" t="n">
+        <v>12676.4</v>
+      </c>
+      <c r="N9" t="n">
+        <v>8044.56</v>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>🟡 反発中</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>🟢 強い買い</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q9" t="n">
         <v>95</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -1460,145 +1573,32 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>RSI適正、25日線上、MACD買い、反発局面</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>54570</v>
-      </c>
-      <c r="X8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>54580</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>55510</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-930</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-1.68</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E9" t="n">
-        <v>8935</v>
-      </c>
-      <c r="F9" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-3.25</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-362.32</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-469.38</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>12763.72</v>
-      </c>
-      <c r="N9" t="n">
-        <v>8014.11</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>65</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>押し目、MACD買い、反発局面</t>
+          <t>RSI適正、25日線上、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>9375</v>
+        <v>8935</v>
       </c>
       <c r="X9" t="n">
-        <v>-440</v>
+        <v>366</v>
       </c>
       <c r="Y9" t="n">
-        <v>-4.69</v>
+        <v>4.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>8935</v>
+        <v>9301</v>
       </c>
       <c r="AA9" t="n">
         <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1065</v>
+        <v>-699</v>
       </c>
       <c r="AC9" t="n">
-        <v>-10.65</v>
+        <v>-6.99</v>
       </c>
     </row>
     <row r="10">
@@ -1628,7 +1628,7 @@
         <v>8.119999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="I10" t="n">
         <v>1.58</v>
@@ -1725,7 +1725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1601"/>
+  <dimension ref="A1:C1610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25742,6 +25742,141 @@
         </is>
       </c>
       <c r="C1601" t="n">
+        <v>41.51</v>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1602" t="n">
+        <v>3355</v>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1603" t="n">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1604" t="n">
+        <v>175.7</v>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1605" t="n">
+        <v>2988</v>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1606" t="n">
+        <v>8181</v>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1607" t="n">
+        <v>4857</v>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1608" t="n">
+        <v>55880</v>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1609" t="n">
+        <v>9301</v>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1610" t="n">
         <v>41.51</v>
       </c>
     </row>
@@ -25756,7 +25891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F264"/>
+  <dimension ref="A1:F265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30472,19 +30607,29 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr">
+      <c r="A262" t="inlineStr"/>
+      <c r="B262" s="1" t="n">
+        <v>46290.5</v>
+      </c>
+      <c r="C262" t="n">
+        <v>215623</v>
+      </c>
+      <c r="D262" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E262" t="n">
+        <v>6333</v>
+      </c>
+      <c r="F262" t="n">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr"/>
-      <c r="C262" t="inlineStr"/>
-      <c r="D262" t="inlineStr"/>
-      <c r="E262" t="inlineStr"/>
-      <c r="F262" t="inlineStr"/>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr"/>
       <c r="B263" t="inlineStr"/>
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr"/>
@@ -30492,16 +30637,24 @@
       <c r="F263" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A264" t="inlineStr"/>
       <c r="B264" t="inlineStr"/>
       <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr"/>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -33019,7 +33172,7 @@
         <v>-1.48</v>
       </c>
       <c r="H25" t="n">
-        <v>1574766</v>
+        <v>1578604</v>
       </c>
       <c r="I25" t="n">
         <v>61.2</v>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>215,623円</t>
+          <t>214,871円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6,333円</t>
+          <t>5,580円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>2.67%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3355</v>
+        <v>3330</v>
       </c>
       <c r="F2" t="n">
-        <v>41.6</v>
+        <v>39.9</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.2</v>
+        <v>-2.9</v>
       </c>
       <c r="H2" t="n">
-        <v>0.71</v>
+        <v>1.1</v>
       </c>
       <c r="I2" t="n">
-        <v>9.91</v>
+        <v>7.92</v>
       </c>
       <c r="J2" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3067.01</v>
+        <v>3066.68</v>
       </c>
       <c r="N2" t="n">
-        <v>2731.7</v>
+        <v>2731.58</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -793,22 +793,22 @@
         <v>3330</v>
       </c>
       <c r="X2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>13420</v>
+        <v>13320</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2620</v>
+        <v>2520</v>
       </c>
       <c r="AC2" t="n">
-        <v>24.26</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="3">
@@ -829,22 +829,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="F3" t="n">
-        <v>53.7</v>
+        <v>52.1</v>
       </c>
       <c r="G3" t="n">
-        <v>1.88</v>
+        <v>1.07</v>
       </c>
       <c r="H3" t="n">
-        <v>0.35</v>
+        <v>0.72</v>
       </c>
       <c r="I3" t="n">
-        <v>8.1</v>
+        <v>7.78</v>
       </c>
       <c r="J3" t="n">
-        <v>7.07</v>
+        <v>7.01</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>435.93</v>
+        <v>435.88</v>
       </c>
       <c r="N3" t="n">
-        <v>415.2</v>
+        <v>415.18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -906,22 +906,22 @@
         <v>488</v>
       </c>
       <c r="X3" t="n">
-        <v>-7</v>
+        <v>-11</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.43</v>
+        <v>-2.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>48100</v>
+        <v>47700</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6100</v>
+        <v>5700</v>
       </c>
       <c r="AC3" t="n">
-        <v>14.52</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="4">
@@ -942,19 +942,19 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>175.7</v>
+        <v>176.1</v>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>51.7</v>
       </c>
       <c r="G4" t="n">
-        <v>2.07</v>
+        <v>2.29</v>
       </c>
       <c r="H4" t="n">
-        <v>0.36</v>
+        <v>0.93</v>
       </c>
       <c r="I4" t="n">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="J4" t="n">
         <v>4.41</v>
@@ -1019,22 +1019,22 @@
         <v>174.9</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.46</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z4" t="n">
-        <v>17570</v>
+        <v>17610</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1770</v>
+        <v>1810</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.2</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="5">
@@ -1055,22 +1055,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>2988</v>
+        <v>2989.5</v>
       </c>
       <c r="F5" t="n">
-        <v>30.6</v>
+        <v>30.9</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.32</v>
+        <v>-2.28</v>
       </c>
       <c r="H5" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="I5" t="n">
-        <v>-8.859999999999999</v>
+        <v>-8.74</v>
       </c>
       <c r="J5" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2942.36</v>
+        <v>2942.38</v>
       </c>
       <c r="N5" t="n">
-        <v>3163.69</v>
+        <v>3163.7</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1131,22 +1131,22 @@
         <v>2969</v>
       </c>
       <c r="X5" t="n">
-        <v>19</v>
+        <v>20.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>38844</v>
+        <v>38864</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>1745</v>
+        <v>1764</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.7</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="6">
@@ -1167,22 +1167,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>8181</v>
+        <v>8100</v>
       </c>
       <c r="F6" t="n">
-        <v>33.8</v>
+        <v>32.5</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.69</v>
+        <v>-5.59</v>
       </c>
       <c r="H6" t="n">
-        <v>0.45</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>-31.08</v>
+        <v>-37.54</v>
       </c>
       <c r="J6" t="n">
-        <v>43.21</v>
+        <v>41.92</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>7788.55</v>
+        <v>7787.47</v>
       </c>
       <c r="N6" t="n">
-        <v>8630.42</v>
+        <v>8630.02</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1243,22 +1243,22 @@
         <v>8196</v>
       </c>
       <c r="X6" t="n">
-        <v>-15</v>
+        <v>-96</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.18</v>
+        <v>-1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>8181</v>
+        <v>8100</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.35</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="7">
@@ -1279,22 +1279,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4857</v>
+        <v>4859</v>
       </c>
       <c r="F7" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.39</v>
+        <v>-0.35</v>
       </c>
       <c r="H7" t="n">
-        <v>0.37</v>
+        <v>0.91</v>
       </c>
       <c r="I7" t="n">
-        <v>30.74</v>
+        <v>30.9</v>
       </c>
       <c r="J7" t="n">
-        <v>49.36</v>
+        <v>49.4</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4716.17</v>
+        <v>4716.2</v>
       </c>
       <c r="N7" t="n">
-        <v>4695.67</v>
+        <v>4695.68</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1319,20 +1319,20 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1349,29 +1349,29 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>RSI適正、押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W7" t="n">
         <v>4811</v>
       </c>
       <c r="X7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>24285</v>
+        <v>24295</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="8">
@@ -1392,22 +1392,22 @@
         <v>55510</v>
       </c>
       <c r="E8" t="n">
-        <v>55880</v>
+        <v>55780</v>
       </c>
       <c r="F8" t="n">
-        <v>58.5</v>
+        <v>58.4</v>
       </c>
       <c r="G8" t="n">
-        <v>5.67</v>
+        <v>5.49</v>
       </c>
       <c r="H8" t="n">
-        <v>0.51</v>
+        <v>0.8</v>
       </c>
       <c r="I8" t="n">
-        <v>-251.21</v>
+        <v>-259.18</v>
       </c>
       <c r="J8" t="n">
-        <v>-614.37</v>
+        <v>-615.97</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1416,14 +1416,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>64604.4</v>
+        <v>64603.07</v>
       </c>
       <c r="N8" t="n">
-        <v>40683.53</v>
+        <v>40683.03</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
 ・MACDは買いシグナルです。
 ・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
@@ -1463,29 +1463,29 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、ゴールデンクロス、+1σ、MACD買い、反発局面</t>
+          <t>RSI適正、25日線上、ゴールデンクロス、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W8" t="n">
         <v>54580</v>
       </c>
       <c r="X8" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>55880</v>
+        <v>55780</v>
       </c>
       <c r="AA8" t="n">
         <v>55510</v>
       </c>
       <c r="AB8" t="n">
-        <v>370</v>
+        <v>270</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.67</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="9">
@@ -1506,22 +1506,22 @@
         <v>10000</v>
       </c>
       <c r="E9" t="n">
-        <v>9301</v>
+        <v>9160</v>
       </c>
       <c r="F9" t="n">
-        <v>54.3</v>
+        <v>53</v>
       </c>
       <c r="G9" t="n">
-        <v>1.02</v>
+        <v>-0.45</v>
       </c>
       <c r="H9" t="n">
-        <v>0.63</v>
+        <v>1.01</v>
       </c>
       <c r="I9" t="n">
-        <v>-325.48</v>
+        <v>-336.73</v>
       </c>
       <c r="J9" t="n">
-        <v>-440.6</v>
+        <v>-442.85</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>12676.4</v>
+        <v>12674.52</v>
       </c>
       <c r="N9" t="n">
-        <v>8044.56</v>
+        <v>8043.86</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1546,20 +1546,20 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1576,29 +1576,29 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD買い、反発局面</t>
+          <t>RSI適正、押し目、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
         <v>8935</v>
       </c>
       <c r="X9" t="n">
-        <v>366</v>
+        <v>225</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.1</v>
+        <v>2.52</v>
       </c>
       <c r="Z9" t="n">
-        <v>9301</v>
+        <v>9160</v>
       </c>
       <c r="AA9" t="n">
         <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-699</v>
+        <v>-840</v>
       </c>
       <c r="AC9" t="n">
-        <v>-6.99</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="10">
@@ -1725,7 +1725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1610"/>
+  <dimension ref="A1:C1619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25877,6 +25877,141 @@
         </is>
       </c>
       <c r="C1610" t="n">
+        <v>41.51</v>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1611" t="n">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1612" t="n">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1613" t="n">
+        <v>176.1</v>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1614" t="n">
+        <v>2989.5</v>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1615" t="n">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1616" t="n">
+        <v>4859</v>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1617" t="n">
+        <v>55780</v>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1618" t="n">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1619" t="n">
         <v>41.51</v>
       </c>
     </row>
@@ -25891,7 +26026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F265"/>
+  <dimension ref="A1:F266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30625,19 +30760,29 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr">
+      <c r="A263" t="inlineStr"/>
+      <c r="B263" s="1" t="n">
+        <v>46290.75</v>
+      </c>
+      <c r="C263" t="n">
+        <v>214871</v>
+      </c>
+      <c r="D263" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E263" t="n">
+        <v>5580</v>
+      </c>
+      <c r="F263" t="n">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr"/>
-      <c r="C263" t="inlineStr"/>
-      <c r="D263" t="inlineStr"/>
-      <c r="E263" t="inlineStr"/>
-      <c r="F263" t="inlineStr"/>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr"/>
       <c r="B264" t="inlineStr"/>
       <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr"/>
@@ -30645,16 +30790,24 @@
       <c r="F264" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A265" t="inlineStr"/>
       <c r="B265" t="inlineStr"/>
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr"/>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -30819,31 +30972,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="F2" t="n">
-        <v>-10</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>-1</v>
+        <v>0.1</v>
       </c>
       <c r="H2" t="n">
-        <v>644200</v>
+        <v>1254600</v>
       </c>
       <c r="I2" t="n">
-        <v>44.5</v>
+        <v>44.1</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.51</v>
+        <v>-1.55</v>
       </c>
       <c r="K2" t="n">
-        <v>0.99</v>
+        <v>1.55</v>
       </c>
       <c r="L2" t="n">
-        <v>22.28</v>
+        <v>19.21</v>
       </c>
       <c r="M2" t="n">
-        <v>34.08</v>
+        <v>31.11</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -30856,10 +31009,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>858.08</v>
+        <v>861.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>1113.64</v>
+        <v>1111.58</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -30867,7 +31020,7 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -30884,6 +31037,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
+・出来高が増加しています。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -30919,31 +31073,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3330</v>
+        <v>3355</v>
       </c>
       <c r="F3" t="n">
-        <v>-10</v>
+        <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.3</v>
+        <v>0.75</v>
       </c>
       <c r="H3" t="n">
-        <v>45200</v>
+        <v>56600</v>
       </c>
       <c r="I3" t="n">
-        <v>34.2</v>
+        <v>41.6</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.84</v>
+        <v>-2.2</v>
       </c>
       <c r="K3" t="n">
-        <v>0.34</v>
+        <v>0.71</v>
       </c>
       <c r="L3" t="n">
-        <v>12.56</v>
+        <v>9.91</v>
       </c>
       <c r="M3" t="n">
-        <v>40.89</v>
+        <v>34.7</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -30956,10 +31110,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3055.51</v>
+        <v>3067.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>2729.13</v>
+        <v>2731.7</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -31019,31 +31173,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1381</v>
+        <v>1378</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>-3</v>
       </c>
       <c r="G4" t="n">
-        <v>1.92</v>
+        <v>-0.22</v>
       </c>
       <c r="H4" t="n">
-        <v>22000</v>
+        <v>4100</v>
       </c>
       <c r="I4" t="n">
-        <v>49.5</v>
+        <v>53.7</v>
       </c>
       <c r="J4" t="n">
-        <v>5.23</v>
+        <v>4.5</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5</v>
+        <v>0.28</v>
       </c>
       <c r="L4" t="n">
-        <v>34.21</v>
+        <v>34.25</v>
       </c>
       <c r="M4" t="n">
-        <v>37.46</v>
+        <v>36.82</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -31052,14 +31206,14 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1212.61</v>
+        <v>1214.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>1638.09</v>
+        <v>1637.12</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -31067,16 +31221,16 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -31085,8 +31239,7 @@
 ・🟢 上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・出来高が増加しています。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
@@ -31121,31 +31274,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3545</v>
+        <v>3580</v>
       </c>
       <c r="F5" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>1.58</v>
+        <v>0.99</v>
       </c>
       <c r="H5" t="n">
-        <v>7600</v>
+        <v>6000</v>
       </c>
       <c r="I5" t="n">
-        <v>48.6</v>
+        <v>62.1</v>
       </c>
       <c r="J5" t="n">
-        <v>2.61</v>
+        <v>3.52</v>
       </c>
       <c r="K5" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="L5" t="n">
-        <v>14.39</v>
+        <v>21.48</v>
       </c>
       <c r="M5" t="n">
-        <v>9.550000000000001</v>
+        <v>11.93</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -31158,10 +31311,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3423.2</v>
+        <v>3426</v>
       </c>
       <c r="Q5" t="n">
-        <v>3160.11</v>
+        <v>3164.8</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -31169,7 +31322,7 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -31186,7 +31339,6 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・RSIは良好な水準です。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -31222,31 +31374,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="F6" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>1.21</v>
+        <v>0.82</v>
       </c>
       <c r="H6" t="n">
-        <v>87500</v>
+        <v>40700</v>
       </c>
       <c r="I6" t="n">
-        <v>60.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>2.38</v>
+        <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>1.47</v>
+        <v>0.73</v>
       </c>
       <c r="L6" t="n">
-        <v>-15.95</v>
+        <v>-11.17</v>
       </c>
       <c r="M6" t="n">
-        <v>-27.69</v>
+        <v>-24.39</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -31259,10 +31411,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1673.89</v>
+        <v>1669.97</v>
       </c>
       <c r="Q6" t="n">
-        <v>1693.91</v>
+        <v>1692.29</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -31270,16 +31422,16 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -31287,6 +31439,7 @@
           <t>【AI分析レポート】
 ・🔴 下降
 ・MACDは買いシグナルです。
+・買われ過ぎ水準です。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 ⚠️ 下落トレンドです。
 無理な買いは避け、反転サインを待ちましょう。</t>
@@ -31322,31 +31475,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="G7" t="n">
-        <v>0.38</v>
+        <v>-0.38</v>
       </c>
       <c r="H7" t="n">
-        <v>14600</v>
+        <v>5900</v>
       </c>
       <c r="I7" t="n">
-        <v>51.9</v>
+        <v>46.4</v>
       </c>
       <c r="J7" t="n">
-        <v>0.21</v>
+        <v>-0.12</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="L7" t="n">
-        <v>-5.06</v>
+        <v>-4.72</v>
       </c>
       <c r="M7" t="n">
-        <v>-6.53</v>
+        <v>-6.16</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -31359,10 +31512,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>538.27</v>
+        <v>538.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>580.13</v>
+        <v>579.04</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -31370,16 +31523,16 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -31423,31 +31576,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1100</v>
+        <v>1092</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>-8</v>
       </c>
       <c r="G8" t="n">
-        <v>0.92</v>
+        <v>-0.73</v>
       </c>
       <c r="H8" t="n">
-        <v>4700</v>
+        <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>34</v>
+        <v>41.1</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.03</v>
+        <v>-2.42</v>
       </c>
       <c r="K8" t="n">
-        <v>1.75</v>
+        <v>0.15</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.84</v>
+        <v>-6.73</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.91</v>
+        <v>-2.87</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -31460,10 +31613,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1058.73</v>
+        <v>1060.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1017.75</v>
+        <v>1016.76</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -31471,7 +31624,7 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -31484,107 +31637,6 @@
         </is>
       </c>
       <c r="V8" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・出来高が増加しています。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>7033.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>マネジメントソリューションズ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PMO支援・DX案件増加</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1575</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-21</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="H9" t="n">
-        <v>103500</v>
-      </c>
-      <c r="I9" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-2.83</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="L9" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="M9" t="n">
-        <v>16.78</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>1461.65</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1384.64</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>65</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -31594,304 +31646,97 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9342.T</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>スマサポ</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7033.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>マネジメントソリューションズ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>監視</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>不動産DX</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>965</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3600</v>
-      </c>
-      <c r="I10" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="L10" t="n">
-        <v>13.52</v>
-      </c>
-      <c r="M10" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PMO支援・DX案件増加</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1579</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H9" t="n">
+        <v>22600</v>
+      </c>
+      <c r="I9" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="M9" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P10" t="n">
-        <v>883.37</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>986.8</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>60</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・出来高が増加しています。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>6971.T</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>京セラ</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>自社株</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>3650</v>
-      </c>
-      <c r="F11" t="n">
-        <v>13</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4843900</v>
-      </c>
-      <c r="I11" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-17.97</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-37.38</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>3657.6</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2957.57</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>100</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2026/10/29</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>あと35日</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>3778.T</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>さくらインターネット(株)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="n">
-        <v>3830</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="H12" t="n">
-        <v>542100</v>
-      </c>
-      <c r="I12" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="L12" t="n">
-        <v>69.84999999999999</v>
-      </c>
-      <c r="M12" t="n">
-        <v>76.88</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>3242.73</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3067.67</v>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="P9" t="n">
+        <v>1464.69</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1385.88</v>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S12" t="n">
-        <v>95</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
+      <c r="S9" t="n">
+        <v>85</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -31902,6 +31747,312 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9342.T</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>スマサポ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>不動産DX</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>967</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H10" t="n">
+        <v>700</v>
+      </c>
+      <c r="I10" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L10" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="M10" t="n">
+        <v>17.82</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>885.67</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>986.6799999999999</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>55</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6971.T</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>京セラ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>自社株</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3750</v>
+      </c>
+      <c r="F11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1246000</v>
+      </c>
+      <c r="I11" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-30.39</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>+2S</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>3658</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2965.79</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>95</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは買いシグナルです。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026/10/29</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>あと34日</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3778.T</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>さくらインターネット(株)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>3745</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-85</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-2.22</v>
+      </c>
+      <c r="H12" t="n">
+        <v>278200</v>
+      </c>
+      <c r="I12" t="n">
+        <v>57</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L12" t="n">
+        <v>67.98</v>
+      </c>
+      <c r="M12" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>3254.29</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3070.72</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>100</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
@@ -31928,31 +32079,31 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>4911</v>
+        <v>5001</v>
       </c>
       <c r="F13" t="n">
-        <v>-41</v>
+        <v>90</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.83</v>
+        <v>1.83</v>
       </c>
       <c r="H13" t="n">
-        <v>34159800</v>
+        <v>15492100</v>
       </c>
       <c r="I13" t="n">
-        <v>41.2</v>
+        <v>47.9</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.09</v>
+        <v>-2.67</v>
       </c>
       <c r="K13" t="n">
-        <v>1.07</v>
+        <v>0.54</v>
       </c>
       <c r="L13" t="n">
-        <v>-79.22</v>
+        <v>-72.76000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-39.22</v>
+        <v>-45.93</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -31965,10 +32116,10 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5069.37</v>
+        <v>5072.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>4513.95</v>
+        <v>4523.94</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -31989,215 +32140,6 @@
         </is>
       </c>
       <c r="V13" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>2026/11/10</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>あと47日</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>166A.T</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>タスキホールディングス</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>何度も高値更新中の強トレンド</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1088</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H14" t="n">
-        <v>238300</v>
-      </c>
-      <c r="I14" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-3.92</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-17.64</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-12.66</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1115.25</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>932.24</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S14" t="n">
-        <v>60</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>5801.T</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>古河電気工業</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>半導体設備関連</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>3807</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-94</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-2.41</v>
-      </c>
-      <c r="H15" t="n">
-        <v>19858900</v>
-      </c>
-      <c r="I15" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-4.71</v>
-      </c>
-      <c r="M15" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>3966.8</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3211.17</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S15" t="n">
-        <v>45</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -32208,6 +32150,215 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2026/11/10</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>あと46日</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>166A.T</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>タスキホールディングス</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>何度も高値更新中の強トレンド</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1097</v>
+      </c>
+      <c r="F14" t="n">
+        <v>9</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H14" t="n">
+        <v>96600</v>
+      </c>
+      <c r="I14" t="n">
+        <v>33</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-2.94</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-16.06</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-13.34</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1117.25</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>933.9299999999999</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>45</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5801.T</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>古河電気工業</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>半導体設備関連</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3823</v>
+      </c>
+      <c r="F15" t="n">
+        <v>16</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12252900</v>
+      </c>
+      <c r="I15" t="n">
+        <v>52</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-6.24</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>3952.37</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3225.58</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>65</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>2026/11/09</t>
@@ -32215,7 +32366,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>あと46日</t>
+          <t>あと45日</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -32242,35 +32393,35 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>4445</v>
+        <v>4600</v>
       </c>
       <c r="F16" t="n">
-        <v>365</v>
+        <v>155</v>
       </c>
       <c r="G16" t="n">
-        <v>8.949999999999999</v>
+        <v>3.49</v>
       </c>
       <c r="H16" t="n">
-        <v>58000</v>
+        <v>29300</v>
       </c>
       <c r="I16" t="n">
-        <v>56</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>8.92</v>
+        <v>12.25</v>
       </c>
       <c r="K16" t="n">
-        <v>2.03</v>
+        <v>0.93</v>
       </c>
       <c r="L16" t="n">
-        <v>63.83</v>
+        <v>101.1</v>
       </c>
       <c r="M16" t="n">
-        <v>62.04</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -32279,10 +32430,10 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3613.6</v>
+        <v>3634.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>2872.19</v>
+        <v>2885.2</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -32303,435 +32454,436 @@
         </is>
       </c>
       <c r="V16" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは買いシグナルです。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
+・25日線から大きく上に乖離しています。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>7012.T</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>川崎重工業(株)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>2421</v>
+      </c>
+      <c r="F17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3864200</v>
+      </c>
+      <c r="I17" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-74.64</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-86.22</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>2722.3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2836.66</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>あと47日</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>トヨタ自動車(株)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4000円で売る予定</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2988</v>
+      </c>
+      <c r="F18" t="n">
+        <v>19</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H18" t="n">
+        <v>8445100</v>
+      </c>
+      <c r="I18" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-8.859999999999999</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>2942.36</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3163.69</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>55</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2026/11/05</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>あと41日</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>8053.T</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>住友商事</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>1785</v>
+      </c>
+      <c r="F19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2524200</v>
+      </c>
+      <c r="I19" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L19" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="M19" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1679.38</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1576.62</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>65</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2026/10/29</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>あと34日</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ブロードリーフ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>500円で売</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>481</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-7</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="H20" t="n">
+        <v>195200</v>
+      </c>
+      <c r="I20" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L20" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>435.93</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>415.2</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>100</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
 ・RSIは良好な水準です。
-・出来高が急増しています。
-・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>7012.T</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>川崎重工業(株)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="n">
-        <v>2400</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="H17" t="n">
-        <v>9020900</v>
-      </c>
-      <c r="I17" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-4.08</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-80.95</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-89.12</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>2728.55</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2834.42</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S17" t="n">
-        <v>30</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは買いシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>あと48日</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>7203.T</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>トヨタ自動車(株)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4000円で売る予定</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>2969</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-56</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-1.85</v>
-      </c>
-      <c r="H18" t="n">
-        <v>33817300</v>
-      </c>
-      <c r="I18" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-2.99</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-6.33</v>
-      </c>
-      <c r="M18" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>2940.52</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3164.21</v>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="S18" t="n">
-        <v>75</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>2026/11/05</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>あと42日</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>8053.T</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>住友商事</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="n">
-        <v>1769</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-27.5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-1.53</v>
-      </c>
-      <c r="H19" t="n">
-        <v>11285900</v>
-      </c>
-      <c r="I19" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>-1.14</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="L19" t="n">
-        <v>18.65</v>
-      </c>
-      <c r="M19" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1678.39</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1573.63</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S19" t="n">
-        <v>65</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>2026/10/29</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>あと35日</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>3673.T</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ブロードリーフ</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>500円で売</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>488</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-3</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="H20" t="n">
-        <v>853500</v>
-      </c>
-      <c r="I20" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="L20" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="M20" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>435.08</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>414.6</v>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S20" t="n">
-        <v>100</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr">
@@ -32758,31 +32910,31 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>8935</v>
+        <v>9301</v>
       </c>
       <c r="F21" t="n">
-        <v>-440</v>
+        <v>366</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.69</v>
+        <v>4.1</v>
       </c>
       <c r="H21" t="n">
-        <v>27368700</v>
+        <v>15586100</v>
       </c>
       <c r="I21" t="n">
-        <v>46.6</v>
+        <v>54.3</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.25</v>
+        <v>1.02</v>
       </c>
       <c r="K21" t="n">
-        <v>0.96</v>
+        <v>0.63</v>
       </c>
       <c r="L21" t="n">
-        <v>-362.32</v>
+        <v>-325.48</v>
       </c>
       <c r="M21" t="n">
-        <v>-469.38</v>
+        <v>-440.6</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -32795,10 +32947,10 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>12763.72</v>
+        <v>12676.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>8014.11</v>
+        <v>8044.56</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -32806,16 +32958,16 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -32836,12 +32988,12 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>あと42日</t>
+          <t>あと41日</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
+          <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
@@ -32859,47 +33011,47 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>54580</v>
+        <v>55880</v>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>1300</v>
       </c>
       <c r="G22" t="n">
-        <v>0.02</v>
+        <v>2.38</v>
       </c>
       <c r="H22" t="n">
-        <v>27809600</v>
+        <v>12985900</v>
       </c>
       <c r="I22" t="n">
-        <v>56.5</v>
+        <v>58.5</v>
       </c>
       <c r="J22" t="n">
-        <v>3.11</v>
+        <v>5.67</v>
       </c>
       <c r="K22" t="n">
-        <v>0.97</v>
+        <v>0.51</v>
       </c>
       <c r="L22" t="n">
-        <v>-497.87</v>
+        <v>-251.21</v>
       </c>
       <c r="M22" t="n">
-        <v>-705.17</v>
+        <v>-614.37</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>64901.2</v>
+        <v>64604.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>40449.37</v>
+        <v>40683.53</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -32907,7 +33059,7 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -32924,8 +33076,9 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
@@ -32937,7 +33090,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>あと36日</t>
+          <t>あと35日</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -32960,31 +33113,31 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>158.9</v>
+        <v>161.4</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.6</v>
+        <v>2.5</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.22</v>
+        <v>1.57</v>
       </c>
       <c r="H23" t="n">
-        <v>79200300</v>
+        <v>31593800</v>
       </c>
       <c r="I23" t="n">
-        <v>45.3</v>
+        <v>54.3</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.34</v>
+        <v>0.05</v>
       </c>
       <c r="K23" t="n">
-        <v>1.4</v>
+        <v>0.59</v>
       </c>
       <c r="L23" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="M23" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -32997,10 +33150,10 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>153.23</v>
+        <v>153.51</v>
       </c>
       <c r="Q23" t="n">
-        <v>150.93</v>
+        <v>151.03</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -33008,16 +33161,16 @@
         </is>
       </c>
       <c r="S23" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -33038,12 +33191,12 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>あと49日</t>
+          <t>あと48日</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
+          <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
@@ -33061,35 +33214,35 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>3490</v>
+        <v>3474</v>
       </c>
       <c r="F24" t="n">
-        <v>181</v>
+        <v>-16</v>
       </c>
       <c r="G24" t="n">
-        <v>5.47</v>
+        <v>-0.46</v>
       </c>
       <c r="H24" t="n">
-        <v>16601300</v>
+        <v>3608100</v>
       </c>
       <c r="I24" t="n">
-        <v>57.6</v>
+        <v>62.3</v>
       </c>
       <c r="J24" t="n">
-        <v>4.24</v>
+        <v>4.18</v>
       </c>
       <c r="K24" t="n">
-        <v>1.52</v>
+        <v>0.36</v>
       </c>
       <c r="L24" t="n">
-        <v>-98.18000000000001</v>
+        <v>-77.17</v>
       </c>
       <c r="M24" t="n">
-        <v>-135.3</v>
+        <v>-123.67</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -33098,10 +33251,10 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3966.36</v>
+        <v>3951.77</v>
       </c>
       <c r="Q24" t="n">
-        <v>3209.74</v>
+        <v>3218.08</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -33126,8 +33279,7 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・出来高が増加しています。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
@@ -33140,7 +33292,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>あと34日</t>
+          <t>あと33日</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -33172,7 +33324,7 @@
         <v>-1.48</v>
       </c>
       <c r="H25" t="n">
-        <v>1578604</v>
+        <v>1582300</v>
       </c>
       <c r="I25" t="n">
         <v>61.2</v>
@@ -33240,7 +33392,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>あと12日</t>
+          <t>あと11日</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -33263,31 +33415,31 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>8196</v>
+        <v>8181</v>
       </c>
       <c r="F26" t="n">
-        <v>-143</v>
+        <v>-15</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.71</v>
+        <v>-0.18</v>
       </c>
       <c r="H26" t="n">
-        <v>6609600</v>
+        <v>2459100</v>
       </c>
       <c r="I26" t="n">
-        <v>29.8</v>
+        <v>33.8</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.77</v>
+        <v>-4.69</v>
       </c>
       <c r="K26" t="n">
-        <v>1.01</v>
+        <v>0.45</v>
       </c>
       <c r="L26" t="n">
-        <v>-17.96</v>
+        <v>-31.08</v>
       </c>
       <c r="M26" t="n">
-        <v>61.78</v>
+        <v>43.21</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -33300,10 +33452,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7779.79</v>
+        <v>7788.55</v>
       </c>
       <c r="Q26" t="n">
-        <v>8654.1</v>
+        <v>8630.42</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -33311,16 +33463,16 @@
         </is>
       </c>
       <c r="S26" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -33328,7 +33480,6 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
-・売られ過ぎ水準です。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -33341,7 +33492,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>あと42日</t>
+          <t>あと41日</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>214,871円</t>
+          <t>214,872円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5,580円</t>
+          <t>5,581円</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>41.51</v>
+        <v>43.26</v>
       </c>
       <c r="F10" t="n">
         <v>58.7</v>
       </c>
       <c r="G10" t="n">
-        <v>8.119999999999999</v>
+        <v>11.89</v>
       </c>
       <c r="H10" t="n">
-        <v>0.86</v>
+        <v>1.21</v>
       </c>
       <c r="I10" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="J10" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1643,14 +1643,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>+2S</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.07</v>
+        <v>33.1</v>
       </c>
       <c r="N10" t="n">
-        <v>31.75</v>
+        <v>31.79</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1681,7 +1681,8 @@
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・25日線から大きく上に乖離しています。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -1689,29 +1690,29 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+1σ、MACD買い、長期上昇</t>
+          <t>RSI適正、上昇加速、+2σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>41.44</v>
+        <v>41.51</v>
       </c>
       <c r="X10" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.75</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.17</v>
+        <v>4.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6071</v>
+        <v>-6070</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.31999999999999</v>
+        <v>-99.29000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1725,7 +1726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1619"/>
+  <dimension ref="A1:C1628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26013,6 +26014,141 @@
       </c>
       <c r="C1619" t="n">
         <v>41.51</v>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1620" t="n">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1621" t="n">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1622" t="n">
+        <v>176.1</v>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1623" t="n">
+        <v>2989.5</v>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1624" t="n">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1625" t="n">
+        <v>4859</v>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1626" t="n">
+        <v>55780</v>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1627" t="n">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1628" t="n">
+        <v>43.26</v>
       </c>
     </row>
   </sheetData>
@@ -26026,7 +26162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F266"/>
+  <dimension ref="A1:F267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30778,19 +30914,29 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr">
+      <c r="A264" t="inlineStr"/>
+      <c r="B264" s="1" t="n">
+        <v>46293.29166666666</v>
+      </c>
+      <c r="C264" t="n">
+        <v>214872</v>
+      </c>
+      <c r="D264" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E264" t="n">
+        <v>5581</v>
+      </c>
+      <c r="F264" t="n">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr"/>
-      <c r="C264" t="inlineStr"/>
-      <c r="D264" t="inlineStr"/>
-      <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr"/>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr"/>
       <c r="B265" t="inlineStr"/>
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr"/>
@@ -30798,16 +30944,24 @@
       <c r="F265" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A266" t="inlineStr"/>
       <c r="B266" t="inlineStr"/>
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr"/>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -30972,31 +31126,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>987</v>
+        <v>1010</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1</v>
+        <v>2.43</v>
       </c>
       <c r="H2" t="n">
-        <v>1254600</v>
+        <v>2063300</v>
       </c>
       <c r="I2" t="n">
-        <v>44.1</v>
+        <v>48.6</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.55</v>
+        <v>0.65</v>
       </c>
       <c r="K2" t="n">
-        <v>1.55</v>
+        <v>2.13</v>
       </c>
       <c r="L2" t="n">
-        <v>19.21</v>
+        <v>21.05</v>
       </c>
       <c r="M2" t="n">
-        <v>31.11</v>
+        <v>31.47</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -31009,10 +31163,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>861.75</v>
+        <v>862.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1111.58</v>
+        <v>1111.69</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -31020,16 +31174,16 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -31037,7 +31191,8 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
-・出来高が増加しています。
+・RSIは良好な水準です。
+・出来高が急増しています。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -31047,7 +31202,7 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
+          <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
@@ -31073,31 +31228,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3355</v>
+        <v>3330</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>56600</v>
+        <v>96700</v>
       </c>
       <c r="I3" t="n">
-        <v>41.6</v>
+        <v>39.9</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.2</v>
+        <v>-2.9</v>
       </c>
       <c r="K3" t="n">
-        <v>0.71</v>
+        <v>1.1</v>
       </c>
       <c r="L3" t="n">
-        <v>9.91</v>
+        <v>7.92</v>
       </c>
       <c r="M3" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -31110,10 +31265,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3067.01</v>
+        <v>3066.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>2731.7</v>
+        <v>2731.58</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -31173,31 +31328,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F4" t="n">
-        <v>-3</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.22</v>
+        <v>0.65</v>
       </c>
       <c r="H4" t="n">
-        <v>4100</v>
+        <v>9300</v>
       </c>
       <c r="I4" t="n">
-        <v>53.7</v>
+        <v>55.6</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>5.37</v>
       </c>
       <c r="K4" t="n">
-        <v>0.28</v>
+        <v>0.59</v>
       </c>
       <c r="L4" t="n">
-        <v>34.25</v>
+        <v>35.21</v>
       </c>
       <c r="M4" t="n">
-        <v>36.82</v>
+        <v>37.01</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -31206,14 +31361,14 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1214.48</v>
+        <v>1214.64</v>
       </c>
       <c r="Q4" t="n">
-        <v>1637.12</v>
+        <v>1637.18</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -31234,6 +31389,611 @@
         </is>
       </c>
       <c r="V4" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5532.T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>リアルゲイト</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>オフィス再生</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3675</v>
+      </c>
+      <c r="F5" t="n">
+        <v>130</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H5" t="n">
+        <v>60300</v>
+      </c>
+      <c r="I5" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="L5" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>+2S</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>3427.27</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3165.28</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは買いシグナルです。
+・出来高が急増しています。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3984.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ユーザーローカル</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AI解析・データ分析</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1623</v>
+      </c>
+      <c r="F6" t="n">
+        <v>37</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H6" t="n">
+        <v>85500</v>
+      </c>
+      <c r="I6" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-9.26</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-24</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>+2S</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1670.29</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1692.41</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは買いシグナルです。
+・買われ過ぎ水準です。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4054.T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>日本情報クリエイト</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>不動産向けクラウド</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>521</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="H7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I7" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-4.72</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-6.16</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>538.36</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>579.04</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>30</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7072.T</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>インティメート・マージャー</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>データマーケティング</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1080</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-20</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I8" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-7.68</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1060.04</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1016.71</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>70</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7033.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>マネジメントソリューションズ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PMO支援・DX案件増加</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1591</v>
+      </c>
+      <c r="F9" t="n">
+        <v>16</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H9" t="n">
+        <v>69700</v>
+      </c>
+      <c r="I9" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L9" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="M9" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1464.85</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1385.94</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>85</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9342.T</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>スマサポ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>不動産DX</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>971</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I10" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>885.72</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>986.7</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>65</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 上昇
@@ -31244,614 +32004,11 @@
 順張りが有利な局面です。</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>5532.T</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>リアルゲイト</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>オフィス再生</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>3580</v>
-      </c>
-      <c r="F5" t="n">
-        <v>35</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L5" t="n">
-        <v>21.48</v>
-      </c>
-      <c r="M5" t="n">
-        <v>11.93</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>3426</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3164.8</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>100</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは買いシグナルです。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>3984.T</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ユーザーローカル</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>AI解析・データ分析</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1599</v>
-      </c>
-      <c r="F6" t="n">
-        <v>13</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="H6" t="n">
-        <v>40700</v>
-      </c>
-      <c r="I6" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-11.17</v>
-      </c>
-      <c r="M6" t="n">
-        <v>-24.39</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>1669.97</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1692.29</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v>35</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは買いシグナルです。
-・買われ過ぎ水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>4054.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>日本情報クリエイト</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>不動産向けクラウド</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>521</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="H7" t="n">
-        <v>5900</v>
-      </c>
-      <c r="I7" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-4.72</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-6.16</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>538.36</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>579.04</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>30</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7072.T</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>インティメート・マージャー</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>データマーケティング</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1092</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-8</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-0.73</v>
-      </c>
-      <c r="H8" t="n">
-        <v>400</v>
-      </c>
-      <c r="I8" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-2.42</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-6.73</v>
-      </c>
-      <c r="M8" t="n">
-        <v>-2.87</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>1060.2</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1016.76</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v>65</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>7033.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>マネジメントソリューションズ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PMO支援・DX案件増加</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1579</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H9" t="n">
-        <v>22600</v>
-      </c>
-      <c r="I9" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-2.43</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="M9" t="n">
-        <v>14.74</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>1464.69</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1385.88</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>85</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9342.T</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>スマサポ</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>不動産DX</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>967</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H10" t="n">
-        <v>700</v>
-      </c>
-      <c r="I10" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="L10" t="n">
-        <v>11.88</v>
-      </c>
-      <c r="M10" t="n">
-        <v>17.82</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>885.67</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>986.6799999999999</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>55</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
+          <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
@@ -31877,31 +32034,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3750</v>
+        <v>3764</v>
       </c>
       <c r="F11" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="G11" t="n">
-        <v>2.74</v>
+        <v>3.12</v>
       </c>
       <c r="H11" t="n">
-        <v>1246000</v>
+        <v>4078000</v>
       </c>
       <c r="I11" t="n">
-        <v>66.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>4.94</v>
+        <v>5.31</v>
       </c>
       <c r="K11" t="n">
-        <v>0.29</v>
+        <v>0.83</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.44</v>
+        <v>-1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>-30.39</v>
+        <v>-30.17</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -31914,10 +32071,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3658</v>
+        <v>3658.19</v>
       </c>
       <c r="Q11" t="n">
-        <v>2965.79</v>
+        <v>2965.86</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -31981,31 +32138,31 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>3745</v>
+        <v>3750</v>
       </c>
       <c r="F12" t="n">
-        <v>-85</v>
+        <v>-80</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.22</v>
+        <v>-2.09</v>
       </c>
       <c r="H12" t="n">
-        <v>278200</v>
+        <v>509300</v>
       </c>
       <c r="I12" t="n">
-        <v>57</v>
+        <v>57.2</v>
       </c>
       <c r="J12" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="K12" t="n">
-        <v>0.41</v>
+        <v>0.71</v>
       </c>
       <c r="L12" t="n">
-        <v>67.98</v>
+        <v>68.38</v>
       </c>
       <c r="M12" t="n">
-        <v>75.09999999999999</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -32018,10 +32175,10 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3254.29</v>
+        <v>3254.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>3070.72</v>
+        <v>3070.75</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -32079,31 +32236,31 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>5001</v>
+        <v>4986</v>
       </c>
       <c r="F13" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="G13" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="H13" t="n">
-        <v>15492100</v>
+        <v>26991600</v>
       </c>
       <c r="I13" t="n">
-        <v>47.9</v>
+        <v>47.5</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.67</v>
+        <v>-2.95</v>
       </c>
       <c r="K13" t="n">
-        <v>0.54</v>
+        <v>0.87</v>
       </c>
       <c r="L13" t="n">
-        <v>-72.76000000000001</v>
+        <v>-73.95</v>
       </c>
       <c r="M13" t="n">
-        <v>-45.93</v>
+        <v>-46.17</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -32116,10 +32273,10 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5072.76</v>
+        <v>5072.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>4523.94</v>
+        <v>4523.86</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -32188,31 +32345,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.83</v>
+        <v>0.74</v>
       </c>
       <c r="H14" t="n">
-        <v>96600</v>
+        <v>208400</v>
       </c>
       <c r="I14" t="n">
-        <v>33</v>
+        <v>32.7</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.94</v>
+        <v>-3.02</v>
       </c>
       <c r="K14" t="n">
-        <v>0.44</v>
+        <v>0.87</v>
       </c>
       <c r="L14" t="n">
-        <v>-16.06</v>
+        <v>-16.14</v>
       </c>
       <c r="M14" t="n">
-        <v>-13.34</v>
+        <v>-13.35</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -32225,7 +32382,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1117.25</v>
+        <v>1117.24</v>
       </c>
       <c r="Q14" t="n">
         <v>933.9299999999999</v>
@@ -32288,31 +32445,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3823</v>
+        <v>3826</v>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G15" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="H15" t="n">
-        <v>12252900</v>
+        <v>19066200</v>
       </c>
       <c r="I15" t="n">
         <v>52</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.83</v>
+        <v>-0.75</v>
       </c>
       <c r="K15" t="n">
-        <v>0.66</v>
+        <v>0.95</v>
       </c>
       <c r="L15" t="n">
-        <v>-6.24</v>
+        <v>-6</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -32325,10 +32482,10 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3952.37</v>
+        <v>3952.41</v>
       </c>
       <c r="Q15" t="n">
-        <v>3225.58</v>
+        <v>3225.59</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -32402,7 +32559,7 @@
         <v>3.49</v>
       </c>
       <c r="H16" t="n">
-        <v>29300</v>
+        <v>51300</v>
       </c>
       <c r="I16" t="n">
         <v>66.59999999999999</v>
@@ -32411,7 +32568,7 @@
         <v>12.25</v>
       </c>
       <c r="K16" t="n">
-        <v>0.93</v>
+        <v>1.42</v>
       </c>
       <c r="L16" t="n">
         <v>101.1</v>
@@ -32491,31 +32648,31 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>2421</v>
+        <v>2408</v>
       </c>
       <c r="F17" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>0.88</v>
+        <v>0.33</v>
       </c>
       <c r="H17" t="n">
-        <v>3864200</v>
+        <v>7358900</v>
       </c>
       <c r="I17" t="n">
-        <v>49.2</v>
+        <v>47.8</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.55</v>
+        <v>-3.06</v>
       </c>
       <c r="K17" t="n">
-        <v>0.42</v>
+        <v>0.74</v>
       </c>
       <c r="L17" t="n">
-        <v>-74.64</v>
+        <v>-75.68000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-86.22</v>
+        <v>-86.43000000000001</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -32528,10 +32685,10 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2722.3</v>
+        <v>2722.13</v>
       </c>
       <c r="Q17" t="n">
-        <v>2836.66</v>
+        <v>2836.59</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -32600,31 +32757,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2988</v>
+        <v>2990</v>
       </c>
       <c r="F18" t="n">
-        <v>19</v>
+        <v>20.5</v>
       </c>
       <c r="G18" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>8445100</v>
+        <v>21084000</v>
       </c>
       <c r="I18" t="n">
-        <v>30.6</v>
+        <v>30.9</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.32</v>
+        <v>-2.28</v>
       </c>
       <c r="K18" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="L18" t="n">
-        <v>-8.859999999999999</v>
+        <v>-8.74</v>
       </c>
       <c r="M18" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -32637,10 +32794,10 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2942.36</v>
+        <v>2942.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>3163.69</v>
+        <v>3163.7</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -32704,31 +32861,31 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>1785</v>
+        <v>1798</v>
       </c>
       <c r="F19" t="n">
-        <v>16.5</v>
+        <v>29.5</v>
       </c>
       <c r="G19" t="n">
-        <v>0.93</v>
+        <v>1.67</v>
       </c>
       <c r="H19" t="n">
-        <v>2524200</v>
+        <v>9076400</v>
       </c>
       <c r="I19" t="n">
-        <v>49.6</v>
+        <v>51.2</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.28</v>
+        <v>0.41</v>
       </c>
       <c r="K19" t="n">
-        <v>0.26</v>
+        <v>0.82</v>
       </c>
       <c r="L19" t="n">
-        <v>15.96</v>
+        <v>16.99</v>
       </c>
       <c r="M19" t="n">
-        <v>25.99</v>
+        <v>26.2</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -32741,10 +32898,10 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1679.38</v>
+        <v>1679.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>1576.62</v>
+        <v>1576.69</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -32752,16 +32909,16 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -32787,7 +32944,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
+          <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
@@ -32813,31 +32970,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="F20" t="n">
-        <v>-7</v>
+        <v>-11</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.43</v>
+        <v>-2.25</v>
       </c>
       <c r="H20" t="n">
-        <v>195200</v>
+        <v>427800</v>
       </c>
       <c r="I20" t="n">
-        <v>53.7</v>
+        <v>52.1</v>
       </c>
       <c r="J20" t="n">
-        <v>1.88</v>
+        <v>1.07</v>
       </c>
       <c r="K20" t="n">
-        <v>0.35</v>
+        <v>0.72</v>
       </c>
       <c r="L20" t="n">
-        <v>8.1</v>
+        <v>7.78</v>
       </c>
       <c r="M20" t="n">
-        <v>7.07</v>
+        <v>7.01</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -32850,10 +33007,10 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>435.93</v>
+        <v>435.88</v>
       </c>
       <c r="Q20" t="n">
-        <v>415.2</v>
+        <v>415.18</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -32910,31 +33067,31 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>9301</v>
+        <v>9160</v>
       </c>
       <c r="F21" t="n">
-        <v>366</v>
+        <v>225</v>
       </c>
       <c r="G21" t="n">
-        <v>4.1</v>
+        <v>2.52</v>
       </c>
       <c r="H21" t="n">
-        <v>15586100</v>
+        <v>27217100</v>
       </c>
       <c r="I21" t="n">
-        <v>54.3</v>
+        <v>53</v>
       </c>
       <c r="J21" t="n">
-        <v>1.02</v>
+        <v>-0.45</v>
       </c>
       <c r="K21" t="n">
-        <v>0.63</v>
+        <v>1.01</v>
       </c>
       <c r="L21" t="n">
-        <v>-325.48</v>
+        <v>-336.73</v>
       </c>
       <c r="M21" t="n">
-        <v>-440.6</v>
+        <v>-442.85</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -32947,10 +33104,10 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>12676.4</v>
+        <v>12674.52</v>
       </c>
       <c r="Q21" t="n">
-        <v>8044.56</v>
+        <v>8043.86</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -32958,16 +33115,16 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -32993,7 +33150,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>⚪ 様子見（押し目ではない）</t>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -33011,31 +33168,31 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>55880</v>
+        <v>55780</v>
       </c>
       <c r="F22" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="G22" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="H22" t="n">
-        <v>12985900</v>
+        <v>21757800</v>
       </c>
       <c r="I22" t="n">
-        <v>58.5</v>
+        <v>58.4</v>
       </c>
       <c r="J22" t="n">
-        <v>5.67</v>
+        <v>5.49</v>
       </c>
       <c r="K22" t="n">
-        <v>0.51</v>
+        <v>0.8</v>
       </c>
       <c r="L22" t="n">
-        <v>-251.21</v>
+        <v>-259.18</v>
       </c>
       <c r="M22" t="n">
-        <v>-614.37</v>
+        <v>-615.97</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -33044,14 +33201,14 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>64604.4</v>
+        <v>64603.07</v>
       </c>
       <c r="Q22" t="n">
-        <v>40683.53</v>
+        <v>40683.03</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -33078,7 +33235,7 @@
 ・MACDは買いシグナルです。
 ・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
@@ -33113,31 +33270,31 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>161.4</v>
+        <v>162.3</v>
       </c>
       <c r="F23" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="G23" t="n">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="H23" t="n">
-        <v>31593800</v>
+        <v>59839600</v>
       </c>
       <c r="I23" t="n">
-        <v>54.3</v>
+        <v>55.7</v>
       </c>
       <c r="J23" t="n">
-        <v>0.05</v>
+        <v>0.59</v>
       </c>
       <c r="K23" t="n">
-        <v>0.59</v>
+        <v>1.02</v>
       </c>
       <c r="L23" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="M23" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -33150,7 +33307,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>153.51</v>
+        <v>153.52</v>
       </c>
       <c r="Q23" t="n">
         <v>151.03</v>
@@ -33214,31 +33371,31 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>3474</v>
+        <v>3478</v>
       </c>
       <c r="F24" t="n">
-        <v>-16</v>
+        <v>-12</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.46</v>
+        <v>-0.34</v>
       </c>
       <c r="H24" t="n">
-        <v>3608100</v>
+        <v>8775000</v>
       </c>
       <c r="I24" t="n">
-        <v>62.3</v>
+        <v>62.5</v>
       </c>
       <c r="J24" t="n">
-        <v>4.18</v>
+        <v>4.29</v>
       </c>
       <c r="K24" t="n">
-        <v>0.36</v>
+        <v>0.78</v>
       </c>
       <c r="L24" t="n">
-        <v>-77.17</v>
+        <v>-76.84999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-123.67</v>
+        <v>-123.61</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -33251,10 +33408,10 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3951.77</v>
+        <v>3951.83</v>
       </c>
       <c r="Q24" t="n">
-        <v>3218.08</v>
+        <v>3218.1</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -33415,31 +33572,31 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>8181</v>
+        <v>8100</v>
       </c>
       <c r="F26" t="n">
-        <v>-15</v>
+        <v>-96</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.18</v>
+        <v>-1.17</v>
       </c>
       <c r="H26" t="n">
-        <v>2459100</v>
+        <v>6295000</v>
       </c>
       <c r="I26" t="n">
-        <v>33.8</v>
+        <v>32.5</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.69</v>
+        <v>-5.59</v>
       </c>
       <c r="K26" t="n">
-        <v>0.45</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>-31.08</v>
+        <v>-37.54</v>
       </c>
       <c r="M26" t="n">
-        <v>43.21</v>
+        <v>41.92</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -33452,10 +33609,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7788.55</v>
+        <v>7787.47</v>
       </c>
       <c r="Q26" t="n">
-        <v>8630.42</v>
+        <v>8630.02</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>214,872円</t>
+          <t>214,064円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5,581円</t>
+          <t>4,774円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -717,22 +717,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3330</v>
+        <v>3360</v>
       </c>
       <c r="F2" t="n">
-        <v>39.9</v>
+        <v>44.5</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.9</v>
+        <v>-2.18</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1</v>
+        <v>0.61</v>
       </c>
       <c r="I2" t="n">
-        <v>7.92</v>
+        <v>6.59</v>
       </c>
       <c r="J2" t="n">
-        <v>34.3</v>
+        <v>28.76</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3066.68</v>
+        <v>3079.65</v>
       </c>
       <c r="N2" t="n">
-        <v>2731.58</v>
+        <v>2734.2</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -793,22 +793,22 @@
         <v>3330</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>13320</v>
+        <v>13440</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2520</v>
+        <v>2640</v>
       </c>
       <c r="AC2" t="n">
-        <v>23.33</v>
+        <v>24.44</v>
       </c>
     </row>
     <row r="3">
@@ -829,22 +829,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F3" t="n">
-        <v>52.1</v>
+        <v>57.7</v>
       </c>
       <c r="G3" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="H3" t="n">
-        <v>0.72</v>
+        <v>0.28</v>
       </c>
       <c r="I3" t="n">
-        <v>7.78</v>
+        <v>7.45</v>
       </c>
       <c r="J3" t="n">
-        <v>7.01</v>
+        <v>7.1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>435.88</v>
+        <v>436.81</v>
       </c>
       <c r="N3" t="n">
-        <v>415.18</v>
+        <v>415.73</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -903,25 +903,25 @@
         </is>
       </c>
       <c r="W3" t="n">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="X3" t="n">
-        <v>-11</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="n">
-        <v>-2.25</v>
+        <v>0.42</v>
       </c>
       <c r="Z3" t="n">
-        <v>47700</v>
+        <v>47900</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>5700</v>
+        <v>5900</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.57</v>
+        <v>14.05</v>
       </c>
     </row>
     <row r="4">
@@ -942,22 +942,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>176.1</v>
+        <v>175.5</v>
       </c>
       <c r="F4" t="n">
-        <v>51.7</v>
+        <v>54.6</v>
       </c>
       <c r="G4" t="n">
-        <v>2.29</v>
+        <v>1.56</v>
       </c>
       <c r="H4" t="n">
-        <v>0.93</v>
+        <v>0.52</v>
       </c>
       <c r="I4" t="n">
-        <v>3.95</v>
+        <v>3.66</v>
       </c>
       <c r="J4" t="n">
-        <v>4.41</v>
+        <v>4.26</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>157.79</v>
+        <v>158.17</v>
       </c>
       <c r="N4" t="n">
-        <v>154.58</v>
+        <v>154.69</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1016,25 +1016,25 @@
         </is>
       </c>
       <c r="W4" t="n">
-        <v>174.9</v>
+        <v>176.1</v>
       </c>
       <c r="X4" t="n">
-        <v>1.2</v>
+        <v>-0.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>17610</v>
+        <v>17550</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1810</v>
+        <v>1750</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.46</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="5">
@@ -1055,22 +1055,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>2989.5</v>
+        <v>3016</v>
       </c>
       <c r="F5" t="n">
-        <v>30.9</v>
+        <v>36.9</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.28</v>
+        <v>-1.51</v>
       </c>
       <c r="H5" t="n">
-        <v>0.75</v>
+        <v>0.34</v>
       </c>
       <c r="I5" t="n">
-        <v>-8.74</v>
+        <v>-8.41</v>
       </c>
       <c r="J5" t="n">
-        <v>3.26</v>
+        <v>0.92</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2942.38</v>
+        <v>2944.96</v>
       </c>
       <c r="N5" t="n">
-        <v>3163.7</v>
+        <v>3163.35</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1128,102 +1128,214 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>2969</v>
+        <v>2989.5</v>
       </c>
       <c r="X5" t="n">
-        <v>20.5</v>
+        <v>26.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="Z5" t="n">
-        <v>38864</v>
+        <v>39208</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>1764</v>
+        <v>2109</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.76</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>三菱商事</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4795</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4845</v>
+      </c>
+      <c r="F6" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I6" t="n">
+        <v>23.13</v>
+      </c>
+      <c r="J6" t="n">
+        <v>44.14</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>4716.36</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4701.58</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>65</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>押し目、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>4859</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-14</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>24225</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>23975</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>250</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>7974.T</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>任天堂</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C7" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>7993</v>
       </c>
-      <c r="E6" t="n">
-        <v>8100</v>
-      </c>
-      <c r="F6" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-5.59</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-37.54</v>
-      </c>
-      <c r="J6" t="n">
-        <v>41.92</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="E7" t="n">
+        <v>8065</v>
+      </c>
+      <c r="F7" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-5.78</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-55.24</v>
+      </c>
+      <c r="J7" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>-1S</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>7787.47</v>
-      </c>
-      <c r="N6" t="n">
-        <v>8630.02</v>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="M7" t="n">
+        <v>7793.13</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8605.219999999999</v>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>🟢 上昇</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>⚪ 様子見</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q7" t="n">
         <v>60</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>★★☆☆☆</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 上昇
@@ -1233,145 +1345,32 @@
 順張りが有利な局面です。</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>8196</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-96</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-1.17</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>8100</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>7993</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>107</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>8058.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>三菱商事</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4795</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4859</v>
-      </c>
-      <c r="F7" t="n">
-        <v>50</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I7" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>4716.2</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4695.68</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>85</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD売り、長期上昇</t>
+          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4811</v>
+        <v>8100</v>
       </c>
       <c r="X7" t="n">
-        <v>48</v>
+        <v>-35</v>
       </c>
       <c r="Y7" t="n">
-        <v>1</v>
+        <v>-0.43</v>
       </c>
       <c r="Z7" t="n">
-        <v>24295</v>
+        <v>8065</v>
       </c>
       <c r="AA7" t="n">
-        <v>23975</v>
+        <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>320</v>
+        <v>72</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.33</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8">
@@ -1392,26 +1391,26 @@
         <v>55510</v>
       </c>
       <c r="E8" t="n">
-        <v>55780</v>
+        <v>54480</v>
       </c>
       <c r="F8" t="n">
-        <v>58.4</v>
+        <v>54.8</v>
       </c>
       <c r="G8" t="n">
-        <v>5.49</v>
+        <v>2.68</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8</v>
+        <v>0.46</v>
       </c>
       <c r="I8" t="n">
-        <v>-259.18</v>
+        <v>-172.93</v>
       </c>
       <c r="J8" t="n">
-        <v>-615.97</v>
+        <v>-527.36</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1420,10 +1419,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>64603.07</v>
+        <v>64371.07</v>
       </c>
       <c r="N8" t="n">
-        <v>40683.03</v>
+        <v>40908.39</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1436,7 +1435,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1449,120 +1448,6 @@
         </is>
       </c>
       <c r="T8" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>RSI適正、25日線上、ゴールデンクロス、MACD買い、反発局面</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>54580</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1200</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>55780</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>55510</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>270</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E9" t="n">
-        <v>9160</v>
-      </c>
-      <c r="F9" t="n">
-        <v>53</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-336.73</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-442.85</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>12674.52</v>
-      </c>
-      <c r="N9" t="n">
-        <v>8043.86</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>85</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -1573,6 +1458,119 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>RSI適正、25日線上、MACD買い、反発局面</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>55780</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-1300</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>54480</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>55510</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-1030</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-1.86</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9153</v>
+      </c>
+      <c r="F9" t="n">
+        <v>53</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-313.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-416.96</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>12596.89</v>
+      </c>
+      <c r="N9" t="n">
+        <v>8073.51</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>85</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
@@ -1580,25 +1578,25 @@
         </is>
       </c>
       <c r="W9" t="n">
-        <v>8935</v>
+        <v>9160</v>
       </c>
       <c r="X9" t="n">
-        <v>225</v>
+        <v>-7</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.52</v>
+        <v>-0.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>9160</v>
+        <v>9153</v>
       </c>
       <c r="AA9" t="n">
         <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-840</v>
+        <v>-847</v>
       </c>
       <c r="AC9" t="n">
-        <v>-8.4</v>
+        <v>-8.470000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1726,7 +1724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1628"/>
+  <dimension ref="A1:C1637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26148,6 +26146,141 @@
         </is>
       </c>
       <c r="C1628" t="n">
+        <v>43.26</v>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1629" t="n">
+        <v>3360</v>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1630" t="n">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1631" t="n">
+        <v>175.5</v>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1632" t="n">
+        <v>3016</v>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1633" t="n">
+        <v>4845</v>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1634" t="n">
+        <v>8065</v>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1635" t="n">
+        <v>54480</v>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1636" t="n">
+        <v>9153</v>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1637" t="n">
         <v>43.26</v>
       </c>
     </row>
@@ -26162,7 +26295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F267"/>
+  <dimension ref="A1:F268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30932,19 +31065,29 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr">
+      <c r="A265" t="inlineStr"/>
+      <c r="B265" s="1" t="n">
+        <v>46293.5</v>
+      </c>
+      <c r="C265" t="n">
+        <v>214064</v>
+      </c>
+      <c r="D265" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E265" t="n">
+        <v>4774</v>
+      </c>
+      <c r="F265" t="n">
+        <v>2.28</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr"/>
-      <c r="C265" t="inlineStr"/>
-      <c r="D265" t="inlineStr"/>
-      <c r="E265" t="inlineStr"/>
-      <c r="F265" t="inlineStr"/>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr"/>
       <c r="B266" t="inlineStr"/>
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr"/>
@@ -30952,16 +31095,24 @@
       <c r="F266" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A267" t="inlineStr"/>
       <c r="B267" t="inlineStr"/>
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr"/>
+      <c r="C268" t="inlineStr"/>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -32111,7 +32262,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>あと34日</t>
+          <t>あと32日</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -32314,7 +32465,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>あと46日</t>
+          <t>あと44日</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -32523,7 +32674,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>あと45日</t>
+          <t>あと43日</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -32726,7 +32877,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>あと47日</t>
+          <t>あと45日</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -32834,7 +32985,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>あと41日</t>
+          <t>あと39日</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -32939,7 +33090,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>あと34日</t>
+          <t>あと32日</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -33145,7 +33296,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>あと41日</t>
+          <t>あと39日</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -33247,7 +33398,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>あと35日</t>
+          <t>あと33日</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -33348,7 +33499,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>あと48日</t>
+          <t>あと46日</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -33449,7 +33600,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>あと33日</t>
+          <t>あと31日</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -33472,31 +33623,31 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>53.08</v>
+        <v>56.22</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8</v>
+        <v>3.14</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.48</v>
+        <v>5.92</v>
       </c>
       <c r="H25" t="n">
-        <v>1582300</v>
+        <v>1657200</v>
       </c>
       <c r="I25" t="n">
-        <v>61.2</v>
+        <v>58.3</v>
       </c>
       <c r="J25" t="n">
-        <v>4.62</v>
+        <v>10.05</v>
       </c>
       <c r="K25" t="n">
-        <v>0.96</v>
+        <v>1.07</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.42</v>
+        <v>0.2</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.28</v>
+        <v>-0.74</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -33509,10 +33660,10 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>58.51</v>
+        <v>58.33</v>
       </c>
       <c r="Q25" t="n">
-        <v>38.51</v>
+        <v>38.86</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -33520,16 +33671,16 @@
         </is>
       </c>
       <c r="S25" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -33537,6 +33688,8 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・25日線から大きく上に乖離しています。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
@@ -33549,7 +33702,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>あと11日</t>
+          <t>あと9日</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -33649,7 +33802,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>あと41日</t>
+          <t>あと39日</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>214,064円</t>
+          <t>212,119円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4,774円</t>
+          <t>2,830円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>1.35%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3360</v>
+        <v>3340</v>
       </c>
       <c r="F2" t="n">
-        <v>44.5</v>
+        <v>43.1</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.18</v>
+        <v>-2.74</v>
       </c>
       <c r="H2" t="n">
-        <v>0.61</v>
+        <v>0.9</v>
       </c>
       <c r="I2" t="n">
-        <v>6.59</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>28.76</v>
+        <v>28.44</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3079.65</v>
+        <v>3079.39</v>
       </c>
       <c r="N2" t="n">
-        <v>2734.2</v>
+        <v>2734.1</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -793,22 +793,22 @@
         <v>3330</v>
       </c>
       <c r="X2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>13440</v>
+        <v>13360</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2640</v>
+        <v>2560</v>
       </c>
       <c r="AC2" t="n">
-        <v>24.44</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="3">
@@ -838,7 +838,7 @@
         <v>1.19</v>
       </c>
       <c r="H3" t="n">
-        <v>0.28</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>7.45</v>
@@ -942,22 +942,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>175.5</v>
+        <v>174.7</v>
       </c>
       <c r="F4" t="n">
-        <v>54.6</v>
+        <v>52.9</v>
       </c>
       <c r="G4" t="n">
-        <v>1.56</v>
+        <v>1.12</v>
       </c>
       <c r="H4" t="n">
-        <v>0.52</v>
+        <v>1.08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="J4" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>158.17</v>
+        <v>158.16</v>
       </c>
       <c r="N4" t="n">
         <v>154.69</v>
@@ -1019,22 +1019,22 @@
         <v>176.1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6</v>
+        <v>-1.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.34</v>
+        <v>-0.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>17550</v>
+        <v>17470</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1750</v>
+        <v>1670</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.08</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="5">
@@ -1055,22 +1055,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3016</v>
+        <v>2986.5</v>
       </c>
       <c r="F5" t="n">
-        <v>36.9</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.51</v>
+        <v>-2.43</v>
       </c>
       <c r="H5" t="n">
-        <v>0.34</v>
+        <v>0.88</v>
       </c>
       <c r="I5" t="n">
-        <v>-8.41</v>
+        <v>-10.77</v>
       </c>
       <c r="J5" t="n">
-        <v>0.92</v>
+        <v>0.45</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1079,14 +1079,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2944.96</v>
+        <v>2944.57</v>
       </c>
       <c r="N5" t="n">
-        <v>3163.35</v>
+        <v>3163.2</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1112,230 +1112,6 @@
         </is>
       </c>
       <c r="T5" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>押し目、MACD売り、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>2989.5</v>
-      </c>
-      <c r="X5" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>39208</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>37099</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2109</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.68</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>8058.T</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>三菱商事</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4795</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4845</v>
-      </c>
-      <c r="F6" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="I6" t="n">
-        <v>23.13</v>
-      </c>
-      <c r="J6" t="n">
-        <v>44.14</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>4716.36</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4701.58</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>65</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>押し目、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>4859</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-14</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>24225</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>23975</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>250</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7993</v>
-      </c>
-      <c r="E7" t="n">
-        <v>8065</v>
-      </c>
-      <c r="F7" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-5.78</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-55.24</v>
-      </c>
-      <c r="J7" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>7793.13</v>
-      </c>
-      <c r="N7" t="n">
-        <v>8605.219999999999</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>60</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 上昇
@@ -1345,32 +1121,258 @@
 順張りが有利な局面です。</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>2989.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>38824</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>37099</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1726</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.65</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>三菱商事</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4795</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4818</v>
+      </c>
+      <c r="F6" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I6" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="J6" t="n">
+        <v>43.71</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>4716</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4701.44</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>🟠 利益確定検討</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>50</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>押し目、デッドクロス、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>4859</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-41</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>24090</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>23975</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>115</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7993</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-6.52</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-60.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>7792.25</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8604.889999999999</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>75</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・売られ過ぎ水準です。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
+          <t>RSI売られすぎ、押し目、-1σ、MACD売り、上昇トレンド</t>
         </is>
       </c>
       <c r="W7" t="n">
         <v>8100</v>
       </c>
       <c r="X7" t="n">
-        <v>-35</v>
+        <v>-101</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.43</v>
+        <v>-1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>8065</v>
+        <v>7999</v>
       </c>
       <c r="AA7" t="n">
         <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.9</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="8">
@@ -1391,22 +1393,22 @@
         <v>55510</v>
       </c>
       <c r="E8" t="n">
-        <v>54480</v>
+        <v>53340</v>
       </c>
       <c r="F8" t="n">
-        <v>54.8</v>
+        <v>52.8</v>
       </c>
       <c r="G8" t="n">
-        <v>2.68</v>
+        <v>0.62</v>
       </c>
       <c r="H8" t="n">
-        <v>0.46</v>
+        <v>0.72</v>
       </c>
       <c r="I8" t="n">
-        <v>-172.93</v>
+        <v>-263.87</v>
       </c>
       <c r="J8" t="n">
-        <v>-527.36</v>
+        <v>-545.55</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1419,10 +1421,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>64371.07</v>
+        <v>64355.87</v>
       </c>
       <c r="N8" t="n">
-        <v>40908.39</v>
+        <v>40902.69</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1468,22 +1470,22 @@
         <v>55780</v>
       </c>
       <c r="X8" t="n">
-        <v>-1300</v>
+        <v>-2440</v>
       </c>
       <c r="Y8" t="n">
-        <v>-2.33</v>
+        <v>-4.37</v>
       </c>
       <c r="Z8" t="n">
-        <v>54480</v>
+        <v>53340</v>
       </c>
       <c r="AA8" t="n">
         <v>55510</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1030</v>
+        <v>-2170</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.86</v>
+        <v>-3.91</v>
       </c>
     </row>
     <row r="9">
@@ -1504,22 +1506,22 @@
         <v>10000</v>
       </c>
       <c r="E9" t="n">
-        <v>9153</v>
+        <v>9093</v>
       </c>
       <c r="F9" t="n">
-        <v>53</v>
+        <v>52.3</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3</v>
+        <v>-0.92</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I9" t="n">
-        <v>-313.4</v>
+        <v>-318.19</v>
       </c>
       <c r="J9" t="n">
-        <v>-416.96</v>
+        <v>-417.92</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1532,10 +1534,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>12596.89</v>
+        <v>12596.09</v>
       </c>
       <c r="N9" t="n">
-        <v>8073.51</v>
+        <v>8073.21</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1581,22 +1583,22 @@
         <v>9160</v>
       </c>
       <c r="X9" t="n">
-        <v>-7</v>
+        <v>-67</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.08</v>
+        <v>-0.73</v>
       </c>
       <c r="Z9" t="n">
-        <v>9153</v>
+        <v>9093</v>
       </c>
       <c r="AA9" t="n">
         <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-847</v>
+        <v>-907</v>
       </c>
       <c r="AC9" t="n">
-        <v>-8.470000000000001</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="10">
@@ -1724,7 +1726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1637"/>
+  <dimension ref="A1:C1646"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26281,6 +26283,141 @@
         </is>
       </c>
       <c r="C1637" t="n">
+        <v>43.26</v>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1638" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1639" t="n">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1640" t="n">
+        <v>174.7</v>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1641" t="n">
+        <v>2986.5</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1642" t="n">
+        <v>4818</v>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1643" t="n">
+        <v>7999</v>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1644" t="n">
+        <v>53340</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1645" t="n">
+        <v>9093</v>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1646" t="n">
         <v>43.26</v>
       </c>
     </row>
@@ -26295,7 +26432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F268"/>
+  <dimension ref="A1:F269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31083,19 +31220,29 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="inlineStr">
+      <c r="A266" t="inlineStr"/>
+      <c r="B266" s="1" t="n">
+        <v>46293.75</v>
+      </c>
+      <c r="C266" t="n">
+        <v>212119</v>
+      </c>
+      <c r="D266" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E266" t="n">
+        <v>2830</v>
+      </c>
+      <c r="F266" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr"/>
-      <c r="C266" t="inlineStr"/>
-      <c r="D266" t="inlineStr"/>
-      <c r="E266" t="inlineStr"/>
-      <c r="F266" t="inlineStr"/>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr"/>
       <c r="B267" t="inlineStr"/>
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr"/>
@@ -31103,16 +31250,24 @@
       <c r="F267" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A268" t="inlineStr"/>
       <c r="B268" t="inlineStr"/>
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr"/>
+      <c r="C269" t="inlineStr"/>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -31277,31 +31432,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1010</v>
+        <v>970</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>-40</v>
       </c>
       <c r="G2" t="n">
-        <v>2.43</v>
+        <v>-3.96</v>
       </c>
       <c r="H2" t="n">
-        <v>2063300</v>
+        <v>955100</v>
       </c>
       <c r="I2" t="n">
-        <v>48.6</v>
+        <v>49.8</v>
       </c>
       <c r="J2" t="n">
-        <v>0.65</v>
+        <v>-3.57</v>
       </c>
       <c r="K2" t="n">
-        <v>2.13</v>
+        <v>0.92</v>
       </c>
       <c r="L2" t="n">
-        <v>21.05</v>
+        <v>16.65</v>
       </c>
       <c r="M2" t="n">
-        <v>31.47</v>
+        <v>28.51</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -31314,10 +31469,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>862.05</v>
+        <v>865.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>1111.69</v>
+        <v>1109.22</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -31325,16 +31480,16 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -31343,7 +31498,6 @@
 ・🟢 上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・出来高が急増しています。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -31353,7 +31507,7 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>⚪ 様子見（押し目ではない）</t>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -31379,31 +31533,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3330</v>
+        <v>3360</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H3" t="n">
-        <v>96700</v>
+        <v>44000</v>
       </c>
       <c r="I3" t="n">
-        <v>39.9</v>
+        <v>44.5</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.9</v>
+        <v>-2.18</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1</v>
+        <v>0.61</v>
       </c>
       <c r="L3" t="n">
-        <v>7.92</v>
+        <v>6.59</v>
       </c>
       <c r="M3" t="n">
-        <v>34.3</v>
+        <v>28.76</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -31416,10 +31570,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3066.68</v>
+        <v>3079.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>2731.58</v>
+        <v>2734.2</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -31479,31 +31633,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1390</v>
+        <v>1384</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>-6</v>
       </c>
       <c r="G4" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="H4" t="n">
+        <v>9900</v>
+      </c>
+      <c r="I4" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.65</v>
       </c>
-      <c r="H4" t="n">
-        <v>9300</v>
-      </c>
-      <c r="I4" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.59</v>
-      </c>
       <c r="L4" t="n">
-        <v>35.21</v>
+        <v>35.11</v>
       </c>
       <c r="M4" t="n">
-        <v>37.01</v>
+        <v>36.63</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -31512,14 +31666,14 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1214.64</v>
+        <v>1217.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>1637.18</v>
+        <v>1635.75</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -31545,7 +31699,7 @@
 ・🟢 上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
@@ -31580,31 +31734,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3675</v>
+        <v>3700</v>
       </c>
       <c r="F5" t="n">
-        <v>130</v>
+        <v>25</v>
       </c>
       <c r="G5" t="n">
-        <v>3.67</v>
+        <v>0.68</v>
       </c>
       <c r="H5" t="n">
-        <v>60300</v>
+        <v>14300</v>
       </c>
       <c r="I5" t="n">
-        <v>66.3</v>
+        <v>65.7</v>
       </c>
       <c r="J5" t="n">
-        <v>6.15</v>
+        <v>6.57</v>
       </c>
       <c r="K5" t="n">
-        <v>3.28</v>
+        <v>0.76</v>
       </c>
       <c r="L5" t="n">
-        <v>29.05</v>
+        <v>42.21</v>
       </c>
       <c r="M5" t="n">
-        <v>13.45</v>
+        <v>19.2</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -31617,10 +31771,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3427.27</v>
+        <v>3432.07</v>
       </c>
       <c r="Q5" t="n">
-        <v>3165.28</v>
+        <v>3170.54</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -31628,7 +31782,7 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -31645,7 +31799,6 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・出来高が急増しています。
 ・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -31681,31 +31834,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1623</v>
+        <v>1571</v>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>-52</v>
       </c>
       <c r="G6" t="n">
-        <v>2.33</v>
+        <v>-3.2</v>
       </c>
       <c r="H6" t="n">
-        <v>85500</v>
+        <v>32500</v>
       </c>
       <c r="I6" t="n">
-        <v>82.5</v>
+        <v>62.6</v>
       </c>
       <c r="J6" t="n">
-        <v>4.64</v>
+        <v>1.25</v>
       </c>
       <c r="K6" t="n">
-        <v>1.32</v>
+        <v>0.5</v>
       </c>
       <c r="L6" t="n">
-        <v>-9.26</v>
+        <v>-8.06</v>
       </c>
       <c r="M6" t="n">
-        <v>-24</v>
+        <v>-20.81</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -31714,14 +31867,14 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>+2S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1670.29</v>
+        <v>1667.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>1692.41</v>
+        <v>1690.71</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -31729,16 +31882,16 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -31746,8 +31899,7 @@
           <t>【AI分析レポート】
 ・🔴 下降
 ・MACDは買いシグナルです。
-・買われ過ぎ水準です。
-・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+・ボリンジャーバンド中心付近で推移しています。
 ⚠️ 下落トレンドです。
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
@@ -31785,28 +31937,28 @@
         <v>521</v>
       </c>
       <c r="F7" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.38</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>10000</v>
+        <v>9100</v>
       </c>
       <c r="I7" t="n">
-        <v>46.4</v>
+        <v>48.1</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.12</v>
+        <v>-0.15</v>
       </c>
       <c r="K7" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="L7" t="n">
-        <v>-4.72</v>
+        <v>-4.4</v>
       </c>
       <c r="M7" t="n">
-        <v>-6.16</v>
+        <v>-5.81</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -31819,10 +31971,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>538.36</v>
+        <v>538.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>579.04</v>
+        <v>577.9299999999999</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -31883,31 +32035,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1080</v>
+        <v>1100</v>
       </c>
       <c r="F8" t="n">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.82</v>
+        <v>1.85</v>
       </c>
       <c r="H8" t="n">
-        <v>2300</v>
+        <v>3800</v>
       </c>
       <c r="I8" t="n">
-        <v>37.6</v>
+        <v>50</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.45</v>
+        <v>-1.61</v>
       </c>
       <c r="K8" t="n">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="L8" t="n">
-        <v>-7.68</v>
+        <v>-6.66</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.06</v>
+        <v>-3.78</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -31916,14 +32068,14 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1060.04</v>
+        <v>1062.11</v>
       </c>
       <c r="Q8" t="n">
-        <v>1016.71</v>
+        <v>1015.7</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -31931,119 +32083,19 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>7033.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>マネジメントソリューションズ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PMO支援・DX案件増加</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1591</v>
-      </c>
-      <c r="F9" t="n">
-        <v>16</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="H9" t="n">
-        <v>69700</v>
-      </c>
-      <c r="I9" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-1.72</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="L9" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="M9" t="n">
-        <v>14.93</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>1464.85</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1385.94</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>85</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -32054,313 +32106,415 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9342.T</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>スマサポ</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7033.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>マネジメントソリューションズ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>監視</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>不動産DX</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>971</v>
-      </c>
-      <c r="F10" t="n">
-        <v>6</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2300</v>
-      </c>
-      <c r="I10" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="L10" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>17.88</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PMO支援・DX案件増加</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1565</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-26</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="H9" t="n">
+        <v>16000</v>
+      </c>
+      <c r="I9" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="M9" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P10" t="n">
-        <v>885.72</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>986.7</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
+      <c r="P9" t="n">
+        <v>1467.8</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1387.15</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
         <v>65</v>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>6971.T</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>京セラ</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>自社株</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>3764</v>
-      </c>
-      <c r="F11" t="n">
-        <v>114</v>
-      </c>
-      <c r="G11" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4078000</v>
-      </c>
-      <c r="I11" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="J11" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-30.17</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>+2S</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>3658.19</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2965.86</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>95</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは買いシグナルです。
-・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2026/10/29</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>あと32日</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>3778.T</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>さくらインターネット(株)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="n">
-        <v>3750</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-80</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="H12" t="n">
-        <v>509300</v>
-      </c>
-      <c r="I12" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="L12" t="n">
-        <v>68.38</v>
-      </c>
-      <c r="M12" t="n">
-        <v>75.18000000000001</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>3254.36</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3070.75</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S12" t="n">
-        <v>100</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9342.T</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>スマサポ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>不動産DX</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>979</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6100</v>
+      </c>
+      <c r="I10" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="L10" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="M10" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>888.24</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>986.77</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>75</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
+・RSIは良好な水準です。
+・出来高が増加しています。
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6971.T</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>京セラ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>自社株</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3747</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-17</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1432500</v>
+      </c>
+      <c r="I11" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-22.06</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>3660.53</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2974.03</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>100</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは買いシグナルです。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026/10/29</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>あと31日</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3778.T</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>さくらインターネット(株)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>3710</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-40</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="H12" t="n">
+        <v>294000</v>
+      </c>
+      <c r="I12" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L12" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="M12" t="n">
+        <v>72.79000000000001</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>3266.85</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3073.68</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>95</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
@@ -32387,31 +32541,31 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>4986</v>
+        <v>5015</v>
       </c>
       <c r="F13" t="n">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="G13" t="n">
-        <v>1.53</v>
+        <v>0.58</v>
       </c>
       <c r="H13" t="n">
-        <v>26991600</v>
+        <v>15402800</v>
       </c>
       <c r="I13" t="n">
-        <v>47.5</v>
+        <v>51.6</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.95</v>
+        <v>-2.15</v>
       </c>
       <c r="K13" t="n">
-        <v>0.87</v>
+        <v>0.53</v>
       </c>
       <c r="L13" t="n">
-        <v>-73.95</v>
+        <v>-66.67</v>
       </c>
       <c r="M13" t="n">
-        <v>-46.17</v>
+        <v>-50.27</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -32424,10 +32578,10 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5072.56</v>
+        <v>5080.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>4523.86</v>
+        <v>4534.05</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -32435,16 +32589,16 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -32465,7 +32619,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>あと44日</t>
+          <t>あと43日</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -32499,28 +32653,28 @@
         <v>1096</v>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>208400</v>
+        <v>252500</v>
       </c>
       <c r="I14" t="n">
-        <v>32.7</v>
+        <v>41</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.02</v>
+        <v>-2.87</v>
       </c>
       <c r="K14" t="n">
-        <v>0.87</v>
+        <v>0.97</v>
       </c>
       <c r="L14" t="n">
-        <v>-16.14</v>
+        <v>-14.77</v>
       </c>
       <c r="M14" t="n">
-        <v>-13.35</v>
+        <v>-13.64</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -32533,10 +32687,10 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1117.24</v>
+        <v>1119.55</v>
       </c>
       <c r="Q14" t="n">
-        <v>933.9299999999999</v>
+        <v>935.49</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -32596,31 +32750,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3826</v>
+        <v>3822</v>
       </c>
       <c r="F15" t="n">
-        <v>19</v>
+        <v>-4</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="H15" t="n">
-        <v>19066200</v>
+        <v>9416800</v>
       </c>
       <c r="I15" t="n">
-        <v>52</v>
+        <v>56.2</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.75</v>
+        <v>-0.91</v>
       </c>
       <c r="K15" t="n">
-        <v>0.95</v>
+        <v>0.51</v>
       </c>
       <c r="L15" t="n">
-        <v>-6</v>
+        <v>-7.26</v>
       </c>
       <c r="M15" t="n">
-        <v>3.04</v>
+        <v>0.98</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -32633,10 +32787,10 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3952.41</v>
+        <v>3943.03</v>
       </c>
       <c r="Q15" t="n">
-        <v>3225.59</v>
+        <v>3239.77</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -32674,7 +32828,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>あと43日</t>
+          <t>あと42日</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -32701,47 +32855,47 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>4600</v>
+        <v>4530</v>
       </c>
       <c r="F16" t="n">
-        <v>155</v>
+        <v>-70</v>
       </c>
       <c r="G16" t="n">
-        <v>3.49</v>
+        <v>-1.52</v>
       </c>
       <c r="H16" t="n">
-        <v>51300</v>
+        <v>23700</v>
       </c>
       <c r="I16" t="n">
-        <v>66.59999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="J16" t="n">
-        <v>12.25</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>1.42</v>
+        <v>0.7</v>
       </c>
       <c r="L16" t="n">
-        <v>101.1</v>
+        <v>123.57</v>
       </c>
       <c r="M16" t="n">
-        <v>69.84999999999999</v>
+        <v>80.59</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>+2S</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3634.87</v>
+        <v>3656.85</v>
       </c>
       <c r="Q16" t="n">
-        <v>2885.2</v>
+        <v>2897.78</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -32766,9 +32920,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
-・25日線から大きく上に乖離しています。
-・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -32799,31 +32951,31 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>2408</v>
+        <v>2410</v>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2661700</v>
+      </c>
+      <c r="I17" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-2.56</v>
+      </c>
+      <c r="K17" t="n">
         <v>0.33</v>
       </c>
-      <c r="H17" t="n">
-        <v>7358900</v>
-      </c>
-      <c r="I17" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-3.06</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.74</v>
-      </c>
       <c r="L17" t="n">
-        <v>-75.68000000000001</v>
+        <v>-70.52</v>
       </c>
       <c r="M17" t="n">
-        <v>-86.43000000000001</v>
+        <v>-83.25</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -32836,10 +32988,10 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2722.13</v>
+        <v>2717.54</v>
       </c>
       <c r="Q17" t="n">
-        <v>2836.59</v>
+        <v>2838.82</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -32877,7 +33029,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>あと45日</t>
+          <t>あと44日</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -32908,31 +33060,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2990</v>
+        <v>3016</v>
       </c>
       <c r="F18" t="n">
-        <v>20.5</v>
+        <v>26.5</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="H18" t="n">
-        <v>21084000</v>
+        <v>9028500</v>
       </c>
       <c r="I18" t="n">
-        <v>30.9</v>
+        <v>36.9</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.28</v>
+        <v>-1.51</v>
       </c>
       <c r="K18" t="n">
-        <v>0.75</v>
+        <v>0.34</v>
       </c>
       <c r="L18" t="n">
-        <v>-8.74</v>
+        <v>-8.41</v>
       </c>
       <c r="M18" t="n">
-        <v>3.26</v>
+        <v>0.92</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -32945,10 +33097,10 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2942.38</v>
+        <v>2944.96</v>
       </c>
       <c r="Q18" t="n">
-        <v>3163.7</v>
+        <v>3163.35</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -32985,7 +33137,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>あと39日</t>
+          <t>あと38日</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -33012,31 +33164,31 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>1798</v>
+        <v>1807</v>
       </c>
       <c r="F19" t="n">
-        <v>29.5</v>
+        <v>9</v>
       </c>
       <c r="G19" t="n">
-        <v>1.67</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
-        <v>9076400</v>
+        <v>2933700</v>
       </c>
       <c r="I19" t="n">
-        <v>51.2</v>
+        <v>45.5</v>
       </c>
       <c r="J19" t="n">
-        <v>0.41</v>
+        <v>0.63</v>
       </c>
       <c r="K19" t="n">
-        <v>0.82</v>
+        <v>0.28</v>
       </c>
       <c r="L19" t="n">
-        <v>16.99</v>
+        <v>16.22</v>
       </c>
       <c r="M19" t="n">
-        <v>26.2</v>
+        <v>24.21</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -33049,10 +33201,10 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1679.55</v>
+        <v>1681.59</v>
       </c>
       <c r="Q19" t="n">
-        <v>1576.69</v>
+        <v>1579.68</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -33060,16 +33212,16 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -33090,7 +33242,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>あと32日</t>
+          <t>あと31日</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -33121,31 +33273,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F20" t="n">
-        <v>-11</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.25</v>
+        <v>0.42</v>
       </c>
       <c r="H20" t="n">
-        <v>427800</v>
+        <v>145700</v>
       </c>
       <c r="I20" t="n">
-        <v>52.1</v>
+        <v>57.7</v>
       </c>
       <c r="J20" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="K20" t="n">
-        <v>0.72</v>
+        <v>0.28</v>
       </c>
       <c r="L20" t="n">
-        <v>7.78</v>
+        <v>7.45</v>
       </c>
       <c r="M20" t="n">
-        <v>7.01</v>
+        <v>7.1</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -33158,10 +33310,10 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>435.88</v>
+        <v>436.81</v>
       </c>
       <c r="Q20" t="n">
-        <v>415.18</v>
+        <v>415.73</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -33218,31 +33370,31 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>9160</v>
+        <v>9153</v>
       </c>
       <c r="F21" t="n">
-        <v>225</v>
+        <v>-7</v>
       </c>
       <c r="G21" t="n">
-        <v>2.52</v>
+        <v>-0.08</v>
       </c>
       <c r="H21" t="n">
-        <v>27217100</v>
+        <v>14481000</v>
       </c>
       <c r="I21" t="n">
         <v>53</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.45</v>
+        <v>-0.3</v>
       </c>
       <c r="K21" t="n">
-        <v>1.01</v>
+        <v>0.6</v>
       </c>
       <c r="L21" t="n">
-        <v>-336.73</v>
+        <v>-313.4</v>
       </c>
       <c r="M21" t="n">
-        <v>-442.85</v>
+        <v>-416.96</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -33255,10 +33407,10 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>12674.52</v>
+        <v>12596.89</v>
       </c>
       <c r="Q21" t="n">
-        <v>8043.86</v>
+        <v>8073.51</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -33296,7 +33448,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>あと39日</t>
+          <t>あと38日</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -33319,35 +33471,35 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>55780</v>
+        <v>54480</v>
       </c>
       <c r="F22" t="n">
-        <v>1200</v>
+        <v>-1300</v>
       </c>
       <c r="G22" t="n">
-        <v>2.2</v>
+        <v>-2.33</v>
       </c>
       <c r="H22" t="n">
-        <v>21757800</v>
+        <v>11119000</v>
       </c>
       <c r="I22" t="n">
-        <v>58.4</v>
+        <v>54.8</v>
       </c>
       <c r="J22" t="n">
-        <v>5.49</v>
+        <v>2.68</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8</v>
+        <v>0.46</v>
       </c>
       <c r="L22" t="n">
-        <v>-259.18</v>
+        <v>-172.93</v>
       </c>
       <c r="M22" t="n">
-        <v>-615.97</v>
+        <v>-527.36</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -33356,10 +33508,10 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>64603.07</v>
+        <v>64371.07</v>
       </c>
       <c r="Q22" t="n">
-        <v>40683.03</v>
+        <v>40908.39</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -33367,7 +33519,7 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -33384,7 +33536,6 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
@@ -33398,7 +33549,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>あと33日</t>
+          <t>あと32日</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -33421,31 +33572,31 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>162.3</v>
+        <v>161.6</v>
       </c>
       <c r="F23" t="n">
-        <v>3.4</v>
+        <v>-0.7</v>
       </c>
       <c r="G23" t="n">
-        <v>2.14</v>
+        <v>-0.43</v>
       </c>
       <c r="H23" t="n">
-        <v>59839600</v>
+        <v>26351400</v>
       </c>
       <c r="I23" t="n">
-        <v>55.7</v>
+        <v>46</v>
       </c>
       <c r="J23" t="n">
-        <v>0.59</v>
+        <v>-0.01</v>
       </c>
       <c r="K23" t="n">
-        <v>1.02</v>
+        <v>0.48</v>
       </c>
       <c r="L23" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="M23" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -33458,10 +33609,10 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>153.52</v>
+        <v>153.78</v>
       </c>
       <c r="Q23" t="n">
-        <v>151.03</v>
+        <v>151.12</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -33469,16 +33620,16 @@
         </is>
       </c>
       <c r="S23" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -33499,12 +33650,12 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>あと46日</t>
+          <t>あと45日</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>⚪ 様子見（押し目ではない）</t>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -33522,35 +33673,35 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>3478</v>
+        <v>3442</v>
       </c>
       <c r="F24" t="n">
-        <v>-12</v>
+        <v>-36</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.34</v>
+        <v>-1.04</v>
       </c>
       <c r="H24" t="n">
-        <v>8775000</v>
+        <v>3959400</v>
       </c>
       <c r="I24" t="n">
-        <v>62.5</v>
+        <v>57.4</v>
       </c>
       <c r="J24" t="n">
-        <v>4.29</v>
+        <v>3.24</v>
       </c>
       <c r="K24" t="n">
-        <v>0.78</v>
+        <v>0.37</v>
       </c>
       <c r="L24" t="n">
-        <v>-76.84999999999999</v>
+        <v>-62.13</v>
       </c>
       <c r="M24" t="n">
-        <v>-123.61</v>
+        <v>-111.31</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -33559,10 +33710,10 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3951.83</v>
+        <v>3942.53</v>
       </c>
       <c r="Q24" t="n">
-        <v>3218.1</v>
+        <v>3226.17</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -33570,7 +33721,7 @@
         </is>
       </c>
       <c r="S24" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -33587,7 +33738,7 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
+・RSIは良好な水準です。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
@@ -33600,7 +33751,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>あと31日</t>
+          <t>あと30日</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -33702,7 +33853,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>あと9日</t>
+          <t>あと8日</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -33725,31 +33876,31 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>8100</v>
+        <v>8065</v>
       </c>
       <c r="F26" t="n">
-        <v>-96</v>
+        <v>-35</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.17</v>
+        <v>-0.43</v>
       </c>
       <c r="H26" t="n">
-        <v>6295000</v>
+        <v>4699900</v>
       </c>
       <c r="I26" t="n">
-        <v>32.5</v>
+        <v>30.8</v>
       </c>
       <c r="J26" t="n">
-        <v>-5.59</v>
+        <v>-5.78</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L26" t="n">
-        <v>-37.54</v>
+        <v>-55.24</v>
       </c>
       <c r="M26" t="n">
-        <v>41.92</v>
+        <v>22.49</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -33762,10 +33913,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7787.47</v>
+        <v>7793.13</v>
       </c>
       <c r="Q26" t="n">
-        <v>8630.02</v>
+        <v>8605.219999999999</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -33802,7 +33953,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>あと39日</t>
+          <t>あと38日</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>212,119円</t>
+          <t>175,283円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2,830円</t>
+          <t>-34,006円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>-16.25%</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -942,7 +942,7 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>174.7</v>
+        <v>172</v>
       </c>
       <c r="F4" t="n">
         <v>52.9</v>
@@ -954,10 +954,10 @@
         <v>1.08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="J4" t="n">
-        <v>4.25</v>
+        <v>4.18</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>158.16</v>
+        <v>155.71</v>
       </c>
       <c r="N4" t="n">
-        <v>154.69</v>
+        <v>152.3</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1016,25 +1016,25 @@
         </is>
       </c>
       <c r="W4" t="n">
-        <v>176.1</v>
+        <v>173.38</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4</v>
+        <v>-1.38</v>
       </c>
       <c r="Y4" t="n">
         <v>-0.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>17470</v>
+        <v>17200</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1670</v>
+        <v>1400</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.57</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1055,7 +1055,7 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>2986.5</v>
+        <v>2936.5</v>
       </c>
       <c r="F5" t="n">
         <v>32</v>
@@ -1067,7 +1067,7 @@
         <v>0.88</v>
       </c>
       <c r="I5" t="n">
-        <v>-10.77</v>
+        <v>-10.59</v>
       </c>
       <c r="J5" t="n">
         <v>0.45</v>
@@ -1083,10 +1083,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2944.57</v>
+        <v>2895.27</v>
       </c>
       <c r="N5" t="n">
-        <v>3163.2</v>
+        <v>3110.24</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1128,102 +1128,215 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>2989.5</v>
+        <v>2939.45</v>
       </c>
       <c r="X5" t="n">
-        <v>-3</v>
+        <v>-2.95</v>
       </c>
       <c r="Y5" t="n">
         <v>-0.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>38824</v>
+        <v>38174</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>1726</v>
+        <v>1076</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.65</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7993</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-6.52</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-60.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>7792.25</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8604.889999999999</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>75</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・売られ過ぎ水準です。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>RSI売られすぎ、押し目、-1σ、MACD売り、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>8100</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-101</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>7999</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7993</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>8058.T</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>三菱商事</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C7" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>4795</v>
       </c>
-      <c r="E6" t="n">
-        <v>4818</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="E7" t="n">
+        <v>4756</v>
+      </c>
+      <c r="F7" t="n">
         <v>36.7</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G7" t="n">
         <v>-1.33</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H7" t="n">
         <v>1.03</v>
       </c>
-      <c r="I6" t="n">
-        <v>20.97</v>
-      </c>
-      <c r="J6" t="n">
-        <v>43.71</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="I7" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>43.15</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>DC</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>4716</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4701.44</v>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="M7" t="n">
+        <v>4655.31</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4640.94</v>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>🟠 利益確定検討</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q7" t="n">
         <v>50</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>★★☆☆☆</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -1234,181 +1347,68 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>押し目、デッドクロス、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>4859</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-41</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>24090</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>23975</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>115</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7993</v>
-      </c>
-      <c r="E7" t="n">
-        <v>7999</v>
-      </c>
-      <c r="F7" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-6.52</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-60.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>21.43</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>7792.25</v>
-      </c>
-      <c r="N7" t="n">
-        <v>8604.889999999999</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>75</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>RSI売られすぎ、押し目、-1σ、MACD売り、上昇トレンド</t>
+          <t>押し目、デッドクロス、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>8100</v>
+        <v>4796.47</v>
       </c>
       <c r="X7" t="n">
-        <v>-101</v>
+        <v>-40.47</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.25</v>
+        <v>-0.84</v>
       </c>
       <c r="Z7" t="n">
-        <v>7999</v>
+        <v>23780</v>
       </c>
       <c r="AA7" t="n">
-        <v>7993</v>
+        <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>6</v>
+        <v>-195</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.08</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>285A.T</t>
+          <t>6976.T</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>キオクシアホールディングス</t>
+          <t>太陽誘電</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>55510</v>
+        <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>53340</v>
+        <v>9048</v>
       </c>
       <c r="F8" t="n">
-        <v>52.8</v>
+        <v>52.3</v>
       </c>
       <c r="G8" t="n">
-        <v>0.62</v>
+        <v>-0.92</v>
       </c>
       <c r="H8" t="n">
-        <v>0.72</v>
+        <v>0.9</v>
       </c>
       <c r="I8" t="n">
-        <v>-263.87</v>
+        <v>-316.61</v>
       </c>
       <c r="J8" t="n">
-        <v>-545.55</v>
+        <v>-415.85</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>64355.87</v>
+        <v>12533.76</v>
       </c>
       <c r="N8" t="n">
-        <v>40902.69</v>
+        <v>8033.25</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1433,20 +1433,20 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1463,142 +1463,149 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD買い、反発局面</t>
+          <t>RSI適正、押し目、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>55780</v>
+        <v>9114.67</v>
       </c>
       <c r="X8" t="n">
-        <v>-2440</v>
+        <v>-66.67</v>
       </c>
       <c r="Y8" t="n">
-        <v>-4.37</v>
+        <v>-0.73</v>
       </c>
       <c r="Z8" t="n">
-        <v>53340</v>
+        <v>9048</v>
       </c>
       <c r="AA8" t="n">
-        <v>55510</v>
+        <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2170</v>
+        <v>-952</v>
       </c>
       <c r="AC8" t="n">
-        <v>-3.91</v>
+        <v>-9.52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6976.T</t>
+          <t>285A.T</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>太陽誘電</t>
+          <t>キオクシアホールディングス</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>10000</v>
+        <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>9093</v>
+        <v>17780</v>
       </c>
       <c r="F9" t="n">
-        <v>52.3</v>
+        <v>24.3</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.92</v>
+        <v>-65.54000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9</v>
+        <v>1.68</v>
       </c>
       <c r="I9" t="n">
-        <v>-318.19</v>
+        <v>-3100.57</v>
       </c>
       <c r="J9" t="n">
-        <v>-417.92</v>
+        <v>-1112.89</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-2S</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>12596.09</v>
+        <v>63881.73</v>
       </c>
       <c r="N9" t="n">
-        <v>8073.21</v>
+        <v>40724.89</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>🟡 反発中</t>
+          <t>🔴 下降</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🔴 売り注意</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr"/>
+・🔴 下降
+・MACDは売りシグナルです。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
+・売られ過ぎ水準です。
+・25日線から大きく下に乖離しています。
+・出来高が増加しています。
+・ボリンジャーバンド-2σ付近です。売られすぎから反発する可能性があります。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>⚠️ 急落</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD買い、反発局面</t>
+          <t>RSI売られすぎ、25日線大幅割れ、出来高微増、デッドクロス、-2σ、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>9160</v>
+        <v>55780</v>
       </c>
       <c r="X9" t="n">
-        <v>-67</v>
+        <v>-38000</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.73</v>
+        <v>-68.12</v>
       </c>
       <c r="Z9" t="n">
-        <v>9093</v>
+        <v>17780</v>
       </c>
       <c r="AA9" t="n">
-        <v>10000</v>
+        <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-907</v>
+        <v>-37730</v>
       </c>
       <c r="AC9" t="n">
-        <v>-9.07</v>
+        <v>-67.97</v>
       </c>
     </row>
     <row r="10">
@@ -1619,22 +1626,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>43.26</v>
+        <v>41.78</v>
       </c>
       <c r="F10" t="n">
-        <v>58.7</v>
+        <v>53.5</v>
       </c>
       <c r="G10" t="n">
-        <v>11.89</v>
+        <v>7.56</v>
       </c>
       <c r="H10" t="n">
-        <v>1.21</v>
+        <v>0.79</v>
       </c>
       <c r="I10" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="J10" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1643,14 +1650,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+2S</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.1</v>
+        <v>33.27</v>
       </c>
       <c r="N10" t="n">
-        <v>31.79</v>
+        <v>31.83</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1663,7 +1670,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1681,8 +1688,7 @@
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
 ・RSIは良好な水準です。
-・25日線から大きく上に乖離しています。
-・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -1690,29 +1696,29 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、上昇加速、+2σ、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>41.51</v>
+        <v>43.26</v>
       </c>
       <c r="X10" t="n">
-        <v>1.75</v>
+        <v>-1.48</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.22</v>
+        <v>-3.42</v>
       </c>
       <c r="Z10" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6070</v>
+        <v>-6071</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.29000000000001</v>
+        <v>-99.31999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1726,7 +1732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1646"/>
+  <dimension ref="A1:C1655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26419,6 +26425,141 @@
       </c>
       <c r="C1646" t="n">
         <v>43.26</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1647" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1648" t="n">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1649" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1650" t="n">
+        <v>2936.5</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1651" t="n">
+        <v>7999</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1652" t="n">
+        <v>4756</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1653" t="n">
+        <v>9048</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1654" t="n">
+        <v>17780</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1655" t="n">
+        <v>41.78</v>
       </c>
     </row>
   </sheetData>
@@ -26432,7 +26573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F269"/>
+  <dimension ref="A1:F270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31238,19 +31379,29 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="inlineStr">
+      <c r="A267" t="inlineStr"/>
+      <c r="B267" s="1" t="n">
+        <v>46294.29166666666</v>
+      </c>
+      <c r="C267" t="n">
+        <v>175283</v>
+      </c>
+      <c r="D267" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E267" t="n">
+        <v>-34006</v>
+      </c>
+      <c r="F267" t="n">
+        <v>-16.25</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr"/>
-      <c r="C267" t="inlineStr"/>
-      <c r="D267" t="inlineStr"/>
-      <c r="E267" t="inlineStr"/>
-      <c r="F267" t="inlineStr"/>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr"/>
       <c r="B268" t="inlineStr"/>
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr"/>
@@ -31258,16 +31409,24 @@
       <c r="F268" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A269" t="inlineStr"/>
       <c r="B269" t="inlineStr"/>
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr"/>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -31432,31 +31591,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="F2" t="n">
-        <v>-40</v>
+        <v>-37</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.96</v>
+        <v>-3.66</v>
       </c>
       <c r="H2" t="n">
-        <v>955100</v>
+        <v>1360200</v>
       </c>
       <c r="I2" t="n">
-        <v>49.8</v>
+        <v>50.4</v>
       </c>
       <c r="J2" t="n">
-        <v>-3.57</v>
+        <v>-3.28</v>
       </c>
       <c r="K2" t="n">
-        <v>0.92</v>
+        <v>1.21</v>
       </c>
       <c r="L2" t="n">
-        <v>16.65</v>
+        <v>16.89</v>
       </c>
       <c r="M2" t="n">
-        <v>28.51</v>
+        <v>28.56</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -31469,10 +31628,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>865.48</v>
+        <v>865.52</v>
       </c>
       <c r="Q2" t="n">
-        <v>1109.22</v>
+        <v>1109.23</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -31480,16 +31639,16 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -31533,31 +31692,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3360</v>
+        <v>3340</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>69700</v>
+      </c>
+      <c r="I3" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="K3" t="n">
         <v>0.9</v>
       </c>
-      <c r="H3" t="n">
-        <v>44000</v>
-      </c>
-      <c r="I3" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-2.18</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.61</v>
-      </c>
       <c r="L3" t="n">
-        <v>6.59</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>28.76</v>
+        <v>28.44</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -31570,10 +31729,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3079.65</v>
+        <v>3079.39</v>
       </c>
       <c r="Q3" t="n">
-        <v>2734.2</v>
+        <v>2734.1</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -31633,31 +31792,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1384</v>
+        <v>1405</v>
       </c>
       <c r="F4" t="n">
-        <v>-6</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.43</v>
+        <v>1.08</v>
       </c>
       <c r="H4" t="n">
-        <v>9900</v>
+        <v>29100</v>
       </c>
       <c r="I4" t="n">
-        <v>55.4</v>
+        <v>58.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.35</v>
+        <v>5.87</v>
       </c>
       <c r="K4" t="n">
-        <v>0.65</v>
+        <v>1.52</v>
       </c>
       <c r="L4" t="n">
-        <v>35.11</v>
+        <v>36.78</v>
       </c>
       <c r="M4" t="n">
-        <v>36.63</v>
+        <v>36.96</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -31666,14 +31825,14 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1217.7</v>
+        <v>1217.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>1635.75</v>
+        <v>1635.85</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -31681,16 +31840,16 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -31699,7 +31858,8 @@
 ・🟢 上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・出来高が増加しています。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
@@ -31734,31 +31894,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3700</v>
+        <v>3710</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>0.68</v>
+        <v>0.95</v>
       </c>
       <c r="H5" t="n">
-        <v>14300</v>
+        <v>25800</v>
       </c>
       <c r="I5" t="n">
-        <v>65.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>6.57</v>
+        <v>6.84</v>
       </c>
       <c r="K5" t="n">
-        <v>0.76</v>
+        <v>1.22</v>
       </c>
       <c r="L5" t="n">
-        <v>42.21</v>
+        <v>43</v>
       </c>
       <c r="M5" t="n">
-        <v>19.2</v>
+        <v>19.36</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -31771,10 +31931,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3432.07</v>
+        <v>3432.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3170.54</v>
+        <v>3170.59</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -31834,31 +31994,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1571</v>
+        <v>1581</v>
       </c>
       <c r="F6" t="n">
-        <v>-52</v>
+        <v>-42</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.2</v>
+        <v>-2.59</v>
       </c>
       <c r="H6" t="n">
-        <v>32500</v>
+        <v>92800</v>
       </c>
       <c r="I6" t="n">
-        <v>62.6</v>
+        <v>65.2</v>
       </c>
       <c r="J6" t="n">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5</v>
+        <v>1.21</v>
       </c>
       <c r="L6" t="n">
-        <v>-8.06</v>
+        <v>-7.26</v>
       </c>
       <c r="M6" t="n">
-        <v>-20.81</v>
+        <v>-20.65</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -31871,10 +32031,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1667.12</v>
+        <v>1667.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1690.71</v>
+        <v>1690.76</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -31882,7 +32042,7 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -31934,31 +32094,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="H7" t="n">
-        <v>9100</v>
+        <v>17400</v>
       </c>
       <c r="I7" t="n">
-        <v>48.1</v>
+        <v>51.7</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.15</v>
+        <v>0.22</v>
       </c>
       <c r="K7" t="n">
-        <v>0.62</v>
+        <v>1.07</v>
       </c>
       <c r="L7" t="n">
-        <v>-4.4</v>
+        <v>-4.24</v>
       </c>
       <c r="M7" t="n">
-        <v>-5.81</v>
+        <v>-5.78</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -31971,10 +32131,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>538.45</v>
+        <v>538.48</v>
       </c>
       <c r="Q7" t="n">
-        <v>577.9299999999999</v>
+        <v>577.9400000000001</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -31982,16 +32142,16 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -32035,67 +32195,475 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1100</v>
+        <v>1121</v>
       </c>
       <c r="F8" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G8" t="n">
-        <v>1.85</v>
+        <v>3.8</v>
       </c>
       <c r="H8" t="n">
-        <v>3800</v>
+        <v>7100</v>
       </c>
       <c r="I8" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1062.39</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1015.8</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>100</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・出来高が増加しています。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7033.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>マネジメントソリューションズ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PMO支援・DX案件増加</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1558</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-33</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>60600</v>
+      </c>
+      <c r="I9" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-3.54</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="M9" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1467.71</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1387.12</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>65</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9342.T</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>スマサポ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>不動産DX</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>953</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-18</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10500</v>
+      </c>
+      <c r="I10" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="M10" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>887.89</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>986.64</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
         <v>50</v>
       </c>
-      <c r="J8" t="n">
-        <v>-1.61</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-6.66</v>
-      </c>
-      <c r="M8" t="n">
-        <v>-3.78</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
+・出来高が急増しています。
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>🟡 調整中押し目（段階的買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6971.T</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>京セラ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>自社株</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3703</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-61</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4858400</v>
+      </c>
+      <c r="I11" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-22.76</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>3659.95</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2973.81</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>100</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは買いシグナルです。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026/10/29</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>あと31日</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3778.T</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>さくらインターネット(株)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>3730</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-20</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="H12" t="n">
+        <v>533900</v>
+      </c>
+      <c r="I12" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L12" t="n">
+        <v>64.84999999999999</v>
+      </c>
+      <c r="M12" t="n">
+        <v>73.11</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P8" t="n">
-        <v>1062.11</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1015.7</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P12" t="n">
+        <v>3267.12</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3073.78</v>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S8" t="n">
-        <v>85</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
+      <c r="S12" t="n">
+        <v>95</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -32106,97 +32674,1123 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5803.T</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>(株)フジクラ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>4957</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-29</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="H13" t="n">
+        <v>26464800</v>
+      </c>
+      <c r="I13" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-71.3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-51.19</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>5079.97</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4533.76</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>65</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2026/11/10</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>あと43日</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>7033.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>マネジメントソリューションズ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>166A.T</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>タスキホールディングス</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>監視</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PMO支援・DX案件増加</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1565</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-26</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-1.63</v>
-      </c>
-      <c r="H9" t="n">
-        <v>16000</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>何度も高値更新中の強トレンド</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1086</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="H14" t="n">
+        <v>747900</v>
+      </c>
+      <c r="I14" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-3.72</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-15.57</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-13.8</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1119.41</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>935.4400000000001</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>55</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・出来高が急増しています。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5801.T</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>古河電気工業</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>半導体設備関連</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3785</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-41</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="H15" t="n">
+        <v>15361700</v>
+      </c>
+      <c r="I15" t="n">
+        <v>55</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-10.21</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>3942.53</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3239.59</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>65</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2026/11/09</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>あと42日</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3374.T</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>内外テック</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>4475</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-2.72</v>
+      </c>
+      <c r="H16" t="n">
+        <v>49700</v>
+      </c>
+      <c r="I16" t="n">
+        <v>66</v>
+      </c>
+      <c r="J16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L16" t="n">
+        <v>119.18</v>
+      </c>
+      <c r="M16" t="n">
+        <v>79.72</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>3656.12</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2897.51</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>100</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは買いシグナルです。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>7012.T</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>川崎重工業(株)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-8</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="H17" t="n">
+        <v>6041400</v>
+      </c>
+      <c r="I17" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-2.95</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-71.31999999999999</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-83.41</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>2717.41</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2838.77</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは買いシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>あと44日</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>トヨタ自動車(株)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4000円で売る予定</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2987</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>26063800</v>
+      </c>
+      <c r="I18" t="n">
+        <v>32</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-10.77</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>2944.57</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3163.2</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>60</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2026/11/05</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>あと38日</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>8053.T</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>住友商事</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>1788</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>11877200</v>
+      </c>
+      <c r="I19" t="n">
+        <v>43</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L19" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="M19" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1681.34</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1579.59</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>65</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2026/10/29</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>あと31日</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ブロードリーフ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>500円で売</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>479</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H20" t="n">
+        <v>388300</v>
+      </c>
+      <c r="I20" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L20" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="M20" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>436.81</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>415.73</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>100</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>9093</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-67</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="H21" t="n">
+        <v>23526900</v>
+      </c>
+      <c r="I21" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-318.19</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-417.92</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>12596.09</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>8073.21</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>85</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2026/11/05</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>あと38日</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>キオクシアホールディングス</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>53340</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-2440</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-4.37</v>
+      </c>
+      <c r="H22" t="n">
+        <v>18399200</v>
+      </c>
+      <c r="I22" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-263.87</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-545.55</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>64355.87</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>40902.69</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>95</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2026/10/30</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>あと32日</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>8729.T</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ソニーファイナンシャル</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>161.1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="H23" t="n">
+        <v>61369000</v>
+      </c>
+      <c r="I23" t="n">
         <v>45.1</v>
       </c>
-      <c r="J9" t="n">
-        <v>-3.12</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="M9" t="n">
-        <v>13.07</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="J23" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P9" t="n">
-        <v>1467.8</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1387.15</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P23" t="n">
+        <v>153.78</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>151.12</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S9" t="n">
+      <c r="S23" t="n">
         <v>65</v>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -32207,1442 +33801,6 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9342.T</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>スマサポ</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>不動産DX</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>979</v>
-      </c>
-      <c r="F10" t="n">
-        <v>8</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="H10" t="n">
-        <v>6100</v>
-      </c>
-      <c r="I10" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="L10" t="n">
-        <v>11.66</v>
-      </c>
-      <c r="M10" t="n">
-        <v>16.64</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>DC</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>888.24</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>986.77</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>75</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
-・RSIは良好な水準です。
-・出来高が増加しています。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>6971.T</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>京セラ</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>自社株</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>3747</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-17</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1432500</v>
-      </c>
-      <c r="I11" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="L11" t="n">
-        <v>10.38</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-22.06</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>3660.53</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2974.03</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>100</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは買いシグナルです。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2026/10/29</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>あと31日</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>3778.T</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>さくらインターネット(株)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="n">
-        <v>3710</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-40</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="H12" t="n">
-        <v>294000</v>
-      </c>
-      <c r="I12" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="L12" t="n">
-        <v>63.25</v>
-      </c>
-      <c r="M12" t="n">
-        <v>72.79000000000001</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>3266.85</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3073.68</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S12" t="n">
-        <v>95</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>5803.T</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>(株)フジクラ</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="n">
-        <v>5015</v>
-      </c>
-      <c r="F13" t="n">
-        <v>29</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="H13" t="n">
-        <v>15402800</v>
-      </c>
-      <c r="I13" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-2.15</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-66.67</v>
-      </c>
-      <c r="M13" t="n">
-        <v>-50.27</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>5080.75</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4534.05</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S13" t="n">
-        <v>65</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>2026/11/10</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>あと43日</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>166A.T</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>タスキホールディングス</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>何度も高値更新中の強トレンド</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1096</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>252500</v>
-      </c>
-      <c r="I14" t="n">
-        <v>41</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-2.87</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-14.77</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-13.64</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1119.55</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>935.49</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S14" t="n">
-        <v>45</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>5801.T</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>古河電気工業</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>半導体設備関連</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>3822</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-4</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>9416800</v>
-      </c>
-      <c r="I15" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-7.26</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>3943.03</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3239.77</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S15" t="n">
-        <v>65</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>2026/11/09</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>あと42日</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>3374.T</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>内外テック</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="n">
-        <v>4530</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-70</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="H16" t="n">
-        <v>23700</v>
-      </c>
-      <c r="I16" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>9.869999999999999</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L16" t="n">
-        <v>123.57</v>
-      </c>
-      <c r="M16" t="n">
-        <v>80.59</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>3656.85</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2897.78</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S16" t="n">
-        <v>100</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは買いシグナルです。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>7012.T</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>川崎重工業(株)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="n">
-        <v>2410</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2661700</v>
-      </c>
-      <c r="I17" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-2.56</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-70.52</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-83.25</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>2717.54</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2838.82</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S17" t="n">
-        <v>30</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>あと44日</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>7203.T</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>トヨタ自動車(株)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4000円で売る予定</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>3016</v>
-      </c>
-      <c r="F18" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="H18" t="n">
-        <v>9028500</v>
-      </c>
-      <c r="I18" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-1.51</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-8.41</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>2944.96</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3163.35</v>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="S18" t="n">
-        <v>55</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>2026/11/05</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>あと38日</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>8053.T</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>住友商事</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="n">
-        <v>1807</v>
-      </c>
-      <c r="F19" t="n">
-        <v>9</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2933700</v>
-      </c>
-      <c r="I19" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="L19" t="n">
-        <v>16.22</v>
-      </c>
-      <c r="M19" t="n">
-        <v>24.21</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1681.59</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1579.68</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S19" t="n">
-        <v>75</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>2026/10/29</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>あと31日</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>3673.T</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ブロードリーフ</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>500円で売</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>479</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H20" t="n">
-        <v>145700</v>
-      </c>
-      <c r="I20" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="L20" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="M20" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>436.81</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>415.73</v>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S20" t="n">
-        <v>100</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="n">
-        <v>9153</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-7</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="H21" t="n">
-        <v>14481000</v>
-      </c>
-      <c r="I21" t="n">
-        <v>53</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-313.4</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-416.96</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>12596.89</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>8073.51</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S21" t="n">
-        <v>85</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>2026/11/05</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>あと38日</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>285A.T</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>キオクシアホールディングス</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="n">
-        <v>54480</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-1300</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-2.33</v>
-      </c>
-      <c r="H22" t="n">
-        <v>11119000</v>
-      </c>
-      <c r="I22" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-172.93</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-527.36</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>64371.07</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>40908.39</v>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S22" t="n">
-        <v>95</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>2026/10/30</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>あと32日</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>8729.T</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ソニーファイナンシャル</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>161.6</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="H23" t="n">
-        <v>26351400</v>
-      </c>
-      <c r="I23" t="n">
-        <v>46</v>
-      </c>
-      <c r="J23" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>153.78</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>151.12</v>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S23" t="n">
-        <v>65</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
       <c r="W23" t="inlineStr">
         <is>
           <t>2026/11/12</t>
@@ -33673,31 +33831,31 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>3442</v>
+        <v>3459</v>
       </c>
       <c r="F24" t="n">
-        <v>-36</v>
+        <v>-19</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.04</v>
+        <v>-0.55</v>
       </c>
       <c r="H24" t="n">
-        <v>3959400</v>
+        <v>9179300</v>
       </c>
       <c r="I24" t="n">
-        <v>57.4</v>
+        <v>58.3</v>
       </c>
       <c r="J24" t="n">
-        <v>3.24</v>
+        <v>3.73</v>
       </c>
       <c r="K24" t="n">
-        <v>0.37</v>
+        <v>0.77</v>
       </c>
       <c r="L24" t="n">
-        <v>-62.13</v>
+        <v>-60.77</v>
       </c>
       <c r="M24" t="n">
-        <v>-111.31</v>
+        <v>-111.04</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -33710,10 +33868,10 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3942.53</v>
+        <v>3942.76</v>
       </c>
       <c r="Q24" t="n">
-        <v>3226.17</v>
+        <v>3226.26</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -33876,31 +34034,31 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>8065</v>
+        <v>7999</v>
       </c>
       <c r="F26" t="n">
-        <v>-35</v>
+        <v>-101</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.43</v>
+        <v>-1.25</v>
       </c>
       <c r="H26" t="n">
-        <v>4699900</v>
+        <v>8814400</v>
       </c>
       <c r="I26" t="n">
-        <v>30.8</v>
+        <v>29.9</v>
       </c>
       <c r="J26" t="n">
-        <v>-5.78</v>
+        <v>-6.52</v>
       </c>
       <c r="K26" t="n">
-        <v>0.75</v>
+        <v>1.24</v>
       </c>
       <c r="L26" t="n">
-        <v>-55.24</v>
+        <v>-60.5</v>
       </c>
       <c r="M26" t="n">
-        <v>22.49</v>
+        <v>21.43</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -33913,10 +34071,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7793.13</v>
+        <v>7792.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>8605.219999999999</v>
+        <v>8604.889999999999</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -33924,16 +34082,16 @@
         </is>
       </c>
       <c r="S26" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -33941,6 +34099,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
+・売られ過ぎ水準です。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>175,283円</t>
+          <t>173,624円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-34,006円</t>
+          <t>-35,666円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.25%</t>
+          <t>-17.04%</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -717,22 +717,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3340</v>
+        <v>3345</v>
       </c>
       <c r="F2" t="n">
-        <v>43.1</v>
+        <v>36.4</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.74</v>
+        <v>-2.51</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9</v>
+        <v>0.23</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="J2" t="n">
-        <v>28.44</v>
+        <v>23.36</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3079.39</v>
+        <v>3092</v>
       </c>
       <c r="N2" t="n">
-        <v>2734.1</v>
+        <v>2736.82</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -790,25 +790,25 @@
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3330</v>
+        <v>3340</v>
       </c>
       <c r="X2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="Z2" t="n">
-        <v>13360</v>
+        <v>13380</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2560</v>
+        <v>2580</v>
       </c>
       <c r="AC2" t="n">
-        <v>23.7</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="3">
@@ -829,22 +829,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="F3" t="n">
-        <v>57.7</v>
+        <v>45.4</v>
       </c>
       <c r="G3" t="n">
-        <v>1.19</v>
+        <v>0.45</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.19</v>
       </c>
       <c r="I3" t="n">
-        <v>7.45</v>
+        <v>6.79</v>
       </c>
       <c r="J3" t="n">
-        <v>7.1</v>
+        <v>7.03</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>436.81</v>
+        <v>437.82</v>
       </c>
       <c r="N3" t="n">
-        <v>415.73</v>
+        <v>416.31</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -869,136 +869,23 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>RSI適正、25日線上、MACD買い、長期上昇</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>477</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>47900</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>42000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>5900</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>14.05</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>9432.T</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NTT</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" t="n">
-        <v>158</v>
-      </c>
-      <c r="E4" t="n">
-        <v>172</v>
-      </c>
-      <c r="F4" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>155.71</v>
-      </c>
-      <c r="N4" t="n">
-        <v>152.3</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>🟢 強い買い</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>95</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -1009,6 +896,119 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>25日線上、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>479</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>47500</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>42000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>5500</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NTT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>158</v>
+      </c>
+      <c r="E4" t="n">
+        <v>171</v>
+      </c>
+      <c r="F4" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>156.07</v>
+      </c>
+      <c r="N4" t="n">
+        <v>152.4</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>🟢 強い買い</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>95</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
@@ -1016,25 +1016,25 @@
         </is>
       </c>
       <c r="W4" t="n">
-        <v>173.38</v>
+        <v>172</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.38</v>
+        <v>-1</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.8</v>
+        <v>-0.58</v>
       </c>
       <c r="Z4" t="n">
-        <v>17200</v>
+        <v>17100</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.859999999999999</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="5">
@@ -1055,22 +1055,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>2936.5</v>
+        <v>2901</v>
       </c>
       <c r="F5" t="n">
         <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.43</v>
+        <v>-3.47</v>
       </c>
       <c r="H5" t="n">
-        <v>0.88</v>
+        <v>0.44</v>
       </c>
       <c r="I5" t="n">
-        <v>-10.59</v>
+        <v>-14.86</v>
       </c>
       <c r="J5" t="n">
-        <v>0.45</v>
+        <v>-2.62</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2895.27</v>
+        <v>2896.85</v>
       </c>
       <c r="N5" t="n">
-        <v>3110.24</v>
+        <v>3109.82</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1128,25 +1128,25 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>2939.45</v>
+        <v>2936.5</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.95</v>
+        <v>-35.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.1</v>
+        <v>-1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>38174</v>
+        <v>37713</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>1076</v>
+        <v>614</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.9</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="6">
@@ -1167,22 +1167,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>7999</v>
+        <v>7896</v>
       </c>
       <c r="F6" t="n">
-        <v>29.9</v>
+        <v>28.7</v>
       </c>
       <c r="G6" t="n">
-        <v>-6.52</v>
+        <v>-7.34</v>
       </c>
       <c r="H6" t="n">
-        <v>1.24</v>
+        <v>0.54</v>
       </c>
       <c r="I6" t="n">
-        <v>-60.5</v>
+        <v>-86.02</v>
       </c>
       <c r="J6" t="n">
-        <v>21.43</v>
+        <v>-0.06</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>7792.25</v>
+        <v>7794.36</v>
       </c>
       <c r="N6" t="n">
-        <v>8604.889999999999</v>
+        <v>8580.299999999999</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1241,25 +1241,25 @@
         </is>
       </c>
       <c r="W6" t="n">
-        <v>8100</v>
+        <v>7999</v>
       </c>
       <c r="X6" t="n">
-        <v>-101</v>
+        <v>-103</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.25</v>
+        <v>-1.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>7999</v>
+        <v>7896</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>6</v>
+        <v>-97</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.08</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="7">
@@ -1280,38 +1280,38 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4756</v>
+        <v>4674</v>
       </c>
       <c r="F7" t="n">
-        <v>36.7</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.33</v>
+        <v>-3.06</v>
       </c>
       <c r="H7" t="n">
-        <v>1.03</v>
+        <v>0.38</v>
       </c>
       <c r="I7" t="n">
-        <v>20.7</v>
+        <v>6.25</v>
       </c>
       <c r="J7" t="n">
-        <v>43.15</v>
+        <v>35.77</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4655.31</v>
+        <v>4654.39</v>
       </c>
       <c r="N7" t="n">
-        <v>4640.94</v>
+        <v>4646.39</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1320,20 +1320,20 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟠 利益確定検討</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1341,8 +1341,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -1350,29 +1349,29 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>押し目、デッドクロス、MACD売り、長期上昇</t>
+          <t>押し目、-1σ、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4796.47</v>
+        <v>4756</v>
       </c>
       <c r="X7" t="n">
-        <v>-40.47</v>
+        <v>-82</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.84</v>
+        <v>-1.72</v>
       </c>
       <c r="Z7" t="n">
-        <v>23780</v>
+        <v>23370</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>-195</v>
+        <v>-605</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="8">
@@ -1393,22 +1392,22 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>9048</v>
+        <v>8968</v>
       </c>
       <c r="F8" t="n">
-        <v>52.3</v>
+        <v>45.5</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.92</v>
+        <v>-1.54</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9</v>
+        <v>0.54</v>
       </c>
       <c r="I8" t="n">
-        <v>-316.61</v>
+        <v>-304.93</v>
       </c>
       <c r="J8" t="n">
-        <v>-415.85</v>
+        <v>-393.66</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1421,10 +1420,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>12533.76</v>
+        <v>12414.85</v>
       </c>
       <c r="N8" t="n">
-        <v>8033.25</v>
+        <v>8061.58</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1433,20 +1432,20 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1463,29 +1462,29 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD買い、反発局面</t>
+          <t>押し目、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>9114.67</v>
+        <v>9048</v>
       </c>
       <c r="X8" t="n">
-        <v>-66.67</v>
+        <v>-80</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.73</v>
+        <v>-0.88</v>
       </c>
       <c r="Z8" t="n">
-        <v>9048</v>
+        <v>8968</v>
       </c>
       <c r="AA8" t="n">
         <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-952</v>
+        <v>-1032</v>
       </c>
       <c r="AC8" t="n">
-        <v>-9.52</v>
+        <v>-10.32</v>
       </c>
     </row>
     <row r="9">
@@ -1506,106 +1505,99 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
+        <v>17655</v>
+      </c>
+      <c r="F9" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-98.15000000000001</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-165.11</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>21347.58</v>
+      </c>
+      <c r="N9" t="n">
+        <v>13707.7</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>65</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>押し目、MACD買い、反発局面</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
         <v>17780</v>
       </c>
-      <c r="F9" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-65.54000000000001</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-3100.57</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-1112.89</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>DC</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-2S</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>63881.73</v>
-      </c>
-      <c r="N9" t="n">
-        <v>40724.89</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>🔴 売り注意</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>10</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
-・売られ過ぎ水準です。
-・25日線から大きく下に乖離しています。
-・出来高が増加しています。
-・ボリンジャーバンド-2σ付近です。売られすぎから反発する可能性があります。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>⚠️ 急落</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>RSI売られすぎ、25日線大幅割れ、出来高微増、デッドクロス、-2σ、MACD売り、下降トレンド</t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>55780</v>
-      </c>
       <c r="X9" t="n">
-        <v>-38000</v>
+        <v>-125</v>
       </c>
       <c r="Y9" t="n">
-        <v>-68.12</v>
+        <v>-0.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>17780</v>
+        <v>17655</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-37730</v>
+        <v>-37855</v>
       </c>
       <c r="AC9" t="n">
-        <v>-67.97</v>
+        <v>-68.19</v>
       </c>
     </row>
     <row r="10">
@@ -1635,7 +1627,7 @@
         <v>7.56</v>
       </c>
       <c r="H10" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="I10" t="n">
         <v>1.74</v>
@@ -1732,7 +1724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1655"/>
+  <dimension ref="A1:C1664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26559,6 +26551,141 @@
         </is>
       </c>
       <c r="C1655" t="n">
+        <v>41.78</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1656" t="n">
+        <v>3345</v>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1657" t="n">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1658" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1659" t="n">
+        <v>2901</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1660" t="n">
+        <v>7896</v>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1661" t="n">
+        <v>4674</v>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1662" t="n">
+        <v>8968</v>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1663" t="n">
+        <v>17655</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1664" t="n">
         <v>41.78</v>
       </c>
     </row>
@@ -26573,7 +26700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F270"/>
+  <dimension ref="A1:F271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31397,19 +31524,29 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="inlineStr">
+      <c r="A268" t="inlineStr"/>
+      <c r="B268" s="1" t="n">
+        <v>46294.5</v>
+      </c>
+      <c r="C268" t="n">
+        <v>173624</v>
+      </c>
+      <c r="D268" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E268" t="n">
+        <v>-35666</v>
+      </c>
+      <c r="F268" t="n">
+        <v>-17.04</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr"/>
-      <c r="C268" t="inlineStr"/>
-      <c r="D268" t="inlineStr"/>
-      <c r="E268" t="inlineStr"/>
-      <c r="F268" t="inlineStr"/>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr"/>
       <c r="B269" t="inlineStr"/>
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr"/>
@@ -31417,16 +31554,24 @@
       <c r="F269" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A270" t="inlineStr"/>
       <c r="B270" t="inlineStr"/>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr"/>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -32499,10 +32644,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3703</v>
+        <v>3675</v>
       </c>
       <c r="F11" t="n">
-        <v>-61</v>
+        <v>-60.54</v>
       </c>
       <c r="G11" t="n">
         <v>-1.62</v>
@@ -32520,10 +32665,10 @@
         <v>0.92</v>
       </c>
       <c r="L11" t="n">
-        <v>6.87</v>
+        <v>6.82</v>
       </c>
       <c r="M11" t="n">
-        <v>-22.76</v>
+        <v>-22.59</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -32536,10 +32681,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3659.95</v>
+        <v>3632.27</v>
       </c>
       <c r="Q11" t="n">
-        <v>2973.81</v>
+        <v>2951.33</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -32700,10 +32845,10 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>4957</v>
+        <v>4938</v>
       </c>
       <c r="F13" t="n">
-        <v>-29</v>
+        <v>-28.89</v>
       </c>
       <c r="G13" t="n">
         <v>-0.58</v>
@@ -32721,10 +32866,10 @@
         <v>0.85</v>
       </c>
       <c r="L13" t="n">
-        <v>-71.3</v>
+        <v>-71.03</v>
       </c>
       <c r="M13" t="n">
-        <v>-51.19</v>
+        <v>-51</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -32737,10 +32882,10 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5079.97</v>
+        <v>5060.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>4533.76</v>
+        <v>4516.38</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -32809,10 +32954,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1086</v>
+        <v>1052</v>
       </c>
       <c r="F14" t="n">
-        <v>-10</v>
+        <v>-9.69</v>
       </c>
       <c r="G14" t="n">
         <v>-0.91</v>
@@ -32830,10 +32975,10 @@
         <v>2.07</v>
       </c>
       <c r="L14" t="n">
-        <v>-15.57</v>
+        <v>-15.08</v>
       </c>
       <c r="M14" t="n">
-        <v>-13.8</v>
+        <v>-13.37</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -32846,10 +32991,10 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1119.41</v>
+        <v>1084.37</v>
       </c>
       <c r="Q14" t="n">
-        <v>935.4400000000001</v>
+        <v>906.15</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -32910,10 +33055,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3785</v>
+        <v>3774</v>
       </c>
       <c r="F15" t="n">
-        <v>-41</v>
+        <v>-40.88</v>
       </c>
       <c r="G15" t="n">
         <v>-1.07</v>
@@ -32931,7 +33076,7 @@
         <v>0.78</v>
       </c>
       <c r="L15" t="n">
-        <v>-10.21</v>
+        <v>-10.18</v>
       </c>
       <c r="M15" t="n">
         <v>0.39</v>
@@ -32947,10 +33092,10 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3942.53</v>
+        <v>3931.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>3239.59</v>
+        <v>3230.17</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -33111,10 +33256,10 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>2400</v>
+        <v>2380</v>
       </c>
       <c r="F17" t="n">
-        <v>-8</v>
+        <v>-7.93</v>
       </c>
       <c r="G17" t="n">
         <v>-0.33</v>
@@ -33132,10 +33277,10 @@
         <v>0.68</v>
       </c>
       <c r="L17" t="n">
-        <v>-71.31999999999999</v>
+        <v>-70.73</v>
       </c>
       <c r="M17" t="n">
-        <v>-83.41</v>
+        <v>-82.70999999999999</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -33148,10 +33293,10 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2717.41</v>
+        <v>2694.76</v>
       </c>
       <c r="Q17" t="n">
-        <v>2838.77</v>
+        <v>2815.11</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -33219,10 +33364,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2987</v>
+        <v>2937</v>
       </c>
       <c r="F18" t="n">
-        <v>-3</v>
+        <v>-2.95</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1</v>
@@ -33240,7 +33385,7 @@
         <v>0.88</v>
       </c>
       <c r="L18" t="n">
-        <v>-10.77</v>
+        <v>-10.59</v>
       </c>
       <c r="M18" t="n">
         <v>0.45</v>
@@ -33256,10 +33401,10 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2944.57</v>
+        <v>2895.27</v>
       </c>
       <c r="Q18" t="n">
-        <v>3163.2</v>
+        <v>3110.24</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -33323,10 +33468,10 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>1788</v>
+        <v>1768</v>
       </c>
       <c r="F19" t="n">
-        <v>-10</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5600000000000001</v>
@@ -33344,10 +33489,10 @@
         <v>0.97</v>
       </c>
       <c r="L19" t="n">
-        <v>14.71</v>
+        <v>14.54</v>
       </c>
       <c r="M19" t="n">
-        <v>23.9</v>
+        <v>23.63</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -33360,10 +33505,10 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1681.34</v>
+        <v>1662.53</v>
       </c>
       <c r="Q19" t="n">
-        <v>1579.59</v>
+        <v>1561.92</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -33528,10 +33673,10 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>9093</v>
+        <v>9048</v>
       </c>
       <c r="F21" t="n">
-        <v>-67</v>
+        <v>-66.67</v>
       </c>
       <c r="G21" t="n">
         <v>-0.73</v>
@@ -33549,10 +33694,10 @@
         <v>0.9</v>
       </c>
       <c r="L21" t="n">
-        <v>-318.19</v>
+        <v>-316.61</v>
       </c>
       <c r="M21" t="n">
-        <v>-417.92</v>
+        <v>-415.85</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -33565,10 +33710,10 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>12596.09</v>
+        <v>12533.76</v>
       </c>
       <c r="Q21" t="n">
-        <v>8073.21</v>
+        <v>8033.25</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -33629,75 +33774,78 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>53340</v>
+        <v>17780</v>
       </c>
       <c r="F22" t="n">
-        <v>-2440</v>
+        <v>-38000</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.37</v>
+        <v>-68.12</v>
       </c>
       <c r="H22" t="n">
-        <v>18399200</v>
+        <v>55197600</v>
       </c>
       <c r="I22" t="n">
-        <v>52.8</v>
+        <v>24.3</v>
       </c>
       <c r="J22" t="n">
-        <v>0.62</v>
+        <v>-65.54000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.72</v>
+        <v>1.68</v>
       </c>
       <c r="L22" t="n">
-        <v>-263.87</v>
+        <v>-3100.57</v>
       </c>
       <c r="M22" t="n">
-        <v>-545.55</v>
+        <v>-1112.89</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-2S</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>64355.87</v>
+        <v>63881.73</v>
       </c>
       <c r="Q22" t="n">
-        <v>40902.69</v>
+        <v>40724.89</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>🟡 反発中</t>
+          <t>🔴 下降</t>
         </is>
       </c>
       <c r="S22" t="n">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>E</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
+・🔴 下降
+・MACDは売りシグナルです。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
+・売られ過ぎ水準です。
+・25日線から大きく下に乖離しています。
+・出来高が増加しています。
+・ボリンジャーバンド-2σ付近です。売られすぎから反発する可能性があります。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -33712,7 +33860,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>⚪ 様子見（押し目ではない）</t>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
         </is>
       </c>
     </row>
@@ -33730,10 +33878,10 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>161.1</v>
+        <v>157.1</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2</v>
+        <v>-1.17</v>
       </c>
       <c r="G23" t="n">
         <v>-0.74</v>
@@ -33751,10 +33899,10 @@
         <v>0.99</v>
       </c>
       <c r="L23" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="M23" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -33767,10 +33915,10 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>153.78</v>
+        <v>149.96</v>
       </c>
       <c r="Q23" t="n">
-        <v>151.12</v>
+        <v>147.37</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -33932,31 +34080,31 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>56.22</v>
+        <v>54.98</v>
       </c>
       <c r="F25" t="n">
-        <v>3.14</v>
+        <v>-1.24</v>
       </c>
       <c r="G25" t="n">
-        <v>5.92</v>
+        <v>-2.21</v>
       </c>
       <c r="H25" t="n">
-        <v>1657200</v>
+        <v>1334733</v>
       </c>
       <c r="I25" t="n">
-        <v>58.3</v>
+        <v>56.7</v>
       </c>
       <c r="J25" t="n">
-        <v>10.05</v>
+        <v>7.42</v>
       </c>
       <c r="K25" t="n">
-        <v>1.07</v>
+        <v>0.86</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.74</v>
+        <v>-0.53</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -33969,10 +34117,10 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>58.33</v>
+        <v>58.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>38.86</v>
+        <v>39.02</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -33980,16 +34128,16 @@
         </is>
       </c>
       <c r="S25" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -33998,7 +34146,6 @@
 ・🟡 反発中
 ・MACDは買いシグナルです。
 ・RSIは良好な水準です。
-・25日線から大きく上に乖離しています。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>173,624円</t>
+          <t>173,910円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-35,666円</t>
+          <t>-35,381円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-17.04%</t>
+          <t>-16.91%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3345</v>
+        <v>3375</v>
       </c>
       <c r="F2" t="n">
-        <v>36.4</v>
+        <v>38.9</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.51</v>
+        <v>-1.67</v>
       </c>
       <c r="H2" t="n">
-        <v>0.23</v>
+        <v>0.73</v>
       </c>
       <c r="I2" t="n">
-        <v>3.05</v>
+        <v>5.44</v>
       </c>
       <c r="J2" t="n">
-        <v>23.36</v>
+        <v>23.84</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3092</v>
+        <v>3092.4</v>
       </c>
       <c r="N2" t="n">
-        <v>2736.82</v>
+        <v>2736.97</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -793,22 +793,22 @@
         <v>3340</v>
       </c>
       <c r="X2" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.15</v>
+        <v>1.05</v>
       </c>
       <c r="Z2" t="n">
-        <v>13380</v>
+        <v>13500</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2580</v>
+        <v>2700</v>
       </c>
       <c r="AC2" t="n">
-        <v>23.89</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -829,22 +829,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F3" t="n">
-        <v>45.4</v>
+        <v>46.2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="H3" t="n">
-        <v>0.19</v>
+        <v>0.8</v>
       </c>
       <c r="I3" t="n">
-        <v>6.79</v>
+        <v>6.94</v>
       </c>
       <c r="J3" t="n">
-        <v>7.03</v>
+        <v>7.07</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>437.82</v>
+        <v>437.85</v>
       </c>
       <c r="N3" t="n">
-        <v>416.31</v>
+        <v>416.32</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -906,22 +906,22 @@
         <v>479</v>
       </c>
       <c r="X3" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.84</v>
+        <v>-0.42</v>
       </c>
       <c r="Z3" t="n">
-        <v>47500</v>
+        <v>47700</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>5500</v>
+        <v>5700</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.1</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="4">
@@ -942,19 +942,19 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>171</v>
+        <v>171.3</v>
       </c>
       <c r="F4" t="n">
-        <v>52.1</v>
+        <v>52.7</v>
       </c>
       <c r="G4" t="n">
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
       <c r="H4" t="n">
-        <v>0.46</v>
+        <v>0.97</v>
       </c>
       <c r="I4" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="J4" t="n">
         <v>3.98</v>
@@ -1019,22 +1019,22 @@
         <v>172</v>
       </c>
       <c r="X4" t="n">
-        <v>-1</v>
+        <v>-0.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.58</v>
+        <v>-0.41</v>
       </c>
       <c r="Z4" t="n">
-        <v>17100</v>
+        <v>17130</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1300</v>
+        <v>1330</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.23</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="5">
@@ -1055,22 +1055,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>2901</v>
+        <v>2881.5</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>30.3</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.47</v>
+        <v>-4.09</v>
       </c>
       <c r="H5" t="n">
-        <v>0.44</v>
+        <v>1.06</v>
       </c>
       <c r="I5" t="n">
-        <v>-14.86</v>
+        <v>-16.42</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.62</v>
+        <v>-2.93</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1083,70 +1083,70 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2896.85</v>
+        <v>2896.59</v>
       </c>
       <c r="N5" t="n">
-        <v>3109.82</v>
+        <v>3109.72</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>🟢 上昇</t>
+          <t>🔴 下降</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🔴 売り注意</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟢 上昇
+・🔴 下降
 ・MACDは売りシグナルです。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
+          <t>押し目、-1σ、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>2936.5</v>
       </c>
       <c r="X5" t="n">
-        <v>-35.5</v>
+        <v>-55</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.21</v>
+        <v>-1.87</v>
       </c>
       <c r="Z5" t="n">
-        <v>37713</v>
+        <v>37460</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>614</v>
+        <v>360</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.66</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="6">
@@ -1176,7 +1176,7 @@
         <v>-7.34</v>
       </c>
       <c r="H6" t="n">
-        <v>0.54</v>
+        <v>0.98</v>
       </c>
       <c r="I6" t="n">
         <v>-86.02</v>
@@ -1280,22 +1280,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4674</v>
+        <v>4637</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>38.3</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.06</v>
+        <v>-3.8</v>
       </c>
       <c r="H7" t="n">
-        <v>0.38</v>
+        <v>1.06</v>
       </c>
       <c r="I7" t="n">
-        <v>6.25</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
-        <v>35.77</v>
+        <v>35.18</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1308,70 +1308,70 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4654.39</v>
+        <v>4653.9</v>
       </c>
       <c r="N7" t="n">
-        <v>4646.39</v>
+        <v>4646.2</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>🟢 強い上昇</t>
+          <t>🔴 下降</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🔴 売り注意</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟢 強い上昇
+・🔴 下降
 ・MACDは売りシグナルです。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、長期上昇</t>
+          <t>押し目、-1σ、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W7" t="n">
         <v>4756</v>
       </c>
       <c r="X7" t="n">
-        <v>-82</v>
+        <v>-119</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.72</v>
+        <v>-2.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>23370</v>
+        <v>23185</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>-605</v>
+        <v>-790</v>
       </c>
       <c r="AC7" t="n">
-        <v>-2.52</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="8">
@@ -1392,22 +1392,22 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>8968</v>
+        <v>9117</v>
       </c>
       <c r="F8" t="n">
-        <v>45.5</v>
+        <v>47.1</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.54</v>
+        <v>0.03</v>
       </c>
       <c r="H8" t="n">
-        <v>0.54</v>
+        <v>0.87</v>
       </c>
       <c r="I8" t="n">
-        <v>-304.93</v>
+        <v>-293.05</v>
       </c>
       <c r="J8" t="n">
-        <v>-393.66</v>
+        <v>-391.29</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>12414.85</v>
+        <v>12416.84</v>
       </c>
       <c r="N8" t="n">
-        <v>8061.58</v>
+        <v>8062.32</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1432,11 +1432,11 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1462,29 +1462,29 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>押し目、MACD買い、反発局面</t>
+          <t>25日線上、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W8" t="n">
         <v>9048</v>
       </c>
       <c r="X8" t="n">
-        <v>-80</v>
+        <v>69</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.88</v>
+        <v>0.76</v>
       </c>
       <c r="Z8" t="n">
-        <v>8968</v>
+        <v>9117</v>
       </c>
       <c r="AA8" t="n">
         <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1032</v>
+        <v>-883</v>
       </c>
       <c r="AC8" t="n">
-        <v>-10.32</v>
+        <v>-8.83</v>
       </c>
     </row>
     <row r="9">
@@ -1505,22 +1505,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>17655</v>
+        <v>17880</v>
       </c>
       <c r="F9" t="n">
-        <v>47.3</v>
+        <v>48.5</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.09</v>
+        <v>1.13</v>
       </c>
       <c r="H9" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="I9" t="n">
-        <v>-98.15000000000001</v>
+        <v>-80.2</v>
       </c>
       <c r="J9" t="n">
-        <v>-165.11</v>
+        <v>-161.52</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>21347.58</v>
+        <v>21350.58</v>
       </c>
       <c r="N9" t="n">
-        <v>13707.7</v>
+        <v>13708.83</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1545,11 +1545,11 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1575,29 +1575,29 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>押し目、MACD買い、反発局面</t>
+          <t>25日線上、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
         <v>17780</v>
       </c>
       <c r="X9" t="n">
-        <v>-125</v>
+        <v>100</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>17655</v>
+        <v>17880</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-37855</v>
+        <v>-37630</v>
       </c>
       <c r="AC9" t="n">
-        <v>-68.19</v>
+        <v>-67.79000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1724,7 +1724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1664"/>
+  <dimension ref="A1:C1673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26686,6 +26686,141 @@
         </is>
       </c>
       <c r="C1664" t="n">
+        <v>41.78</v>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1665" t="n">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1666" t="n">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1667" t="n">
+        <v>171.3</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1668" t="n">
+        <v>2881.5</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1669" t="n">
+        <v>7896</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1670" t="n">
+        <v>4637</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1671" t="n">
+        <v>9117</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1672" t="n">
+        <v>17880</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1673" t="n">
         <v>41.78</v>
       </c>
     </row>
@@ -26700,7 +26835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F271"/>
+  <dimension ref="A1:F272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31542,19 +31677,29 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="inlineStr">
+      <c r="A269" t="inlineStr"/>
+      <c r="B269" s="1" t="n">
+        <v>46294.75</v>
+      </c>
+      <c r="C269" t="n">
+        <v>173910</v>
+      </c>
+      <c r="D269" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E269" t="n">
+        <v>-35381</v>
+      </c>
+      <c r="F269" t="n">
+        <v>-16.91</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr"/>
-      <c r="C269" t="inlineStr"/>
-      <c r="D269" t="inlineStr"/>
-      <c r="E269" t="inlineStr"/>
-      <c r="F269" t="inlineStr"/>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr"/>
       <c r="B270" t="inlineStr"/>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr"/>
@@ -31562,16 +31707,24 @@
       <c r="F270" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A271" t="inlineStr"/>
       <c r="B271" t="inlineStr"/>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr"/>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -31736,31 +31889,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="F2" t="n">
-        <v>-37</v>
+        <v>-6</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.66</v>
+        <v>-0.62</v>
       </c>
       <c r="H2" t="n">
-        <v>1360200</v>
+        <v>209600</v>
       </c>
       <c r="I2" t="n">
-        <v>50.4</v>
+        <v>32.1</v>
       </c>
       <c r="J2" t="n">
-        <v>-3.28</v>
+        <v>-3.85</v>
       </c>
       <c r="K2" t="n">
-        <v>1.21</v>
+        <v>0.21</v>
       </c>
       <c r="L2" t="n">
-        <v>16.89</v>
+        <v>12.96</v>
       </c>
       <c r="M2" t="n">
-        <v>28.56</v>
+        <v>25.44</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -31769,14 +31922,14 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>865.52</v>
+        <v>868.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>1109.23</v>
+        <v>1107.27</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -31784,16 +31937,16 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -31801,8 +31954,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
@@ -31837,31 +31989,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3340</v>
+        <v>3345</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="H3" t="n">
-        <v>69700</v>
+        <v>14600</v>
       </c>
       <c r="I3" t="n">
-        <v>43.1</v>
+        <v>36.4</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.74</v>
+        <v>-2.51</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9</v>
+        <v>0.23</v>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="M3" t="n">
-        <v>28.44</v>
+        <v>23.36</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -31874,10 +32026,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3079.39</v>
+        <v>3092</v>
       </c>
       <c r="Q3" t="n">
-        <v>2734.1</v>
+        <v>2736.82</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -31937,31 +32089,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1405</v>
+        <v>1451</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="G4" t="n">
-        <v>1.08</v>
+        <v>3.27</v>
       </c>
       <c r="H4" t="n">
-        <v>29100</v>
+        <v>12700</v>
       </c>
       <c r="I4" t="n">
-        <v>58.5</v>
+        <v>56.8</v>
       </c>
       <c r="J4" t="n">
-        <v>5.87</v>
+        <v>8.59</v>
       </c>
       <c r="K4" t="n">
-        <v>1.52</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>36.78</v>
+        <v>41.27</v>
       </c>
       <c r="M4" t="n">
-        <v>36.96</v>
+        <v>37.83</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -31974,10 +32126,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1217.98</v>
+        <v>1221.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>1635.85</v>
+        <v>1634.94</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -31985,7 +32137,7 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -32001,9 +32153,8 @@
         <is>
           <t>【AI分析レポート】
 ・🟢 上昇
-・MACDは売りシグナルです。
+・MACDは買いシグナルです。
 ・RSIは良好な水準です。
-・出来高が増加しています。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -32039,31 +32190,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3710</v>
+        <v>3650</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>-60</v>
       </c>
       <c r="G5" t="n">
-        <v>0.95</v>
+        <v>-1.62</v>
       </c>
       <c r="H5" t="n">
-        <v>25800</v>
+        <v>4700</v>
       </c>
       <c r="I5" t="n">
-        <v>66.09999999999999</v>
+        <v>51</v>
       </c>
       <c r="J5" t="n">
-        <v>6.84</v>
+        <v>4.92</v>
       </c>
       <c r="K5" t="n">
-        <v>1.22</v>
+        <v>0.22</v>
       </c>
       <c r="L5" t="n">
-        <v>43</v>
+        <v>48.66</v>
       </c>
       <c r="M5" t="n">
-        <v>19.36</v>
+        <v>25.22</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -32072,14 +32223,14 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>+2S</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3432.2</v>
+        <v>3435.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>3170.59</v>
+        <v>3175.8</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -32087,7 +32238,7 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -32104,7 +32255,8 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+・RSIは良好な水準です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -32139,31 +32291,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1581</v>
+        <v>1560</v>
       </c>
       <c r="F6" t="n">
-        <v>-42</v>
+        <v>-21</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.59</v>
+        <v>-1.33</v>
       </c>
       <c r="H6" t="n">
-        <v>92800</v>
+        <v>12300</v>
       </c>
       <c r="I6" t="n">
-        <v>65.2</v>
+        <v>51.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1.86</v>
+        <v>0.65</v>
       </c>
       <c r="K6" t="n">
-        <v>1.21</v>
+        <v>0.19</v>
       </c>
       <c r="L6" t="n">
-        <v>-7.26</v>
+        <v>-7.29</v>
       </c>
       <c r="M6" t="n">
-        <v>-20.65</v>
+        <v>-17.98</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -32176,10 +32328,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1667.25</v>
+        <v>1664.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>1690.76</v>
+        <v>1689.14</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -32187,7 +32339,7 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -32200,106 +32352,6 @@
         </is>
       </c>
       <c r="V6" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは買いシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>4054.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>日本情報クリエイト</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>不動産向けクラウド</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>523</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="H7" t="n">
-        <v>17400</v>
-      </c>
-      <c r="I7" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-4.24</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-5.78</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>538.48</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>577.9400000000001</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>60</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🔴 下降
@@ -32310,6 +32362,108 @@
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4054.T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>日本情報クリエイト</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>不動産向けクラウド</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>522</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2100</v>
+      </c>
+      <c r="I7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-3.89</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>538.61</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>576.86</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>75</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは買いシグナルです。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
@@ -32340,31 +32494,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1121</v>
+        <v>1110</v>
       </c>
       <c r="F8" t="n">
-        <v>41</v>
+        <v>-11</v>
       </c>
       <c r="G8" t="n">
-        <v>3.8</v>
+        <v>-0.98</v>
       </c>
       <c r="H8" t="n">
-        <v>7100</v>
+        <v>300</v>
       </c>
       <c r="I8" t="n">
-        <v>56.3</v>
+        <v>49.1</v>
       </c>
       <c r="J8" t="n">
-        <v>0.19</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>1.71</v>
+        <v>0.08</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.98</v>
+        <v>-3.69</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.45</v>
+        <v>-3.5</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -32377,10 +32531,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1062.39</v>
+        <v>1063.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>1015.8</v>
+        <v>1014.86</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -32388,427 +32542,19 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・出来高が増加しています。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>7033.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>マネジメントソリューションズ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PMO支援・DX案件増加</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1558</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-33</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-2.07</v>
-      </c>
-      <c r="H9" t="n">
-        <v>60600</v>
-      </c>
-      <c r="I9" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-3.54</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="M9" t="n">
-        <v>12.96</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>1467.71</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1387.12</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>65</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9342.T</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>スマサポ</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>不動産DX</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>953</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-18</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-1.85</v>
-      </c>
-      <c r="H10" t="n">
-        <v>10500</v>
-      </c>
-      <c r="I10" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-1.92</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="L10" t="n">
-        <v>9.58</v>
-      </c>
-      <c r="M10" t="n">
-        <v>16.22</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>DC</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>887.89</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>986.64</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>50</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
-・出来高が急増しています。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>🟡 調整中押し目（段階的買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>6971.T</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>京セラ</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>自社株</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>3675</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-60.54</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-1.62</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4858400</v>
-      </c>
-      <c r="I11" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="L11" t="n">
-        <v>6.82</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-22.59</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>3632.27</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2951.33</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>100</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは買いシグナルです。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2026/10/29</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>あと31日</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>3778.T</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>さくらインターネット(株)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="n">
-        <v>3730</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-20</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="H12" t="n">
-        <v>533900</v>
-      </c>
-      <c r="I12" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="L12" t="n">
-        <v>64.84999999999999</v>
-      </c>
-      <c r="M12" t="n">
-        <v>73.11</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>3267.12</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3073.78</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S12" t="n">
-        <v>95</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -32819,11 +32565,417 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7033.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>マネジメントソリューションズ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PMO支援・DX案件増加</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1560</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H9" t="n">
+        <v>13800</v>
+      </c>
+      <c r="I9" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-3.05</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="M9" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1470.52</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1388.41</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>65</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9342.T</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>スマサポ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>不動産DX</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>912</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-41</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I10" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-6.04</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="M10" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>-2S</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>889.75</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>986.4400000000001</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>80</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・売られ過ぎ水準です。
+・ボリンジャーバンド-2σ付近です。売られすぎから反発する可能性があります。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6971.T</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>京セラ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>自社株</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3686</v>
+      </c>
+      <c r="F11" t="n">
+        <v>11</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>864100</v>
+      </c>
+      <c r="I11" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="L11" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-15.27</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>3633.42</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2959.39</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>100</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは買いシグナルです。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026/10/29</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>あと30日</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3778.T</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>さくらインターネット(株)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>3635</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-95</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="H12" t="n">
+        <v>233300</v>
+      </c>
+      <c r="I12" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L12" t="n">
+        <v>53.77</v>
+      </c>
+      <c r="M12" t="n">
+        <v>69.23999999999999</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>3279.17</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3076.21</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>65</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>⚪ 様子見（押し目ではない）</t>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -32845,31 +32997,31 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>4938</v>
+        <v>4923</v>
       </c>
       <c r="F13" t="n">
-        <v>-28.89</v>
+        <v>-15</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.58</v>
+        <v>-0.3</v>
       </c>
       <c r="H13" t="n">
-        <v>26464800</v>
+        <v>13577700</v>
       </c>
       <c r="I13" t="n">
-        <v>50.2</v>
+        <v>47</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.24</v>
+        <v>-3.23</v>
       </c>
       <c r="K13" t="n">
-        <v>0.85</v>
+        <v>0.49</v>
       </c>
       <c r="L13" t="n">
-        <v>-71.03</v>
+        <v>-69.34</v>
       </c>
       <c r="M13" t="n">
-        <v>-51</v>
+        <v>-54.67</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -32882,10 +33034,10 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5060.5</v>
+        <v>5066.39</v>
       </c>
       <c r="Q13" t="n">
-        <v>4516.38</v>
+        <v>4527.49</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -32893,16 +33045,16 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -32923,7 +33075,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>あと43日</t>
+          <t>あと42日</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -32954,31 +33106,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1052</v>
+        <v>1037</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.69</v>
+        <v>-15</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.91</v>
+        <v>-1.43</v>
       </c>
       <c r="H14" t="n">
-        <v>747900</v>
+        <v>274300</v>
       </c>
       <c r="I14" t="n">
-        <v>38.6</v>
+        <v>40.1</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.72</v>
+        <v>-4.8</v>
       </c>
       <c r="K14" t="n">
-        <v>2.07</v>
+        <v>0.76</v>
       </c>
       <c r="L14" t="n">
-        <v>-15.08</v>
+        <v>-15.68</v>
       </c>
       <c r="M14" t="n">
-        <v>-13.37</v>
+        <v>-13.83</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -32991,10 +33143,10 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1084.37</v>
+        <v>1085.64</v>
       </c>
       <c r="Q14" t="n">
-        <v>906.15</v>
+        <v>907.59</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -33002,16 +33154,16 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -33019,7 +33171,6 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは売りシグナルです。
-・出来高が急増しています。
 ・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
@@ -33055,31 +33206,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3774</v>
+        <v>3685</v>
       </c>
       <c r="F15" t="n">
-        <v>-40.88</v>
+        <v>-89</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.07</v>
+        <v>-2.36</v>
       </c>
       <c r="H15" t="n">
-        <v>15361700</v>
+        <v>10275100</v>
       </c>
       <c r="I15" t="n">
-        <v>55</v>
+        <v>45.3</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.83</v>
+        <v>-3.98</v>
       </c>
       <c r="K15" t="n">
-        <v>0.78</v>
+        <v>0.6</v>
       </c>
       <c r="L15" t="n">
-        <v>-10.18</v>
+        <v>-20.45</v>
       </c>
       <c r="M15" t="n">
-        <v>0.39</v>
+        <v>-3.78</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -33088,14 +33239,14 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3931.08</v>
+        <v>3918.39</v>
       </c>
       <c r="Q15" t="n">
-        <v>3230.17</v>
+        <v>3243.84</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -33103,16 +33254,16 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -33121,7 +33272,7 @@
 ・🟡 反発中
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
@@ -33133,7 +33284,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>あと42日</t>
+          <t>あと41日</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -33160,31 +33311,31 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>4475</v>
+        <v>4790</v>
       </c>
       <c r="F16" t="n">
-        <v>-125</v>
+        <v>315</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.72</v>
+        <v>7.04</v>
       </c>
       <c r="H16" t="n">
-        <v>49700</v>
+        <v>51800</v>
       </c>
       <c r="I16" t="n">
-        <v>66</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>8.6</v>
+        <v>15.29</v>
       </c>
       <c r="K16" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="L16" t="n">
-        <v>119.18</v>
+        <v>157.12</v>
       </c>
       <c r="M16" t="n">
-        <v>79.72</v>
+        <v>95.2</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -33193,14 +33344,14 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>+2S</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3656.12</v>
+        <v>3681.21</v>
       </c>
       <c r="Q16" t="n">
-        <v>2897.51</v>
+        <v>2911.41</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -33208,16 +33359,16 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -33225,7 +33376,8 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・25日線から大きく上に乖離しています。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -33256,31 +33408,31 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>2380</v>
+        <v>2340</v>
       </c>
       <c r="F17" t="n">
-        <v>-7.93</v>
+        <v>-40.5</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.33</v>
+        <v>-1.7</v>
       </c>
       <c r="H17" t="n">
-        <v>6041400</v>
+        <v>3092000</v>
       </c>
       <c r="I17" t="n">
-        <v>44.3</v>
+        <v>42.1</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.95</v>
+        <v>-4.11</v>
       </c>
       <c r="K17" t="n">
-        <v>0.68</v>
+        <v>0.43</v>
       </c>
       <c r="L17" t="n">
-        <v>-70.73</v>
+        <v>-69.77</v>
       </c>
       <c r="M17" t="n">
-        <v>-82.70999999999999</v>
+        <v>-80.12</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -33289,14 +33441,14 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2694.76</v>
+        <v>2689</v>
       </c>
       <c r="Q17" t="n">
-        <v>2815.11</v>
+        <v>2817.1</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -33304,7 +33456,7 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -33321,7 +33473,7 @@
           <t>【AI分析レポート】
 ・🔴 下降
 ・MACDは買いシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 ⚠️ 下落トレンドです。
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
@@ -33333,7 +33485,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>あと44日</t>
+          <t>あと43日</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -33364,31 +33516,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2937</v>
+        <v>2901</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.95</v>
+        <v>-35.5</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1</v>
+        <v>-1.21</v>
       </c>
       <c r="H18" t="n">
-        <v>26063800</v>
+        <v>12411600</v>
       </c>
       <c r="I18" t="n">
         <v>32</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.43</v>
+        <v>-3.47</v>
       </c>
       <c r="K18" t="n">
-        <v>0.88</v>
+        <v>0.44</v>
       </c>
       <c r="L18" t="n">
-        <v>-10.59</v>
+        <v>-14.86</v>
       </c>
       <c r="M18" t="n">
-        <v>0.45</v>
+        <v>-2.62</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -33401,10 +33553,10 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2895.27</v>
+        <v>2896.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>3110.24</v>
+        <v>3109.82</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -33441,7 +33593,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>あと38日</t>
+          <t>あと37日</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -33468,35 +33620,35 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>1768</v>
+        <v>1750</v>
       </c>
       <c r="F19" t="n">
-        <v>-9.890000000000001</v>
+        <v>-18</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.02</v>
       </c>
       <c r="H19" t="n">
-        <v>11877200</v>
+        <v>2702400</v>
       </c>
       <c r="I19" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.39</v>
+        <v>-1.55</v>
       </c>
       <c r="K19" t="n">
-        <v>0.97</v>
+        <v>0.25</v>
       </c>
       <c r="L19" t="n">
-        <v>14.54</v>
+        <v>11.17</v>
       </c>
       <c r="M19" t="n">
-        <v>23.63</v>
+        <v>21.14</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -33505,10 +33657,10 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1662.53</v>
+        <v>1664.22</v>
       </c>
       <c r="Q19" t="n">
-        <v>1561.92</v>
+        <v>1564.75</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -33516,16 +33668,16 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -33533,6 +33685,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -33545,12 +33698,12 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>あと31日</t>
+          <t>あと30日</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
+          <t>🟡 調整中押し目（段階的買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -33576,31 +33729,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="G20" t="n">
-        <v>0.42</v>
+        <v>-0.84</v>
       </c>
       <c r="H20" t="n">
-        <v>388300</v>
+        <v>86800</v>
       </c>
       <c r="I20" t="n">
-        <v>57.7</v>
+        <v>45.4</v>
       </c>
       <c r="J20" t="n">
-        <v>1.19</v>
+        <v>0.45</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.19</v>
       </c>
       <c r="L20" t="n">
-        <v>7.45</v>
+        <v>6.79</v>
       </c>
       <c r="M20" t="n">
-        <v>7.1</v>
+        <v>7.03</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -33613,10 +33766,10 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>436.81</v>
+        <v>437.82</v>
       </c>
       <c r="Q20" t="n">
-        <v>415.73</v>
+        <v>416.31</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -33624,23 +33777,23 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
-・MACDは買いシグナルです。
+・MACDは売りシグナルです。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
@@ -33673,31 +33826,31 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>9048</v>
+        <v>8968</v>
       </c>
       <c r="F21" t="n">
-        <v>-66.67</v>
+        <v>-80</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.73</v>
+        <v>-0.88</v>
       </c>
       <c r="H21" t="n">
-        <v>23526900</v>
+        <v>12650500</v>
       </c>
       <c r="I21" t="n">
-        <v>52.3</v>
+        <v>45.5</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.92</v>
+        <v>-1.54</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9</v>
+        <v>0.54</v>
       </c>
       <c r="L21" t="n">
-        <v>-316.61</v>
+        <v>-304.93</v>
       </c>
       <c r="M21" t="n">
-        <v>-415.85</v>
+        <v>-393.66</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -33710,10 +33863,10 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>12533.76</v>
+        <v>12414.85</v>
       </c>
       <c r="Q21" t="n">
-        <v>8033.25</v>
+        <v>8061.58</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -33721,16 +33874,16 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -33751,7 +33904,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>あと38日</t>
+          <t>あと37日</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -33774,78 +33927,75 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>17780</v>
+        <v>17655</v>
       </c>
       <c r="F22" t="n">
-        <v>-38000</v>
+        <v>-125</v>
       </c>
       <c r="G22" t="n">
-        <v>-68.12</v>
+        <v>-0.7</v>
       </c>
       <c r="H22" t="n">
-        <v>55197600</v>
+        <v>23177900</v>
       </c>
       <c r="I22" t="n">
-        <v>24.3</v>
+        <v>47.3</v>
       </c>
       <c r="J22" t="n">
-        <v>-65.54000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="K22" t="n">
-        <v>1.68</v>
+        <v>0.35</v>
       </c>
       <c r="L22" t="n">
-        <v>-3100.57</v>
+        <v>-98.15000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-1112.89</v>
+        <v>-165.11</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>-2S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>63881.73</v>
+        <v>21347.58</v>
       </c>
       <c r="Q22" t="n">
-        <v>40724.89</v>
+        <v>13707.7</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>🔴 下降</t>
+          <t>🟡 反発中</t>
         </is>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🔴 下降
-・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
-・売られ過ぎ水準です。
-・25日線から大きく下に乖離しています。
-・出来高が増加しています。
-・ボリンジャーバンド-2σ付近です。売られすぎから反発する可能性があります。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
+・🟡 反発中
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -33855,12 +34005,12 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>あと32日</t>
+          <t>あと31日</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -33878,35 +34028,35 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>157.1</v>
+        <v>158</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.17</v>
+        <v>0.9</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.74</v>
+        <v>0.57</v>
       </c>
       <c r="H23" t="n">
-        <v>61369000</v>
+        <v>27136500</v>
       </c>
       <c r="I23" t="n">
-        <v>45.1</v>
+        <v>43.8</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.31</v>
+        <v>0.14</v>
       </c>
       <c r="K23" t="n">
-        <v>0.99</v>
+        <v>0.48</v>
       </c>
       <c r="L23" t="n">
-        <v>1.02</v>
+        <v>0.97</v>
       </c>
       <c r="M23" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -33915,10 +34065,10 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>149.96</v>
+        <v>150.16</v>
       </c>
       <c r="Q23" t="n">
-        <v>147.37</v>
+        <v>147.45</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -33926,16 +34076,16 @@
         </is>
       </c>
       <c r="S23" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -33943,7 +34093,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・RSIは良好な水準です。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -33956,12 +34106,12 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>あと45日</t>
+          <t>あと44日</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
+          <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
@@ -33979,31 +34129,31 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>3459</v>
+        <v>3434</v>
       </c>
       <c r="F24" t="n">
-        <v>-19</v>
+        <v>-25</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.55</v>
+        <v>-0.72</v>
       </c>
       <c r="H24" t="n">
-        <v>9179300</v>
+        <v>3148600</v>
       </c>
       <c r="I24" t="n">
-        <v>58.3</v>
+        <v>56.5</v>
       </c>
       <c r="J24" t="n">
-        <v>3.73</v>
+        <v>3.02</v>
       </c>
       <c r="K24" t="n">
-        <v>0.77</v>
+        <v>0.3</v>
       </c>
       <c r="L24" t="n">
-        <v>-60.77</v>
+        <v>-49.48</v>
       </c>
       <c r="M24" t="n">
-        <v>-111.04</v>
+        <v>-98.73</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -34012,14 +34162,14 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3942.76</v>
+        <v>3929.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>3226.26</v>
+        <v>3234.49</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -34040,6 +34190,107 @@
         </is>
       </c>
       <c r="V24" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>2026/10/28</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>あと29日</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PENG</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ペンギン・ソリューションズ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>54.98</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1337400</v>
+      </c>
+      <c r="I25" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>95</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -34050,107 +34301,6 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>2026/10/28</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>あと30日</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>PENG</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ペンギン・ソリューションズ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="n">
-        <v>54.98</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-1.24</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-2.21</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1334733</v>
-      </c>
-      <c r="I25" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="J25" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>58.28</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>39.02</v>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S25" t="n">
-        <v>95</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="W25" t="inlineStr">
         <is>
           <t>2026/10/06</t>
@@ -34158,7 +34308,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>あと8日</t>
+          <t>あと7日</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -34181,31 +34331,31 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>7999</v>
+        <v>7896</v>
       </c>
       <c r="F26" t="n">
-        <v>-101</v>
+        <v>-103</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.25</v>
+        <v>-1.29</v>
       </c>
       <c r="H26" t="n">
-        <v>8814400</v>
+        <v>3407600</v>
       </c>
       <c r="I26" t="n">
-        <v>29.9</v>
+        <v>28.7</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.52</v>
+        <v>-7.34</v>
       </c>
       <c r="K26" t="n">
-        <v>1.24</v>
+        <v>0.54</v>
       </c>
       <c r="L26" t="n">
-        <v>-60.5</v>
+        <v>-86.02</v>
       </c>
       <c r="M26" t="n">
-        <v>21.43</v>
+        <v>-0.06</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -34218,10 +34368,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7792.25</v>
+        <v>7794.36</v>
       </c>
       <c r="Q26" t="n">
-        <v>8604.889999999999</v>
+        <v>8580.299999999999</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -34259,7 +34409,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>あと38日</t>
+          <t>あと37日</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>173,910円</t>
+          <t>173,909円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-35,381円</t>
+          <t>-35,382円</t>
         </is>
       </c>
     </row>
@@ -1618,22 +1618,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>41.78</v>
+        <v>41.02</v>
       </c>
       <c r="F10" t="n">
-        <v>53.5</v>
+        <v>54.9</v>
       </c>
       <c r="G10" t="n">
-        <v>7.56</v>
+        <v>4.97</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="I10" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="J10" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1642,14 +1642,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.27</v>
+        <v>33.39</v>
       </c>
       <c r="N10" t="n">
-        <v>31.83</v>
+        <v>31.86</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -1688,29 +1688,29 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+1σ、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>43.26</v>
+        <v>41.78</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.48</v>
+        <v>-0.76</v>
       </c>
       <c r="Y10" t="n">
-        <v>-3.42</v>
+        <v>-1.82</v>
       </c>
       <c r="Z10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6071</v>
+        <v>-6072</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.31999999999999</v>
+        <v>-99.33</v>
       </c>
     </row>
   </sheetData>
@@ -1724,7 +1724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1673"/>
+  <dimension ref="A1:C1682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26822,6 +26822,141 @@
       </c>
       <c r="C1673" t="n">
         <v>41.78</v>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1674" t="n">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1675" t="n">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1676" t="n">
+        <v>171.3</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1677" t="n">
+        <v>2881.5</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1678" t="n">
+        <v>7896</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1679" t="n">
+        <v>4637</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1680" t="n">
+        <v>9117</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1681" t="n">
+        <v>17880</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1682" t="n">
+        <v>41.02</v>
       </c>
     </row>
   </sheetData>
@@ -26835,7 +26970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F272"/>
+  <dimension ref="A1:F273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31695,19 +31830,29 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="inlineStr">
+      <c r="A270" t="inlineStr"/>
+      <c r="B270" s="1" t="n">
+        <v>46295.29236111111</v>
+      </c>
+      <c r="C270" t="n">
+        <v>173909</v>
+      </c>
+      <c r="D270" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E270" t="n">
+        <v>-35382</v>
+      </c>
+      <c r="F270" t="n">
+        <v>-16.91</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr"/>
-      <c r="C270" t="inlineStr"/>
-      <c r="D270" t="inlineStr"/>
-      <c r="E270" t="inlineStr"/>
-      <c r="F270" t="inlineStr"/>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr"/>
       <c r="B271" t="inlineStr"/>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr"/>
@@ -31715,16 +31860,24 @@
       <c r="F271" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A272" t="inlineStr"/>
       <c r="B272" t="inlineStr"/>
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr"/>
+      <c r="C273" t="inlineStr"/>
+      <c r="D273" t="inlineStr"/>
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -31889,31 +32042,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>967</v>
+        <v>977</v>
       </c>
       <c r="F2" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.62</v>
+        <v>0.41</v>
       </c>
       <c r="H2" t="n">
-        <v>209600</v>
+        <v>572500</v>
       </c>
       <c r="I2" t="n">
-        <v>32.1</v>
+        <v>34.3</v>
       </c>
       <c r="J2" t="n">
-        <v>-3.85</v>
+        <v>-2.9</v>
       </c>
       <c r="K2" t="n">
-        <v>0.21</v>
+        <v>0.53</v>
       </c>
       <c r="L2" t="n">
-        <v>12.96</v>
+        <v>13.75</v>
       </c>
       <c r="M2" t="n">
-        <v>25.44</v>
+        <v>25.6</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -31922,14 +32075,14 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>868.6</v>
+        <v>868.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>1107.27</v>
+        <v>1107.32</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -31937,7 +32090,7 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -31954,7 +32107,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
@@ -31989,31 +32142,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3345</v>
+        <v>3375</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="G3" t="n">
-        <v>0.15</v>
+        <v>1.05</v>
       </c>
       <c r="H3" t="n">
-        <v>14600</v>
+        <v>50600</v>
       </c>
       <c r="I3" t="n">
-        <v>36.4</v>
+        <v>38.9</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.51</v>
+        <v>-1.67</v>
       </c>
       <c r="K3" t="n">
-        <v>0.23</v>
+        <v>0.73</v>
       </c>
       <c r="L3" t="n">
-        <v>3.05</v>
+        <v>5.44</v>
       </c>
       <c r="M3" t="n">
-        <v>23.36</v>
+        <v>23.84</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -32026,10 +32179,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3092</v>
+        <v>3092.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>2736.82</v>
+        <v>2736.97</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -32089,31 +32242,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1451</v>
+        <v>1462</v>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G4" t="n">
-        <v>3.27</v>
+        <v>4.06</v>
       </c>
       <c r="H4" t="n">
-        <v>12700</v>
+        <v>32200</v>
       </c>
       <c r="I4" t="n">
-        <v>56.8</v>
+        <v>58.3</v>
       </c>
       <c r="J4" t="n">
-        <v>8.59</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.64</v>
       </c>
       <c r="L4" t="n">
-        <v>41.27</v>
+        <v>42.14</v>
       </c>
       <c r="M4" t="n">
-        <v>37.83</v>
+        <v>38</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -32126,10 +32279,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1221.66</v>
+        <v>1221.81</v>
       </c>
       <c r="Q4" t="n">
-        <v>1634.94</v>
+        <v>1634.99</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -32155,6 +32308,7 @@
 ・🟢 上昇
 ・MACDは買いシグナルです。
 ・RSIは良好な水準です。
+・出来高が増加しています。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -32190,31 +32344,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3650</v>
+        <v>3595</v>
       </c>
       <c r="F5" t="n">
-        <v>-60</v>
+        <v>-115</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.62</v>
+        <v>-3.1</v>
       </c>
       <c r="H5" t="n">
-        <v>4700</v>
+        <v>13500</v>
       </c>
       <c r="I5" t="n">
-        <v>51</v>
+        <v>47.4</v>
       </c>
       <c r="J5" t="n">
-        <v>4.92</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0.22</v>
+        <v>0.59</v>
       </c>
       <c r="L5" t="n">
-        <v>48.66</v>
+        <v>44.27</v>
       </c>
       <c r="M5" t="n">
-        <v>25.22</v>
+        <v>24.34</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -32227,10 +32381,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3435.67</v>
+        <v>3434.93</v>
       </c>
       <c r="Q5" t="n">
-        <v>3175.8</v>
+        <v>3175.53</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -32238,7 +32392,7 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -32291,31 +32445,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1560</v>
+        <v>1554</v>
       </c>
       <c r="F6" t="n">
-        <v>-21</v>
+        <v>-27</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.33</v>
+        <v>-1.71</v>
       </c>
       <c r="H6" t="n">
-        <v>12300</v>
+        <v>35300</v>
       </c>
       <c r="I6" t="n">
-        <v>51.8</v>
+        <v>50.4</v>
       </c>
       <c r="J6" t="n">
-        <v>0.65</v>
+        <v>0.28</v>
       </c>
       <c r="K6" t="n">
-        <v>0.19</v>
+        <v>0.5</v>
       </c>
       <c r="L6" t="n">
-        <v>-7.29</v>
+        <v>-7.76</v>
       </c>
       <c r="M6" t="n">
-        <v>-17.98</v>
+        <v>-18.08</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -32328,10 +32482,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1664.12</v>
+        <v>1664.04</v>
       </c>
       <c r="Q6" t="n">
-        <v>1689.14</v>
+        <v>1689.11</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -32401,7 +32555,7 @@
         <v>-0.19</v>
       </c>
       <c r="H7" t="n">
-        <v>2100</v>
+        <v>5800</v>
       </c>
       <c r="I7" t="n">
         <v>50</v>
@@ -32410,7 +32564,7 @@
         <v>0.01</v>
       </c>
       <c r="K7" t="n">
-        <v>0.16</v>
+        <v>0.41</v>
       </c>
       <c r="L7" t="n">
         <v>-3.89</v>
@@ -32494,31 +32648,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1110</v>
+        <v>1105</v>
       </c>
       <c r="F8" t="n">
-        <v>-11</v>
+        <v>-16</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.98</v>
+        <v>-1.43</v>
       </c>
       <c r="H8" t="n">
-        <v>300</v>
+        <v>1800</v>
       </c>
       <c r="I8" t="n">
-        <v>49.1</v>
+        <v>47.6</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.99</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08</v>
+        <v>0.45</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.69</v>
+        <v>-4.09</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.5</v>
+        <v>-3.58</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -32531,10 +32685,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1063.33</v>
+        <v>1063.27</v>
       </c>
       <c r="Q8" t="n">
-        <v>1014.86</v>
+        <v>1014.84</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -32595,31 +32749,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1560</v>
+        <v>1545</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>-13</v>
       </c>
       <c r="G9" t="n">
-        <v>0.13</v>
+        <v>-0.83</v>
       </c>
       <c r="H9" t="n">
-        <v>13800</v>
+        <v>51600</v>
       </c>
       <c r="I9" t="n">
-        <v>39.1</v>
+        <v>37</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.05</v>
+        <v>-3.94</v>
       </c>
       <c r="K9" t="n">
-        <v>0.11</v>
+        <v>0.39</v>
       </c>
       <c r="L9" t="n">
-        <v>3.24</v>
+        <v>2.04</v>
       </c>
       <c r="M9" t="n">
-        <v>11.01</v>
+        <v>10.77</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -32628,14 +32782,14 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1470.52</v>
+        <v>1470.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>1388.41</v>
+        <v>1388.34</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -32643,7 +32797,7 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -32660,7 +32814,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -32695,31 +32849,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>912</v>
+        <v>875</v>
       </c>
       <c r="F10" t="n">
-        <v>-41</v>
+        <v>-78</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.3</v>
+        <v>-8.18</v>
       </c>
       <c r="H10" t="n">
-        <v>4500</v>
+        <v>7400</v>
       </c>
       <c r="I10" t="n">
-        <v>20.2</v>
+        <v>15.7</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.04</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.92</v>
+        <v>1.36</v>
       </c>
       <c r="L10" t="n">
-        <v>4.16</v>
+        <v>1.21</v>
       </c>
       <c r="M10" t="n">
-        <v>13.81</v>
+        <v>13.22</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -32732,45 +32886,45 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>889.75</v>
+        <v>889.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>986.4400000000001</v>
+        <v>986.25</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>🟢 上昇</t>
+          <t>🔴 下降</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟢 上昇
+・🔴 下降
 ・MACDは売りシグナルです。
 ・売られ過ぎ水準です。
 ・ボリンジャーバンド-2σ付近です。売られすぎから反発する可能性があります。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
         </is>
       </c>
     </row>
@@ -32796,31 +32950,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3686</v>
+        <v>3685</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="H11" t="n">
-        <v>864100</v>
+        <v>4482800</v>
       </c>
       <c r="I11" t="n">
-        <v>63.7</v>
+        <v>63.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="K11" t="n">
-        <v>0.19</v>
+        <v>0.84</v>
       </c>
       <c r="L11" t="n">
-        <v>13.98</v>
+        <v>13.9</v>
       </c>
       <c r="M11" t="n">
-        <v>-15.27</v>
+        <v>-15.29</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -32833,10 +32987,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3633.42</v>
+        <v>3633.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>2959.39</v>
+        <v>2959.38</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -32900,31 +33054,31 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>3635</v>
+        <v>3595</v>
       </c>
       <c r="F12" t="n">
-        <v>-95</v>
+        <v>-135</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.55</v>
+        <v>-3.62</v>
       </c>
       <c r="H12" t="n">
-        <v>233300</v>
+        <v>560700</v>
       </c>
       <c r="I12" t="n">
-        <v>49.4</v>
+        <v>47.7</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.05</v>
+        <v>-2.09</v>
       </c>
       <c r="K12" t="n">
-        <v>0.42</v>
+        <v>0.91</v>
       </c>
       <c r="L12" t="n">
-        <v>53.77</v>
+        <v>50.58</v>
       </c>
       <c r="M12" t="n">
-        <v>69.23999999999999</v>
+        <v>68.61</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -32937,10 +33091,10 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3279.17</v>
+        <v>3278.64</v>
       </c>
       <c r="Q12" t="n">
-        <v>3076.21</v>
+        <v>3076.01</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -32997,31 +33151,31 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>4923</v>
+        <v>4931</v>
       </c>
       <c r="F13" t="n">
-        <v>-15</v>
+        <v>-7</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3</v>
+        <v>-0.14</v>
       </c>
       <c r="H13" t="n">
-        <v>13577700</v>
+        <v>24796700</v>
       </c>
       <c r="I13" t="n">
-        <v>47</v>
+        <v>47.2</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.23</v>
+        <v>-3.08</v>
       </c>
       <c r="K13" t="n">
-        <v>0.49</v>
+        <v>0.83</v>
       </c>
       <c r="L13" t="n">
-        <v>-69.34</v>
+        <v>-68.7</v>
       </c>
       <c r="M13" t="n">
-        <v>-54.67</v>
+        <v>-54.54</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -33034,10 +33188,10 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5066.39</v>
+        <v>5066.49</v>
       </c>
       <c r="Q13" t="n">
-        <v>4527.49</v>
+        <v>4527.53</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -33106,31 +33260,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1037</v>
+        <v>1027</v>
       </c>
       <c r="F14" t="n">
-        <v>-15</v>
+        <v>-25</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.43</v>
+        <v>-2.38</v>
       </c>
       <c r="H14" t="n">
-        <v>274300</v>
+        <v>656700</v>
       </c>
       <c r="I14" t="n">
-        <v>40.1</v>
+        <v>37.8</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.8</v>
+        <v>-5.68</v>
       </c>
       <c r="K14" t="n">
-        <v>0.76</v>
+        <v>1.5</v>
       </c>
       <c r="L14" t="n">
-        <v>-15.68</v>
+        <v>-16.47</v>
       </c>
       <c r="M14" t="n">
-        <v>-13.83</v>
+        <v>-13.99</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -33139,14 +33293,14 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1085.64</v>
+        <v>1085.51</v>
       </c>
       <c r="Q14" t="n">
-        <v>907.59</v>
+        <v>907.54</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -33154,16 +33308,16 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -33171,7 +33325,8 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
+・出来高が増加しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
@@ -33206,31 +33361,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3685</v>
+        <v>3684</v>
       </c>
       <c r="F15" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.36</v>
+        <v>-2.38</v>
       </c>
       <c r="H15" t="n">
-        <v>10275100</v>
+        <v>17735900</v>
       </c>
       <c r="I15" t="n">
         <v>45.3</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.98</v>
+        <v>-4</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6</v>
+        <v>0.95</v>
       </c>
       <c r="L15" t="n">
-        <v>-20.45</v>
+        <v>-20.53</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.78</v>
+        <v>-3.79</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -33243,7 +33398,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3918.39</v>
+        <v>3918.38</v>
       </c>
       <c r="Q15" t="n">
         <v>3243.84</v>
@@ -33311,31 +33466,31 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>4790</v>
+        <v>4795</v>
       </c>
       <c r="F16" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="G16" t="n">
-        <v>7.04</v>
+        <v>7.15</v>
       </c>
       <c r="H16" t="n">
-        <v>51800</v>
+        <v>76800</v>
       </c>
       <c r="I16" t="n">
-        <v>69.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="J16" t="n">
-        <v>15.29</v>
+        <v>15.41</v>
       </c>
       <c r="K16" t="n">
-        <v>1.15</v>
+        <v>1.53</v>
       </c>
       <c r="L16" t="n">
-        <v>157.12</v>
+        <v>157.52</v>
       </c>
       <c r="M16" t="n">
-        <v>95.2</v>
+        <v>95.28</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -33348,10 +33503,10 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3681.21</v>
+        <v>3681.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>2911.41</v>
+        <v>2911.44</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -33359,16 +33514,16 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -33376,7 +33531,9 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
+・買われ過ぎ水準です。
 ・25日線から大きく上に乖離しています。
+・出来高が増加しています。
 ・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -33408,31 +33565,31 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>2340</v>
+        <v>2355</v>
       </c>
       <c r="F17" t="n">
-        <v>-40.5</v>
+        <v>-25.5</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.7</v>
+        <v>-1.07</v>
       </c>
       <c r="H17" t="n">
-        <v>3092000</v>
+        <v>7059900</v>
       </c>
       <c r="I17" t="n">
-        <v>42.1</v>
+        <v>43.5</v>
       </c>
       <c r="J17" t="n">
-        <v>-4.11</v>
+        <v>-3.52</v>
       </c>
       <c r="K17" t="n">
-        <v>0.43</v>
+        <v>0.88</v>
       </c>
       <c r="L17" t="n">
-        <v>-69.77</v>
+        <v>-68.56999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-80.12</v>
+        <v>-79.88</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -33441,14 +33598,14 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2689</v>
+        <v>2689.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>2817.1</v>
+        <v>2817.18</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -33456,7 +33613,7 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -33473,132 +33630,132 @@
           <t>【AI分析レポート】
 ・🔴 下降
 ・MACDは買いシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>あと43日</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>トヨタ自動車(株)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4000円で売る予定</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2882</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-55</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="H18" t="n">
+        <v>34117700</v>
+      </c>
+      <c r="I18" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-4.09</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-16.42</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>2896.59</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3109.72</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは売りシグナルです。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 ⚠️ 下落トレンドです。
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>あと43日</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2026/11/05</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>あと37日</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
         <is>
           <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>7203.T</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>トヨタ自動車(株)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4000円で売る予定</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>2901</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-35.5</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-1.21</v>
-      </c>
-      <c r="H18" t="n">
-        <v>12411600</v>
-      </c>
-      <c r="I18" t="n">
-        <v>32</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-3.47</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-14.86</v>
-      </c>
-      <c r="M18" t="n">
-        <v>-2.62</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>2896.85</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3109.82</v>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="S18" t="n">
-        <v>60</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>2026/11/05</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>あと37日</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -33620,31 +33777,31 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>1750</v>
+        <v>1735</v>
       </c>
       <c r="F19" t="n">
-        <v>-18</v>
+        <v>-33.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.02</v>
+        <v>-1.89</v>
       </c>
       <c r="H19" t="n">
-        <v>2702400</v>
+        <v>10651500</v>
       </c>
       <c r="I19" t="n">
-        <v>43.5</v>
+        <v>41.8</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.55</v>
+        <v>-2.39</v>
       </c>
       <c r="K19" t="n">
-        <v>0.25</v>
+        <v>0.85</v>
       </c>
       <c r="L19" t="n">
-        <v>11.17</v>
+        <v>9.93</v>
       </c>
       <c r="M19" t="n">
-        <v>21.14</v>
+        <v>20.89</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -33653,34 +33810,442 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1664.02</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1564.67</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>55</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2026/10/29</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>あと30日</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>🟡 調整中押し目（段階的買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ブロードリーフ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>500円で売</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>477</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="H20" t="n">
+        <v>418600</v>
+      </c>
+      <c r="I20" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L20" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="M20" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P19" t="n">
-        <v>1664.22</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1564.75</v>
-      </c>
-      <c r="R19" t="inlineStr">
+      <c r="P20" t="n">
+        <v>437.85</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>416.32</v>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S19" t="n">
+      <c r="S20" t="n">
+        <v>75</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>9117</v>
+      </c>
+      <c r="F21" t="n">
+        <v>69</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H21" t="n">
+        <v>21902900</v>
+      </c>
+      <c r="I21" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-293.05</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-391.29</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>12416.84</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>8062.32</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>75</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2026/11/05</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>あと37日</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>キオクシアホールディングス</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>17880</v>
+      </c>
+      <c r="F22" t="n">
+        <v>100</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H22" t="n">
+        <v>41572200</v>
+      </c>
+      <c r="I22" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-80.2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-161.52</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>21350.58</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>13708.83</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>75</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2026/10/30</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>あと31日</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>8729.T</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ソニーファイナンシャル</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>156.8</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="H23" t="n">
+        <v>57168900</v>
+      </c>
+      <c r="I23" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>150.14</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>147.45</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
         <v>50</v>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>★★☆☆☆</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -33691,427 +34256,19 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>2026/10/29</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>あと30日</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>2026/11/12</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>あと44日</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
         <is>
           <t>🟡 調整中押し目（段階的買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>3673.T</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ブロードリーフ</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>500円で売</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>475</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-4</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="H20" t="n">
-        <v>86800</v>
-      </c>
-      <c r="I20" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L20" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="M20" t="n">
-        <v>7.03</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>437.82</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>416.31</v>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S20" t="n">
-        <v>75</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="n">
-        <v>8968</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-80</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="H21" t="n">
-        <v>12650500</v>
-      </c>
-      <c r="I21" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-304.93</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-393.66</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>12414.85</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>8061.58</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S21" t="n">
-        <v>65</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>2026/11/05</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>あと37日</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>285A.T</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>キオクシアホールディングス</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="n">
-        <v>17655</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-125</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="H22" t="n">
-        <v>23177900</v>
-      </c>
-      <c r="I22" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-98.15000000000001</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-165.11</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>21347.58</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>13707.7</v>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S22" t="n">
-        <v>65</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>2026/10/30</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>あと31日</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>8729.T</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ソニーファイナンシャル</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>158</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="H23" t="n">
-        <v>27136500</v>
-      </c>
-      <c r="I23" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>DC</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>150.16</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>147.45</v>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S23" t="n">
-        <v>60</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>2026/11/12</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>あと44日</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
@@ -34129,31 +34286,31 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>3434</v>
+        <v>3458</v>
       </c>
       <c r="F24" t="n">
-        <v>-25</v>
+        <v>-1</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.72</v>
+        <v>-0.03</v>
       </c>
       <c r="H24" t="n">
-        <v>3148600</v>
+        <v>8395300</v>
       </c>
       <c r="I24" t="n">
-        <v>56.5</v>
+        <v>57.8</v>
       </c>
       <c r="J24" t="n">
-        <v>3.02</v>
+        <v>3.71</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3</v>
+        <v>0.72</v>
       </c>
       <c r="L24" t="n">
-        <v>-49.48</v>
+        <v>-47.56</v>
       </c>
       <c r="M24" t="n">
-        <v>-98.73</v>
+        <v>-98.34999999999999</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -34162,14 +34319,14 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3929.95</v>
+        <v>3930.27</v>
       </c>
       <c r="Q24" t="n">
-        <v>3234.49</v>
+        <v>3234.61</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -34190,107 +34347,6 @@
         </is>
       </c>
       <c r="V24" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>2026/10/28</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>あと29日</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>PENG</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ペンギン・ソリューションズ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="n">
-        <v>54.98</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-1.24</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-2.21</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1337400</v>
-      </c>
-      <c r="I25" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="J25" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>58.28</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>39.02</v>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S25" t="n">
-        <v>95</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -34301,6 +34357,107 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>2026/10/28</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>あと29日</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PENG</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ペンギン・ソリューションズ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>54.98</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1337400</v>
+      </c>
+      <c r="I25" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>95</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr">
         <is>
           <t>2026/10/06</t>
@@ -34340,7 +34497,7 @@
         <v>-1.29</v>
       </c>
       <c r="H26" t="n">
-        <v>3407600</v>
+        <v>6801600</v>
       </c>
       <c r="I26" t="n">
         <v>28.7</v>
@@ -34349,7 +34506,7 @@
         <v>-7.34</v>
       </c>
       <c r="K26" t="n">
-        <v>0.54</v>
+        <v>0.98</v>
       </c>
       <c r="L26" t="n">
         <v>-86.02</v>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>173,909円</t>
+          <t>173,302円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-35,382円</t>
+          <t>-35,988円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.91%</t>
+          <t>-17.2%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3375</v>
+        <v>3350</v>
       </c>
       <c r="F2" t="n">
-        <v>38.9</v>
+        <v>40.6</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.67</v>
+        <v>-2.35</v>
       </c>
       <c r="H2" t="n">
-        <v>0.73</v>
+        <v>1.06</v>
       </c>
       <c r="I2" t="n">
-        <v>5.44</v>
+        <v>3.73</v>
       </c>
       <c r="J2" t="n">
-        <v>23.84</v>
+        <v>19.82</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3092.4</v>
+        <v>3105.71</v>
       </c>
       <c r="N2" t="n">
-        <v>2736.97</v>
+        <v>2739.78</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -790,25 +790,25 @@
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3340</v>
+        <v>3375</v>
       </c>
       <c r="X2" t="n">
-        <v>35</v>
+        <v>-25</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.05</v>
+        <v>-0.74</v>
       </c>
       <c r="Z2" t="n">
-        <v>13500</v>
+        <v>13400</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2700</v>
+        <v>2600</v>
       </c>
       <c r="AC2" t="n">
-        <v>25</v>
+        <v>24.07</v>
       </c>
     </row>
     <row r="3">
@@ -829,22 +829,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="F3" t="n">
-        <v>46.2</v>
+        <v>48.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.85</v>
+        <v>-2.83</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8</v>
+        <v>0.43</v>
       </c>
       <c r="I3" t="n">
-        <v>6.94</v>
+        <v>5.04</v>
       </c>
       <c r="J3" t="n">
-        <v>7.07</v>
+        <v>6.66</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>437.85</v>
+        <v>438.57</v>
       </c>
       <c r="N3" t="n">
-        <v>416.32</v>
+        <v>416.83</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -899,29 +899,29 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25日線上、MACD売り、長期上昇</t>
+          <t>押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="X3" t="n">
-        <v>-2</v>
+        <v>-18</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.42</v>
+        <v>-3.77</v>
       </c>
       <c r="Z3" t="n">
-        <v>47700</v>
+        <v>45900</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>5700</v>
+        <v>3900</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.57</v>
+        <v>9.289999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -942,22 +942,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>171.3</v>
+        <v>170.6</v>
       </c>
       <c r="F4" t="n">
-        <v>52.7</v>
+        <v>59.9</v>
       </c>
       <c r="G4" t="n">
-        <v>0.42</v>
+        <v>-0.16</v>
       </c>
       <c r="H4" t="n">
-        <v>0.97</v>
+        <v>0.41</v>
       </c>
       <c r="I4" t="n">
-        <v>3.18</v>
+        <v>2.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.98</v>
+        <v>3.75</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>156.07</v>
+        <v>156.39</v>
       </c>
       <c r="N4" t="n">
-        <v>152.4</v>
+        <v>152.5</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,20 +982,20 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,11 +1012,11 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+          <t>RSI適正、押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>172</v>
+        <v>171.3</v>
       </c>
       <c r="X4" t="n">
         <v>-0.7</v>
@@ -1025,16 +1025,16 @@
         <v>-0.41</v>
       </c>
       <c r="Z4" t="n">
-        <v>17130</v>
+        <v>17060</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1330</v>
+        <v>1260</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.42</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="5">
@@ -1055,22 +1055,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>2881.5</v>
+        <v>2898</v>
       </c>
       <c r="F5" t="n">
-        <v>30.3</v>
+        <v>30.7</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.09</v>
+        <v>-3.31</v>
       </c>
       <c r="H5" t="n">
-        <v>1.06</v>
+        <v>0.37</v>
       </c>
       <c r="I5" t="n">
-        <v>-16.42</v>
+        <v>-19.48</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.93</v>
+        <v>-6.24</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2896.59</v>
+        <v>2898.34</v>
       </c>
       <c r="N5" t="n">
-        <v>3109.72</v>
+        <v>3109.46</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1128,25 +1128,25 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>2936.5</v>
+        <v>2881.5</v>
       </c>
       <c r="X5" t="n">
-        <v>-55</v>
+        <v>16.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.87</v>
+        <v>0.57</v>
       </c>
       <c r="Z5" t="n">
-        <v>37460</v>
+        <v>37674</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>360</v>
+        <v>575</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.97</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="6">
@@ -1167,22 +1167,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>7896</v>
+        <v>7882</v>
       </c>
       <c r="F6" t="n">
-        <v>28.7</v>
+        <v>29.7</v>
       </c>
       <c r="G6" t="n">
-        <v>-7.34</v>
+        <v>-7.19</v>
       </c>
       <c r="H6" t="n">
-        <v>0.98</v>
+        <v>0.42</v>
       </c>
       <c r="I6" t="n">
-        <v>-86.02</v>
+        <v>-106.16</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.06</v>
+        <v>-21.28</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>7794.36</v>
+        <v>7803.25</v>
       </c>
       <c r="N6" t="n">
-        <v>8580.299999999999</v>
+        <v>8556.620000000001</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1241,25 +1241,25 @@
         </is>
       </c>
       <c r="W6" t="n">
-        <v>7999</v>
+        <v>7896</v>
       </c>
       <c r="X6" t="n">
-        <v>-103</v>
+        <v>-14</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.29</v>
+        <v>-0.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>7896</v>
+        <v>7882</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>-97</v>
+        <v>-111</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1.21</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="7">
@@ -1280,22 +1280,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4637</v>
+        <v>4726</v>
       </c>
       <c r="F7" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.8</v>
+        <v>-1.95</v>
       </c>
       <c r="H7" t="n">
-        <v>1.06</v>
+        <v>0.33</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>-3.27</v>
       </c>
       <c r="J7" t="n">
-        <v>35.18</v>
+        <v>27.49</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1304,74 +1304,74 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4653.9</v>
+        <v>4656.17</v>
       </c>
       <c r="N7" t="n">
-        <v>4646.2</v>
+        <v>4651.85</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>🔴 下降</t>
+          <t>🟢 強い上昇</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🔴 売り注意</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🔴 下降
+・🟢 強い上昇
 ・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、下降トレンド</t>
+          <t>押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4756</v>
+        <v>4637</v>
       </c>
       <c r="X7" t="n">
-        <v>-119</v>
+        <v>89</v>
       </c>
       <c r="Y7" t="n">
-        <v>-2.5</v>
+        <v>1.92</v>
       </c>
       <c r="Z7" t="n">
-        <v>23185</v>
+        <v>23630</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>-790</v>
+        <v>-345</v>
       </c>
       <c r="AC7" t="n">
-        <v>-3.3</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="8">
@@ -1392,38 +1392,38 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>9117</v>
+        <v>9450</v>
       </c>
       <c r="F8" t="n">
-        <v>47.1</v>
+        <v>46.4</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03</v>
+        <v>3.6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="I8" t="n">
-        <v>-293.05</v>
+        <v>-244.68</v>
       </c>
       <c r="J8" t="n">
-        <v>-391.29</v>
+        <v>-361.97</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>12416.84</v>
+        <v>12335.14</v>
       </c>
       <c r="N8" t="n">
-        <v>8062.32</v>
+        <v>8092.48</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1432,20 +1432,20 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1453,125 +1453,125 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・RSIは良好な水準です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>25日線上、ゴールデンクロス、+1σ、MACD買い、反発局面</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>9117</v>
+      </c>
+      <c r="X8" t="n">
+        <v>333</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>9450</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-550</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>キオクシアホールディングス</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>55510</v>
+      </c>
+      <c r="E9" t="n">
+        <v>18265</v>
+      </c>
+      <c r="F9" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-42.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-137.72</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>21280.78</v>
+      </c>
+      <c r="N9" t="n">
+        <v>13784.79</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>75</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
 ・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>25日線上、MACD買い、反発局面</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>9048</v>
-      </c>
-      <c r="X8" t="n">
-        <v>69</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>9117</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-883</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-8.83</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>285A.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>キオクシアホールディングス</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>55510</v>
-      </c>
-      <c r="E9" t="n">
-        <v>17880</v>
-      </c>
-      <c r="F9" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-80.2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-161.52</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>21350.58</v>
-      </c>
-      <c r="N9" t="n">
-        <v>13708.83</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>75</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
@@ -1579,25 +1579,25 @@
         </is>
       </c>
       <c r="W9" t="n">
-        <v>17780</v>
+        <v>17880</v>
       </c>
       <c r="X9" t="n">
-        <v>100</v>
+        <v>385</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>17880</v>
+        <v>18265</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-37630</v>
+        <v>-37245</v>
       </c>
       <c r="AC9" t="n">
-        <v>-67.79000000000001</v>
+        <v>-67.09999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1724,7 +1724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1682"/>
+  <dimension ref="A1:C1691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26956,6 +26956,141 @@
         </is>
       </c>
       <c r="C1682" t="n">
+        <v>41.02</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1683" t="n">
+        <v>3350</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1684" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1685" t="n">
+        <v>170.6</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1686" t="n">
+        <v>2898</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1687" t="n">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1688" t="n">
+        <v>4726</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1689" t="n">
+        <v>9450</v>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1690" t="n">
+        <v>18265</v>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1691" t="n">
         <v>41.02</v>
       </c>
     </row>
@@ -26970,7 +27105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F273"/>
+  <dimension ref="A1:F274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31848,19 +31983,29 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="inlineStr">
+      <c r="A271" t="inlineStr"/>
+      <c r="B271" s="1" t="n">
+        <v>46295.5</v>
+      </c>
+      <c r="C271" t="n">
+        <v>173302</v>
+      </c>
+      <c r="D271" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E271" t="n">
+        <v>-35988</v>
+      </c>
+      <c r="F271" t="n">
+        <v>-17.2</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr"/>
-      <c r="C271" t="inlineStr"/>
-      <c r="D271" t="inlineStr"/>
-      <c r="E271" t="inlineStr"/>
-      <c r="F271" t="inlineStr"/>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr"/>
       <c r="B272" t="inlineStr"/>
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr"/>
@@ -31868,16 +32013,24 @@
       <c r="F272" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A273" t="inlineStr"/>
       <c r="B273" t="inlineStr"/>
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr"/>
+      <c r="C274" t="inlineStr"/>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr"/>
+      <c r="F274" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -34387,31 +34540,31 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>54.98</v>
+        <v>55.79</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.24</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.21</v>
+        <v>1.47</v>
       </c>
       <c r="H25" t="n">
-        <v>1337400</v>
+        <v>1191525</v>
       </c>
       <c r="I25" t="n">
-        <v>56.7</v>
+        <v>58.4</v>
       </c>
       <c r="J25" t="n">
-        <v>7.42</v>
+        <v>8.57</v>
       </c>
       <c r="K25" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="L25" t="n">
-        <v>0.34</v>
+        <v>0.52</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.53</v>
+        <v>-0.32</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -34424,10 +34577,10 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>58.28</v>
+        <v>58.17</v>
       </c>
       <c r="Q25" t="n">
-        <v>39.02</v>
+        <v>39.19</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>173,302円</t>
+          <t>174,869円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-35,988円</t>
+          <t>-34,421円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-16.45%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3350</v>
+        <v>3375</v>
       </c>
       <c r="F2" t="n">
-        <v>40.6</v>
+        <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.35</v>
+        <v>-1.65</v>
       </c>
       <c r="H2" t="n">
-        <v>1.06</v>
+        <v>1.66</v>
       </c>
       <c r="I2" t="n">
-        <v>3.73</v>
+        <v>5.72</v>
       </c>
       <c r="J2" t="n">
-        <v>19.82</v>
+        <v>20.22</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3105.71</v>
+        <v>3106.04</v>
       </c>
       <c r="N2" t="n">
-        <v>2739.78</v>
+        <v>2739.91</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -778,6 +778,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
+・出来高が増加しています。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -786,29 +787,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>押し目、出来高微増、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>3375</v>
       </c>
       <c r="X2" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.74</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>13400</v>
+        <v>13500</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="AC2" t="n">
-        <v>24.07</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -829,22 +830,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="F3" t="n">
-        <v>48.5</v>
+        <v>54.4</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.83</v>
+        <v>-0.59</v>
       </c>
       <c r="H3" t="n">
-        <v>0.43</v>
+        <v>1.2</v>
       </c>
       <c r="I3" t="n">
-        <v>5.04</v>
+        <v>5.91</v>
       </c>
       <c r="J3" t="n">
-        <v>6.66</v>
+        <v>6.83</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -857,10 +858,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>438.57</v>
+        <v>438.71</v>
       </c>
       <c r="N3" t="n">
-        <v>416.83</v>
+        <v>416.88</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -869,20 +870,20 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -899,29 +900,29 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>RSI適正、押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W3" t="n">
         <v>477</v>
       </c>
       <c r="X3" t="n">
-        <v>-18</v>
+        <v>-7</v>
       </c>
       <c r="Y3" t="n">
-        <v>-3.77</v>
+        <v>-1.47</v>
       </c>
       <c r="Z3" t="n">
-        <v>45900</v>
+        <v>47000</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>3900</v>
+        <v>5000</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.289999999999999</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="4">
@@ -942,22 +943,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>170.6</v>
+        <v>171.6</v>
       </c>
       <c r="F4" t="n">
-        <v>59.9</v>
+        <v>62.3</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.16</v>
+        <v>0.4</v>
       </c>
       <c r="H4" t="n">
-        <v>0.41</v>
+        <v>0.93</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -970,10 +971,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>156.39</v>
+        <v>156.4</v>
       </c>
       <c r="N4" t="n">
-        <v>152.5</v>
+        <v>152.51</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,361 +983,23 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>RSI適正、押し目、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>171.3</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>17060</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>15800</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1260</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.97</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>7203.T</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>トヨタ自動車</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>13</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2853.77</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2898</v>
-      </c>
-      <c r="F5" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-3.31</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-19.48</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-6.24</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>2898.34</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3109.46</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>🔴 売り注意</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>15</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>押し目、-1σ、MACD売り、下降トレンド</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>2881.5</v>
-      </c>
-      <c r="X5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>37674</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>37099</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>575</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>7993</v>
-      </c>
-      <c r="E6" t="n">
-        <v>7882</v>
-      </c>
-      <c r="F6" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-7.19</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-106.16</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-21.28</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>7803.25</v>
-      </c>
-      <c r="N6" t="n">
-        <v>8556.620000000001</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>75</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>RSI売られすぎ、押し目、-1σ、MACD売り、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>7896</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-14</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>7882</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>7993</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-111</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-1.39</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>8058.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>三菱商事</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4795</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4726</v>
-      </c>
-      <c r="F7" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-1.95</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-3.27</v>
-      </c>
-      <c r="J7" t="n">
-        <v>27.49</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>4656.17</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4651.85</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>65</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -1346,32 +1009,368 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>171.3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>17160</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>15800</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1360</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8.609999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>トヨタ自動車</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2853.77</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2920</v>
+      </c>
+      <c r="F5" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-17.73</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-5.89</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>2898.63</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3109.57</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>60</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>2881.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>37960</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>37099</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>861</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>三菱商事</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4795</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F6" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J6" t="n">
+        <v>28.17</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>4656.74</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4652.07</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>65</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>押し目、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>4637</v>
+      </c>
+      <c r="X6" t="n">
+        <v>132</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>23845</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>23975</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-130</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7993</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7944</v>
+      </c>
+      <c r="F7" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-6.49</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-101.21</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-20.29</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>7804.08</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8556.93</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>60</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4637</v>
+        <v>7896</v>
       </c>
       <c r="X7" t="n">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.92</v>
+        <v>0.61</v>
       </c>
       <c r="Z7" t="n">
-        <v>23630</v>
+        <v>7944</v>
       </c>
       <c r="AA7" t="n">
-        <v>23975</v>
+        <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>-345</v>
+        <v>-49</v>
       </c>
       <c r="AC7" t="n">
-        <v>-1.44</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="8">
@@ -1392,38 +1391,38 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>9450</v>
+        <v>9324</v>
       </c>
       <c r="F8" t="n">
-        <v>46.4</v>
+        <v>44.8</v>
       </c>
       <c r="G8" t="n">
-        <v>3.6</v>
+        <v>2.27</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9</v>
+        <v>1.32</v>
       </c>
       <c r="I8" t="n">
-        <v>-244.68</v>
+        <v>-254.73</v>
       </c>
       <c r="J8" t="n">
-        <v>-361.97</v>
+        <v>-363.98</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>12335.14</v>
+        <v>12333.46</v>
       </c>
       <c r="N8" t="n">
-        <v>8092.48</v>
+        <v>8091.85</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1432,137 +1431,23 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
-・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>25日線上、ゴールデンクロス、+1σ、MACD買い、反発局面</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>9117</v>
-      </c>
-      <c r="X8" t="n">
-        <v>333</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>9450</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-550</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>285A.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>キオクシアホールディングス</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>55510</v>
-      </c>
-      <c r="E9" t="n">
-        <v>18265</v>
-      </c>
-      <c r="F9" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-42.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-137.72</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>21280.78</v>
-      </c>
-      <c r="N9" t="n">
-        <v>13784.79</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>75</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -1572,6 +1457,118 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>25日線上、MACD買い、反発局面</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>9117</v>
+      </c>
+      <c r="X8" t="n">
+        <v>207</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>9324</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-676</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-6.76</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>キオクシアホールディングス</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>55510</v>
+      </c>
+      <c r="E9" t="n">
+        <v>18095</v>
+      </c>
+      <c r="F9" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-56.06</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-140.43</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>21278.51</v>
+      </c>
+      <c r="N9" t="n">
+        <v>13783.94</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>75</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
@@ -1582,22 +1579,22 @@
         <v>17880</v>
       </c>
       <c r="X9" t="n">
-        <v>385</v>
+        <v>215</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>18265</v>
+        <v>18095</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-37245</v>
+        <v>-37415</v>
       </c>
       <c r="AC9" t="n">
-        <v>-67.09999999999999</v>
+        <v>-67.40000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1724,7 +1721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1691"/>
+  <dimension ref="A1:C1700"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27091,6 +27088,141 @@
         </is>
       </c>
       <c r="C1691" t="n">
+        <v>41.02</v>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1692" t="n">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1693" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1694" t="n">
+        <v>171.6</v>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1695" t="n">
+        <v>2920</v>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1696" t="n">
+        <v>4769</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1697" t="n">
+        <v>7944</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1698" t="n">
+        <v>9324</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1699" t="n">
+        <v>18095</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1700" t="n">
         <v>41.02</v>
       </c>
     </row>
@@ -27105,7 +27237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F274"/>
+  <dimension ref="A1:F275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32001,19 +32133,29 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="inlineStr">
+      <c r="A272" t="inlineStr"/>
+      <c r="B272" s="1" t="n">
+        <v>46295.75</v>
+      </c>
+      <c r="C272" t="n">
+        <v>174869</v>
+      </c>
+      <c r="D272" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E272" t="n">
+        <v>-34421</v>
+      </c>
+      <c r="F272" t="n">
+        <v>-16.45</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr"/>
-      <c r="C272" t="inlineStr"/>
-      <c r="D272" t="inlineStr"/>
-      <c r="E272" t="inlineStr"/>
-      <c r="F272" t="inlineStr"/>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr"/>
       <c r="B273" t="inlineStr"/>
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr"/>
@@ -32021,16 +32163,24 @@
       <c r="F273" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A274" t="inlineStr"/>
       <c r="B274" t="inlineStr"/>
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr"/>
+      <c r="C275" t="inlineStr"/>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="inlineStr"/>
+      <c r="F275" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -32195,31 +32345,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>977</v>
+        <v>999</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G2" t="n">
-        <v>0.41</v>
+        <v>2.25</v>
       </c>
       <c r="H2" t="n">
-        <v>572500</v>
+        <v>928100</v>
       </c>
       <c r="I2" t="n">
-        <v>34.3</v>
+        <v>40.8</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.9</v>
+        <v>-0.85</v>
       </c>
       <c r="K2" t="n">
-        <v>0.53</v>
+        <v>0.83</v>
       </c>
       <c r="L2" t="n">
-        <v>13.75</v>
+        <v>12.9</v>
       </c>
       <c r="M2" t="n">
-        <v>25.6</v>
+        <v>23.06</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -32232,10 +32382,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>868.73</v>
+        <v>872.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>1107.32</v>
+        <v>1105.62</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -32295,31 +32445,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3375</v>
+        <v>3350</v>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>-25</v>
       </c>
       <c r="G3" t="n">
-        <v>1.05</v>
+        <v>-0.74</v>
       </c>
       <c r="H3" t="n">
-        <v>50600</v>
+        <v>70900</v>
       </c>
       <c r="I3" t="n">
-        <v>38.9</v>
+        <v>40.6</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.67</v>
+        <v>-2.35</v>
       </c>
       <c r="K3" t="n">
-        <v>0.73</v>
+        <v>1.06</v>
       </c>
       <c r="L3" t="n">
-        <v>5.44</v>
+        <v>3.73</v>
       </c>
       <c r="M3" t="n">
-        <v>23.84</v>
+        <v>19.82</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -32332,10 +32482,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3092.4</v>
+        <v>3105.71</v>
       </c>
       <c r="Q3" t="n">
-        <v>2736.97</v>
+        <v>2739.78</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -32395,31 +32545,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1462</v>
+        <v>1455</v>
       </c>
       <c r="F4" t="n">
-        <v>57</v>
+        <v>-7</v>
       </c>
       <c r="G4" t="n">
-        <v>4.06</v>
+        <v>-0.48</v>
       </c>
       <c r="H4" t="n">
-        <v>32200</v>
+        <v>10200</v>
       </c>
       <c r="I4" t="n">
-        <v>58.3</v>
+        <v>57.7</v>
       </c>
       <c r="J4" t="n">
-        <v>9.380000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>1.64</v>
+        <v>0.5</v>
       </c>
       <c r="L4" t="n">
-        <v>42.14</v>
+        <v>45.31</v>
       </c>
       <c r="M4" t="n">
-        <v>38</v>
+        <v>39.46</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -32432,10 +32582,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1221.81</v>
+        <v>1225.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>1634.99</v>
+        <v>1634.49</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -32461,7 +32611,6 @@
 ・🟢 上昇
 ・MACDは買いシグナルです。
 ・RSIは良好な水準です。
-・出来高が増加しています。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -32497,31 +32646,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3595</v>
+        <v>3605</v>
       </c>
       <c r="F5" t="n">
-        <v>-115</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.1</v>
+        <v>0.28</v>
       </c>
       <c r="H5" t="n">
-        <v>13500</v>
+        <v>10200</v>
       </c>
       <c r="I5" t="n">
-        <v>47.4</v>
+        <v>50.3</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="K5" t="n">
-        <v>0.59</v>
+        <v>0.43</v>
       </c>
       <c r="L5" t="n">
-        <v>44.27</v>
+        <v>45.56</v>
       </c>
       <c r="M5" t="n">
-        <v>24.34</v>
+        <v>28.58</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -32534,10 +32683,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3434.93</v>
+        <v>3437.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>3175.53</v>
+        <v>3180.89</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -32545,7 +32694,7 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -32598,31 +32747,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1554</v>
+        <v>1528</v>
       </c>
       <c r="F6" t="n">
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.71</v>
+        <v>-1.67</v>
       </c>
       <c r="H6" t="n">
-        <v>35300</v>
+        <v>64300</v>
       </c>
       <c r="I6" t="n">
-        <v>50.4</v>
+        <v>42.7</v>
       </c>
       <c r="J6" t="n">
-        <v>0.28</v>
+        <v>-1.28</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5</v>
+        <v>0.88</v>
       </c>
       <c r="L6" t="n">
-        <v>-7.76</v>
+        <v>-10.15</v>
       </c>
       <c r="M6" t="n">
-        <v>-18.08</v>
+        <v>-16.49</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -32635,10 +32784,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1664.04</v>
+        <v>1660.74</v>
       </c>
       <c r="Q6" t="n">
-        <v>1689.11</v>
+        <v>1687.36</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -32646,16 +32795,16 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -32663,7 +32812,6 @@
           <t>【AI分析レポート】
 ・🔴 下降
 ・MACDは買いシグナルです。
-・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 ⚠️ 下落トレンドです。
 無理な買いは避け、反転サインを待ちましょう。</t>
@@ -32699,7 +32847,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F7" t="n">
         <v>-1</v>
@@ -32708,26 +32856,26 @@
         <v>-0.19</v>
       </c>
       <c r="H7" t="n">
-        <v>5800</v>
+        <v>9200</v>
       </c>
       <c r="I7" t="n">
-        <v>50</v>
+        <v>44.8</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01</v>
+        <v>-0.12</v>
       </c>
       <c r="K7" t="n">
-        <v>0.41</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.89</v>
+        <v>-3.66</v>
       </c>
       <c r="M7" t="n">
-        <v>-5.4</v>
+        <v>-5.05</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -32736,10 +32884,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>538.61</v>
+        <v>538.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>576.86</v>
+        <v>575.84</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -32747,16 +32895,16 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -32764,8 +32912,6 @@
           <t>【AI分析レポート】
 ・🔴 下降
 ・MACDは買いシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
-・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 ⚠️ 下落トレンドです。
 無理な買いは避け、反転サインを待ちましょう。</t>
@@ -32801,31 +32947,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="F8" t="n">
-        <v>-16</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.43</v>
+        <v>0.45</v>
       </c>
       <c r="H8" t="n">
-        <v>1800</v>
+        <v>700</v>
       </c>
       <c r="I8" t="n">
-        <v>47.6</v>
+        <v>44</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.99</v>
+        <v>-0.32</v>
       </c>
       <c r="K8" t="n">
-        <v>0.45</v>
+        <v>0.21</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.09</v>
+        <v>-2.94</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.58</v>
+        <v>-3.45</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -32838,10 +32984,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1063.27</v>
+        <v>1064.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>1014.84</v>
+        <v>1014.38</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -32849,19 +32995,425 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは買いシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7033.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>マネジメントソリューションズ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PMO支援・DX案件増加</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1540</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="H9" t="n">
+        <v>17100</v>
+      </c>
+      <c r="I9" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-3.86</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="M9" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1472.32</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1389.61</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>70</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9342.T</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>スマサポ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>不動産DX</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>876</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H10" t="n">
+        <v>900</v>
+      </c>
+      <c r="I10" t="n">
+        <v>13</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-9.390000000000001</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-5.29</v>
+      </c>
+      <c r="M10" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>-2S</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>890.61</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>985.9400000000001</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>35</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは売りシグナルです。
+・売られ過ぎ水準です。
+・ボリンジャーバンド-2σ付近です。売られすぎから反発する可能性があります。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6971.T</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>京セラ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>自社株</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3639</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-46</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1245900</v>
+      </c>
+      <c r="I11" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L11" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-9.109999999999999</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>3634.86</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2967.17</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>100</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026/10/29</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>あと29日</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3778.T</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>さくらインターネット(株)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>3640</v>
+      </c>
+      <c r="F12" t="n">
+        <v>45</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H12" t="n">
+        <v>249500</v>
+      </c>
+      <c r="I12" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L12" t="n">
+        <v>42.41</v>
+      </c>
+      <c r="M12" t="n">
+        <v>63.37</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>3291.6</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3078.41</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>85</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -32872,402 +33424,825 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>7033.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>マネジメントソリューションズ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5803.T</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>(株)フジクラ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>監視</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PMO支援・DX案件増加</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1545</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-13</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="H9" t="n">
-        <v>51600</v>
-      </c>
-      <c r="I9" t="n">
-        <v>37</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-3.94</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="M9" t="n">
-        <v>10.77</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>5229</v>
+      </c>
+      <c r="F13" t="n">
+        <v>298</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="H13" t="n">
+        <v>23176700</v>
+      </c>
+      <c r="I13" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-42.33</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-52.1</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>5080.51</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4539.96</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>100</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2026/11/10</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>あと41日</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>166A.T</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>タスキホールディングス</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>何度も高値更新中の強トレンド</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1016</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-11</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="H14" t="n">
+        <v>256700</v>
+      </c>
+      <c r="I14" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-6.36</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-18.25</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-14.84</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>-1S</t>
         </is>
       </c>
-      <c r="P9" t="n">
-        <v>1470.32</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1388.34</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P14" t="n">
+        <v>1085.85</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>908.92</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>65</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・売られ過ぎ水準です。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5801.T</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>古河電気工業</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>半導体設備関連</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3839</v>
+      </c>
+      <c r="F15" t="n">
+        <v>155</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="H15" t="n">
+        <v>11051700</v>
+      </c>
+      <c r="I15" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-16.04</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-6.24</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>3915</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3258.23</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>75</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2026/11/09</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>あと40日</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3374.T</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>内外テック</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>4895</v>
+      </c>
+      <c r="F16" t="n">
+        <v>100</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H16" t="n">
+        <v>34900</v>
+      </c>
+      <c r="I16" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="J16" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L16" t="n">
+        <v>193.73</v>
+      </c>
+      <c r="M16" t="n">
+        <v>114.97</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>+2S</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>3708.81</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2925.96</v>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S9" t="n">
-        <v>70</v>
-      </c>
-      <c r="T9" t="inlineStr">
+      <c r="S16" t="n">
+        <v>85</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは買いシグナルです。
+・25日線から大きく上に乖離しています。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>7012.T</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>川崎重工業(株)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>2366</v>
+      </c>
+      <c r="F17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2730500</v>
+      </c>
+      <c r="I17" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-65.18000000000001</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-76.94</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>2682.94</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2819.3</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは買いシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>あと42日</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>トヨタ自動車(株)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4000円で売る予定</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2898</v>
+      </c>
+      <c r="F18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H18" t="n">
+        <v>9063200</v>
+      </c>
+      <c r="I18" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-3.31</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-19.48</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-6.24</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>2898.34</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3109.46</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは売りシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2026/11/05</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>あと36日</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>8053.T</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>住友商事</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>1760</v>
+      </c>
+      <c r="F19" t="n">
+        <v>25</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1995200</v>
+      </c>
+      <c r="I19" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="M19" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1666.59</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1567.56</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>65</v>
+      </c>
+      <c r="T19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2026/10/29</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>あと29日</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
         <is>
           <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9342.T</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>スマサポ</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>不動産DX</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>875</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-78</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-8.18</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7400</v>
-      </c>
-      <c r="I10" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-9.720000000000001</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M10" t="n">
-        <v>13.22</v>
-      </c>
-      <c r="N10" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ブロードリーフ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>500円で売</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>459</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-18</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="H20" t="n">
+        <v>198300</v>
+      </c>
+      <c r="I20" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="M20" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>-2S</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>889.25</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>986.25</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>35</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・ボリンジャーバンド-2σ付近です。売られすぎから反発する可能性があります。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>6971.T</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>京セラ</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>自社株</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>3685</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4482800</v>
-      </c>
-      <c r="I11" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="L11" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-15.29</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>3633.41</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2959.38</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>438.57</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>416.83</v>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S11" t="n">
-        <v>100</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは買いシグナルです。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2026/10/29</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>あと30日</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>3778.T</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>さくらインターネット(株)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="n">
-        <v>3595</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-135</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-3.62</v>
-      </c>
-      <c r="H12" t="n">
-        <v>560700</v>
-      </c>
-      <c r="I12" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="L12" t="n">
-        <v>50.58</v>
-      </c>
-      <c r="M12" t="n">
-        <v>68.61</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>3278.64</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3076.01</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S12" t="n">
+      <c r="S20" t="n">
         <v>65</v>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -33278,828 +34253,295 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
         <is>
           <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>5803.T</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>(株)フジクラ</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>監視</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="n">
-        <v>4931</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-7</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="H13" t="n">
-        <v>24796700</v>
-      </c>
-      <c r="I13" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-3.08</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-68.7</v>
-      </c>
-      <c r="M13" t="n">
-        <v>-54.54</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>5066.49</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4527.53</v>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>9450</v>
+      </c>
+      <c r="F21" t="n">
+        <v>333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H21" t="n">
+        <v>22076500</v>
+      </c>
+      <c r="I21" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-244.68</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-361.97</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>12335.14</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>8092.48</v>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>🟡 反発中</t>
         </is>
       </c>
-      <c r="S13" t="n">
-        <v>45</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
+      <c r="S21" t="n">
+        <v>90</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
-・MACDは売りシグナルです。
+・MACDは買いシグナルです。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・RSIは良好な水準です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2026/11/05</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>あと36日</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>キオクシアホールディングス</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>18265</v>
+      </c>
+      <c r="F22" t="n">
+        <v>385</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H22" t="n">
+        <v>22760000</v>
+      </c>
+      <c r="I22" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-42.5</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-137.72</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>21280.78</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>13784.79</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>75</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
 ・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>2026/11/10</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>あと42日</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>166A.T</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>タスキホールディングス</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>何度も高値更新中の強トレンド</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1027</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-25</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="H14" t="n">
-        <v>656700</v>
-      </c>
-      <c r="I14" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-5.68</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-16.47</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-13.99</v>
-      </c>
-      <c r="N14" t="inlineStr">
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2026/10/30</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>あと30日</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>8729.T</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ソニーファイナンシャル</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>157.1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H23" t="n">
+        <v>25678600</v>
+      </c>
+      <c r="I23" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1085.51</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>907.54</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S14" t="n">
-        <v>55</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・出来高が増加しています。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>5801.T</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>古河電気工業</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>半導体設備関連</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>3684</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-90</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="H15" t="n">
-        <v>17735900</v>
-      </c>
-      <c r="I15" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-4</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-20.53</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-3.79</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>3918.38</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3243.84</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S15" t="n">
-        <v>50</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>2026/11/09</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>あと41日</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>3374.T</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>内外テック</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="n">
-        <v>4795</v>
-      </c>
-      <c r="F16" t="n">
-        <v>320</v>
-      </c>
-      <c r="G16" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="H16" t="n">
-        <v>76800</v>
-      </c>
-      <c r="I16" t="n">
-        <v>70</v>
-      </c>
-      <c r="J16" t="n">
-        <v>15.41</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="L16" t="n">
-        <v>157.52</v>
-      </c>
-      <c r="M16" t="n">
-        <v>95.28</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>+2S</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>3681.28</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2911.44</v>
-      </c>
-      <c r="R16" t="inlineStr">
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>150.32</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>147.54</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S16" t="n">
-        <v>90</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは買いシグナルです。
-・買われ過ぎ水準です。
-・25日線から大きく上に乖離しています。
-・出来高が増加しています。
-・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>7012.T</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>川崎重工業(株)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="n">
-        <v>2355</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-25.5</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="H17" t="n">
-        <v>7059900</v>
-      </c>
-      <c r="I17" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-3.52</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-68.56999999999999</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-79.88</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>2689.2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2817.18</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S17" t="n">
-        <v>30</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは買いシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>あと43日</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>7203.T</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>トヨタ自動車(株)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4000円で売る予定</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>2882</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-55</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-1.87</v>
-      </c>
-      <c r="H18" t="n">
-        <v>34117700</v>
-      </c>
-      <c r="I18" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-4.09</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-16.42</v>
-      </c>
-      <c r="M18" t="n">
-        <v>-2.93</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>2896.59</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3109.72</v>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S18" t="n">
-        <v>15</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>2026/11/05</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>あと37日</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>8053.T</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>住友商事</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="n">
-        <v>1735</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-33.5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-1.89</v>
-      </c>
-      <c r="H19" t="n">
-        <v>10651500</v>
-      </c>
-      <c r="I19" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>-2.39</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="L19" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="M19" t="n">
-        <v>20.89</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>DC</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1664.02</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1564.67</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S19" t="n">
-        <v>55</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>2026/10/29</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>あと30日</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>🟡 調整中押し目（段階的買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>3673.T</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ブロードリーフ</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>500円で売</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>477</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-2</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="H20" t="n">
-        <v>418600</v>
-      </c>
-      <c r="I20" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L20" t="n">
-        <v>6.94</v>
-      </c>
-      <c r="M20" t="n">
-        <v>7.07</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>437.85</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>416.32</v>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S20" t="n">
-        <v>75</v>
-      </c>
-      <c r="T20" t="inlineStr">
+      <c r="S23" t="n">
+        <v>65</v>
+      </c>
+      <c r="T23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -34110,305 +34552,6 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="n">
-        <v>9117</v>
-      </c>
-      <c r="F21" t="n">
-        <v>69</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="H21" t="n">
-        <v>21902900</v>
-      </c>
-      <c r="I21" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-293.05</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-391.29</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>12416.84</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>8062.32</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S21" t="n">
-        <v>75</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>2026/11/05</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>あと37日</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>285A.T</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>キオクシアホールディングス</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="n">
-        <v>17880</v>
-      </c>
-      <c r="F22" t="n">
-        <v>100</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="H22" t="n">
-        <v>41572200</v>
-      </c>
-      <c r="I22" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-80.2</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-161.52</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>21350.58</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>13708.83</v>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S22" t="n">
-        <v>75</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>2026/10/30</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>あと31日</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>8729.T</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ソニーファイナンシャル</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>156.8</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="H23" t="n">
-        <v>57168900</v>
-      </c>
-      <c r="I23" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>DC</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>150.14</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>147.45</v>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S23" t="n">
-        <v>50</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
       <c r="W23" t="inlineStr">
         <is>
           <t>2026/11/12</t>
@@ -34416,12 +34559,12 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>あと44日</t>
+          <t>あと43日</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>🟡 調整中押し目（段階的買い足し検討）</t>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -34439,31 +34582,31 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>3458</v>
+        <v>3470</v>
       </c>
       <c r="F24" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.03</v>
+        <v>0.35</v>
       </c>
       <c r="H24" t="n">
-        <v>8395300</v>
+        <v>3171200</v>
       </c>
       <c r="I24" t="n">
-        <v>57.8</v>
+        <v>53.7</v>
       </c>
       <c r="J24" t="n">
-        <v>3.71</v>
+        <v>4.02</v>
       </c>
       <c r="K24" t="n">
-        <v>0.72</v>
+        <v>0.34</v>
       </c>
       <c r="L24" t="n">
-        <v>-47.56</v>
+        <v>-35.71</v>
       </c>
       <c r="M24" t="n">
-        <v>-98.34999999999999</v>
+        <v>-85.81999999999999</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -34476,10 +34619,10 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3930.27</v>
+        <v>3919.09</v>
       </c>
       <c r="Q24" t="n">
-        <v>3234.61</v>
+        <v>3243.02</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -34517,7 +34660,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>あと29日</t>
+          <t>あと28日</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -34549,7 +34692,7 @@
         <v>1.47</v>
       </c>
       <c r="H25" t="n">
-        <v>1191525</v>
+        <v>1194900</v>
       </c>
       <c r="I25" t="n">
         <v>58.4</v>
@@ -34618,7 +34761,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>あと7日</t>
+          <t>あと6日</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -34641,31 +34784,31 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>7896</v>
+        <v>7882</v>
       </c>
       <c r="F26" t="n">
-        <v>-103</v>
+        <v>-14</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.29</v>
+        <v>-0.18</v>
       </c>
       <c r="H26" t="n">
-        <v>6801600</v>
+        <v>2610200</v>
       </c>
       <c r="I26" t="n">
-        <v>28.7</v>
+        <v>29.7</v>
       </c>
       <c r="J26" t="n">
-        <v>-7.34</v>
+        <v>-7.19</v>
       </c>
       <c r="K26" t="n">
-        <v>0.98</v>
+        <v>0.42</v>
       </c>
       <c r="L26" t="n">
-        <v>-86.02</v>
+        <v>-106.16</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.06</v>
+        <v>-21.28</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -34678,10 +34821,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7794.36</v>
+        <v>7803.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>8580.299999999999</v>
+        <v>8556.620000000001</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -34719,7 +34862,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>あと37日</t>
+          <t>あと36日</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -1615,19 +1615,19 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>41.02</v>
+        <v>41.07</v>
       </c>
       <c r="F10" t="n">
-        <v>54.9</v>
+        <v>59.3</v>
       </c>
       <c r="G10" t="n">
-        <v>4.97</v>
+        <v>4.82</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7</v>
+        <v>0.92</v>
       </c>
       <c r="I10" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="J10" t="n">
         <v>1.56</v>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.39</v>
+        <v>33.53</v>
       </c>
       <c r="N10" t="n">
-        <v>31.86</v>
+        <v>31.89</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
-・MACDは買いシグナルです。
+・MACDは売りシグナルです。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
@@ -1685,17 +1685,17 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>41.78</v>
+        <v>41.02</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.76</v>
+        <v>0.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1.82</v>
+        <v>0.12</v>
       </c>
       <c r="Z10" t="n">
         <v>41</v>
@@ -1721,7 +1721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1700"/>
+  <dimension ref="A1:C1709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27224,6 +27224,141 @@
       </c>
       <c r="C1700" t="n">
         <v>41.02</v>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1701" t="n">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1702" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1703" t="n">
+        <v>171.6</v>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1704" t="n">
+        <v>2920</v>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1705" t="n">
+        <v>4769</v>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1706" t="n">
+        <v>7944</v>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1707" t="n">
+        <v>9324</v>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1708" t="n">
+        <v>18095</v>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1709" t="n">
+        <v>41.07</v>
       </c>
     </row>
   </sheetData>
@@ -27237,7 +27372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F275"/>
+  <dimension ref="A1:F276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32151,19 +32286,29 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="inlineStr">
+      <c r="A273" t="inlineStr"/>
+      <c r="B273" s="1" t="n">
+        <v>46296.29166666666</v>
+      </c>
+      <c r="C273" t="n">
+        <v>174869</v>
+      </c>
+      <c r="D273" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E273" t="n">
+        <v>-34421</v>
+      </c>
+      <c r="F273" t="n">
+        <v>-16.45</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr"/>
-      <c r="C273" t="inlineStr"/>
-      <c r="D273" t="inlineStr"/>
-      <c r="E273" t="inlineStr"/>
-      <c r="F273" t="inlineStr"/>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr"/>
       <c r="B274" t="inlineStr"/>
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr"/>
@@ -32171,16 +32316,24 @@
       <c r="F274" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A275" t="inlineStr"/>
       <c r="B275" t="inlineStr"/>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr"/>
+      <c r="C276" t="inlineStr"/>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -32345,31 +32498,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G2" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="H2" t="n">
-        <v>928100</v>
+        <v>1317000</v>
       </c>
       <c r="I2" t="n">
-        <v>40.8</v>
+        <v>40.3</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.85</v>
+        <v>-1.04</v>
       </c>
       <c r="K2" t="n">
-        <v>0.83</v>
+        <v>1.11</v>
       </c>
       <c r="L2" t="n">
-        <v>12.9</v>
+        <v>12.74</v>
       </c>
       <c r="M2" t="n">
-        <v>23.06</v>
+        <v>23.02</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -32382,10 +32535,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>872.8</v>
+        <v>872.77</v>
       </c>
       <c r="Q2" t="n">
-        <v>1105.62</v>
+        <v>1105.61</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -32445,31 +32598,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3350</v>
+        <v>3375</v>
       </c>
       <c r="F3" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.74</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>70900</v>
+        <v>130700</v>
       </c>
       <c r="I3" t="n">
-        <v>40.6</v>
+        <v>42</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.35</v>
+        <v>-1.65</v>
       </c>
       <c r="K3" t="n">
-        <v>1.06</v>
+        <v>1.66</v>
       </c>
       <c r="L3" t="n">
-        <v>3.73</v>
+        <v>5.72</v>
       </c>
       <c r="M3" t="n">
-        <v>19.82</v>
+        <v>20.22</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -32482,10 +32635,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3105.71</v>
+        <v>3106.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>2739.78</v>
+        <v>2739.91</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -32493,7 +32646,7 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -32510,6 +32663,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
+・出来高が増加しています。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -32545,31 +32699,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1455</v>
+        <v>1468</v>
       </c>
       <c r="F4" t="n">
-        <v>-7</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.48</v>
+        <v>0.41</v>
       </c>
       <c r="H4" t="n">
-        <v>10200</v>
+        <v>23800</v>
       </c>
       <c r="I4" t="n">
-        <v>57.7</v>
+        <v>59.8</v>
       </c>
       <c r="J4" t="n">
-        <v>8.140000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5</v>
+        <v>1.02</v>
       </c>
       <c r="L4" t="n">
-        <v>45.31</v>
+        <v>46.34</v>
       </c>
       <c r="M4" t="n">
-        <v>39.46</v>
+        <v>39.67</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -32582,10 +32736,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1225.91</v>
+        <v>1226.09</v>
       </c>
       <c r="Q4" t="n">
-        <v>1634.49</v>
+        <v>1634.56</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -32646,31 +32800,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3605</v>
+        <v>3600</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.28</v>
+        <v>0.14</v>
       </c>
       <c r="H5" t="n">
-        <v>10200</v>
+        <v>15500</v>
       </c>
       <c r="I5" t="n">
-        <v>50.3</v>
+        <v>50</v>
       </c>
       <c r="J5" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="K5" t="n">
-        <v>0.43</v>
+        <v>0.63</v>
       </c>
       <c r="L5" t="n">
-        <v>45.56</v>
+        <v>45.16</v>
       </c>
       <c r="M5" t="n">
-        <v>28.58</v>
+        <v>28.5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -32683,10 +32837,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3437.4</v>
+        <v>3437.33</v>
       </c>
       <c r="Q5" t="n">
-        <v>3180.89</v>
+        <v>3180.86</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -32747,31 +32901,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1528</v>
+        <v>1545</v>
       </c>
       <c r="F6" t="n">
-        <v>-26</v>
+        <v>-9</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.67</v>
+        <v>-0.58</v>
       </c>
       <c r="H6" t="n">
-        <v>64300</v>
+        <v>126300</v>
       </c>
       <c r="I6" t="n">
-        <v>42.7</v>
+        <v>46</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.28</v>
+        <v>-0.22</v>
       </c>
       <c r="K6" t="n">
-        <v>0.88</v>
+        <v>1.48</v>
       </c>
       <c r="L6" t="n">
-        <v>-10.15</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-16.49</v>
+        <v>-16.22</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -32784,10 +32938,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1660.74</v>
+        <v>1660.97</v>
       </c>
       <c r="Q6" t="n">
-        <v>1687.36</v>
+        <v>1687.45</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -32808,6 +32962,107 @@
         </is>
       </c>
       <c r="V6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4054.T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>日本情報クリエイト</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>不動産向けクラウド</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>520</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="H7" t="n">
+        <v>14100</v>
+      </c>
+      <c r="I7" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-3.74</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-5.07</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>538.73</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>575.83</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>30</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🔴 下降
@@ -32817,106 +33072,6 @@
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>4054.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>日本情報クリエイト</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>不動産向けクラウド</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>521</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="H7" t="n">
-        <v>9200</v>
-      </c>
-      <c r="I7" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-3.66</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-5.05</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>538.75</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>575.84</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>30</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは買いシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
@@ -32947,31 +33102,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.45</v>
+        <v>0.54</v>
       </c>
       <c r="H8" t="n">
-        <v>700</v>
+        <v>8000</v>
       </c>
       <c r="I8" t="n">
-        <v>44</v>
+        <v>44.4</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.32</v>
+        <v>-0.23</v>
       </c>
       <c r="K8" t="n">
-        <v>0.21</v>
+        <v>1.67</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.94</v>
+        <v>-2.86</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.45</v>
+        <v>-3.43</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -32984,7 +33139,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1064.87</v>
+        <v>1064.88</v>
       </c>
       <c r="Q8" t="n">
         <v>1014.38</v>
@@ -32995,16 +33150,16 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -33012,6 +33167,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
+・出来高が増加しています。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -33047,31 +33203,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="F9" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>17100</v>
+        <v>59300</v>
       </c>
       <c r="I9" t="n">
-        <v>40.6</v>
+        <v>41.3</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.86</v>
+        <v>-3.56</v>
       </c>
       <c r="K9" t="n">
-        <v>0.28</v>
+        <v>0.86</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.75</v>
+        <v>-0.35</v>
       </c>
       <c r="M9" t="n">
-        <v>8.470000000000001</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -33084,10 +33240,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1472.32</v>
+        <v>1472.39</v>
       </c>
       <c r="Q9" t="n">
-        <v>1389.61</v>
+        <v>1389.63</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -33147,31 +33303,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>876</v>
+        <v>883</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>0.11</v>
+        <v>0.91</v>
       </c>
       <c r="H10" t="n">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="I10" t="n">
-        <v>13</v>
+        <v>16.7</v>
       </c>
       <c r="J10" t="n">
-        <v>-9.390000000000001</v>
+        <v>-8.69</v>
       </c>
       <c r="K10" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="L10" t="n">
-        <v>-5.29</v>
+        <v>-4.74</v>
       </c>
       <c r="M10" t="n">
-        <v>9.52</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -33184,10 +33340,10 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>890.61</v>
+        <v>890.71</v>
       </c>
       <c r="Q10" t="n">
-        <v>985.9400000000001</v>
+        <v>985.98</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -33248,31 +33404,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3639</v>
+        <v>3646</v>
       </c>
       <c r="F11" t="n">
-        <v>-46</v>
+        <v>-39</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.25</v>
+        <v>-1.06</v>
       </c>
       <c r="H11" t="n">
-        <v>1245900</v>
+        <v>6101400</v>
       </c>
       <c r="I11" t="n">
-        <v>57.9</v>
+        <v>58.4</v>
       </c>
       <c r="J11" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="K11" t="n">
-        <v>0.32</v>
+        <v>1.25</v>
       </c>
       <c r="L11" t="n">
-        <v>15.63</v>
+        <v>16.19</v>
       </c>
       <c r="M11" t="n">
-        <v>-9.109999999999999</v>
+        <v>-8.99</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -33285,10 +33441,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3634.86</v>
+        <v>3634.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>2967.17</v>
+        <v>2967.21</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -33353,31 +33509,31 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>3640</v>
+        <v>3620</v>
       </c>
       <c r="F12" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="G12" t="n">
-        <v>1.25</v>
+        <v>0.7</v>
       </c>
       <c r="H12" t="n">
-        <v>249500</v>
+        <v>494200</v>
       </c>
       <c r="I12" t="n">
-        <v>50.4</v>
+        <v>49.6</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.46</v>
       </c>
       <c r="K12" t="n">
-        <v>0.52</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>42.41</v>
+        <v>40.82</v>
       </c>
       <c r="M12" t="n">
-        <v>63.37</v>
+        <v>63.05</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -33390,10 +33546,10 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3291.6</v>
+        <v>3291.33</v>
       </c>
       <c r="Q12" t="n">
-        <v>3078.41</v>
+        <v>3078.31</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -33401,16 +33557,16 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -33450,31 +33606,31 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>5229</v>
+        <v>5224</v>
       </c>
       <c r="F13" t="n">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="G13" t="n">
-        <v>6.04</v>
+        <v>5.94</v>
       </c>
       <c r="H13" t="n">
-        <v>23176700</v>
+        <v>38875400</v>
       </c>
       <c r="I13" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="J13" t="n">
-        <v>2.81</v>
+        <v>2.71</v>
       </c>
       <c r="K13" t="n">
-        <v>0.85</v>
+        <v>1.28</v>
       </c>
       <c r="L13" t="n">
-        <v>-42.33</v>
+        <v>-42.73</v>
       </c>
       <c r="M13" t="n">
-        <v>-52.1</v>
+        <v>-52.18</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -33487,10 +33643,10 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5080.51</v>
+        <v>5080.44</v>
       </c>
       <c r="Q13" t="n">
-        <v>4539.96</v>
+        <v>4539.94</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -33559,31 +33715,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1016</v>
+        <v>1008</v>
       </c>
       <c r="F14" t="n">
-        <v>-11</v>
+        <v>-19</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.07</v>
+        <v>-1.85</v>
       </c>
       <c r="H14" t="n">
-        <v>256700</v>
+        <v>605800</v>
       </c>
       <c r="I14" t="n">
-        <v>28.5</v>
+        <v>27.2</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.36</v>
+        <v>-7.07</v>
       </c>
       <c r="K14" t="n">
-        <v>0.61</v>
+        <v>1.23</v>
       </c>
       <c r="L14" t="n">
-        <v>-18.25</v>
+        <v>-18.89</v>
       </c>
       <c r="M14" t="n">
-        <v>-14.84</v>
+        <v>-14.97</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -33596,10 +33752,10 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1085.85</v>
+        <v>1085.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>908.92</v>
+        <v>908.88</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -33660,31 +33816,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3839</v>
+        <v>3856</v>
       </c>
       <c r="F15" t="n">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="G15" t="n">
-        <v>4.21</v>
+        <v>4.67</v>
       </c>
       <c r="H15" t="n">
-        <v>11051700</v>
+        <v>18582500</v>
       </c>
       <c r="I15" t="n">
-        <v>50.3</v>
+        <v>50.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="K15" t="n">
-        <v>0.67</v>
+        <v>1.03</v>
       </c>
       <c r="L15" t="n">
-        <v>-16.04</v>
+        <v>-14.69</v>
       </c>
       <c r="M15" t="n">
-        <v>-6.24</v>
+        <v>-5.97</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -33697,10 +33853,10 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3915</v>
+        <v>3915.23</v>
       </c>
       <c r="Q15" t="n">
-        <v>3258.23</v>
+        <v>3258.32</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -33743,7 +33899,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
+          <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
@@ -33765,31 +33921,31 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>4895</v>
+        <v>4915</v>
       </c>
       <c r="F16" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G16" t="n">
-        <v>2.09</v>
+        <v>2.5</v>
       </c>
       <c r="H16" t="n">
-        <v>34900</v>
+        <v>57200</v>
       </c>
       <c r="I16" t="n">
-        <v>68.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="J16" t="n">
-        <v>16.84</v>
+        <v>17.3</v>
       </c>
       <c r="K16" t="n">
-        <v>0.64</v>
+        <v>0.98</v>
       </c>
       <c r="L16" t="n">
-        <v>193.73</v>
+        <v>195.33</v>
       </c>
       <c r="M16" t="n">
-        <v>114.97</v>
+        <v>115.29</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -33802,10 +33958,10 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3708.81</v>
+        <v>3709.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>2925.96</v>
+        <v>2926.06</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -33862,31 +34018,31 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="F17" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
       <c r="H17" t="n">
-        <v>2730500</v>
+        <v>6447900</v>
       </c>
       <c r="I17" t="n">
-        <v>37.6</v>
+        <v>37.3</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.71</v>
+        <v>-2.77</v>
       </c>
       <c r="K17" t="n">
-        <v>0.42</v>
+        <v>0.9</v>
       </c>
       <c r="L17" t="n">
-        <v>-65.18000000000001</v>
+        <v>-65.3</v>
       </c>
       <c r="M17" t="n">
-        <v>-76.94</v>
+        <v>-76.97</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -33899,10 +34055,10 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2682.94</v>
+        <v>2682.92</v>
       </c>
       <c r="Q17" t="n">
-        <v>2819.3</v>
+        <v>2819.29</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -33970,31 +34126,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2898</v>
+        <v>2920</v>
       </c>
       <c r="F18" t="n">
-        <v>16.5</v>
+        <v>38.5</v>
       </c>
       <c r="G18" t="n">
-        <v>0.57</v>
+        <v>1.34</v>
       </c>
       <c r="H18" t="n">
-        <v>9063200</v>
+        <v>29166700</v>
       </c>
       <c r="I18" t="n">
-        <v>30.7</v>
+        <v>34.5</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.31</v>
+        <v>-2.6</v>
       </c>
       <c r="K18" t="n">
-        <v>0.37</v>
+        <v>1.01</v>
       </c>
       <c r="L18" t="n">
-        <v>-19.48</v>
+        <v>-17.73</v>
       </c>
       <c r="M18" t="n">
-        <v>-6.24</v>
+        <v>-5.89</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -34007,37 +34163,37 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2898.34</v>
+        <v>2898.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>3109.46</v>
+        <v>3109.57</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>🔴 下降</t>
+          <t>🟢 上昇</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🔴 下降
+・🟢 上昇
 ・MACDは売りシグナルです。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -34052,7 +34208,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
         </is>
       </c>
     </row>
@@ -34074,31 +34230,31 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>1760</v>
+        <v>1770</v>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>35.5</v>
       </c>
       <c r="G19" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="H19" t="n">
-        <v>1995200</v>
+        <v>11246900</v>
       </c>
       <c r="I19" t="n">
-        <v>37.7</v>
+        <v>39.4</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.14</v>
+        <v>-0.57</v>
       </c>
       <c r="K19" t="n">
-        <v>0.22</v>
+        <v>1.04</v>
       </c>
       <c r="L19" t="n">
-        <v>8.199999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>18.36</v>
+        <v>18.52</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -34111,10 +34267,10 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1666.59</v>
+        <v>1666.73</v>
       </c>
       <c r="Q19" t="n">
-        <v>1567.56</v>
+        <v>1567.61</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -34182,31 +34338,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="F20" t="n">
-        <v>-18</v>
+        <v>-7</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.77</v>
+        <v>-1.47</v>
       </c>
       <c r="H20" t="n">
-        <v>198300</v>
+        <v>659300</v>
       </c>
       <c r="I20" t="n">
-        <v>48.5</v>
+        <v>54.4</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.83</v>
+        <v>-0.59</v>
       </c>
       <c r="K20" t="n">
-        <v>0.43</v>
+        <v>1.2</v>
       </c>
       <c r="L20" t="n">
-        <v>5.04</v>
+        <v>5.91</v>
       </c>
       <c r="M20" t="n">
-        <v>6.66</v>
+        <v>6.83</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -34219,10 +34375,10 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>438.57</v>
+        <v>438.71</v>
       </c>
       <c r="Q20" t="n">
-        <v>416.83</v>
+        <v>416.88</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -34230,16 +34386,16 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -34279,47 +34435,47 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>9450</v>
+        <v>9324</v>
       </c>
       <c r="F21" t="n">
-        <v>333</v>
+        <v>207</v>
       </c>
       <c r="G21" t="n">
-        <v>3.65</v>
+        <v>2.27</v>
       </c>
       <c r="H21" t="n">
-        <v>22076500</v>
+        <v>35988200</v>
       </c>
       <c r="I21" t="n">
-        <v>46.4</v>
+        <v>44.8</v>
       </c>
       <c r="J21" t="n">
-        <v>3.6</v>
+        <v>2.27</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9</v>
+        <v>1.32</v>
       </c>
       <c r="L21" t="n">
-        <v>-244.68</v>
+        <v>-254.73</v>
       </c>
       <c r="M21" t="n">
-        <v>-361.97</v>
+        <v>-363.98</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>12335.14</v>
+        <v>12333.46</v>
       </c>
       <c r="Q21" t="n">
-        <v>8092.48</v>
+        <v>8091.85</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -34327,121 +34483,19 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
-・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>2026/11/05</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>あと36日</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>285A.T</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>キオクシアホールディングス</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="n">
-        <v>18265</v>
-      </c>
-      <c r="F22" t="n">
-        <v>385</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="H22" t="n">
-        <v>22760000</v>
-      </c>
-      <c r="I22" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-42.5</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-137.72</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>21280.78</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>13784.79</v>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S22" t="n">
-        <v>75</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -34451,6 +34505,106 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2026/11/05</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>あと36日</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>キオクシアホールディングス</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>18095</v>
+      </c>
+      <c r="F22" t="n">
+        <v>215</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>39125500</v>
+      </c>
+      <c r="I22" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-56.06</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-140.43</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>21278.51</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>13783.94</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>75</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr">
         <is>
           <t>2026/10/30</t>
@@ -34481,31 +34635,31 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>157.1</v>
+        <v>157.9</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="G23" t="n">
-        <v>0.19</v>
+        <v>0.7</v>
       </c>
       <c r="H23" t="n">
-        <v>25678600</v>
+        <v>62320700</v>
       </c>
       <c r="I23" t="n">
-        <v>48.3</v>
+        <v>50.3</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.43</v>
+        <v>0.06</v>
       </c>
       <c r="K23" t="n">
-        <v>0.45</v>
+        <v>0.97</v>
       </c>
       <c r="L23" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="M23" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -34518,7 +34672,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>150.32</v>
+        <v>150.33</v>
       </c>
       <c r="Q23" t="n">
         <v>147.54</v>
@@ -34529,16 +34683,16 @@
         </is>
       </c>
       <c r="S23" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -34564,7 +34718,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
+          <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
@@ -34582,31 +34736,31 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>3470</v>
+        <v>3477</v>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G24" t="n">
-        <v>0.35</v>
+        <v>0.55</v>
       </c>
       <c r="H24" t="n">
-        <v>3171200</v>
+        <v>11373700</v>
       </c>
       <c r="I24" t="n">
-        <v>53.7</v>
+        <v>54</v>
       </c>
       <c r="J24" t="n">
-        <v>4.02</v>
+        <v>4.23</v>
       </c>
       <c r="K24" t="n">
-        <v>0.34</v>
+        <v>1.05</v>
       </c>
       <c r="L24" t="n">
-        <v>-35.71</v>
+        <v>-35.16</v>
       </c>
       <c r="M24" t="n">
-        <v>-85.81999999999999</v>
+        <v>-85.70999999999999</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -34619,10 +34773,10 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3919.09</v>
+        <v>3919.19</v>
       </c>
       <c r="Q24" t="n">
-        <v>3243.02</v>
+        <v>3243.05</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -34784,31 +34938,31 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>7882</v>
+        <v>7944</v>
       </c>
       <c r="F26" t="n">
-        <v>-14</v>
+        <v>48</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.18</v>
+        <v>0.61</v>
       </c>
       <c r="H26" t="n">
-        <v>2610200</v>
+        <v>6727400</v>
       </c>
       <c r="I26" t="n">
-        <v>29.7</v>
+        <v>31.5</v>
       </c>
       <c r="J26" t="n">
-        <v>-7.19</v>
+        <v>-6.49</v>
       </c>
       <c r="K26" t="n">
-        <v>0.42</v>
+        <v>0.95</v>
       </c>
       <c r="L26" t="n">
-        <v>-106.16</v>
+        <v>-101.21</v>
       </c>
       <c r="M26" t="n">
-        <v>-21.28</v>
+        <v>-20.29</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -34821,10 +34975,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7803.25</v>
+        <v>7804.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>8556.620000000001</v>
+        <v>8556.93</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -34832,16 +34986,16 @@
         </is>
       </c>
       <c r="S26" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -34849,7 +35003,6 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
-・売られ過ぎ水準です。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>174,869円</t>
+          <t>175,652円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-34,421円</t>
+          <t>-33,637円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.45%</t>
+          <t>-16.07%</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -717,22 +717,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3375</v>
+        <v>3360</v>
       </c>
       <c r="F2" t="n">
-        <v>42</v>
+        <v>45.3</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.65</v>
+        <v>-2.09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.66</v>
+        <v>0.22</v>
       </c>
       <c r="I2" t="n">
-        <v>5.72</v>
+        <v>4.69</v>
       </c>
       <c r="J2" t="n">
-        <v>20.22</v>
+        <v>17.11</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3106.04</v>
+        <v>3120.6</v>
       </c>
       <c r="N2" t="n">
-        <v>2739.91</v>
+        <v>2742.75</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -774,119 +774,6 @@
         </is>
       </c>
       <c r="T2" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・出来高が増加しています。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>押し目、出来高微増、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W2" t="n">
-        <v>3375</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>13500</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>10800</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2700</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>3673.T</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ブロードリーフ</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>100</v>
-      </c>
-      <c r="D3" t="n">
-        <v>420</v>
-      </c>
-      <c r="E3" t="n">
-        <v>470</v>
-      </c>
-      <c r="F3" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>5.91</v>
-      </c>
-      <c r="J3" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>438.71</v>
-      </c>
-      <c r="N3" t="n">
-        <v>416.88</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>85</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -897,144 +784,258 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>RSI適正、押し目、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>477</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-1.47</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>47000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>42000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>5000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>11.9</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>9432.T</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NTT</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>押し目、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>3375</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>13440</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>10800</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2640</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>24.44</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ブロードリーフ</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>100</v>
       </c>
-      <c r="D4" t="n">
-        <v>158</v>
-      </c>
-      <c r="E4" t="n">
-        <v>171.6</v>
-      </c>
-      <c r="F4" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="D3" t="n">
+        <v>420</v>
+      </c>
+      <c r="E3" t="n">
+        <v>468</v>
+      </c>
+      <c r="F3" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="M4" t="n">
-        <v>156.4</v>
-      </c>
-      <c r="N4" t="n">
-        <v>152.51</v>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="M3" t="n">
+        <v>439.66</v>
+      </c>
+      <c r="N3" t="n">
+        <v>417.46</v>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>🟢 強い買い</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>95</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>85</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
+・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>RSI適正、押し目、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>470</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>46800</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>42000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>11.43</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NTT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>158</v>
+      </c>
+      <c r="E4" t="n">
+        <v>170.7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>156.7</v>
+      </c>
+      <c r="N4" t="n">
+        <v>152.61</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>85</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+          <t>RSI適正、押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>171.3</v>
+        <v>171.6</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3</v>
+        <v>-0.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.18</v>
+        <v>-0.52</v>
       </c>
       <c r="Z4" t="n">
-        <v>17160</v>
+        <v>17070</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1360</v>
+        <v>1270</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.609999999999999</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1055,22 +1056,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>2920</v>
+        <v>2910.5</v>
       </c>
       <c r="F5" t="n">
-        <v>34.5</v>
+        <v>48.5</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.6</v>
+        <v>-2.71</v>
       </c>
       <c r="H5" t="n">
-        <v>1.01</v>
+        <v>0.39</v>
       </c>
       <c r="I5" t="n">
-        <v>-17.73</v>
+        <v>-19.31</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.89</v>
+        <v>-8.57</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1083,10 +1084,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2898.63</v>
+        <v>2901.42</v>
       </c>
       <c r="N5" t="n">
-        <v>3109.57</v>
+        <v>3109.56</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1112,6 +1113,237 @@
         </is>
       </c>
       <c r="T5" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>2920</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>37836</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>37099</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>738</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10185</v>
+      </c>
+      <c r="F6" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-153.12</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-321.81</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>+2S</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>12248.62</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8124.57</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>🟢 強い買い</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>90</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
+・25日線から大きく上に乖離しています。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>🚀 急騰</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>RSI適正、上昇加速、ゴールデンクロス、+2σ、MACD買い、反発局面</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>9324</v>
+      </c>
+      <c r="X6" t="n">
+        <v>861</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>10185</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>185</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7993</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7920</v>
+      </c>
+      <c r="F7" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-6.39</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-113.87</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-39</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>7814.43</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8534.469999999999</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>60</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 上昇
@@ -1121,480 +1353,257 @@
 順張りが有利な局面です。</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
         <is>
           <t>押し目、-1σ、MACD売り、上昇トレンド</t>
         </is>
       </c>
-      <c r="W5" t="n">
-        <v>2881.5</v>
-      </c>
-      <c r="X5" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>37960</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>37099</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>861</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.32</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="W7" t="n">
+        <v>7944</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-24</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>7920</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>7993</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-73</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>8058.T</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>三菱商事</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D8" t="n">
         <v>4795</v>
       </c>
-      <c r="E6" t="n">
-        <v>4769</v>
-      </c>
-      <c r="F6" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="J6" t="n">
-        <v>28.17</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="E8" t="n">
+        <v>4701</v>
+      </c>
+      <c r="F8" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-2.48</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-7.73</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>4656.74</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4652.07</v>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>4658.81</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4657.63</v>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>⚪ 様子見</t>
         </is>
       </c>
-      <c r="Q6" t="n">
-        <v>65</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="Q8" t="n">
+        <v>70</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>押し目、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>4637</v>
-      </c>
-      <c r="X6" t="n">
-        <v>132</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>23845</v>
-      </c>
-      <c r="AA6" t="n">
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>押し目、-1σ、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>4769</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-68</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>23505</v>
+      </c>
+      <c r="AA8" t="n">
         <v>23975</v>
       </c>
-      <c r="AB6" t="n">
-        <v>-130</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+      <c r="AB8" t="n">
+        <v>-470</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-1.96</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>キオクシアホールディングス</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>1</v>
       </c>
-      <c r="D7" t="n">
-        <v>7993</v>
-      </c>
-      <c r="E7" t="n">
-        <v>7944</v>
-      </c>
-      <c r="F7" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-6.49</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-101.21</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-20.29</v>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="D9" t="n">
+        <v>55510</v>
+      </c>
+      <c r="E9" t="n">
+        <v>18855</v>
+      </c>
+      <c r="F9" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>24.12</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-107.52</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>7804.08</v>
-      </c>
-      <c r="N7" t="n">
-        <v>8556.93</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>60</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W7" t="n">
-        <v>7896</v>
-      </c>
-      <c r="X7" t="n">
-        <v>48</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>7944</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>7993</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-49</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-0.61</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E8" t="n">
-        <v>9324</v>
-      </c>
-      <c r="F8" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-254.73</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-363.98</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>12333.46</v>
-      </c>
-      <c r="N8" t="n">
-        <v>8091.85</v>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>21194.62</v>
+      </c>
+      <c r="N9" t="n">
+        <v>13863.2</v>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>🟡 反発中</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>🟡 買い</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q9" t="n">
         <v>75</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
+・RSIは良好な水準です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>25日線上、MACD買い、反発局面</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>9117</v>
-      </c>
-      <c r="X8" t="n">
-        <v>207</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>9324</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-676</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-6.76</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>285A.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>キオクシアホールディングス</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>55510</v>
-      </c>
-      <c r="E9" t="n">
-        <v>18095</v>
-      </c>
-      <c r="F9" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-56.06</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-140.43</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>21278.51</v>
-      </c>
-      <c r="N9" t="n">
-        <v>13783.94</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>75</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>25日線上、MACD買い、反発局面</t>
+          <t>25日線上、+1σ、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>17880</v>
+        <v>18095</v>
       </c>
       <c r="X9" t="n">
-        <v>215</v>
+        <v>760</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>18095</v>
+        <v>18855</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-37415</v>
+        <v>-36655</v>
       </c>
       <c r="AC9" t="n">
-        <v>-67.40000000000001</v>
+        <v>-66.03</v>
       </c>
     </row>
     <row r="10">
@@ -1624,7 +1633,7 @@
         <v>4.82</v>
       </c>
       <c r="H10" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="I10" t="n">
         <v>1.56</v>
@@ -1721,7 +1730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1709"/>
+  <dimension ref="A1:C1718"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27358,6 +27367,141 @@
         </is>
       </c>
       <c r="C1709" t="n">
+        <v>41.07</v>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1710" t="n">
+        <v>3360</v>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1711" t="n">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1712" t="n">
+        <v>170.7</v>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1713" t="n">
+        <v>2910.5</v>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1714" t="n">
+        <v>10185</v>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1715" t="n">
+        <v>7920</v>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1716" t="n">
+        <v>4701</v>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1717" t="n">
+        <v>18855</v>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1718" t="n">
         <v>41.07</v>
       </c>
     </row>
@@ -27372,7 +27516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F276"/>
+  <dimension ref="A1:F277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32304,19 +32448,29 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="inlineStr">
+      <c r="A274" t="inlineStr"/>
+      <c r="B274" s="1" t="n">
+        <v>46296.5</v>
+      </c>
+      <c r="C274" t="n">
+        <v>175652</v>
+      </c>
+      <c r="D274" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E274" t="n">
+        <v>-33637</v>
+      </c>
+      <c r="F274" t="n">
+        <v>-16.07</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr"/>
-      <c r="C274" t="inlineStr"/>
-      <c r="D274" t="inlineStr"/>
-      <c r="E274" t="inlineStr"/>
-      <c r="F274" t="inlineStr"/>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr"/>
       <c r="B275" t="inlineStr"/>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr"/>
@@ -32324,16 +32478,24 @@
       <c r="F275" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A276" t="inlineStr"/>
       <c r="B276" t="inlineStr"/>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr"/>
+      <c r="C277" t="inlineStr"/>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -34837,31 +34999,31 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>55.79</v>
+        <v>54.69</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8100000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="G25" t="n">
-        <v>1.47</v>
+        <v>-1.97</v>
       </c>
       <c r="H25" t="n">
-        <v>1194900</v>
+        <v>1419113</v>
       </c>
       <c r="I25" t="n">
-        <v>58.4</v>
+        <v>61.3</v>
       </c>
       <c r="J25" t="n">
-        <v>8.57</v>
+        <v>6.08</v>
       </c>
       <c r="K25" t="n">
-        <v>0.82</v>
+        <v>0.99</v>
       </c>
       <c r="L25" t="n">
-        <v>0.52</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.32</v>
+        <v>-0.14</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -34874,10 +35036,10 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>58.17</v>
+        <v>58.04</v>
       </c>
       <c r="Q25" t="n">
-        <v>39.19</v>
+        <v>39.35</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -34902,7 +35064,6 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
-・RSIは良好な水準です。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>175,652円</t>
+          <t>176,686円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-33,637円</t>
+          <t>-32,604円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.07%</t>
+          <t>-15.58%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3360</v>
+        <v>3435</v>
       </c>
       <c r="F2" t="n">
-        <v>45.3</v>
+        <v>51.1</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.09</v>
+        <v>0.01</v>
       </c>
       <c r="H2" t="n">
-        <v>0.22</v>
+        <v>0.52</v>
       </c>
       <c r="I2" t="n">
-        <v>4.69</v>
+        <v>10.67</v>
       </c>
       <c r="J2" t="n">
-        <v>17.11</v>
+        <v>18.31</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3120.6</v>
+        <v>3121.6</v>
       </c>
       <c r="N2" t="n">
-        <v>2742.75</v>
+        <v>2743.12</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -757,20 +757,20 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -787,29 +787,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>3375</v>
       </c>
       <c r="X2" t="n">
-        <v>-15</v>
+        <v>60</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.44</v>
+        <v>1.78</v>
       </c>
       <c r="Z2" t="n">
-        <v>13440</v>
+        <v>13740</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2640</v>
+        <v>2940</v>
       </c>
       <c r="AC2" t="n">
-        <v>24.44</v>
+        <v>27.22</v>
       </c>
     </row>
     <row r="3">
@@ -830,22 +830,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F3" t="n">
-        <v>53.3</v>
+        <v>54.9</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.07</v>
+        <v>-0.46</v>
       </c>
       <c r="H3" t="n">
-        <v>0.26</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>4.88</v>
+        <v>5.12</v>
       </c>
       <c r="J3" t="n">
-        <v>6.44</v>
+        <v>6.49</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>439.66</v>
+        <v>439.7</v>
       </c>
       <c r="N3" t="n">
-        <v>417.46</v>
+        <v>417.47</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -907,22 +907,22 @@
         <v>470</v>
       </c>
       <c r="X3" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.43</v>
+        <v>0.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>46800</v>
+        <v>47100</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>4800</v>
+        <v>5100</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.43</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="4">
@@ -943,22 +943,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>170.7</v>
+        <v>170.3</v>
       </c>
       <c r="F4" t="n">
-        <v>53.4</v>
+        <v>52.4</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.28</v>
+        <v>-0.51</v>
       </c>
       <c r="H4" t="n">
-        <v>0.51</v>
+        <v>1.15</v>
       </c>
       <c r="I4" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1020,22 +1020,22 @@
         <v>171.6</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.9</v>
+        <v>-1.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.52</v>
+        <v>-0.76</v>
       </c>
       <c r="Z4" t="n">
-        <v>17070</v>
+        <v>17030</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1270</v>
+        <v>1230</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.039999999999999</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="5">
@@ -1056,22 +1056,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>2910.5</v>
+        <v>2925</v>
       </c>
       <c r="F5" t="n">
-        <v>48.5</v>
+        <v>51.1</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.71</v>
+        <v>-2.24</v>
       </c>
       <c r="H5" t="n">
-        <v>0.39</v>
+        <v>0.98</v>
       </c>
       <c r="I5" t="n">
-        <v>-19.31</v>
+        <v>-18.15</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.57</v>
+        <v>-8.34</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2901.42</v>
+        <v>2901.61</v>
       </c>
       <c r="N5" t="n">
-        <v>3109.56</v>
+        <v>3109.64</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1096,20 +1096,20 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1118,7 +1118,7 @@
 ・🟢 上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
@@ -1126,29 +1126,29 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
+          <t>RSI適正、押し目、MACD売り、上昇トレンド</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>2920</v>
       </c>
       <c r="X5" t="n">
-        <v>-9.5</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.33</v>
+        <v>0.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>37836</v>
+        <v>38025</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>738</v>
+        <v>926</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6">
@@ -1169,22 +1169,22 @@
         <v>10000</v>
       </c>
       <c r="E6" t="n">
-        <v>10185</v>
+        <v>10100</v>
       </c>
       <c r="F6" t="n">
-        <v>63.3</v>
+        <v>62.6</v>
       </c>
       <c r="G6" t="n">
-        <v>11.19</v>
+        <v>10.3</v>
       </c>
       <c r="H6" t="n">
-        <v>0.87</v>
+        <v>1.14</v>
       </c>
       <c r="I6" t="n">
-        <v>-153.12</v>
+        <v>-159.9</v>
       </c>
       <c r="J6" t="n">
-        <v>-321.81</v>
+        <v>-323.16</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>12248.62</v>
+        <v>12247.49</v>
       </c>
       <c r="N6" t="n">
-        <v>8124.57</v>
+        <v>8124.15</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1251,22 +1251,22 @@
         <v>9324</v>
       </c>
       <c r="X6" t="n">
-        <v>861</v>
+        <v>776</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.23</v>
+        <v>8.32</v>
       </c>
       <c r="Z6" t="n">
-        <v>10185</v>
+        <v>10100</v>
       </c>
       <c r="AA6" t="n">
         <v>10000</v>
       </c>
       <c r="AB6" t="n">
-        <v>185</v>
+        <v>100</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1287,22 +1287,22 @@
         <v>7993</v>
       </c>
       <c r="E7" t="n">
-        <v>7920</v>
+        <v>7940</v>
       </c>
       <c r="F7" t="n">
-        <v>31.1</v>
+        <v>31.4</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.39</v>
+        <v>-6.16</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="I7" t="n">
-        <v>-113.87</v>
+        <v>-112.27</v>
       </c>
       <c r="J7" t="n">
-        <v>-39</v>
+        <v>-38.68</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>7814.43</v>
+        <v>7814.69</v>
       </c>
       <c r="N7" t="n">
-        <v>8534.469999999999</v>
+        <v>8534.57</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1363,22 +1363,22 @@
         <v>7944</v>
       </c>
       <c r="X7" t="n">
-        <v>-24</v>
+        <v>-4</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.3</v>
+        <v>-0.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>7920</v>
+        <v>7940</v>
       </c>
       <c r="AA7" t="n">
         <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>-73</v>
+        <v>-53</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.91</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="8">
@@ -1399,22 +1399,22 @@
         <v>4795</v>
       </c>
       <c r="E8" t="n">
-        <v>4701</v>
+        <v>4722</v>
       </c>
       <c r="F8" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.48</v>
+        <v>-2.06</v>
       </c>
       <c r="H8" t="n">
-        <v>0.36</v>
+        <v>0.91</v>
       </c>
       <c r="I8" t="n">
-        <v>-7.73</v>
+        <v>-6.06</v>
       </c>
       <c r="J8" t="n">
-        <v>20.99</v>
+        <v>21.33</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1423,14 +1423,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4658.81</v>
+        <v>4659.09</v>
       </c>
       <c r="N8" t="n">
-        <v>4657.63</v>
+        <v>4657.74</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -1468,29 +1468,29 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、長期上昇</t>
+          <t>押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W8" t="n">
         <v>4769</v>
       </c>
       <c r="X8" t="n">
-        <v>-68</v>
+        <v>-47</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.43</v>
+        <v>-0.99</v>
       </c>
       <c r="Z8" t="n">
-        <v>23505</v>
+        <v>23610</v>
       </c>
       <c r="AA8" t="n">
         <v>23975</v>
       </c>
       <c r="AB8" t="n">
-        <v>-470</v>
+        <v>-365</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.96</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="9">
@@ -1511,22 +1511,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>18855</v>
+        <v>19100</v>
       </c>
       <c r="F9" t="n">
-        <v>48.2</v>
+        <v>49.8</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2</v>
+        <v>7.52</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6</v>
+        <v>1.03</v>
       </c>
       <c r="I9" t="n">
-        <v>24.12</v>
+        <v>43.66</v>
       </c>
       <c r="J9" t="n">
-        <v>-107.52</v>
+        <v>-103.61</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>21194.62</v>
+        <v>21197.89</v>
       </c>
       <c r="N9" t="n">
-        <v>13863.2</v>
+        <v>13864.42</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1578,7 +1578,11 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>🚀 急騰</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>25日線上、+1σ、MACD買い、反発局面</t>
@@ -1588,22 +1592,22 @@
         <v>18095</v>
       </c>
       <c r="X9" t="n">
-        <v>760</v>
+        <v>1005</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.2</v>
+        <v>5.55</v>
       </c>
       <c r="Z9" t="n">
-        <v>18855</v>
+        <v>19100</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-36655</v>
+        <v>-36410</v>
       </c>
       <c r="AC9" t="n">
-        <v>-66.03</v>
+        <v>-65.59</v>
       </c>
     </row>
     <row r="10">
@@ -1730,7 +1734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1718"/>
+  <dimension ref="A1:C1727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27502,6 +27506,141 @@
         </is>
       </c>
       <c r="C1718" t="n">
+        <v>41.07</v>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1719" t="n">
+        <v>3435</v>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1720" t="n">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1721" t="n">
+        <v>170.3</v>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1722" t="n">
+        <v>2925</v>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1723" t="n">
+        <v>10100</v>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1724" t="n">
+        <v>7940</v>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1725" t="n">
+        <v>4722</v>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1726" t="n">
+        <v>19100</v>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1727" t="n">
         <v>41.07</v>
       </c>
     </row>
@@ -27516,7 +27655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F277"/>
+  <dimension ref="A1:F278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32466,19 +32605,29 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="inlineStr">
+      <c r="A275" t="inlineStr"/>
+      <c r="B275" s="1" t="n">
+        <v>46296.75</v>
+      </c>
+      <c r="C275" t="n">
+        <v>176686</v>
+      </c>
+      <c r="D275" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E275" t="n">
+        <v>-32604</v>
+      </c>
+      <c r="F275" t="n">
+        <v>-15.58</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr"/>
-      <c r="C275" t="inlineStr"/>
-      <c r="D275" t="inlineStr"/>
-      <c r="E275" t="inlineStr"/>
-      <c r="F275" t="inlineStr"/>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr"/>
       <c r="B276" t="inlineStr"/>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr"/>
@@ -32486,16 +32635,24 @@
       <c r="F276" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A277" t="inlineStr"/>
       <c r="B277" t="inlineStr"/>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr"/>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="inlineStr"/>
+      <c r="F278" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -32660,31 +32817,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>-6</v>
       </c>
       <c r="G2" t="n">
-        <v>2.05</v>
+        <v>-0.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1317000</v>
+        <v>460000</v>
       </c>
       <c r="I2" t="n">
-        <v>40.3</v>
+        <v>38.4</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.04</v>
+        <v>-1.67</v>
       </c>
       <c r="K2" t="n">
-        <v>1.11</v>
+        <v>0.4</v>
       </c>
       <c r="L2" t="n">
-        <v>12.74</v>
+        <v>11.32</v>
       </c>
       <c r="M2" t="n">
-        <v>23.02</v>
+        <v>20.68</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -32697,10 +32854,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>872.77</v>
+        <v>876.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>1105.61</v>
+        <v>1104.11</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -32760,31 +32917,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3375</v>
+        <v>3360</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0.44</v>
       </c>
       <c r="H3" t="n">
-        <v>130700</v>
+        <v>16100</v>
       </c>
       <c r="I3" t="n">
-        <v>42</v>
+        <v>45.3</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.65</v>
+        <v>-2.09</v>
       </c>
       <c r="K3" t="n">
-        <v>1.66</v>
+        <v>0.22</v>
       </c>
       <c r="L3" t="n">
-        <v>5.72</v>
+        <v>4.69</v>
       </c>
       <c r="M3" t="n">
-        <v>20.22</v>
+        <v>17.11</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -32797,10 +32954,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3106.04</v>
+        <v>3120.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2739.91</v>
+        <v>2742.75</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -32808,7 +32965,7 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -32825,7 +32982,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・出来高が増加しています。
+・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -32861,31 +33018,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1468</v>
+        <v>1457</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>-11</v>
       </c>
       <c r="G4" t="n">
-        <v>0.41</v>
+        <v>-0.75</v>
       </c>
       <c r="H4" t="n">
-        <v>23800</v>
+        <v>9000</v>
       </c>
       <c r="I4" t="n">
-        <v>59.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>9.07</v>
+        <v>7.6</v>
       </c>
       <c r="K4" t="n">
-        <v>1.02</v>
+        <v>0.44</v>
       </c>
       <c r="L4" t="n">
-        <v>46.34</v>
+        <v>48.23</v>
       </c>
       <c r="M4" t="n">
-        <v>39.67</v>
+        <v>41.38</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -32898,10 +33055,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1226.09</v>
+        <v>1230.59</v>
       </c>
       <c r="Q4" t="n">
-        <v>1634.56</v>
+        <v>1633.89</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -32909,7 +33066,7 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -32926,7 +33083,6 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは買いシグナルです。
-・RSIは良好な水準です。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -32962,31 +33118,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3600</v>
+        <v>3555</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>-45</v>
       </c>
       <c r="G5" t="n">
-        <v>0.14</v>
+        <v>-1.25</v>
       </c>
       <c r="H5" t="n">
-        <v>15500</v>
+        <v>4200</v>
       </c>
       <c r="I5" t="n">
-        <v>50</v>
+        <v>54.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.29</v>
+        <v>1.85</v>
       </c>
       <c r="K5" t="n">
-        <v>0.63</v>
+        <v>0.18</v>
       </c>
       <c r="L5" t="n">
-        <v>45.16</v>
+        <v>41.75</v>
       </c>
       <c r="M5" t="n">
-        <v>28.5</v>
+        <v>31.15</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -32995,14 +33151,14 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3437.33</v>
+        <v>3440.47</v>
       </c>
       <c r="Q5" t="n">
-        <v>3180.86</v>
+        <v>3186.66</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -33028,7 +33184,7 @@
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -33063,31 +33219,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1545</v>
+        <v>1550</v>
       </c>
       <c r="F6" t="n">
-        <v>-9</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.58</v>
+        <v>0.32</v>
       </c>
       <c r="H6" t="n">
-        <v>126300</v>
+        <v>19900</v>
       </c>
       <c r="I6" t="n">
-        <v>46</v>
+        <v>53.7</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.22</v>
+        <v>0.16</v>
       </c>
       <c r="K6" t="n">
-        <v>1.48</v>
+        <v>0.28</v>
       </c>
       <c r="L6" t="n">
-        <v>-8.789999999999999</v>
+        <v>-9.1</v>
       </c>
       <c r="M6" t="n">
-        <v>-16.22</v>
+        <v>-14.79</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -33100,10 +33256,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1660.97</v>
+        <v>1657.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>1687.45</v>
+        <v>1685.7</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -33111,16 +33267,16 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -33164,7 +33320,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F7" t="n">
         <v>-2</v>
@@ -33173,38 +33329,38 @@
         <v>-0.38</v>
       </c>
       <c r="H7" t="n">
-        <v>14100</v>
+        <v>7700</v>
       </c>
       <c r="I7" t="n">
-        <v>43.3</v>
+        <v>50</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3</v>
+        <v>-0.59</v>
       </c>
       <c r="K7" t="n">
-        <v>1.14</v>
+        <v>0.7</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.74</v>
+        <v>-3.73</v>
       </c>
       <c r="M7" t="n">
-        <v>-5.07</v>
+        <v>-4.8</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>538.73</v>
+        <v>538.85</v>
       </c>
       <c r="Q7" t="n">
-        <v>575.83</v>
+        <v>574.85</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -33212,7 +33368,7 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -33229,7 +33385,9 @@
           <t>【AI分析レポート】
 ・🔴 下降
 ・MACDは買いシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
+・RSIは良好な水準です。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 ⚠️ 下落トレンドです。
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
@@ -33267,28 +33425,28 @@
         <v>1111</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>8000</v>
+        <v>1300</v>
       </c>
       <c r="I8" t="n">
-        <v>44.4</v>
+        <v>47.7</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.67</v>
+        <v>0.32</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.86</v>
+        <v>-1.87</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.43</v>
+        <v>-3.12</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -33301,10 +33459,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1064.88</v>
+        <v>1067.03</v>
       </c>
       <c r="Q8" t="n">
-        <v>1014.38</v>
+        <v>1014.18</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -33312,7 +33470,7 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -33329,7 +33487,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・出来高が増加しています。
+・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -33365,31 +33523,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1545</v>
+        <v>1540</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="H9" t="n">
-        <v>59300</v>
+        <v>12700</v>
       </c>
       <c r="I9" t="n">
-        <v>41.3</v>
+        <v>39.7</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.56</v>
+        <v>-3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>0.86</v>
+        <v>0.25</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.35</v>
+        <v>-2.62</v>
       </c>
       <c r="M9" t="n">
-        <v>8.550000000000001</v>
+        <v>6.32</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -33402,10 +33560,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1472.39</v>
+        <v>1474.77</v>
       </c>
       <c r="Q9" t="n">
-        <v>1389.63</v>
+        <v>1390.9</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -33566,31 +33724,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3646</v>
+        <v>3723</v>
       </c>
       <c r="F11" t="n">
-        <v>-39</v>
+        <v>77</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.06</v>
+        <v>2.11</v>
       </c>
       <c r="H11" t="n">
-        <v>6101400</v>
+        <v>1365900</v>
       </c>
       <c r="I11" t="n">
-        <v>58.4</v>
+        <v>75.3</v>
       </c>
       <c r="J11" t="n">
-        <v>2.47</v>
+        <v>4.43</v>
       </c>
       <c r="K11" t="n">
-        <v>1.25</v>
+        <v>0.33</v>
       </c>
       <c r="L11" t="n">
-        <v>16.19</v>
+        <v>23.94</v>
       </c>
       <c r="M11" t="n">
-        <v>-8.99</v>
+        <v>-2.41</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -33599,34 +33757,236 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>3637.01</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2975.35</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>90</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは買いシグナルです。
+・買われ過ぎ水準です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026/10/29</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>あと28日</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3778.T</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>さくらインターネット(株)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>3950</v>
+      </c>
+      <c r="F12" t="n">
+        <v>330</v>
+      </c>
+      <c r="G12" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>758400</v>
+      </c>
+      <c r="I12" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L12" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="M12" t="n">
+        <v>62.24</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>3308.87</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3082.67</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>95</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5803.T</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>(株)フジクラ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>5277</v>
+      </c>
+      <c r="F13" t="n">
+        <v>53</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H13" t="n">
+        <v>20909000</v>
+      </c>
+      <c r="I13" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-17.66</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-45.27</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P11" t="n">
-        <v>3634.96</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2967.21</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P13" t="n">
+        <v>5095.78</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4552.25</v>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S11" t="n">
+      <c r="S13" t="n">
         <v>100</v>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -33637,101 +33997,730 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2026/11/10</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>あと40日</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>166A.T</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>タスキホールディングス</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>何度も高値更新中の強トレンド</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1004</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>298400</v>
+      </c>
+      <c r="I14" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-6.88</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-20.89</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-16.15</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1085.43</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>910.25</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>65</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・売られ過ぎ水準です。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5801.T</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>古河電気工業</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>半導体設備関連</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4059</v>
+      </c>
+      <c r="F15" t="n">
+        <v>203</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="H15" t="n">
+        <v>13642500</v>
+      </c>
+      <c r="I15" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L15" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-3.53</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>3915.13</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3273.62</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>100</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは買いシグナルです。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2026/11/09</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>あと39日</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3374.T</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>内外テック</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>4985</v>
+      </c>
+      <c r="F16" t="n">
+        <v>70</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H16" t="n">
+        <v>41800</v>
+      </c>
+      <c r="I16" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L16" t="n">
+        <v>228.31</v>
+      </c>
+      <c r="M16" t="n">
+        <v>137.89</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>+2S</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>3738.07</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2940.98</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>70</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは買いシグナルです。
+・買われ過ぎ水準です。
+・25日線から大きく上に乖離しています。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>7012.T</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>川崎重工業(株)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>監視</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>2341</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-23.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3666400</v>
+      </c>
+      <c r="I17" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-63.87</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-74.34999999999999</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>2677.78</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2821.02</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>あと41日</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>❌ 買い足し非推奨（トレンド弱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>トヨタ自動車(株)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4000円で売る予定</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2911</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="H18" t="n">
+        <v>9308800</v>
+      </c>
+      <c r="I18" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-19.31</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-8.57</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>2901.42</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3109.56</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>60</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2026/11/05</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>あと35日</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>8053.T</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>住友商事</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>1749</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-21</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3326600</v>
+      </c>
+      <c r="I19" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L19" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="M19" t="n">
+        <v>16.13</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1669.66</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1570.49</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>65</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>2026/10/29</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>あと29日</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>3778.T</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>さくらインターネット(株)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="n">
-        <v>3620</v>
-      </c>
-      <c r="F12" t="n">
-        <v>25</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H12" t="n">
-        <v>494200</v>
-      </c>
-      <c r="I12" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-1.46</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="L12" t="n">
-        <v>40.82</v>
-      </c>
-      <c r="M12" t="n">
-        <v>63.05</v>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>あと28日</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ブロードリーフ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>保有中</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>500円で売</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>468</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="H20" t="n">
+        <v>103300</v>
+      </c>
+      <c r="I20" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="M20" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="P12" t="n">
-        <v>3291.33</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3078.31</v>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="P20" t="n">
+        <v>439.66</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>417.46</v>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="S12" t="n">
-        <v>65</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
+      <c r="S20" t="n">
+        <v>85</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -33742,835 +34731,6 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>5803.T</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>(株)フジクラ</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="n">
-        <v>5224</v>
-      </c>
-      <c r="F13" t="n">
-        <v>293</v>
-      </c>
-      <c r="G13" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="H13" t="n">
-        <v>38875400</v>
-      </c>
-      <c r="I13" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-42.73</v>
-      </c>
-      <c r="M13" t="n">
-        <v>-52.18</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>5080.44</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4539.94</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S13" t="n">
-        <v>100</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>2026/11/10</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>あと41日</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>166A.T</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>タスキホールディングス</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>何度も高値更新中の強トレンド</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1008</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-19</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-1.85</v>
-      </c>
-      <c r="H14" t="n">
-        <v>605800</v>
-      </c>
-      <c r="I14" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-7.07</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-18.89</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-14.97</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1085.75</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>908.88</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S14" t="n">
-        <v>65</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>5801.T</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>古河電気工業</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>半導体設備関連</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>3856</v>
-      </c>
-      <c r="F15" t="n">
-        <v>172</v>
-      </c>
-      <c r="G15" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="H15" t="n">
-        <v>18582500</v>
-      </c>
-      <c r="I15" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-14.69</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-5.97</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>3915.23</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3258.32</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S15" t="n">
-        <v>75</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>2026/11/09</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>あと40日</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>3374.T</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>内外テック</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="n">
-        <v>4915</v>
-      </c>
-      <c r="F16" t="n">
-        <v>120</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H16" t="n">
-        <v>57200</v>
-      </c>
-      <c r="I16" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="J16" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="L16" t="n">
-        <v>195.33</v>
-      </c>
-      <c r="M16" t="n">
-        <v>115.29</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>+2S</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>3709.08</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2926.06</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S16" t="n">
-        <v>85</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは買いシグナルです。
-・25日線から大きく上に乖離しています。
-・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>7012.T</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>川崎重工業(株)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>監視</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="n">
-        <v>2365</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H17" t="n">
-        <v>6447900</v>
-      </c>
-      <c r="I17" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-2.77</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-65.3</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-76.97</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>2682.92</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2819.29</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S17" t="n">
-        <v>30</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは買いシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>あと42日</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>❌ 買い足し非推奨（トレンド弱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>7203.T</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>トヨタ自動車(株)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4000円で売る予定</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>2920</v>
-      </c>
-      <c r="F18" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="H18" t="n">
-        <v>29166700</v>
-      </c>
-      <c r="I18" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-17.73</v>
-      </c>
-      <c r="M18" t="n">
-        <v>-5.89</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>2898.63</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3109.57</v>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="S18" t="n">
-        <v>60</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>2026/11/05</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>あと36日</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>8053.T</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>住友商事</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="n">
-        <v>1770</v>
-      </c>
-      <c r="F19" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="H19" t="n">
-        <v>11246900</v>
-      </c>
-      <c r="I19" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="L19" t="n">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="M19" t="n">
-        <v>18.52</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1666.73</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1567.61</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S19" t="n">
-        <v>65</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>2026/10/29</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>あと29日</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>3673.T</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ブロードリーフ</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>保有中</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>500円で売</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>470</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-7</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-1.47</v>
-      </c>
-      <c r="H20" t="n">
-        <v>659300</v>
-      </c>
-      <c r="I20" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>5.91</v>
-      </c>
-      <c r="M20" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>438.71</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>416.88</v>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S20" t="n">
-        <v>85</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr">
@@ -34597,47 +34757,47 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>9324</v>
+        <v>10185</v>
       </c>
       <c r="F21" t="n">
-        <v>207</v>
+        <v>861</v>
       </c>
       <c r="G21" t="n">
-        <v>2.27</v>
+        <v>9.23</v>
       </c>
       <c r="H21" t="n">
-        <v>35988200</v>
+        <v>22797500</v>
       </c>
       <c r="I21" t="n">
-        <v>44.8</v>
+        <v>63.3</v>
       </c>
       <c r="J21" t="n">
-        <v>2.27</v>
+        <v>11.19</v>
       </c>
       <c r="K21" t="n">
-        <v>1.32</v>
+        <v>0.87</v>
       </c>
       <c r="L21" t="n">
-        <v>-254.73</v>
+        <v>-153.12</v>
       </c>
       <c r="M21" t="n">
-        <v>-363.98</v>
+        <v>-321.81</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+2S</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>12333.46</v>
+        <v>12248.62</v>
       </c>
       <c r="Q21" t="n">
-        <v>8091.85</v>
+        <v>8124.57</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -34645,16 +34805,16 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -34662,7 +34822,9 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
+・25日線から大きく上に乖離しています。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
@@ -34674,7 +34836,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>あと36日</t>
+          <t>あと35日</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -34697,31 +34859,31 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>18095</v>
+        <v>18855</v>
       </c>
       <c r="F22" t="n">
-        <v>215</v>
+        <v>760</v>
       </c>
       <c r="G22" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="H22" t="n">
-        <v>39125500</v>
+        <v>27233100</v>
       </c>
       <c r="I22" t="n">
-        <v>38.8</v>
+        <v>48.2</v>
       </c>
       <c r="J22" t="n">
-        <v>2.35</v>
+        <v>6.2</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="L22" t="n">
-        <v>-56.06</v>
+        <v>24.12</v>
       </c>
       <c r="M22" t="n">
-        <v>-140.43</v>
+        <v>-107.52</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -34730,14 +34892,14 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>21278.51</v>
+        <v>21194.62</v>
       </c>
       <c r="Q22" t="n">
-        <v>13783.94</v>
+        <v>13863.2</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -34758,207 +34920,6 @@
         </is>
       </c>
       <c r="V22" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>2026/10/30</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>あと30日</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>8729.T</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ソニーファイナンシャル</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>157.9</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H23" t="n">
-        <v>62320700</v>
-      </c>
-      <c r="I23" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>150.33</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>147.54</v>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="S23" t="n">
-        <v>95</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>2026/11/12</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>あと43日</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>6723.T</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>ルネサスエレクトロニクス</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="n">
-        <v>3477</v>
-      </c>
-      <c r="F24" t="n">
-        <v>19</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H24" t="n">
-        <v>11373700</v>
-      </c>
-      <c r="I24" t="n">
-        <v>54</v>
-      </c>
-      <c r="J24" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="L24" t="n">
-        <v>-35.16</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-85.70999999999999</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>3919.19</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3243.05</v>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S24" t="n">
-        <v>95</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -34969,97 +34930,197 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>2026/10/28</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>あと28日</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2026/10/30</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>あと29日</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
         <is>
           <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>PENG</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ペンギン・ソリューションズ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="n">
-        <v>54.69</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-1.97</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1419113</v>
-      </c>
-      <c r="I25" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="J25" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="N25" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>8729.T</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ソニーファイナンシャル</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>153.7</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-2.66</v>
+      </c>
+      <c r="H23" t="n">
+        <v>41103400</v>
+      </c>
+      <c r="I23" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-2.52</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>150.54</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>147.61</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>70</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>2026/11/12</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>あと42日</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>🟢 押し目買い候補（買い足し検討）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6723.T</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ルネサスエレクトロニクス</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>3555</v>
+      </c>
+      <c r="F24" t="n">
+        <v>78</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4017600</v>
+      </c>
+      <c r="I24" t="n">
+        <v>68</v>
+      </c>
+      <c r="J24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-18.81</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-72.33</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>+1S</t>
         </is>
       </c>
-      <c r="P25" t="n">
-        <v>58.04</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>39.35</v>
-      </c>
-      <c r="R25" t="inlineStr">
+      <c r="P24" t="n">
+        <v>3909.76</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3251.3</v>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>🟡 反発中</t>
         </is>
       </c>
-      <c r="S25" t="n">
-        <v>95</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
+      <c r="S24" t="n">
+        <v>85</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -35069,6 +35130,106 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>2026/10/28</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>あと27日</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PENG</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ペンギン・ソリューションズ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>54.69</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1446100</v>
+      </c>
+      <c r="I25" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>58.04</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>95</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr">
         <is>
           <t>2026/10/06</t>
@@ -35076,7 +35237,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>あと6日</t>
+          <t>あと5日</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -35099,31 +35260,31 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>7944</v>
+        <v>7920</v>
       </c>
       <c r="F26" t="n">
-        <v>48</v>
+        <v>-24</v>
       </c>
       <c r="G26" t="n">
-        <v>0.61</v>
+        <v>-0.3</v>
       </c>
       <c r="H26" t="n">
-        <v>6727400</v>
+        <v>3189400</v>
       </c>
       <c r="I26" t="n">
-        <v>31.5</v>
+        <v>31.1</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.49</v>
+        <v>-6.39</v>
       </c>
       <c r="K26" t="n">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="L26" t="n">
-        <v>-101.21</v>
+        <v>-113.87</v>
       </c>
       <c r="M26" t="n">
-        <v>-20.29</v>
+        <v>-39</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -35136,10 +35297,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7804.08</v>
+        <v>7814.43</v>
       </c>
       <c r="Q26" t="n">
-        <v>8556.93</v>
+        <v>8534.469999999999</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -35176,7 +35337,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>あと36日</t>
+          <t>あと35日</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>176,686円</t>
+          <t>176,687円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-32,604円</t>
+          <t>-32,603円</t>
         </is>
       </c>
     </row>
@@ -1628,19 +1628,19 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>41.07</v>
+        <v>41.92</v>
       </c>
       <c r="F10" t="n">
-        <v>59.3</v>
+        <v>55.1</v>
       </c>
       <c r="G10" t="n">
-        <v>4.82</v>
+        <v>6.5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="J10" t="n">
         <v>1.56</v>
@@ -1652,14 +1652,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.53</v>
+        <v>33.68</v>
       </c>
       <c r="N10" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -1698,29 +1698,29 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、長期上昇</t>
+          <t>RSI適正、25日線上、+1σ、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>41.02</v>
+        <v>41.07</v>
       </c>
       <c r="X10" t="n">
-        <v>0.05</v>
+        <v>0.85</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.12</v>
+        <v>2.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6072</v>
+        <v>-6071</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.33</v>
+        <v>-99.31</v>
       </c>
     </row>
   </sheetData>
@@ -1734,7 +1734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1727"/>
+  <dimension ref="A1:C1736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27642,6 +27642,141 @@
       </c>
       <c r="C1727" t="n">
         <v>41.07</v>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1728" t="n">
+        <v>3435</v>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1729" t="n">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1730" t="n">
+        <v>170.3</v>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1731" t="n">
+        <v>2925</v>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1732" t="n">
+        <v>10100</v>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1733" t="n">
+        <v>7940</v>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1734" t="n">
+        <v>4722</v>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1735" t="n">
+        <v>19100</v>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1736" t="n">
+        <v>41.92</v>
       </c>
     </row>
   </sheetData>
@@ -27655,7 +27790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F278"/>
+  <dimension ref="A1:F279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32623,19 +32758,29 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr">
+      <c r="A276" t="inlineStr"/>
+      <c r="B276" s="1" t="n">
+        <v>46297.29166666666</v>
+      </c>
+      <c r="C276" t="n">
+        <v>176687</v>
+      </c>
+      <c r="D276" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E276" t="n">
+        <v>-32603</v>
+      </c>
+      <c r="F276" t="n">
+        <v>-15.58</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr"/>
-      <c r="C276" t="inlineStr"/>
-      <c r="D276" t="inlineStr"/>
-      <c r="E276" t="inlineStr"/>
-      <c r="F276" t="inlineStr"/>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr"/>
       <c r="B277" t="inlineStr"/>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr"/>
@@ -32643,16 +32788,24 @@
       <c r="F277" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A278" t="inlineStr"/>
       <c r="B278" t="inlineStr"/>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr"/>
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -32817,31 +32970,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>991</v>
+        <v>982</v>
       </c>
       <c r="F2" t="n">
-        <v>-6</v>
+        <v>-15</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.6</v>
+        <v>-1.5</v>
       </c>
       <c r="H2" t="n">
-        <v>460000</v>
+        <v>764100</v>
       </c>
       <c r="I2" t="n">
-        <v>38.4</v>
+        <v>37</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.67</v>
+        <v>-2.53</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4</v>
+        <v>0.63</v>
       </c>
       <c r="L2" t="n">
-        <v>11.32</v>
+        <v>10.6</v>
       </c>
       <c r="M2" t="n">
-        <v>20.68</v>
+        <v>20.54</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -32854,10 +33007,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>876.87</v>
+        <v>876.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>1104.11</v>
+        <v>1104.06</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -32917,31 +33070,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3360</v>
+        <v>3435</v>
       </c>
       <c r="F3" t="n">
-        <v>-15</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.44</v>
+        <v>1.78</v>
       </c>
       <c r="H3" t="n">
-        <v>16100</v>
+        <v>40200</v>
       </c>
       <c r="I3" t="n">
-        <v>45.3</v>
+        <v>51.1</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.09</v>
+        <v>0.01</v>
       </c>
       <c r="K3" t="n">
-        <v>0.22</v>
+        <v>0.52</v>
       </c>
       <c r="L3" t="n">
-        <v>4.69</v>
+        <v>10.67</v>
       </c>
       <c r="M3" t="n">
-        <v>17.11</v>
+        <v>18.31</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -32954,10 +33107,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3120.6</v>
+        <v>3121.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2742.75</v>
+        <v>2743.12</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -32965,16 +33118,16 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -32992,7 +33145,7 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>🟢 押し目買い候補（買い足し検討）</t>
+          <t>⚪ 様子見（押し目ではない）</t>
         </is>
       </c>
     </row>
@@ -33018,31 +33171,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1457</v>
+        <v>1460</v>
       </c>
       <c r="F4" t="n">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.75</v>
+        <v>-0.54</v>
       </c>
       <c r="H4" t="n">
-        <v>9000</v>
+        <v>18300</v>
       </c>
       <c r="I4" t="n">
-        <v>65.59999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="J4" t="n">
-        <v>7.6</v>
+        <v>7.81</v>
       </c>
       <c r="K4" t="n">
-        <v>0.44</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>48.23</v>
+        <v>48.47</v>
       </c>
       <c r="M4" t="n">
-        <v>41.38</v>
+        <v>41.43</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -33055,10 +33208,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1230.59</v>
+        <v>1230.63</v>
       </c>
       <c r="Q4" t="n">
-        <v>1633.89</v>
+        <v>1633.9</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -33118,31 +33271,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3555</v>
+        <v>3495</v>
       </c>
       <c r="F5" t="n">
-        <v>-45</v>
+        <v>-105</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.25</v>
+        <v>-2.92</v>
       </c>
       <c r="H5" t="n">
-        <v>4200</v>
+        <v>14500</v>
       </c>
       <c r="I5" t="n">
-        <v>54.4</v>
+        <v>50</v>
       </c>
       <c r="J5" t="n">
-        <v>1.85</v>
+        <v>0.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0.18</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>41.75</v>
+        <v>36.96</v>
       </c>
       <c r="M5" t="n">
-        <v>31.15</v>
+        <v>30.2</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -33155,10 +33308,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3440.47</v>
+        <v>3439.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>3186.66</v>
+        <v>3186.36</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -33219,31 +33372,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1550</v>
+        <v>1559</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>0.32</v>
+        <v>0.91</v>
       </c>
       <c r="H6" t="n">
-        <v>19900</v>
+        <v>52600</v>
       </c>
       <c r="I6" t="n">
-        <v>53.7</v>
+        <v>55.7</v>
       </c>
       <c r="J6" t="n">
-        <v>0.16</v>
+        <v>0.72</v>
       </c>
       <c r="K6" t="n">
-        <v>0.28</v>
+        <v>0.67</v>
       </c>
       <c r="L6" t="n">
-        <v>-9.1</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-14.79</v>
+        <v>-14.65</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -33256,10 +33409,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1657.84</v>
+        <v>1657.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>1685.7</v>
+        <v>1685.75</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -33320,64 +33473,64 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="F7" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.38</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>7700</v>
+        <v>12800</v>
       </c>
       <c r="I7" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-4.77</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>538.88</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>574.86</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
         <v>50</v>
       </c>
-      <c r="J7" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-3.73</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>DC</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>538.85</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>574.85</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>40</v>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -33385,9 +33538,8 @@
           <t>【AI分析レポート】
 ・🔴 下降
 ・MACDは買いシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
 ・RSIは良好な水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド中心付近で推移しています。
 ⚠️ 下落トレンドです。
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
@@ -33422,31 +33574,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="H8" t="n">
-        <v>1300</v>
+        <v>2800</v>
       </c>
       <c r="I8" t="n">
-        <v>47.7</v>
+        <v>47.3</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="K8" t="n">
-        <v>0.32</v>
+        <v>0.64</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.87</v>
+        <v>-1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.12</v>
+        <v>-3.14</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -33459,10 +33611,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1067.03</v>
+        <v>1067.01</v>
       </c>
       <c r="Q8" t="n">
-        <v>1014.18</v>
+        <v>1014.17</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -33470,16 +33622,16 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -33523,31 +33675,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="F9" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.32</v>
+        <v>-0.13</v>
       </c>
       <c r="H9" t="n">
-        <v>12700</v>
+        <v>57000</v>
       </c>
       <c r="I9" t="n">
-        <v>39.7</v>
+        <v>40.1</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.45</v>
+        <v>-3.27</v>
       </c>
       <c r="K9" t="n">
-        <v>0.25</v>
+        <v>0.96</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.62</v>
+        <v>-2.38</v>
       </c>
       <c r="M9" t="n">
-        <v>6.32</v>
+        <v>6.36</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -33560,10 +33712,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1474.77</v>
+        <v>1474.81</v>
       </c>
       <c r="Q9" t="n">
-        <v>1390.9</v>
+        <v>1390.92</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -33623,31 +33775,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>-5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.91</v>
+        <v>-0.57</v>
       </c>
       <c r="H10" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>16.7</v>
+        <v>17.3</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.69</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.24</v>
+        <v>0.09</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.74</v>
+        <v>-9.73</v>
       </c>
       <c r="M10" t="n">
-        <v>9.630000000000001</v>
+        <v>5.76</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -33660,10 +33812,10 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>890.71</v>
+        <v>891.89</v>
       </c>
       <c r="Q10" t="n">
-        <v>985.98</v>
+        <v>985.8200000000001</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -33724,31 +33876,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3723</v>
+        <v>3728</v>
       </c>
       <c r="F11" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G11" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="H11" t="n">
-        <v>1365900</v>
+        <v>5554200</v>
       </c>
       <c r="I11" t="n">
-        <v>75.3</v>
+        <v>75.5</v>
       </c>
       <c r="J11" t="n">
-        <v>4.43</v>
+        <v>4.56</v>
       </c>
       <c r="K11" t="n">
-        <v>0.33</v>
+        <v>1.11</v>
       </c>
       <c r="L11" t="n">
-        <v>23.94</v>
+        <v>24.34</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.41</v>
+        <v>-2.33</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -33761,10 +33913,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3637.01</v>
+        <v>3637.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>2975.35</v>
+        <v>2975.38</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -33829,31 +33981,31 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>3950</v>
+        <v>4000</v>
       </c>
       <c r="F12" t="n">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="G12" t="n">
-        <v>9.119999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="H12" t="n">
-        <v>758400</v>
+        <v>1518900</v>
       </c>
       <c r="I12" t="n">
-        <v>58.5</v>
+        <v>59.9</v>
       </c>
       <c r="J12" t="n">
-        <v>6.95</v>
+        <v>8.25</v>
       </c>
       <c r="K12" t="n">
-        <v>1.33</v>
+        <v>2.1</v>
       </c>
       <c r="L12" t="n">
-        <v>59.03</v>
+        <v>63.01</v>
       </c>
       <c r="M12" t="n">
-        <v>62.24</v>
+        <v>63.04</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -33862,14 +34014,14 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>+2S</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3308.87</v>
+        <v>3309.53</v>
       </c>
       <c r="Q12" t="n">
-        <v>3082.67</v>
+        <v>3082.92</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -33895,7 +34047,8 @@
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・出来高が急増しています。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -33926,31 +34079,31 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>5277</v>
+        <v>5368</v>
       </c>
       <c r="F13" t="n">
-        <v>53</v>
+        <v>144</v>
       </c>
       <c r="G13" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="H13" t="n">
-        <v>20909000</v>
+        <v>36851000</v>
       </c>
       <c r="I13" t="n">
-        <v>55.7</v>
+        <v>57.8</v>
       </c>
       <c r="J13" t="n">
-        <v>3.53</v>
+        <v>5.24</v>
       </c>
       <c r="K13" t="n">
-        <v>0.76</v>
+        <v>1.2</v>
       </c>
       <c r="L13" t="n">
-        <v>-17.66</v>
+        <v>-10.4</v>
       </c>
       <c r="M13" t="n">
-        <v>-45.27</v>
+        <v>-43.82</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -33959,14 +34112,14 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5095.78</v>
+        <v>5097</v>
       </c>
       <c r="Q13" t="n">
-        <v>4552.25</v>
+        <v>4552.71</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -33992,7 +34145,7 @@
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -34035,31 +34188,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="F14" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>298400</v>
+        <v>603600</v>
       </c>
       <c r="I14" t="n">
-        <v>28.9</v>
+        <v>29.6</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.88</v>
+        <v>-6.52</v>
       </c>
       <c r="K14" t="n">
-        <v>0.59</v>
+        <v>1.07</v>
       </c>
       <c r="L14" t="n">
-        <v>-20.89</v>
+        <v>-20.57</v>
       </c>
       <c r="M14" t="n">
-        <v>-16.15</v>
+        <v>-16.09</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -34072,10 +34225,10 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1085.43</v>
+        <v>1085.48</v>
       </c>
       <c r="Q14" t="n">
-        <v>910.25</v>
+        <v>910.27</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -34136,31 +34289,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4059</v>
+        <v>4113</v>
       </c>
       <c r="F15" t="n">
-        <v>203</v>
+        <v>257</v>
       </c>
       <c r="G15" t="n">
-        <v>5.26</v>
+        <v>6.66</v>
       </c>
       <c r="H15" t="n">
-        <v>13642500</v>
+        <v>23440100</v>
       </c>
       <c r="I15" t="n">
-        <v>61.4</v>
+        <v>62.6</v>
       </c>
       <c r="J15" t="n">
-        <v>5.23</v>
+        <v>6.57</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.24</v>
       </c>
       <c r="L15" t="n">
-        <v>6.25</v>
+        <v>10.56</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.53</v>
+        <v>-2.67</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -34173,10 +34326,10 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3915.13</v>
+        <v>3915.85</v>
       </c>
       <c r="Q15" t="n">
-        <v>3273.62</v>
+        <v>3273.89</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -34240,31 +34393,31 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>4985</v>
+        <v>5040</v>
       </c>
       <c r="F16" t="n">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="G16" t="n">
-        <v>1.42</v>
+        <v>2.54</v>
       </c>
       <c r="H16" t="n">
-        <v>41800</v>
+        <v>80600</v>
       </c>
       <c r="I16" t="n">
-        <v>79.7</v>
+        <v>80.3</v>
       </c>
       <c r="J16" t="n">
-        <v>17.93</v>
+        <v>19.17</v>
       </c>
       <c r="K16" t="n">
-        <v>0.76</v>
+        <v>1.28</v>
       </c>
       <c r="L16" t="n">
-        <v>228.31</v>
+        <v>232.7</v>
       </c>
       <c r="M16" t="n">
-        <v>137.89</v>
+        <v>138.77</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -34277,10 +34430,10 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3738.07</v>
+        <v>3738.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>2940.98</v>
+        <v>2941.25</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -34338,31 +34491,31 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>2341</v>
+        <v>2352</v>
       </c>
       <c r="F17" t="n">
-        <v>-23.5</v>
+        <v>-12.5</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.99</v>
+        <v>-0.53</v>
       </c>
       <c r="H17" t="n">
-        <v>3666400</v>
+        <v>7314800</v>
       </c>
       <c r="I17" t="n">
-        <v>46.2</v>
+        <v>47.8</v>
       </c>
       <c r="J17" t="n">
-        <v>-3.37</v>
+        <v>-2.93</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6</v>
+        <v>1.07</v>
       </c>
       <c r="L17" t="n">
-        <v>-63.87</v>
+        <v>-62.99</v>
       </c>
       <c r="M17" t="n">
-        <v>-74.34999999999999</v>
+        <v>-74.17</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -34375,10 +34528,10 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2677.78</v>
+        <v>2677.92</v>
       </c>
       <c r="Q17" t="n">
-        <v>2821.02</v>
+        <v>2821.07</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -34447,31 +34600,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2911</v>
+        <v>2925</v>
       </c>
       <c r="F18" t="n">
-        <v>-9.5</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.33</v>
+        <v>0.17</v>
       </c>
       <c r="H18" t="n">
-        <v>9308800</v>
+        <v>26937700</v>
       </c>
       <c r="I18" t="n">
-        <v>48.5</v>
+        <v>51.1</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.71</v>
+        <v>-2.24</v>
       </c>
       <c r="K18" t="n">
-        <v>0.39</v>
+        <v>0.98</v>
       </c>
       <c r="L18" t="n">
-        <v>-19.31</v>
+        <v>-18.15</v>
       </c>
       <c r="M18" t="n">
-        <v>-8.57</v>
+        <v>-8.34</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -34480,14 +34633,14 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2901.42</v>
+        <v>2901.61</v>
       </c>
       <c r="Q18" t="n">
-        <v>3109.56</v>
+        <v>3109.64</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -34495,16 +34648,16 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -34513,7 +34666,7 @@
 ・🟢 上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
@@ -34552,31 +34705,31 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>1749</v>
+        <v>1752</v>
       </c>
       <c r="F19" t="n">
-        <v>-21</v>
+        <v>-18.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.19</v>
+        <v>-1.05</v>
       </c>
       <c r="H19" t="n">
-        <v>3326600</v>
+        <v>10839000</v>
       </c>
       <c r="I19" t="n">
-        <v>40.6</v>
+        <v>40.9</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.75</v>
+        <v>-1.61</v>
       </c>
       <c r="K19" t="n">
-        <v>0.36</v>
+        <v>1.01</v>
       </c>
       <c r="L19" t="n">
-        <v>6.56</v>
+        <v>6.76</v>
       </c>
       <c r="M19" t="n">
-        <v>16.13</v>
+        <v>16.17</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -34589,10 +34742,10 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1669.66</v>
+        <v>1669.69</v>
       </c>
       <c r="Q19" t="n">
-        <v>1570.49</v>
+        <v>1570.5</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -34660,31 +34813,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F20" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.43</v>
+        <v>0.21</v>
       </c>
       <c r="H20" t="n">
-        <v>103300</v>
+        <v>363800</v>
       </c>
       <c r="I20" t="n">
-        <v>53.3</v>
+        <v>54.9</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.07</v>
+        <v>-0.46</v>
       </c>
       <c r="K20" t="n">
-        <v>0.26</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>4.88</v>
+        <v>5.12</v>
       </c>
       <c r="M20" t="n">
-        <v>6.44</v>
+        <v>6.49</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -34697,10 +34850,10 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>439.66</v>
+        <v>439.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>417.46</v>
+        <v>417.47</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -34757,31 +34910,31 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>10185</v>
+        <v>10100</v>
       </c>
       <c r="F21" t="n">
-        <v>861</v>
+        <v>776</v>
       </c>
       <c r="G21" t="n">
-        <v>9.23</v>
+        <v>8.32</v>
       </c>
       <c r="H21" t="n">
-        <v>22797500</v>
+        <v>31966500</v>
       </c>
       <c r="I21" t="n">
-        <v>63.3</v>
+        <v>62.6</v>
       </c>
       <c r="J21" t="n">
-        <v>11.19</v>
+        <v>10.3</v>
       </c>
       <c r="K21" t="n">
-        <v>0.87</v>
+        <v>1.14</v>
       </c>
       <c r="L21" t="n">
-        <v>-153.12</v>
+        <v>-159.9</v>
       </c>
       <c r="M21" t="n">
-        <v>-321.81</v>
+        <v>-323.16</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -34794,10 +34947,10 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>12248.62</v>
+        <v>12247.49</v>
       </c>
       <c r="Q21" t="n">
-        <v>8124.57</v>
+        <v>8124.15</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -34859,31 +35012,31 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>18855</v>
+        <v>19100</v>
       </c>
       <c r="F22" t="n">
-        <v>760</v>
+        <v>1005</v>
       </c>
       <c r="G22" t="n">
-        <v>4.2</v>
+        <v>5.55</v>
       </c>
       <c r="H22" t="n">
-        <v>27233100</v>
+        <v>52342100</v>
       </c>
       <c r="I22" t="n">
-        <v>48.2</v>
+        <v>49.8</v>
       </c>
       <c r="J22" t="n">
-        <v>6.2</v>
+        <v>7.52</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6</v>
+        <v>1.03</v>
       </c>
       <c r="L22" t="n">
-        <v>24.12</v>
+        <v>43.66</v>
       </c>
       <c r="M22" t="n">
-        <v>-107.52</v>
+        <v>-103.61</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -34896,10 +35049,10 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>21194.62</v>
+        <v>21197.89</v>
       </c>
       <c r="Q22" t="n">
-        <v>13863.2</v>
+        <v>13864.42</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -34960,31 +35113,31 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>153.7</v>
+        <v>153.2</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.2</v>
+        <v>-4.7</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.66</v>
+        <v>-2.98</v>
       </c>
       <c r="H23" t="n">
-        <v>41103400</v>
+        <v>81456600</v>
       </c>
       <c r="I23" t="n">
-        <v>40.9</v>
+        <v>40.1</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.52</v>
+        <v>-2.83</v>
       </c>
       <c r="K23" t="n">
-        <v>0.73</v>
+        <v>1.26</v>
       </c>
       <c r="L23" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="M23" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -34993,14 +35146,14 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>-2S</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>150.54</v>
+        <v>150.53</v>
       </c>
       <c r="Q23" t="n">
-        <v>147.61</v>
+        <v>147.6</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -35008,7 +35161,7 @@
         </is>
       </c>
       <c r="S23" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -35025,7 +35178,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド-2σ付近です。売られすぎから反発する可能性があります。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -35060,31 +35213,31 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>3555</v>
+        <v>3616</v>
       </c>
       <c r="F24" t="n">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="G24" t="n">
-        <v>2.24</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>4017600</v>
+        <v>10171500</v>
       </c>
       <c r="I24" t="n">
-        <v>68</v>
+        <v>70.2</v>
       </c>
       <c r="J24" t="n">
-        <v>6.4</v>
+        <v>8.15</v>
       </c>
       <c r="K24" t="n">
-        <v>0.48</v>
+        <v>1.06</v>
       </c>
       <c r="L24" t="n">
-        <v>-18.81</v>
+        <v>-13.95</v>
       </c>
       <c r="M24" t="n">
-        <v>-72.33</v>
+        <v>-71.36</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -35093,34 +35246,135 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
+          <t>+2S</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>3910.57</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3251.6</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>75</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・買われ過ぎ水準です。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>2026/10/28</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>あと27日</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>⚪ 様子見（押し目ではない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PENG</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ペンギン・ソリューションズ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>54.69</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1446100</v>
+      </c>
+      <c r="I25" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
           <t>+1S</t>
         </is>
       </c>
-      <c r="P24" t="n">
-        <v>3909.76</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3251.3</v>
-      </c>
-      <c r="R24" t="inlineStr">
+      <c r="P25" t="n">
+        <v>58.04</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>🟡 反発中</t>
         </is>
       </c>
-      <c r="S24" t="n">
-        <v>85</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
+      <c r="S25" t="n">
+        <v>95</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -35130,106 +35384,6 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>2026/10/28</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>あと27日</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>⚪ 様子見（押し目ではない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>PENG</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ペンギン・ソリューションズ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="n">
-        <v>54.69</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-1.97</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1446100</v>
-      </c>
-      <c r="I25" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="J25" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>58.04</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>39.35</v>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="S25" t="n">
-        <v>95</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="W25" t="inlineStr">
         <is>
           <t>2026/10/06</t>
@@ -35260,31 +35414,31 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>7920</v>
+        <v>7940</v>
       </c>
       <c r="F26" t="n">
-        <v>-24</v>
+        <v>-4</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.3</v>
+        <v>-0.05</v>
       </c>
       <c r="H26" t="n">
-        <v>3189400</v>
+        <v>6447100</v>
       </c>
       <c r="I26" t="n">
-        <v>31.1</v>
+        <v>31.4</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.39</v>
+        <v>-6.16</v>
       </c>
       <c r="K26" t="n">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="L26" t="n">
-        <v>-113.87</v>
+        <v>-112.27</v>
       </c>
       <c r="M26" t="n">
-        <v>-39</v>
+        <v>-38.68</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -35297,10 +35451,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7814.43</v>
+        <v>7814.69</v>
       </c>
       <c r="Q26" t="n">
-        <v>8534.469999999999</v>
+        <v>8534.57</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>176,687円</t>
+          <t>174,415円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-32,603円</t>
+          <t>-34,875円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.58%</t>
+          <t>-16.66%</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -717,22 +717,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3435</v>
+        <v>3360</v>
       </c>
       <c r="F2" t="n">
-        <v>51.1</v>
+        <v>52.6</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01</v>
+        <v>-2.11</v>
       </c>
       <c r="H2" t="n">
-        <v>0.52</v>
+        <v>0.36</v>
       </c>
       <c r="I2" t="n">
-        <v>10.67</v>
+        <v>8.44</v>
       </c>
       <c r="J2" t="n">
-        <v>18.31</v>
+        <v>16.33</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3121.6</v>
+        <v>3134.41</v>
       </c>
       <c r="N2" t="n">
-        <v>2743.12</v>
+        <v>2745.87</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -757,20 +757,20 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -787,29 +787,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+          <t>RSI適正、押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3375</v>
+        <v>3435</v>
       </c>
       <c r="X2" t="n">
-        <v>60</v>
+        <v>-75</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.78</v>
+        <v>-2.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>13740</v>
+        <v>13440</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2940</v>
+        <v>2640</v>
       </c>
       <c r="AC2" t="n">
-        <v>27.22</v>
+        <v>24.44</v>
       </c>
     </row>
     <row r="3">
@@ -830,26 +830,26 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="F3" t="n">
-        <v>54.9</v>
+        <v>63.3</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.46</v>
+        <v>-1.55</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="I3" t="n">
-        <v>5.12</v>
+        <v>4.04</v>
       </c>
       <c r="J3" t="n">
-        <v>6.49</v>
+        <v>6</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>439.7</v>
+        <v>440.69</v>
       </c>
       <c r="N3" t="n">
-        <v>417.47</v>
+        <v>418.01</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -870,20 +870,20 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -891,151 +891,152 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>RSI適正、押し目、デッドクロス、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>471</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>46600</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>42000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>4600</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>10.95</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NTT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>158</v>
+      </c>
+      <c r="E4" t="n">
+        <v>169.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>157.01</v>
+      </c>
+      <c r="N4" t="n">
+        <v>152.7</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>🟠 利益確定検討</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>50</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>RSI適正、押し目、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>470</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>47100</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>42000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>5100</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>12.14</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>9432.T</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NTT</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" t="n">
-        <v>158</v>
-      </c>
-      <c r="E4" t="n">
-        <v>170.3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>156.7</v>
-      </c>
-      <c r="N4" t="n">
-        <v>152.61</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>85</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD売り、長期上昇</t>
+          <t>押し目、デッドクロス、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>171.6</v>
+        <v>170.3</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.76</v>
+        <v>-0.59</v>
       </c>
       <c r="Z4" t="n">
-        <v>17030</v>
+        <v>16930</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1230</v>
+        <v>1130</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.78</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="5">
@@ -1056,22 +1057,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>2925</v>
+        <v>2855</v>
       </c>
       <c r="F5" t="n">
-        <v>51.1</v>
+        <v>40.5</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.24</v>
+        <v>-4.36</v>
       </c>
       <c r="H5" t="n">
-        <v>0.98</v>
+        <v>0.54</v>
       </c>
       <c r="I5" t="n">
-        <v>-18.15</v>
+        <v>-23.86</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.34</v>
+        <v>-11.44</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1080,75 +1081,74 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2901.61</v>
+        <v>2903.29</v>
       </c>
       <c r="N5" t="n">
-        <v>3109.64</v>
+        <v>3108.88</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>🟢 上昇</t>
+          <t>🔴 下降</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🔴 売り注意</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟢 上昇
+・🔴 下降
 ・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD売り、上昇トレンド</t>
+          <t>押し目、-1σ、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>2920</v>
+        <v>2925</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>-70</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.17</v>
+        <v>-2.39</v>
       </c>
       <c r="Z5" t="n">
-        <v>38025</v>
+        <v>37115</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>926</v>
+        <v>16</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.5</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="6">
@@ -1169,26 +1169,26 @@
         <v>10000</v>
       </c>
       <c r="E6" t="n">
-        <v>10100</v>
+        <v>9871</v>
       </c>
       <c r="F6" t="n">
-        <v>62.6</v>
+        <v>60.5</v>
       </c>
       <c r="G6" t="n">
-        <v>10.3</v>
+        <v>7.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1.14</v>
+        <v>0.73</v>
       </c>
       <c r="I6" t="n">
-        <v>-159.9</v>
+        <v>-102.06</v>
       </c>
       <c r="J6" t="n">
-        <v>-323.16</v>
+        <v>-278.94</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>12247.49</v>
+        <v>12170.47</v>
       </c>
       <c r="N6" t="n">
-        <v>8124.15</v>
+        <v>8154.44</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1209,20 +1209,20 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1230,43 +1230,37 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
-・25日線から大きく上に乖離しています。
 ・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>RSI適正、上昇加速、ゴールデンクロス、+2σ、MACD買い、反発局面</t>
+          <t>RSI適正、25日線上、+2σ、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>9324</v>
+        <v>10100</v>
       </c>
       <c r="X6" t="n">
-        <v>776</v>
+        <v>-229</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.32</v>
+        <v>-2.27</v>
       </c>
       <c r="Z6" t="n">
-        <v>10100</v>
+        <v>9871</v>
       </c>
       <c r="AA6" t="n">
         <v>10000</v>
       </c>
       <c r="AB6" t="n">
-        <v>100</v>
+        <v>-129</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="7">
@@ -1287,22 +1281,22 @@
         <v>7993</v>
       </c>
       <c r="E7" t="n">
-        <v>7940</v>
+        <v>7832</v>
       </c>
       <c r="F7" t="n">
-        <v>31.4</v>
+        <v>35.3</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.16</v>
+        <v>-6.98</v>
       </c>
       <c r="H7" t="n">
-        <v>0.92</v>
+        <v>0.45</v>
       </c>
       <c r="I7" t="n">
-        <v>-112.27</v>
+        <v>-128.28</v>
       </c>
       <c r="J7" t="n">
-        <v>-38.68</v>
+        <v>-56.6</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1315,10 +1309,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>7814.69</v>
+        <v>7823.47</v>
       </c>
       <c r="N7" t="n">
-        <v>8534.57</v>
+        <v>8510.59</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1360,25 +1354,25 @@
         </is>
       </c>
       <c r="W7" t="n">
-        <v>7944</v>
+        <v>7940</v>
       </c>
       <c r="X7" t="n">
-        <v>-4</v>
+        <v>-108</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.05</v>
+        <v>-1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>7940</v>
+        <v>7832</v>
       </c>
       <c r="AA7" t="n">
         <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>-53</v>
+        <v>-161</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.66</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="8">
@@ -1399,22 +1393,22 @@
         <v>4795</v>
       </c>
       <c r="E8" t="n">
-        <v>4722</v>
+        <v>4683</v>
       </c>
       <c r="F8" t="n">
-        <v>42.1</v>
+        <v>32.3</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.06</v>
+        <v>-2.85</v>
       </c>
       <c r="H8" t="n">
-        <v>0.91</v>
+        <v>0.37</v>
       </c>
       <c r="I8" t="n">
-        <v>-6.06</v>
+        <v>-13.97</v>
       </c>
       <c r="J8" t="n">
-        <v>21.33</v>
+        <v>14.27</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1423,18 +1417,18 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4659.09</v>
+        <v>4659.9</v>
       </c>
       <c r="N8" t="n">
-        <v>4657.74</v>
+        <v>4662.39</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>🟢 強い上昇</t>
+          <t>🟢 上昇</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1443,54 +1437,54 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟢 強い上昇
+・🟢 上昇
 ・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>4769</v>
+        <v>4722</v>
       </c>
       <c r="X8" t="n">
-        <v>-47</v>
+        <v>-39</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.99</v>
+        <v>-0.83</v>
       </c>
       <c r="Z8" t="n">
-        <v>23610</v>
+        <v>23415</v>
       </c>
       <c r="AA8" t="n">
         <v>23975</v>
       </c>
       <c r="AB8" t="n">
-        <v>-365</v>
+        <v>-560</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.52</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="9">
@@ -1511,22 +1505,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>19100</v>
+        <v>19170</v>
       </c>
       <c r="F9" t="n">
-        <v>49.8</v>
+        <v>51.1</v>
       </c>
       <c r="G9" t="n">
-        <v>7.52</v>
+        <v>7.41</v>
       </c>
       <c r="H9" t="n">
-        <v>1.03</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>43.66</v>
+        <v>126.88</v>
       </c>
       <c r="J9" t="n">
-        <v>-103.61</v>
+        <v>-57.51</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1539,10 +1533,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>21197.89</v>
+        <v>21092.6</v>
       </c>
       <c r="N9" t="n">
-        <v>13864.42</v>
+        <v>13945.16</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1551,20 +1545,20 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1578,36 +1572,32 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>25日線上、+1σ、MACD買い、反発局面</t>
+          <t>RSI適正、25日線上、+1σ、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>18095</v>
+        <v>19100</v>
       </c>
       <c r="X9" t="n">
-        <v>1005</v>
+        <v>70</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.55</v>
+        <v>0.37</v>
       </c>
       <c r="Z9" t="n">
-        <v>19100</v>
+        <v>19170</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-36410</v>
+        <v>-36340</v>
       </c>
       <c r="AC9" t="n">
-        <v>-65.59</v>
+        <v>-65.47</v>
       </c>
     </row>
     <row r="10">
@@ -1734,7 +1724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1736"/>
+  <dimension ref="A1:C1745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27776,6 +27766,141 @@
         </is>
       </c>
       <c r="C1736" t="n">
+        <v>41.92</v>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1737" t="n">
+        <v>3360</v>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1738" t="n">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1739" t="n">
+        <v>169.3</v>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1740" t="n">
+        <v>2855</v>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1741" t="n">
+        <v>9871</v>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1742" t="n">
+        <v>7832</v>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1743" t="n">
+        <v>4683</v>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1744" t="n">
+        <v>19170</v>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1745" t="n">
         <v>41.92</v>
       </c>
     </row>
@@ -27790,7 +27915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F279"/>
+  <dimension ref="A1:F280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32776,19 +32901,29 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" t="inlineStr">
+      <c r="A277" t="inlineStr"/>
+      <c r="B277" s="1" t="n">
+        <v>46297.5</v>
+      </c>
+      <c r="C277" t="n">
+        <v>174415</v>
+      </c>
+      <c r="D277" t="n">
+        <v>209290</v>
+      </c>
+      <c r="E277" t="n">
+        <v>-34875</v>
+      </c>
+      <c r="F277" t="n">
+        <v>-16.66</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
         <is>
           <t>総損益率</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr"/>
-      <c r="C277" t="inlineStr"/>
-      <c r="D277" t="inlineStr"/>
-      <c r="E277" t="inlineStr"/>
-      <c r="F277" t="inlineStr"/>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr"/>
       <c r="B278" t="inlineStr"/>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr"/>
@@ -32796,16 +32931,24 @@
       <c r="F278" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>総損益率</t>
-        </is>
-      </c>
+      <c r="A279" t="inlineStr"/>
       <c r="B279" t="inlineStr"/>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>総損益率</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr"/>
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -35314,31 +35457,31 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>54.69</v>
+        <v>54.98</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1</v>
+        <v>0.29</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.97</v>
+        <v>0.53</v>
       </c>
       <c r="H25" t="n">
-        <v>1446100</v>
+        <v>1155705</v>
       </c>
       <c r="I25" t="n">
-        <v>61.3</v>
+        <v>57.8</v>
       </c>
       <c r="J25" t="n">
-        <v>6.08</v>
+        <v>6.38</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.14</v>
+        <v>0.01</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -35351,10 +35494,10 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>58.04</v>
+        <v>57.92</v>
       </c>
       <c r="Q25" t="n">
-        <v>39.35</v>
+        <v>39.52</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -35379,6 +35522,7 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
+・RSIは良好な水準です。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>

--- a/dashboard.xlsx
+++ b/dashboard.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>174,415円</t>
+          <t>174,760円</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-34,875円</t>
+          <t>-34,529円</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.66%</t>
+          <t>-16.5%</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -717,22 +717,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3360</v>
+        <v>3370</v>
       </c>
       <c r="F2" t="n">
-        <v>52.6</v>
+        <v>53.4</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.11</v>
+        <v>-1.83</v>
       </c>
       <c r="H2" t="n">
-        <v>0.36</v>
+        <v>0.64</v>
       </c>
       <c r="I2" t="n">
-        <v>8.44</v>
+        <v>9.24</v>
       </c>
       <c r="J2" t="n">
-        <v>16.33</v>
+        <v>16.49</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3134.41</v>
+        <v>3134.55</v>
       </c>
       <c r="N2" t="n">
-        <v>2745.87</v>
+        <v>2745.92</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -794,22 +794,22 @@
         <v>3435</v>
       </c>
       <c r="X2" t="n">
-        <v>-75</v>
+        <v>-65</v>
       </c>
       <c r="Y2" t="n">
-        <v>-2.18</v>
+        <v>-1.89</v>
       </c>
       <c r="Z2" t="n">
-        <v>13440</v>
+        <v>13480</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2640</v>
+        <v>2680</v>
       </c>
       <c r="AC2" t="n">
-        <v>24.44</v>
+        <v>24.81</v>
       </c>
     </row>
     <row r="3">
@@ -830,22 +830,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F3" t="n">
-        <v>63.3</v>
+        <v>61.7</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.55</v>
+        <v>-1.96</v>
       </c>
       <c r="H3" t="n">
-        <v>0.45</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
-        <v>4.04</v>
+        <v>3.88</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>5.97</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>440.69</v>
+        <v>440.67</v>
       </c>
       <c r="N3" t="n">
-        <v>418.01</v>
+        <v>418</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -907,22 +907,22 @@
         <v>471</v>
       </c>
       <c r="X3" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.06</v>
+        <v>-1.49</v>
       </c>
       <c r="Z3" t="n">
-        <v>46600</v>
+        <v>46400</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>4600</v>
+        <v>4400</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.95</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="4">
@@ -943,22 +943,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>169.3</v>
+        <v>169.9</v>
       </c>
       <c r="F4" t="n">
-        <v>49.4</v>
+        <v>50.9</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.15</v>
+        <v>-0.82</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="J4" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>157.01</v>
+        <v>157.02</v>
       </c>
       <c r="N4" t="n">
         <v>152.7</v>
@@ -983,20 +983,20 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟠 利益確定検討</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1014,106 +1014,218 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>押し目、デッドクロス、MACD売り、長期上昇</t>
+          <t>RSI適正、押し目、デッドクロス、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>170.3</v>
       </c>
       <c r="X4" t="n">
-        <v>-1</v>
+        <v>-0.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.59</v>
+        <v>-0.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>16930</v>
+        <v>16990</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1130</v>
+        <v>1190</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.15</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10095</v>
+      </c>
+      <c r="F5" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-84.19</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-275.37</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>+2S</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>12173.46</v>
+      </c>
+      <c r="N5" t="n">
+        <v>8155.56</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>85</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>RSI適正、25日線上、+2σ、MACD買い、反発局面</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>10100</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>10095</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>7203.T</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>トヨタ自動車</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C6" t="n">
         <v>13</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>2853.77</v>
       </c>
-      <c r="E5" t="n">
-        <v>2855</v>
-      </c>
-      <c r="F5" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-4.36</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-23.86</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-11.44</v>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="E6" t="n">
+        <v>2856.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-4.31</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-23.74</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-11.42</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>-1S</t>
         </is>
       </c>
-      <c r="M5" t="n">
-        <v>2903.29</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3108.88</v>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="M6" t="n">
+        <v>2903.31</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3108.89</v>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>🔴 下降</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>🔴 売り注意</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q6" t="n">
         <v>15</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🔴 下降
@@ -1123,144 +1235,32 @@
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>押し目、-1σ、MACD売り、下降トレンド</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>2925</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-70</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-2.39</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>37115</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>37099</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E6" t="n">
-        <v>9871</v>
-      </c>
-      <c r="F6" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-102.06</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-278.94</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>+2S</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>12170.47</v>
-      </c>
-      <c r="N6" t="n">
-        <v>8154.44</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>85</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+2σ、MACD買い、反発局面</t>
+          <t>押し目、-1σ、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>10100</v>
+        <v>2925</v>
       </c>
       <c r="X6" t="n">
-        <v>-229</v>
+        <v>-68.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>-2.27</v>
+        <v>-2.34</v>
       </c>
       <c r="Z6" t="n">
-        <v>9871</v>
+        <v>37134</v>
       </c>
       <c r="AA6" t="n">
-        <v>10000</v>
+        <v>37099</v>
       </c>
       <c r="AB6" t="n">
-  